--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="783">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282133102417</t>
+    <t xml:space="preserve">3.87282061576843</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">3.87105965614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87458181381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86577653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401438713074</t>
+    <t xml:space="preserve">3.87458276748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86577582359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401534080505</t>
   </si>
   <si>
     <t xml:space="preserve">3.78652381896973</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">3.79532933235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77771782875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977933883667</t>
+    <t xml:space="preserve">3.77771735191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977910041809</t>
   </si>
   <si>
     <t xml:space="preserve">3.67733097076416</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">3.65443563461304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.663241147995</t>
+    <t xml:space="preserve">3.66324138641357</t>
   </si>
   <si>
     <t xml:space="preserve">3.6438684463501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48712396621704</t>
+    <t xml:space="preserve">3.48712420463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.61040639877319</t>
@@ -92,85 +92,85 @@
     <t xml:space="preserve">3.68965888023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66676378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60336184501648</t>
+    <t xml:space="preserve">3.66676354408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6033616065979</t>
   </si>
   <si>
     <t xml:space="preserve">3.68085312843323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56637740135193</t>
+    <t xml:space="preserve">3.56637692451477</t>
   </si>
   <si>
     <t xml:space="preserve">3.539959192276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6156895160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915204048157</t>
+    <t xml:space="preserve">3.61568999290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915227890015</t>
   </si>
   <si>
     <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091347694397</t>
+    <t xml:space="preserve">3.65091300010681</t>
   </si>
   <si>
     <t xml:space="preserve">3.64210724830627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431517601013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75130081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294131278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79356813430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86225438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.814701795578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368763923645</t>
+    <t xml:space="preserve">3.59455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431493759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.751300573349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294107437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7935688495636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86225414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941891670227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368811607361</t>
   </si>
   <si>
     <t xml:space="preserve">3.73721027374268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71255445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192715644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891255378723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538991928101</t>
+    <t xml:space="preserve">3.71255397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72135949134827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891207695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538968086243</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953889846802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74601721763611</t>
+    <t xml:space="preserve">3.74601650238037</t>
   </si>
   <si>
     <t xml:space="preserve">3.73016571998596</t>
@@ -179,16 +179,16 @@
     <t xml:space="preserve">3.6984646320343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68613648414612</t>
+    <t xml:space="preserve">3.6861367225647</t>
   </si>
   <si>
     <t xml:space="preserve">3.72488236427307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82350826263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383477210999</t>
+    <t xml:space="preserve">3.82350873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383524894714</t>
   </si>
   <si>
     <t xml:space="preserve">3.91861152648926</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">3.98377466201782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94326829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508936882019</t>
+    <t xml:space="preserve">3.9432680606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508960723877</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855363368988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395546913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087980270386</t>
+    <t xml:space="preserve">3.91332769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96088004112244</t>
   </si>
   <si>
     <t xml:space="preserve">3.89219450950623</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.93622326850891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92741751670837</t>
+    <t xml:space="preserve">3.92741727828979</t>
   </si>
   <si>
     <t xml:space="preserve">3.88338780403137</t>
@@ -236,37 +236,37 @@
     <t xml:space="preserve">4.02612829208374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97220778465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759985923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04410219192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98299169540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95423316955566</t>
+    <t xml:space="preserve">3.97220754623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759938240051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04410314559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98299145698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9542338848114</t>
   </si>
   <si>
     <t xml:space="preserve">3.93625926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88233828544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92727255821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367792129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560705184937</t>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9272723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560681343079</t>
   </si>
   <si>
     <t xml:space="preserve">3.8913254737854</t>
@@ -275,46 +275,46 @@
     <t xml:space="preserve">3.86436462402344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86256742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8194305896759</t>
+    <t xml:space="preserve">3.86256670951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81943011283875</t>
   </si>
   <si>
     <t xml:space="preserve">3.70799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76550889015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59475755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273121833801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67923450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63070511817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62171840667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65766620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103194236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318902015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632657051086</t>
+    <t xml:space="preserve">3.7655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59475779533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273145675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67923474311829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070487976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62171864509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65766644477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63789486885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632633209229</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">3.64688158035278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6918158531189</t>
+    <t xml:space="preserve">3.69181609153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.73675084114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75652170181274</t>
+    <t xml:space="preserve">3.75652146339417</t>
   </si>
   <si>
     <t xml:space="preserve">3.80325365066528</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">3.86616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8176326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044268608093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394011497498</t>
+    <t xml:space="preserve">3.81763243675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044316291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246878623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
   </si>
   <si>
     <t xml:space="preserve">3.77449512481689</t>
@@ -356,37 +356,37 @@
     <t xml:space="preserve">3.79067182540894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77629327774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753522872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75112962722778</t>
+    <t xml:space="preserve">3.77629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887438774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753499031067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7511293888092</t>
   </si>
   <si>
     <t xml:space="preserve">3.80145621299744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348255157471</t>
+    <t xml:space="preserve">3.7331554889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348207473755</t>
   </si>
   <si>
     <t xml:space="preserve">3.72416925430298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057414054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371145248413</t>
+    <t xml:space="preserve">3.77090096473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371169090271</t>
   </si>
   <si>
     <t xml:space="preserve">3.72596645355225</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">3.70978975296021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70260047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854804039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956109046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72237157821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72776389122009</t>
+    <t xml:space="preserve">3.70260071754456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956132888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72237205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72776317596436</t>
   </si>
   <si>
     <t xml:space="preserve">3.75292730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75831937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541072845459</t>
+    <t xml:space="preserve">3.75831913948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541096687317</t>
   </si>
   <si>
     <t xml:space="preserve">3.68462681770325</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">3.7133846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78168535232544</t>
+    <t xml:space="preserve">3.78168487548828</t>
   </si>
   <si>
     <t xml:space="preserve">3.83380913734436</t>
@@ -446,55 +446,55 @@
     <t xml:space="preserve">3.81224060058594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81583499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82661962509155</t>
+    <t xml:space="preserve">3.81583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82661986351013</t>
   </si>
   <si>
     <t xml:space="preserve">3.82841730117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92547559738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9003119468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335133552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740377426147</t>
+    <t xml:space="preserve">3.92547535896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740401268005</t>
   </si>
   <si>
     <t xml:space="preserve">3.87514877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94165229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929913520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243573188782</t>
+    <t xml:space="preserve">3.94165182113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9524359703064</t>
   </si>
   <si>
     <t xml:space="preserve">3.98119425773621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97939682006836</t>
+    <t xml:space="preserve">3.97939705848694</t>
   </si>
   <si>
     <t xml:space="preserve">3.88413572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94884157180786</t>
+    <t xml:space="preserve">3.9488410949707</t>
   </si>
   <si>
     <t xml:space="preserve">3.87874364852905</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">4.0530891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01714181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06207609176636</t>
+    <t xml:space="preserve">4.01714086532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0620756149292</t>
   </si>
   <si>
     <t xml:space="preserve">4.07106351852417</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">4.14295816421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06926488876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08903646469116</t>
+    <t xml:space="preserve">4.06926536560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08903741836548</t>
   </si>
   <si>
     <t xml:space="preserve">4.40357780456543</t>
@@ -539,82 +539,82 @@
     <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34606218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32808828353882</t>
+    <t xml:space="preserve">4.34606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32808876037598</t>
   </si>
   <si>
     <t xml:space="preserve">4.27236986160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11599683761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9847891330719</t>
+    <t xml:space="preserve">4.11599779129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03691339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98478865623474</t>
   </si>
   <si>
     <t xml:space="preserve">4.04230499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603060722351</t>
+    <t xml:space="preserve">3.95603084564209</t>
   </si>
   <si>
     <t xml:space="preserve">3.92008328437805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91828560829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704365730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099888801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795902252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90390658378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524621963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96359658241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99112153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194670677185</t>
+    <t xml:space="preserve">3.91828632354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9326651096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795926094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90390634536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524598121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9635968208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99112176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194718360901</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524669647217</t>
+    <t xml:space="preserve">3.94524645805359</t>
   </si>
   <si>
     <t xml:space="preserve">3.89019632339478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87184596061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92689681053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452083587646</t>
+    <t xml:space="preserve">3.87184619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452131271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.12874603271484</t>
@@ -623,49 +623,49 @@
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691164016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10672616958618</t>
+    <t xml:space="preserve">4.12691116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10672664642334</t>
   </si>
   <si>
     <t xml:space="preserve">4.05901622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03699636459351</t>
+    <t xml:space="preserve">4.03699684143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.99479150772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05351114273071</t>
+    <t xml:space="preserve">4.05351161956787</t>
   </si>
   <si>
     <t xml:space="preserve">4.0828709602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07369661331177</t>
+    <t xml:space="preserve">4.03332662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07369613647461</t>
   </si>
   <si>
     <t xml:space="preserve">4.09204626083374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08103609085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09021186828613</t>
+    <t xml:space="preserve">4.08103704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09021139144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.06268644332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15260124206543</t>
+    <t xml:space="preserve">4.15260171890259</t>
   </si>
   <si>
     <t xml:space="preserve">4.15627145767212</t>
@@ -674,28 +674,28 @@
     <t xml:space="preserve">4.16544628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11039686203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09388113021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20948648452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15443658828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11957120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13608551025391</t>
+    <t xml:space="preserve">4.11039638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09388160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20948600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15443563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13792085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507677078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11957168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13608598709106</t>
   </si>
   <si>
     <t xml:space="preserve">4.15076637268066</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">4.10305643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278575897217</t>
+    <t xml:space="preserve">4.17278623580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002687454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10122108459473</t>
+    <t xml:space="preserve">4.07002639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10122156143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.16911697387695</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">4.21132135391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09755229949951</t>
+    <t xml:space="preserve">4.09755182266235</t>
   </si>
   <si>
     <t xml:space="preserve">4.05167627334595</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">4.07920169830322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13425159454346</t>
+    <t xml:space="preserve">4.1342511177063</t>
   </si>
   <si>
     <t xml:space="preserve">4.21866130828857</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">4.1489315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1911358833313</t>
+    <t xml:space="preserve">4.19113636016846</t>
   </si>
   <si>
     <t xml:space="preserve">4.19297170639038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99662709236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04433631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561668395996</t>
+    <t xml:space="preserve">3.99662661552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04433679580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561644554138</t>
   </si>
   <si>
     <t xml:space="preserve">3.94341135025024</t>
@@ -782,64 +782,64 @@
     <t xml:space="preserve">4.0204815864563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92322659492493</t>
+    <t xml:space="preserve">3.92322611808777</t>
   </si>
   <si>
     <t xml:space="preserve">4.03516101837158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08654165267944</t>
+    <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
     <t xml:space="preserve">4.04800653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96726655960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506122589111</t>
+    <t xml:space="preserve">3.96726632118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506170272827</t>
   </si>
   <si>
     <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00029611587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97277164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93790674209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9984610080719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04617118835449</t>
+    <t xml:space="preserve">4.0002965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97277188301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93790650367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846148490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04617166519165</t>
   </si>
   <si>
     <t xml:space="preserve">3.88102173805237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85349631309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442128181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89937138557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854716300964</t>
+    <t xml:space="preserve">3.85349678993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442175865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514666557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89937162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854692459106</t>
   </si>
   <si>
     <t xml:space="preserve">3.93607139587402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86267185211182</t>
+    <t xml:space="preserve">3.86267161369324</t>
   </si>
   <si>
     <t xml:space="preserve">3.82597160339355</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">3.78927183151245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80762147903442</t>
+    <t xml:space="preserve">3.807621717453</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039432525635</t>
@@ -857,61 +857,61 @@
     <t xml:space="preserve">4.04857444763184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03918075561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97342681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221348762512</t>
+    <t xml:space="preserve">4.03918123245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97342705726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99221396446228</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403336524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827919006348</t>
+    <t xml:space="preserve">3.96403288841248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827942848206</t>
   </si>
   <si>
     <t xml:space="preserve">3.91706609725952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77616429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101714134216</t>
+    <t xml:space="preserve">3.77616477012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.75737762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73859095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71041035652161</t>
+    <t xml:space="preserve">3.73859047889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
     <t xml:space="preserve">3.63526272773743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62586951255798</t>
+    <t xml:space="preserve">3.6258692741394</t>
   </si>
   <si>
     <t xml:space="preserve">3.52254176139832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42860746383667</t>
+    <t xml:space="preserve">3.42860698699951</t>
   </si>
   <si>
     <t xml:space="preserve">3.28770542144775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35345983505249</t>
+    <t xml:space="preserve">3.35345935821533</t>
   </si>
   <si>
     <t xml:space="preserve">3.33467268943787</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">3.45678782463074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46618103981018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36285305023193</t>
+    <t xml:space="preserve">3.4661808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36285281181335</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
@@ -941,40 +941,40 @@
     <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47557473182678</t>
+    <t xml:space="preserve">3.47557425498962</t>
   </si>
   <si>
     <t xml:space="preserve">3.49436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3158860206604</t>
+    <t xml:space="preserve">3.31588578224182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50375485420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65404987335205</t>
+    <t xml:space="preserve">3.56950879096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50375461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65405011177063</t>
   </si>
   <si>
     <t xml:space="preserve">3.48496794700623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68222999572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59768891334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647582054138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66344332695007</t>
+    <t xml:space="preserve">3.68223023414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59768915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66344356536865</t>
   </si>
   <si>
     <t xml:space="preserve">3.58829569816589</t>
@@ -989,49 +989,49 @@
     <t xml:space="preserve">3.56011533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57890200614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64465618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6728367805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51314830780029</t>
+    <t xml:space="preserve">3.57890224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67283654212952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51314806938171</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54921507835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62637209892273</t>
+    <t xml:space="preserve">3.54921531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62637186050415</t>
   </si>
   <si>
     <t xml:space="preserve">3.58779358863831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66495037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68423962593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068542480469</t>
+    <t xml:space="preserve">3.66495013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68423938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
     <t xml:space="preserve">3.7999746799469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210715293884</t>
+    <t xml:space="preserve">3.74210739135742</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855319023132</t>
+    <t xml:space="preserve">3.83855295181274</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52992606163025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47205805778503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51063656806946</t>
+    <t xml:space="preserve">3.52992582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47205829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51063680648804</t>
   </si>
   <si>
     <t xml:space="preserve">3.41419053077698</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">3.43347978591919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4527690410614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37561202049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39490127563477</t>
+    <t xml:space="preserve">3.45276880264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37561225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39490151405334</t>
   </si>
   <si>
     <t xml:space="preserve">3.33703374862671</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85480332374573</t>
+    <t xml:space="preserve">2.91267108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
     <t xml:space="preserve">2.71977877616882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83551430702209</t>
+    <t xml:space="preserve">2.83551406860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.97053861618042</t>
@@ -1130,25 +1130,25 @@
     <t xml:space="preserve">3.08627390861511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12485265731812</t>
+    <t xml:space="preserve">3.12485241889954</t>
   </si>
   <si>
     <t xml:space="preserve">2.98982787132263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95124936103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8162248134613</t>
+    <t xml:space="preserve">2.95124959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81622505187988</t>
   </si>
   <si>
     <t xml:space="preserve">2.79693579673767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75835728645325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77764654159546</t>
+    <t xml:space="preserve">2.75835704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
     <t xml:space="preserve">2.73906803131104</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">2.5847544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50759744644165</t>
+    <t xml:space="preserve">2.50759768486023</t>
   </si>
   <si>
     <t xml:space="preserve">2.46901917457581</t>
@@ -1178,37 +1178,37 @@
     <t xml:space="preserve">2.16039180755615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04465651512146</t>
+    <t xml:space="preserve">2.04465627670288</t>
   </si>
   <si>
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23754858970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02536702156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19897031784058</t>
+    <t xml:space="preserve">2.14110255241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23754835128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02536749839783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.198970079422</t>
   </si>
   <si>
     <t xml:space="preserve">2.12181329727173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25683760643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29541611671448</t>
+    <t xml:space="preserve">2.25683784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648235321045</t>
+    <t xml:space="preserve">2.26648259162903</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">2.36292862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506086349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22790384292603</t>
+    <t xml:space="preserve">2.30506110191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2279040813446</t>
   </si>
   <si>
     <t xml:space="preserve">2.24719309806824</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">2.35328388214111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32434988021851</t>
+    <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
     <t xml:space="preserve">2.17968106269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18932557106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17003655433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1314582824707</t>
+    <t xml:space="preserve">2.18932580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17003631591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13145804405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.08323502540588</t>
@@ -1265,34 +1265,34 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216878890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07359051704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03501200675964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98678874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92409896850586</t>
+    <t xml:space="preserve">2.11216855049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07359027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03501152992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98678886890411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92409884929657</t>
   </si>
   <si>
     <t xml:space="preserve">1.92892122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93856573104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95785510540009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20861482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15074729919434</t>
+    <t xml:space="preserve">1.93856585025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9578549861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20861458778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15074706077576</t>
   </si>
   <si>
     <t xml:space="preserve">2.37257313728333</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">2.38221764564514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56546545028687</t>
+    <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
     <t xml:space="preserve">2.87409257888794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66191148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64262223243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59439921379089</t>
+    <t xml:space="preserve">2.66191124916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64262199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59439897537231</t>
   </si>
   <si>
     <t xml:space="preserve">2.68120050430298</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">2.65226674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61368823051453</t>
+    <t xml:space="preserve">2.61368846893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.53653168678284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52688694000244</t>
+    <t xml:space="preserve">2.52688670158386</t>
   </si>
   <si>
     <t xml:space="preserve">2.51724195480347</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013426780701</t>
+    <t xml:space="preserve">2.71013450622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78729104995728</t>
+    <t xml:space="preserve">2.72942328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78729152679443</t>
   </si>
   <si>
     <t xml:space="preserve">2.94160485267639</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">2.9608941078186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03805112838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16343092918396</t>
+    <t xml:space="preserve">3.03805088996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16343069076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23094296455383</t>
+    <t xml:space="preserve">3.23094320297241</t>
   </si>
   <si>
     <t xml:space="preserve">3.24058747291565</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">3.19236469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17307543754578</t>
+    <t xml:space="preserve">3.1730751991272</t>
   </si>
   <si>
     <t xml:space="preserve">3.13449716567993</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">3.15378618240356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26952147483826</t>
+    <t xml:space="preserve">3.26952171325684</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3080997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32738924026489</t>
+    <t xml:space="preserve">3.30810022354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
     <t xml:space="preserve">3.25023198127747</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">3.09591865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0766294002533</t>
+    <t xml:space="preserve">3.07662916183472</t>
   </si>
   <si>
     <t xml:space="preserve">3.01876187324524</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">2.92231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93196034431458</t>
+    <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
     <t xml:space="preserve">2.90302634239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88373708724976</t>
+    <t xml:space="preserve">2.88373732566833</t>
   </si>
   <si>
     <t xml:space="preserve">2.86444807052612</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
+    <t xml:space="preserve">3.59743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71317315101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79033017158508</t>
+    <t xml:space="preserve">3.71317338943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
     <t xml:space="preserve">3.88677644729614</t>
@@ -1460,55 +1460,55 @@
     <t xml:space="preserve">3.95428848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9446439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98322248458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073404312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97357749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07002401351929</t>
+    <t xml:space="preserve">3.94464373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9832227230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073499679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97357773780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07002305984497</t>
   </si>
   <si>
     <t xml:space="preserve">4.20504856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26291656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30149459838867</t>
+    <t xml:space="preserve">4.26291608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30149412155151</t>
   </si>
   <si>
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971761703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3400731086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39794063568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42687463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45580768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22433757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08931303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03144502639771</t>
+    <t xml:space="preserve">4.34971714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34007263183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39794015884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4268741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45580816268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22433710098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08931255340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03144550323486</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40758562088013</t>
+    <t xml:space="preserve">4.40758514404297</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5329647064209</t>
+    <t xml:space="preserve">4.53296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3690071105957</t>
+    <t xml:space="preserve">4.36900663375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.12789154052734</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">4.16647005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25327110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1857590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14718103408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02180099487305</t>
+    <t xml:space="preserve">4.25327157974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18575954437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14718055725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02180051803589</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
@@ -1562,31 +1562,31 @@
     <t xml:space="preserve">4.33042812347412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51367521286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46545267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37865114212036</t>
+    <t xml:space="preserve">4.51367568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46545314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.48474168777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47509717941284</t>
+    <t xml:space="preserve">4.47509670257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.49438619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41722965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64869976043701</t>
+    <t xml:space="preserve">4.44616365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41722917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64870023727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.80301380157471</t>
@@ -1595,25 +1595,25 @@
     <t xml:space="preserve">4.72585725784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6390552520752</t>
+    <t xml:space="preserve">4.63905572891235</t>
   </si>
   <si>
     <t xml:space="preserve">4.62941074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61012172698975</t>
+    <t xml:space="preserve">4.6101222038269</t>
   </si>
   <si>
     <t xml:space="preserve">4.57154273986816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682554244995</t>
+    <t xml:space="preserve">4.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682506561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
@@ -1637,25 +1637,25 @@
     <t xml:space="preserve">4.97661638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0151948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45884704589844</t>
+    <t xml:space="preserve">5.01519536972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45884656906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.59387159347534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28524446487427</t>
+    <t xml:space="preserve">5.49742555618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28524398803711</t>
   </si>
   <si>
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026853561401</t>
+    <t xml:space="preserve">5.42026901245117</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">4.86088180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84159183502197</t>
+    <t xml:space="preserve">4.84159231185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.93803834915161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73550128936768</t>
+    <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
     <t xml:space="preserve">4.70608854293823</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96100187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13748025894165</t>
+    <t xml:space="preserve">4.87276220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9610013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432725906372</t>
+    <t xml:space="preserve">5.00021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432773590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667579650879</t>
+    <t xml:space="preserve">4.67667531967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1733,25 +1733,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413246154785</t>
+    <t xml:space="preserve">4.72569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413198471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73550176620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687107086182</t>
+    <t xml:space="preserve">4.92178440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687154769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1781,16 +1778,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000118255615</t>
+    <t xml:space="preserve">4.74530601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000165939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5982403755188</t>
+    <t xml:space="preserve">4.59824085235596</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1799,7 +1796,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921913146973</t>
+    <t xml:space="preserve">4.54921865463257</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1826,40 +1823,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254451751709</t>
+    <t xml:space="preserve">4.38254499435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32371854782104</t>
+    <t xml:space="preserve">4.3237190246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508832931519</t>
+    <t xml:space="preserve">4.264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508880615234</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1374363899231</t>
+    <t xml:space="preserve">4.13743591308594</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352375030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117521286011</t>
+    <t xml:space="preserve">4.33352327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117568969727</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1868,7 +1865,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274074554443</t>
+    <t xml:space="preserve">4.37274026870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1883,10 +1880,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16684913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19626235961914</t>
+    <t xml:space="preserve">4.1668496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1962628364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -46400,7 +46397,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1681" t="s">
-        <v>577</v>
+        <v>552</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46556,7 +46553,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46634,7 +46631,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46660,7 +46657,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46686,7 +46683,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1692" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46738,7 +46735,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1694" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46764,7 +46761,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1695" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46816,7 +46813,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46842,7 +46839,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1698" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46868,7 +46865,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1699" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46894,7 +46891,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1700" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46920,7 +46917,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1701" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46946,7 +46943,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47076,7 +47073,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47102,7 +47099,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1708" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47128,7 +47125,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1709" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47154,7 +47151,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1710" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47206,7 +47203,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47232,7 +47229,7 @@
         <v>4.5</v>
       </c>
       <c r="G1713" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47258,7 +47255,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47284,7 +47281,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47310,7 +47307,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47336,7 +47333,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47362,7 +47359,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1718" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47414,7 +47411,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1720" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47440,7 +47437,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47466,7 +47463,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1722" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47544,7 +47541,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1725" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47570,7 +47567,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1726" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47596,7 +47593,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47622,7 +47619,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1728" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47648,7 +47645,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1729" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47674,7 +47671,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47700,7 +47697,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1731" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47726,7 +47723,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1732" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47752,7 +47749,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1733" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47830,7 +47827,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1736" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47856,7 +47853,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1737" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47882,7 +47879,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1738" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47934,7 +47931,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1740" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47960,7 +47957,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1741" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47986,7 +47983,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1742" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48064,7 +48061,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1745" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48090,7 +48087,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1746" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48142,7 +48139,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1748" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48168,7 +48165,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1749" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48194,7 +48191,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1750" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48220,7 +48217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1751" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48246,7 +48243,7 @@
         <v>4.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48272,7 +48269,7 @@
         <v>4.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48298,7 +48295,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1754" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48324,7 +48321,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1755" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48350,7 +48347,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1756" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48376,7 +48373,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1757" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48402,7 +48399,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48428,7 +48425,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1759" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48454,7 +48451,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1760" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48480,7 +48477,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1761" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48506,7 +48503,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1762" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48532,7 +48529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1763" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48558,7 +48555,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48584,7 +48581,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1765" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48610,7 +48607,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1766" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48636,7 +48633,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1767" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48662,7 +48659,7 @@
         <v>4.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48688,7 +48685,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1769" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48714,7 +48711,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1770" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48740,7 +48737,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1771" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48766,7 +48763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1772" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48792,7 +48789,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1773" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48818,7 +48815,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1774" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48844,7 +48841,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1775" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48870,7 +48867,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48896,7 +48893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1777" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48922,7 +48919,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1778" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48948,7 +48945,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1779" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48974,7 +48971,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1780" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49000,7 +48997,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1781" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49026,7 +49023,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1782" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49052,7 +49049,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49078,7 +49075,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49104,7 +49101,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1785" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49130,7 +49127,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49156,7 +49153,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1787" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49182,7 +49179,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1788" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49208,7 +49205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49234,7 +49231,7 @@
         <v>4.5</v>
       </c>
       <c r="G1790" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49260,7 +49257,7 @@
         <v>4.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49286,7 +49283,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49312,7 +49309,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49338,7 +49335,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49364,7 +49361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1795" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49390,7 +49387,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1796" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49416,7 +49413,7 @@
         <v>4.75</v>
       </c>
       <c r="G1797" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49442,7 +49439,7 @@
         <v>4.75</v>
       </c>
       <c r="G1798" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49468,7 +49465,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1799" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49494,7 +49491,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49546,7 +49543,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1802" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49572,7 +49569,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1803" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49598,7 +49595,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1804" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49624,7 +49621,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1805" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49650,7 +49647,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1806" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49676,7 +49673,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1807" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49702,7 +49699,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1808" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49728,7 +49725,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1809" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49754,7 +49751,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1810" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49780,7 +49777,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1811" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49806,7 +49803,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1812" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49832,7 +49829,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1813" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49858,7 +49855,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1814" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49884,7 +49881,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1815" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49910,7 +49907,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1816" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49936,7 +49933,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1817" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49962,7 +49959,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49988,7 +49985,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1819" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50014,7 +50011,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1820" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50040,7 +50037,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1821" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50066,7 +50063,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1822" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50092,7 +50089,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1823" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50118,7 +50115,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1824" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50196,7 +50193,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50352,7 +50349,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50378,7 +50375,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1834" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50404,7 +50401,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1835" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50430,7 +50427,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1836" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50456,7 +50453,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1837" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50534,7 +50531,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1840" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50586,7 +50583,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1842" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50638,7 +50635,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1844" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50690,7 +50687,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1846" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50716,7 +50713,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1847" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50742,7 +50739,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1848" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50768,7 +50765,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1849" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50794,7 +50791,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1850" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50820,7 +50817,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1851" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50846,7 +50843,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50872,7 +50869,7 @@
         <v>4.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50898,7 +50895,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1854" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50924,7 +50921,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1855" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50950,7 +50947,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1856" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50976,7 +50973,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51002,7 +50999,7 @@
         <v>4.5</v>
       </c>
       <c r="G1858" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51028,7 +51025,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1859" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51054,7 +51051,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51080,7 +51077,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1861" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51106,7 +51103,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51132,7 +51129,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1863" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51158,7 +51155,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1864" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51184,7 +51181,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1865" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51210,7 +51207,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1866" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51236,7 +51233,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51262,7 +51259,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1868" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51288,7 +51285,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1869" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51314,7 +51311,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51340,7 +51337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1871" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51366,7 +51363,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1872" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51392,7 +51389,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1873" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51418,7 +51415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1874" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51444,7 +51441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1875" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51470,7 +51467,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1876" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51496,7 +51493,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1877" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51522,7 +51519,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51548,7 +51545,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1879" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51574,7 +51571,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1880" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51600,7 +51597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1881" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51626,7 +51623,7 @@
         <v>4.5</v>
       </c>
       <c r="G1882" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51652,7 +51649,7 @@
         <v>4.5</v>
       </c>
       <c r="G1883" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51678,7 +51675,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51704,7 +51701,7 @@
         <v>4.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51730,7 +51727,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1886" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51756,7 +51753,7 @@
         <v>4.5</v>
       </c>
       <c r="G1887" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51782,7 +51779,7 @@
         <v>4.5</v>
       </c>
       <c r="G1888" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51808,7 +51805,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51834,7 +51831,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1890" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51860,7 +51857,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1891" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51886,7 +51883,7 @@
         <v>4.5</v>
       </c>
       <c r="G1892" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51912,7 +51909,7 @@
         <v>4.5</v>
       </c>
       <c r="G1893" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51938,7 +51935,7 @@
         <v>4.5</v>
       </c>
       <c r="G1894" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51964,7 +51961,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51990,7 +51987,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52016,7 +52013,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1897" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52042,7 +52039,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1898" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52068,7 +52065,7 @@
         <v>4.5</v>
       </c>
       <c r="G1899" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52094,7 +52091,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1900" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52120,7 +52117,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1901" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52146,7 +52143,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1902" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52172,7 +52169,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52198,7 +52195,7 @@
         <v>4.5</v>
       </c>
       <c r="G1904" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52224,7 +52221,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1905" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52250,7 +52247,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1906" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52276,7 +52273,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1907" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52302,7 +52299,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1908" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52328,7 +52325,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1909" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52354,7 +52351,7 @@
         <v>4.75</v>
       </c>
       <c r="G1910" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52380,7 +52377,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52406,7 +52403,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1912" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52432,7 +52429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1913" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52458,7 +52455,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52484,7 +52481,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1915" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52510,7 +52507,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1916" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52536,7 +52533,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1917" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52562,7 +52559,7 @@
         <v>4.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52588,7 +52585,7 @@
         <v>4.75</v>
       </c>
       <c r="G1919" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52614,7 +52611,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1920" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52640,7 +52637,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1921" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52666,7 +52663,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1922" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52692,7 +52689,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52718,7 +52715,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1924" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52744,7 +52741,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52770,7 +52767,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1926" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52796,7 +52793,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1927" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52822,7 +52819,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1928" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52848,7 +52845,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1929" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52874,7 +52871,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1930" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52900,7 +52897,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1931" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52926,7 +52923,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1932" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52952,7 +52949,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1933" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52978,7 +52975,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1934" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53004,7 +53001,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1935" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53030,7 +53027,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1936" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53056,7 +53053,7 @@
         <v>4.5</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53082,7 +53079,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1938" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53108,7 +53105,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1939" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53134,7 +53131,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1940" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53160,7 +53157,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53186,7 +53183,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1942" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53212,7 +53209,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1943" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53238,7 +53235,7 @@
         <v>4.5</v>
       </c>
       <c r="G1944" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53264,7 +53261,7 @@
         <v>4.5</v>
       </c>
       <c r="G1945" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53290,7 +53287,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1946" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53316,7 +53313,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1947" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53342,7 +53339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1948" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53368,7 +53365,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1949" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53394,7 +53391,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1950" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53420,7 +53417,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1951" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53446,7 +53443,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1952" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53472,7 +53469,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1953" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53498,7 +53495,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1954" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53524,7 +53521,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53550,7 +53547,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1956" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53576,7 +53573,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1957" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53602,7 +53599,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1958" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53628,7 +53625,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1959" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53654,7 +53651,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1960" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53680,7 +53677,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1961" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53706,7 +53703,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53732,7 +53729,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1963" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53758,7 +53755,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1964" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53784,7 +53781,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1965" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53810,7 +53807,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1966" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53836,7 +53833,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1967" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53862,7 +53859,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1968" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53888,7 +53885,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1969" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53914,7 +53911,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1970" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53940,7 +53937,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53966,7 +53963,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1972" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53992,7 +53989,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54018,7 +54015,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1974" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54044,7 +54041,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1975" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54070,7 +54067,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54096,7 +54093,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54122,7 +54119,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1978" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54148,7 +54145,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1979" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54174,7 +54171,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54200,7 +54197,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54226,7 +54223,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1982" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54252,7 +54249,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1983" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54278,7 +54275,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1984" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54304,7 +54301,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1985" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54330,7 +54327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1986" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54356,7 +54353,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54382,7 +54379,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1988" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54408,7 +54405,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1989" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54434,7 +54431,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54460,7 +54457,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1991" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54486,7 +54483,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54512,7 +54509,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1993" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54538,7 +54535,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54564,7 +54561,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1995" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54590,7 +54587,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1996" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54616,7 +54613,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54642,7 +54639,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54668,7 +54665,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1999" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54694,7 +54691,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2000" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54720,7 +54717,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2001" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54746,7 +54743,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2002" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54772,7 +54769,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2003" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54798,7 +54795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2004" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54824,7 +54821,7 @@
         <v>4.75</v>
       </c>
       <c r="G2005" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54850,7 +54847,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2006" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54876,7 +54873,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2007" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54902,7 +54899,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2008" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54928,7 +54925,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2009" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54954,7 +54951,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2010" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54980,7 +54977,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2011" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55006,7 +55003,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2012" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55032,7 +55029,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55058,7 +55055,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55084,7 +55081,7 @@
         <v>4.5</v>
       </c>
       <c r="G2015" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55110,7 +55107,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2016" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55136,7 +55133,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2017" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55162,7 +55159,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2018" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55188,7 +55185,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2019" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55214,7 +55211,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2020" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55240,7 +55237,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2021" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55266,7 +55263,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2022" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55292,7 +55289,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2023" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55318,7 +55315,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2024" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55344,7 +55341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2025" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55370,7 +55367,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2026" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55396,7 +55393,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2027" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55422,7 +55419,7 @@
         <v>4.75</v>
       </c>
       <c r="G2028" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55448,7 +55445,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2029" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55474,7 +55471,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2030" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55500,7 +55497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2031" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55526,7 +55523,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2032" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55552,7 +55549,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2033" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55578,7 +55575,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2034" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55604,7 +55601,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2035" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55630,7 +55627,7 @@
         <v>5</v>
       </c>
       <c r="G2036" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55656,7 +55653,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55682,7 +55679,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2038" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55708,7 +55705,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2039" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55734,7 +55731,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55760,7 +55757,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55786,7 +55783,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2042" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55812,7 +55809,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2043" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55838,7 +55835,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2044" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55864,7 +55861,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2045" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55890,7 +55887,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2046" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55916,7 +55913,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55942,7 +55939,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2048" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55968,7 +55965,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2049" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55994,7 +55991,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2050" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56020,7 +56017,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2051" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56046,7 +56043,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2052" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56072,7 +56069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2053" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56098,7 +56095,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2054" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56124,7 +56121,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56150,7 +56147,7 @@
         <v>5</v>
       </c>
       <c r="G2056" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56176,7 +56173,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56202,7 +56199,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56228,7 +56225,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2059" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56254,7 +56251,7 @@
         <v>5</v>
       </c>
       <c r="G2060" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56280,7 +56277,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2061" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56306,7 +56303,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2062" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56332,7 +56329,7 @@
         <v>5</v>
       </c>
       <c r="G2063" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56358,7 +56355,7 @@
         <v>5</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56384,7 +56381,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2065" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56410,7 +56407,7 @@
         <v>5</v>
       </c>
       <c r="G2066" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56436,7 +56433,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2067" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56462,7 +56459,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2068" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56488,7 +56485,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2069" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56514,7 +56511,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2070" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56540,7 +56537,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2071" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56566,7 +56563,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2072" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56592,7 +56589,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2073" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56618,7 +56615,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2074" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56644,7 +56641,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2075" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56670,7 +56667,7 @@
         <v>5.5</v>
       </c>
       <c r="G2076" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56696,7 +56693,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56722,7 +56719,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56748,7 +56745,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2079" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56774,7 +56771,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2080" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56800,7 +56797,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56826,7 +56823,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2082" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56852,7 +56849,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2083" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56878,7 +56875,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2084" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56904,7 +56901,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2085" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56930,7 +56927,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2086" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56956,7 +56953,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2087" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56982,7 +56979,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2088" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57008,7 +57005,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2089" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57034,7 +57031,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2090" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57060,7 +57057,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57086,7 +57083,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2092" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57112,7 +57109,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2093" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57138,7 +57135,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2094" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57164,7 +57161,7 @@
         <v>5</v>
       </c>
       <c r="G2095" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57190,7 +57187,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2096" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57216,7 +57213,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2097" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57242,7 +57239,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57268,7 +57265,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2099" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57294,7 +57291,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2100" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57320,7 +57317,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2101" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57346,7 +57343,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57372,7 +57369,7 @@
         <v>5</v>
       </c>
       <c r="G2103" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57398,7 +57395,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57424,7 +57421,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2105" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57450,7 +57447,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2106" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57476,7 +57473,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2107" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57502,7 +57499,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2108" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57528,7 +57525,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2109" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57554,7 +57551,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57580,7 +57577,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57606,7 +57603,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2112" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57632,7 +57629,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2113" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57658,7 +57655,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2114" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57684,7 +57681,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2115" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57710,7 +57707,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57736,7 +57733,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2117" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57762,7 +57759,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2118" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57788,7 +57785,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2119" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57814,7 +57811,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2120" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57840,7 +57837,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2121" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57866,7 +57863,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2122" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57892,7 +57889,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57918,7 +57915,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57944,7 +57941,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57970,7 +57967,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2126" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57996,7 +57993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2127" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58022,7 +58019,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2128" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58048,7 +58045,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2129" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58074,7 +58071,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58100,7 +58097,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2131" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58126,7 +58123,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2132" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58152,7 +58149,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2133" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58178,7 +58175,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2134" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58204,7 +58201,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2135" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58230,7 +58227,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2136" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58256,7 +58253,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58282,7 +58279,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2138" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58308,7 +58305,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2139" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58334,7 +58331,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2140" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58360,7 +58357,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2141" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58386,7 +58383,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2142" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58412,7 +58409,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2143" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58438,7 +58435,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2144" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58464,7 +58461,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2145" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58490,7 +58487,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2146" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58516,7 +58513,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2147" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58542,7 +58539,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2148" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58568,7 +58565,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2149" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58594,7 +58591,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58620,7 +58617,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2151" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58646,7 +58643,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2152" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58672,7 +58669,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2153" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58698,7 +58695,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2154" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58724,7 +58721,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2155" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58750,7 +58747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2156" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58776,7 +58773,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2157" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58802,7 +58799,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2158" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58828,7 +58825,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58854,7 +58851,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2160" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58880,7 +58877,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58906,7 +58903,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2162" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58932,7 +58929,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2163" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58958,7 +58955,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2164" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58984,7 +58981,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2165" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59010,7 +59007,7 @@
         <v>4.75</v>
       </c>
       <c r="G2166" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59036,7 +59033,7 @@
         <v>4.75</v>
       </c>
       <c r="G2167" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59062,7 +59059,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2168" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59088,7 +59085,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59114,7 +59111,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2170" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59140,7 +59137,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59166,7 +59163,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2172" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59192,7 +59189,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2173" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59218,7 +59215,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2174" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59244,7 +59241,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2175" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59270,7 +59267,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59296,7 +59293,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2177" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59322,7 +59319,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2178" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59348,7 +59345,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2179" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59374,7 +59371,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2180" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59400,7 +59397,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2181" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59426,7 +59423,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2182" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59452,7 +59449,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2183" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59478,7 +59475,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2184" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59504,7 +59501,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2185" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59530,7 +59527,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2186" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59556,7 +59553,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2187" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59582,7 +59579,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2188" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59608,7 +59605,7 @@
         <v>4.25</v>
       </c>
       <c r="G2189" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59634,7 +59631,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2190" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59660,7 +59657,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2191" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59686,7 +59683,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2192" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59712,7 +59709,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2193" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59738,7 +59735,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2194" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59764,7 +59761,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2195" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59790,7 +59787,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2196" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59816,7 +59813,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59842,7 +59839,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2198" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59868,7 +59865,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59894,7 +59891,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2200" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59920,7 +59917,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2201" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59946,7 +59943,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2202" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59972,7 +59969,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59998,7 +59995,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60024,7 +60021,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2205" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60050,7 +60047,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2206" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60076,7 +60073,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2207" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60102,7 +60099,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60128,7 +60125,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2209" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60154,7 +60151,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2210" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60180,7 +60177,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2211" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60206,7 +60203,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60232,7 +60229,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2213" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60258,7 +60255,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2214" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60284,7 +60281,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60310,7 +60307,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2216" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60336,7 +60333,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2217" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60362,7 +60359,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2218" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60388,7 +60385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2219" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60414,7 +60411,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2220" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60440,7 +60437,7 @@
         <v>4.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60466,7 +60463,7 @@
         <v>4.5</v>
       </c>
       <c r="G2222" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60492,7 +60489,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2223" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60518,7 +60515,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60544,7 +60541,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2225" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60570,7 +60567,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2226" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60596,7 +60593,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2227" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60622,7 +60619,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2228" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60648,7 +60645,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2229" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60674,7 +60671,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2230" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60700,7 +60697,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2231" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60726,7 +60723,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2232" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60752,7 +60749,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60778,7 +60775,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60804,7 +60801,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2235" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60830,7 +60827,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2236" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60856,7 +60853,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2237" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60882,7 +60879,7 @@
         <v>4.5</v>
       </c>
       <c r="G2238" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60908,7 +60905,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2239" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60934,7 +60931,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2240" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60960,7 +60957,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2241" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60986,7 +60983,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2242" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61012,7 +61009,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2243" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61038,7 +61035,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2244" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61064,7 +61061,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2245" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61090,7 +61087,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2246" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61116,7 +61113,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2247" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61142,7 +61139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2248" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61168,7 +61165,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2249" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61194,7 +61191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2250" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61220,7 +61217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2251" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61246,7 +61243,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2252" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61272,7 +61269,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61298,7 +61295,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2254" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61324,7 +61321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2255" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61350,7 +61347,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2256" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61376,7 +61373,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2257" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61402,7 +61399,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2258" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61428,7 +61425,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2259" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61454,7 +61451,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2260" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61480,7 +61477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61506,7 +61503,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61532,7 +61529,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2263" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61558,7 +61555,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2264" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61584,7 +61581,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2265" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61610,7 +61607,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2266" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61636,7 +61633,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2267" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61662,7 +61659,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61688,7 +61685,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2269" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61714,7 +61711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2270" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61740,7 +61737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2271" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61766,7 +61763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2272" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61792,7 +61789,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2273" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61818,7 +61815,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2274" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61844,7 +61841,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2275" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61870,7 +61867,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2276" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61896,7 +61893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2277" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61922,7 +61919,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2278" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61948,7 +61945,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2279" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61974,7 +61971,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2280" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62000,7 +61997,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2281" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62026,7 +62023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2282" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62052,7 +62049,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2283" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62078,7 +62075,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2284" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62104,7 +62101,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2285" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62130,7 +62127,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62156,7 +62153,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2287" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62182,7 +62179,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2288" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62208,7 +62205,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2289" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62234,7 +62231,7 @@
         <v>4.5</v>
       </c>
       <c r="G2290" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62260,7 +62257,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2291" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62286,7 +62283,7 @@
         <v>4.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62312,7 +62309,7 @@
         <v>4.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62338,7 +62335,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2294" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62364,7 +62361,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2295" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62390,7 +62387,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2296" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62416,7 +62413,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2297" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62442,7 +62439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2298" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62468,7 +62465,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2299" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62494,7 +62491,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2300" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62520,7 +62517,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2301" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62546,7 +62543,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2302" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62572,7 +62569,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2303" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62598,7 +62595,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62624,7 +62621,7 @@
         <v>4.5</v>
       </c>
       <c r="G2305" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62650,7 +62647,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2306" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62676,7 +62673,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2307" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62702,7 +62699,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2308" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62728,7 +62725,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62754,7 +62751,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2310" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62780,7 +62777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2311" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62806,7 +62803,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2312" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62832,7 +62829,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2313" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62858,7 +62855,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2314" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62884,7 +62881,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2315" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62910,7 +62907,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2316" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62936,7 +62933,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2317" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62962,7 +62959,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62988,7 +62985,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2319" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63014,7 +63011,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2320" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63040,7 +63037,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63066,7 +63063,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2322" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63092,7 +63089,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2323" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63118,7 +63115,7 @@
         <v>4.25</v>
       </c>
       <c r="G2324" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63144,7 +63141,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2325" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63170,7 +63167,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2326" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63196,7 +63193,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2327" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63222,7 +63219,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2328" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63248,7 +63245,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63274,7 +63271,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2330" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63300,7 +63297,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2331" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63326,7 +63323,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2332" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63352,7 +63349,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2333" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63378,7 +63375,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2334" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63404,7 +63401,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2335" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63430,7 +63427,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2336" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63456,7 +63453,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2337" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63482,7 +63479,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2338" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63508,7 +63505,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2339" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63534,7 +63531,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2340" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63560,7 +63557,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2341" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63586,7 +63583,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2342" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63612,7 +63609,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2343" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63638,7 +63635,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2344" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63664,7 +63661,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2345" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63690,7 +63687,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2346" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63716,7 +63713,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2347" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63742,7 +63739,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2348" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63768,7 +63765,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63794,7 +63791,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2350" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63820,7 +63817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2351" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63846,7 +63843,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2352" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63872,7 +63869,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2353" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63898,7 +63895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2354" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63924,7 +63921,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2355" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63950,7 +63947,7 @@
         <v>4</v>
       </c>
       <c r="G2356" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63976,7 +63973,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2357" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64002,7 +63999,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2358" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64028,7 +64025,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2359" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64054,7 +64051,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2360" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64080,7 +64077,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2361" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64106,7 +64103,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2362" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64132,7 +64129,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2363" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64158,7 +64155,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2364" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64184,7 +64181,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2365" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64210,7 +64207,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2366" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64236,7 +64233,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2367" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64262,7 +64259,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2368" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64288,7 +64285,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2369" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64314,7 +64311,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2370" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64340,7 +64337,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2371" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64366,7 +64363,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2372" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64392,7 +64389,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2373" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64418,7 +64415,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2374" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64444,7 +64441,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2375" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64470,7 +64467,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64496,7 +64493,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2377" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64522,7 +64519,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2378" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64548,7 +64545,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2379" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64574,7 +64571,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2380" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64600,7 +64597,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2381" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64626,7 +64623,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2382" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64652,7 +64649,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2383" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64678,7 +64675,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64704,7 +64701,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64730,7 +64727,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64756,7 +64753,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64782,7 +64779,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2388" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64808,7 +64805,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2389" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64834,7 +64831,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2390" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64860,7 +64857,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2391" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64886,7 +64883,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2392" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64912,7 +64909,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2393" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64938,7 +64935,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2394" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64964,7 +64961,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2395" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64990,7 +64987,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2396" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65016,7 +65013,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65042,7 +65039,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2398" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65068,7 +65065,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2399" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65094,7 +65091,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2400" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65120,7 +65117,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2401" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65146,7 +65143,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2402" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65172,7 +65169,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2403" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65198,7 +65195,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2404" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65224,7 +65221,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2405" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65250,7 +65247,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65276,7 +65273,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2407" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65302,7 +65299,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2408" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65328,7 +65325,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2409" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65354,7 +65351,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65380,7 +65377,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65406,7 +65403,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2412" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65432,7 +65429,7 @@
         <v>4</v>
       </c>
       <c r="G2413" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65458,7 +65455,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2414" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65484,7 +65481,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2415" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65510,7 +65507,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2416" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65536,7 +65533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65562,7 +65559,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2418" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65588,7 +65585,7 @@
         <v>4</v>
       </c>
       <c r="G2419" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65614,7 +65611,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2420" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65640,7 +65637,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2421" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65666,7 +65663,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2422" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65692,7 +65689,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2423" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65718,7 +65715,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65744,7 +65741,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2425" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65770,7 +65767,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2426" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65796,7 +65793,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2427" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65822,7 +65819,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2428" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65848,7 +65845,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65874,7 +65871,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2430" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65900,7 +65897,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2431" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65926,7 +65923,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2432" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65952,7 +65949,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2433" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65978,7 +65975,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2434" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66004,7 +66001,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2435" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66030,7 +66027,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2436" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66056,7 +66053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2437" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66082,7 +66079,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2438" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66108,7 +66105,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2439" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66134,7 +66131,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66160,7 +66157,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66186,7 +66183,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2442" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66212,7 +66209,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2443" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66238,7 +66235,7 @@
         <v>4</v>
       </c>
       <c r="G2444" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66264,7 +66261,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2445" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66290,7 +66287,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2446" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66316,7 +66313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2447" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66342,7 +66339,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66368,7 +66365,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2449" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66394,7 +66391,7 @@
         <v>4</v>
       </c>
       <c r="G2450" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66420,7 +66417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2451" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66446,7 +66443,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2452" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66472,7 +66469,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2453" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66498,7 +66495,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2454" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66524,7 +66521,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2455" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66550,7 +66547,7 @@
         <v>4</v>
       </c>
       <c r="G2456" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66576,7 +66573,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2457" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66602,7 +66599,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2458" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66628,7 +66625,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2459" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66654,7 +66651,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2460" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66680,7 +66677,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2461" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66706,7 +66703,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2462" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66732,7 +66729,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66758,7 +66755,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2464" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66784,7 +66781,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2465" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66810,7 +66807,7 @@
         <v>4</v>
       </c>
       <c r="G2466" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66836,7 +66833,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2467" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66862,7 +66859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2468" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66888,7 +66885,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2469" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66914,7 +66911,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2470" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66940,7 +66937,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2471" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66966,7 +66963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2472" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66992,7 +66989,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2473" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67018,7 +67015,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2474" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67044,7 +67041,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67070,7 +67067,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67096,7 +67093,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2477" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67122,7 +67119,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2478" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67148,7 +67145,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2479" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67174,7 +67171,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2480" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67200,7 +67197,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2481" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67226,7 +67223,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2482" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67252,7 +67249,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2483" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67278,7 +67275,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2484" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67304,7 +67301,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67330,7 +67327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2486" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67356,7 +67353,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2487" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67382,7 +67379,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67408,7 +67405,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2489" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67434,9 +67431,61 @@
         <v>4.25</v>
       </c>
       <c r="G2490" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.2916666667</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>713</v>
+      </c>
+      <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6286111111</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>1506</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>4.15999984741211</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>773</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="782">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282061576843</t>
+    <t xml:space="preserve">3.87282085418701</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105965614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458229064941</t>
+    <t xml:space="preserve">3.87105989456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458181381226</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86401557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7424943447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79532933235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977957725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67733073234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443563461304</t>
+    <t xml:space="preserve">3.8640148639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652358055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74249410629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79532909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771735191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443539619446</t>
   </si>
   <si>
     <t xml:space="preserve">3.66324138641357</t>
@@ -92,43 +92,43 @@
     <t xml:space="preserve">3.68965911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66676354408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60336136817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637740135193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53995943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568999290466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915204048157</t>
+    <t xml:space="preserve">3.66676378250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336184501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637692451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6156895160675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915251731873</t>
   </si>
   <si>
     <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091347694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210772514343</t>
+    <t xml:space="preserve">3.65091300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210748672485</t>
   </si>
   <si>
     <t xml:space="preserve">3.59455537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71431565284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75130009651184</t>
+    <t xml:space="preserve">3.71431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.751300573349</t>
   </si>
   <si>
     <t xml:space="preserve">3.81294107437134</t>
@@ -143,67 +143,67 @@
     <t xml:space="preserve">3.81470251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80941891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7372100353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255421638489</t>
+    <t xml:space="preserve">3.80941915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368811607361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255397796631</t>
   </si>
   <si>
     <t xml:space="preserve">3.73192715644836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.721360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891207695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538944244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74953866004944</t>
+    <t xml:space="preserve">3.72135996818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74953889846802</t>
   </si>
   <si>
     <t xml:space="preserve">3.74601674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73016595840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846487045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613624572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488307952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350826263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383501052856</t>
+    <t xml:space="preserve">3.73016619682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846415519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350850105286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383548736572</t>
   </si>
   <si>
     <t xml:space="preserve">3.91861152648926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93446278572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98377537727356</t>
+    <t xml:space="preserve">3.93446230888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9837749004364</t>
   </si>
   <si>
     <t xml:space="preserve">3.9432680606842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91508984565735</t>
+    <t xml:space="preserve">3.91508913040161</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855363368988</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">3.91332793235779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89395475387573</t>
+    <t xml:space="preserve">3.89395523071289</t>
   </si>
   <si>
     <t xml:space="preserve">3.96087980270386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89219427108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622279167175</t>
+    <t xml:space="preserve">3.89219403266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622374534607</t>
   </si>
   <si>
     <t xml:space="preserve">3.92741751670837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88338804244995</t>
+    <t xml:space="preserve">3.88338828086853</t>
   </si>
   <si>
     <t xml:space="preserve">3.99916791915894</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">3.98299121856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95423412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625950813293</t>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625903129578</t>
   </si>
   <si>
     <t xml:space="preserve">3.88233780860901</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">3.92727255821228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92367839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560681343079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89132499694824</t>
+    <t xml:space="preserve">3.92367792129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560633659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89132523536682</t>
   </si>
   <si>
     <t xml:space="preserve">3.86436438560486</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">3.86256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81943011283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799255371094</t>
+    <t xml:space="preserve">3.81943035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799279212952</t>
   </si>
   <si>
     <t xml:space="preserve">3.7655086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59475755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273145675659</t>
+    <t xml:space="preserve">3.59475779533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273169517517</t>
   </si>
   <si>
     <t xml:space="preserve">3.67923450469971</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.63070511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62171840667725</t>
+    <t xml:space="preserve">3.62171864509583</t>
   </si>
   <si>
     <t xml:space="preserve">3.65766620635986</t>
@@ -308,22 +308,22 @@
     <t xml:space="preserve">3.63789486885071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68103194236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318949699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632609367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60374474525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6468813419342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6918158531189</t>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632657051086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60374522209167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64688158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69181609153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.73675084114075</t>
@@ -332,79 +332,79 @@
     <t xml:space="preserve">3.75652146339417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80325365066528</t>
+    <t xml:space="preserve">3.8032534122467</t>
   </si>
   <si>
     <t xml:space="preserve">3.86616182327271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81763243675232</t>
+    <t xml:space="preserve">3.8176326751709</t>
   </si>
   <si>
     <t xml:space="preserve">3.81044268608093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7924690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74393963813782</t>
+    <t xml:space="preserve">3.79246854782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
   </si>
   <si>
     <t xml:space="preserve">3.77449584007263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79067206382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77629327774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887438774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75112962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80145645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73315620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348278999329</t>
+    <t xml:space="preserve">3.79067158699036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7762930393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753451347351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75112986564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80145621299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348255157471</t>
   </si>
   <si>
     <t xml:space="preserve">3.72416877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090072631836</t>
+    <t xml:space="preserve">3.77090120315552</t>
   </si>
   <si>
     <t xml:space="preserve">3.72057390213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76371121406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978951454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70260071754456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854780197144</t>
+    <t xml:space="preserve">3.76371145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596669197083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978975296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70260047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854804039001</t>
   </si>
   <si>
     <t xml:space="preserve">3.72956132888794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72237157821655</t>
+    <t xml:space="preserve">3.72237133979797</t>
   </si>
   <si>
     <t xml:space="preserve">3.72776389122009</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">3.75292730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75831913948059</t>
+    <t xml:space="preserve">3.75831937789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.69541072845459</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">3.68462657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69361352920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66485548019409</t>
+    <t xml:space="preserve">3.69361329078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66485571861267</t>
   </si>
   <si>
     <t xml:space="preserve">3.68822145462036</t>
@@ -434,52 +434,52 @@
     <t xml:space="preserve">3.73135852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71338438987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168559074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8338086605072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8122410774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81583476066589</t>
+    <t xml:space="preserve">3.7133846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380913734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81583523750305</t>
   </si>
   <si>
     <t xml:space="preserve">3.82661938667297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82841753959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547583580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90031266212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335181236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740425109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8751482963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165253639221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929913520813</t>
+    <t xml:space="preserve">3.82841730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547535896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639143943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87514853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94165205955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929865837097</t>
   </si>
   <si>
     <t xml:space="preserve">3.95243573188782</t>
@@ -491,46 +491,46 @@
     <t xml:space="preserve">3.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88413524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94884157180786</t>
+    <t xml:space="preserve">3.88413572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9488410949707</t>
   </si>
   <si>
     <t xml:space="preserve">3.87874341011047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01534461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02073621749878</t>
+    <t xml:space="preserve">4.01534414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0207371711731</t>
   </si>
   <si>
     <t xml:space="preserve">4.00815439224243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0405068397522</t>
+    <t xml:space="preserve">4.04050731658936</t>
   </si>
   <si>
     <t xml:space="preserve">4.05308961868286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01714086532593</t>
+    <t xml:space="preserve">4.01714134216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207609176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07106304168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14295768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06926536560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08903694152832</t>
+    <t xml:space="preserve">4.07106351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14295816421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06926584243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08903741836548</t>
   </si>
   <si>
     <t xml:space="preserve">4.40357780456543</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">4.34606218338013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34785985946655</t>
+    <t xml:space="preserve">4.34785938262939</t>
   </si>
   <si>
     <t xml:space="preserve">4.32808828353882</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">4.11599731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03691291809082</t>
+    <t xml:space="preserve">4.03691339492798</t>
   </si>
   <si>
     <t xml:space="preserve">3.98478865623474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603084564209</t>
+    <t xml:space="preserve">4.04230451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603036880493</t>
   </si>
   <si>
     <t xml:space="preserve">3.92008328437805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91828656196594</t>
+    <t xml:space="preserve">3.91828608512878</t>
   </si>
   <si>
     <t xml:space="preserve">3.94704437255859</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">3.86795902252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90390729904175</t>
+    <t xml:space="preserve">3.90390634536743</t>
   </si>
   <si>
     <t xml:space="preserve">3.94524645805359</t>
@@ -2355,6 +2355,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.19000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28999996185303</t>
   </si>
 </sst>
 </file>
@@ -67511,7 +67514,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.5312962963</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>2600</v>
@@ -67532,6 +67535,32 @@
         <v>710</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6110416667</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>4728</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>781</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282109260559</t>
+    <t xml:space="preserve">3.87282085418701</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105989456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458276748657</t>
+    <t xml:space="preserve">3.87106013298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86401557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652381896973</t>
+    <t xml:space="preserve">3.86401534080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652429580688</t>
   </si>
   <si>
     <t xml:space="preserve">3.74249410629272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79532980918884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771735191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977910041809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.677330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443539619446</t>
+    <t xml:space="preserve">3.79532933235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771782875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977957725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67733073234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443563461304</t>
   </si>
   <si>
     <t xml:space="preserve">3.663241147995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6438684463501</t>
+    <t xml:space="preserve">3.64386868476868</t>
   </si>
   <si>
     <t xml:space="preserve">3.48712396621704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61040639877319</t>
+    <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
     <t xml:space="preserve">3.68965911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66676354408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6033616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085312843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637692451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
+    <t xml:space="preserve">3.6667640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336136817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637716293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995943069458</t>
   </si>
   <si>
     <t xml:space="preserve">3.6156895160675</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">3.64210724830627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59455513954163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431493759155</t>
+    <t xml:space="preserve">3.59455561637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431541442871</t>
   </si>
   <si>
     <t xml:space="preserve">3.751300573349</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">3.86225438117981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368859291077</t>
+    <t xml:space="preserve">3.81470251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941891670227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368811607361</t>
   </si>
   <si>
     <t xml:space="preserve">3.73721075057983</t>
@@ -155,52 +155,52 @@
     <t xml:space="preserve">3.71255397796631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73192715644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891207695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538920402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74953842163086</t>
+    <t xml:space="preserve">3.73192739486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.721360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74953889846802</t>
   </si>
   <si>
     <t xml:space="preserve">3.74601650238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7301664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613696098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488236427307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350873947144</t>
+    <t xml:space="preserve">3.73016619682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846487045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488284111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8235080242157</t>
   </si>
   <si>
     <t xml:space="preserve">3.95383453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9186110496521</t>
+    <t xml:space="preserve">3.91861152648926</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446207046509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98377466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9432680606842</t>
+    <t xml:space="preserve">3.98377513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94326782226562</t>
   </si>
   <si>
     <t xml:space="preserve">3.91508913040161</t>
@@ -209,67 +209,67 @@
     <t xml:space="preserve">3.98553586006165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395499229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087956428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219403266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741703987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338780403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02612829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220754623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018025398254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759985923767</t>
+    <t xml:space="preserve">3.91332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96087980270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219355583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622326850891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741751670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338804244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0261287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220683097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759938240051</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410219192505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98299145698547</t>
+    <t xml:space="preserve">3.98299121856689</t>
   </si>
   <si>
     <t xml:space="preserve">3.95423364639282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93625998497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9272723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367792129517</t>
+    <t xml:space="preserve">3.93625974655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233828544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92727303504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
   </si>
   <si>
     <t xml:space="preserve">3.83560705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89132523536682</t>
+    <t xml:space="preserve">3.89132499694824</t>
   </si>
   <si>
     <t xml:space="preserve">3.86436486244202</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">3.86256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81943011283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59475779533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273169517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67923450469971</t>
+    <t xml:space="preserve">3.81942987442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799231529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76550889015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59475755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273145675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67923426628113</t>
   </si>
   <si>
     <t xml:space="preserve">3.63070511817932</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.62171864509583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65766620635986</t>
+    <t xml:space="preserve">3.65766644477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.63789463043213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68103241920471</t>
+    <t xml:space="preserve">3.68103194236755</t>
   </si>
   <si>
     <t xml:space="preserve">3.57318902015686</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">3.61632633209229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60374474525452</t>
+    <t xml:space="preserve">3.6037449836731</t>
   </si>
   <si>
     <t xml:space="preserve">3.64688181877136</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">3.69181609153748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73675060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652146339417</t>
+    <t xml:space="preserve">3.73675084114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652170181274</t>
   </si>
   <si>
     <t xml:space="preserve">3.80325365066528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86616182327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8176326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044292449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246973991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394011497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449512481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067182540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77629327774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753499031067</t>
+    <t xml:space="preserve">3.86616206169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81763315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044268608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7924690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449560165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067206382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887414932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753475189209</t>
   </si>
   <si>
     <t xml:space="preserve">3.75112962722778</t>
@@ -371,40 +371,40 @@
     <t xml:space="preserve">3.80145621299744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73315572738647</t>
+    <t xml:space="preserve">3.7331554889679</t>
   </si>
   <si>
     <t xml:space="preserve">3.78348255157471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72416925430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090120315552</t>
+    <t xml:space="preserve">3.7241690158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77090096473694</t>
   </si>
   <si>
     <t xml:space="preserve">3.72057390213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76371145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596621513367</t>
+    <t xml:space="preserve">3.76371192932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596597671509</t>
   </si>
   <si>
     <t xml:space="preserve">3.70978951454163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70260047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854756355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72237181663513</t>
+    <t xml:space="preserve">3.70260000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854804039001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72237205505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.72776365280151</t>
@@ -413,85 +413,88 @@
     <t xml:space="preserve">3.75292682647705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75831937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541072845459</t>
+    <t xml:space="preserve">3.75831913948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541096687317</t>
   </si>
   <si>
     <t xml:space="preserve">3.68462657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69361329078674</t>
+    <t xml:space="preserve">3.69361352920532</t>
   </si>
   <si>
     <t xml:space="preserve">3.66485571861267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68822121620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135828971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380842208862</t>
+    <t xml:space="preserve">3.68822145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338438987732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168559074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380889892578</t>
   </si>
   <si>
     <t xml:space="preserve">3.81224060058594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81583476066589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82661962509155</t>
+    <t xml:space="preserve">3.81583452224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82661938667297</t>
   </si>
   <si>
     <t xml:space="preserve">3.82841730117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92547583580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188000679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90031218528748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335157394409</t>
+    <t xml:space="preserve">3.92547488212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335133552551</t>
   </si>
   <si>
     <t xml:space="preserve">3.84639096260071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83740329742432</t>
+    <t xml:space="preserve">3.83740377426147</t>
   </si>
   <si>
     <t xml:space="preserve">3.87514853477478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94165253639221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929913520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243620872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98119425773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97939658164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413524627686</t>
+    <t xml:space="preserve">3.94165134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929889678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243573188782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98119378089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413572311401</t>
   </si>
   <si>
     <t xml:space="preserve">3.9488410949707</t>
@@ -500,73 +503,73 @@
     <t xml:space="preserve">3.87874341011047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01534461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02073669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00815439224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04050779342651</t>
+    <t xml:space="preserve">4.01534414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02073621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00815534591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04050731658936</t>
   </si>
   <si>
     <t xml:space="preserve">4.05308961868286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01714086532593</t>
+    <t xml:space="preserve">4.01714181900024</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207609176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07106351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14295864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06926536560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08903741836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40357828140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37661743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34606170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785985946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32808828353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27236938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03691339492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98478865623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008376121521</t>
+    <t xml:space="preserve">4.07106304168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14295816421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06926584243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08903694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40357875823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37661695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34606218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32808876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27236986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03691291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9847891330719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04230546951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603108406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008304595947</t>
   </si>
   <si>
     <t xml:space="preserve">3.91828584671021</t>
@@ -575,61 +578,61 @@
     <t xml:space="preserve">3.94704413414001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9326651096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099888801575</t>
+    <t xml:space="preserve">3.93266463279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099912643433</t>
   </si>
   <si>
     <t xml:space="preserve">3.86795878410339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90390682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524645805359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9635968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99112176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194670677185</t>
+    <t xml:space="preserve">3.90390729904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96359658241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99112153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194718360901</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524693489075</t>
+    <t xml:space="preserve">3.94524717330933</t>
   </si>
   <si>
     <t xml:space="preserve">3.89019632339478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87184691429138</t>
+    <t xml:space="preserve">3.87184619903564</t>
   </si>
   <si>
     <t xml:space="preserve">3.92689657211304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06452178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.128746509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17462158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12691116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10672616958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05901622772217</t>
+    <t xml:space="preserve">4.06452131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17462205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12691164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10672664642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05901575088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.03699684143066</t>
@@ -638,52 +641,52 @@
     <t xml:space="preserve">3.99479150772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05351114273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0828709602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03332662582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07369565963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09204626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08103704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534696578979</t>
+    <t xml:space="preserve">4.05351161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08287191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03332710266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07369661331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08103609085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534648895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.09021139144897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0626859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15260171890259</t>
+    <t xml:space="preserve">4.06268644332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15260124206543</t>
   </si>
   <si>
     <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16544580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11039638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09388160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20948553085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1544361114502</t>
+    <t xml:space="preserve">4.16544675827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11039686203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09388113021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20948648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15443658828735</t>
   </si>
   <si>
     <t xml:space="preserve">4.13792181015015</t>
@@ -692,28 +695,28 @@
     <t xml:space="preserve">4.12507677078247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1195707321167</t>
+    <t xml:space="preserve">4.11957120895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.13608598709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15076684951782</t>
+    <t xml:space="preserve">4.15076637268066</t>
   </si>
   <si>
     <t xml:space="preserve">4.10305643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278623580933</t>
+    <t xml:space="preserve">4.17278575897217</t>
   </si>
   <si>
     <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002592086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10122108459473</t>
+    <t xml:space="preserve">4.07002639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10122156143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.16911697387695</t>
@@ -725,7 +728,7 @@
     <t xml:space="preserve">4.21132135391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0975513458252</t>
+    <t xml:space="preserve">4.09755182266235</t>
   </si>
   <si>
     <t xml:space="preserve">4.05167627334595</t>
@@ -734,7 +737,7 @@
     <t xml:space="preserve">4.01864671707153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07920122146606</t>
+    <t xml:space="preserve">4.07920169830322</t>
   </si>
   <si>
     <t xml:space="preserve">4.13425159454346</t>
@@ -743,40 +746,40 @@
     <t xml:space="preserve">4.21866130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13241672515869</t>
+    <t xml:space="preserve">4.13241624832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.12140655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11590194702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11773586273193</t>
+    <t xml:space="preserve">4.11590147018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11773633956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.14709663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1489315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19113636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19297122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662613868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04433679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341111183167</t>
+    <t xml:space="preserve">4.14893102645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1911358833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19297170639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662661552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04433631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341135025024</t>
   </si>
   <si>
     <t xml:space="preserve">4.0204815864563</t>
@@ -785,43 +788,43 @@
     <t xml:space="preserve">3.92322659492493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03516149520874</t>
+    <t xml:space="preserve">4.03516101837158</t>
   </si>
   <si>
     <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726632118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772103309631</t>
+    <t xml:space="preserve">4.04800701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
     <t xml:space="preserve">4.0002965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97277140617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93790698051453</t>
+    <t xml:space="preserve">3.97277164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93790626525879</t>
   </si>
   <si>
     <t xml:space="preserve">3.99846148490906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04617166519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88102149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349631309509</t>
+    <t xml:space="preserve">4.04617118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349678993225</t>
   </si>
   <si>
     <t xml:space="preserve">3.95442175865173</t>
@@ -830,34 +833,34 @@
     <t xml:space="preserve">3.83514642715454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89937162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854692459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93607139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267161369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82597184181213</t>
+    <t xml:space="preserve">3.89937114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854716300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93607187271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267185211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82597160339355</t>
   </si>
   <si>
     <t xml:space="preserve">3.78927183151245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80762195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04857444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03918123245239</t>
+    <t xml:space="preserve">3.807621717453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04857492446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03918075561523</t>
   </si>
   <si>
     <t xml:space="preserve">3.97342681884766</t>
@@ -869,22 +872,22 @@
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9170663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616477012634</t>
+    <t xml:space="preserve">3.96403336524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827990531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91706609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75737762451172</t>
+    <t xml:space="preserve">3.7573778629303</t>
   </si>
   <si>
     <t xml:space="preserve">3.73859095573425</t>
@@ -899,7 +902,7 @@
     <t xml:space="preserve">3.63526296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62586903572083</t>
+    <t xml:space="preserve">3.62586951255798</t>
   </si>
   <si>
     <t xml:space="preserve">3.52254152297974</t>
@@ -914,31 +917,31 @@
     <t xml:space="preserve">3.35345959663391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33467268943787</t>
+    <t xml:space="preserve">3.33467245101929</t>
   </si>
   <si>
     <t xml:space="preserve">3.37224650382996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3816397190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45678758621216</t>
+    <t xml:space="preserve">3.38163995742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45678782463074</t>
   </si>
   <si>
     <t xml:space="preserve">3.4661808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36285281181335</t>
+    <t xml:space="preserve">3.36285305023193</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800091743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40042686462402</t>
+    <t xml:space="preserve">3.43800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
     <t xml:space="preserve">3.4755744934082</t>
@@ -947,19 +950,19 @@
     <t xml:space="preserve">3.49436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31588578224182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708236694336</t>
+    <t xml:space="preserve">3.31588554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
     <t xml:space="preserve">3.56950879096985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50375485420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65404987335205</t>
+    <t xml:space="preserve">3.50375461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65405011177063</t>
   </si>
   <si>
     <t xml:space="preserve">3.48496794700623</t>
@@ -968,7 +971,7 @@
     <t xml:space="preserve">3.68223023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5976893901825</t>
+    <t xml:space="preserve">3.59768891334534</t>
   </si>
   <si>
     <t xml:space="preserve">3.61647605895996</t>
@@ -977,19 +980,19 @@
     <t xml:space="preserve">3.66344332695007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58829569816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55072212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56011533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57890200614929</t>
+    <t xml:space="preserve">3.58829545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5507218837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193521499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56011557579041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57890224456787</t>
   </si>
   <si>
     <t xml:space="preserve">3.64465641975403</t>
@@ -998,22 +1001,22 @@
     <t xml:space="preserve">3.6728367805481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51314806938171</t>
+    <t xml:space="preserve">3.51314783096313</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54921507835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62637186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58779335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495013237</t>
+    <t xml:space="preserve">3.54921531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62637209892273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58779358863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495037078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1022,13 +1025,13 @@
     <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79997491836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210739135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81926417350769</t>
+    <t xml:space="preserve">3.7999746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210715293884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81926393508911</t>
   </si>
   <si>
     <t xml:space="preserve">3.83855319023132</t>
@@ -1040,16 +1043,13 @@
     <t xml:space="preserve">3.76139640808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72281789779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64566135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708260536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56850457191467</t>
+    <t xml:space="preserve">3.72281765937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64566111564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">3.52992582321167</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">3.47205829620361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51063656806946</t>
+    <t xml:space="preserve">3.51063680648804</t>
   </si>
   <si>
     <t xml:space="preserve">3.41419053077698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43347954750061</t>
+    <t xml:space="preserve">3.43347978591919</t>
   </si>
   <si>
     <t xml:space="preserve">3.45276880264282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37561225891113</t>
+    <t xml:space="preserve">3.37561202049255</t>
   </si>
   <si>
     <t xml:space="preserve">3.39490151405334</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">3.27916598320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18271994590759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22129845619202</t>
+    <t xml:space="preserve">3.18272018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22129821777344</t>
   </si>
   <si>
     <t xml:space="preserve">3.14414167404175</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">3.2020092010498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556316375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0669846534729</t>
+    <t xml:space="preserve">3.1055634021759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06698489189148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85480356216431</t>
+    <t xml:space="preserve">2.91267108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85480332374573</t>
   </si>
   <si>
     <t xml:space="preserve">2.71977877616882</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.83551406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.970538854599</t>
+    <t xml:space="preserve">2.97053861618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">3.12485241889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98982763290405</t>
+    <t xml:space="preserve">2.98982787132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.95124959945679</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">2.81622505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79693603515625</t>
+    <t xml:space="preserve">2.79693579673767</t>
   </si>
   <si>
     <t xml:space="preserve">2.75835704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77764678001404</t>
+    <t xml:space="preserve">2.77764654159546</t>
   </si>
   <si>
     <t xml:space="preserve">2.73906803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54617595672607</t>
+    <t xml:space="preserve">2.54617619514465</t>
   </si>
   <si>
     <t xml:space="preserve">2.62333297729492</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">2.60404372215271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5847544670105</t>
+    <t xml:space="preserve">2.58475470542908</t>
   </si>
   <si>
     <t xml:space="preserve">2.50759768486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46901893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33399486541748</t>
+    <t xml:space="preserve">2.46901917457581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3339946269989</t>
   </si>
   <si>
     <t xml:space="preserve">2.16039180755615</t>
@@ -1184,25 +1184,25 @@
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110255241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23754858970642</t>
+    <t xml:space="preserve">2.14110279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23754835128784</t>
   </si>
   <si>
     <t xml:space="preserve">2.02536725997925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.198970079422</t>
+    <t xml:space="preserve">2.19897031784058</t>
   </si>
   <si>
     <t xml:space="preserve">2.12181329727173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25683784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29541611671448</t>
+    <t xml:space="preserve">2.25683760643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.31470537185669</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">2.43044090270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27612709999084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577160835266</t>
+    <t xml:space="preserve">2.27612686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577136993408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292862892151</t>
+    <t xml:space="preserve">2.36292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506086349487</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35328412055969</t>
+    <t xml:space="preserve">2.35328388214111</t>
   </si>
   <si>
     <t xml:space="preserve">2.32435011863708</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">2.17968106269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18932557106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17003631591797</t>
+    <t xml:space="preserve">2.18932580947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17003655433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.13145804405212</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.03501176834106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98678886890411</t>
+    <t xml:space="preserve">1.9867889881134</t>
   </si>
   <si>
     <t xml:space="preserve">1.92409884929657</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">1.92892122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93856573104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95785510540009</t>
+    <t xml:space="preserve">1.93856585025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9578549861908</t>
   </si>
   <si>
     <t xml:space="preserve">2.20861482620239</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">2.15074706077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37257289886475</t>
+    <t xml:space="preserve">2.37257313728333</t>
   </si>
   <si>
     <t xml:space="preserve">2.38221764564514</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66191124916077</t>
+    <t xml:space="preserve">2.87409257888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66191148757935</t>
   </si>
   <si>
     <t xml:space="preserve">2.64262199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59439921379089</t>
+    <t xml:space="preserve">2.59439897537231</t>
   </si>
   <si>
     <t xml:space="preserve">2.68120050430298</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">2.65226674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61368823051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53653144836426</t>
+    <t xml:space="preserve">2.61368846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53653168678284</t>
   </si>
   <si>
     <t xml:space="preserve">2.52688670158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51724219322205</t>
+    <t xml:space="preserve">2.51724195480347</t>
   </si>
   <si>
     <t xml:space="preserve">2.70048975944519</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">2.71013426780701</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69084501266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72942352294922</t>
+    <t xml:space="preserve">2.69084525108337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72942328453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.78729128837585</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98018288612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9608941078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03805112838745</t>
+    <t xml:space="preserve">2.98018336296082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089386940002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03805088996887</t>
   </si>
   <si>
     <t xml:space="preserve">3.16343069076538</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">3.17307543754578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952171325684</t>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378642082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952147483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25023221969604</t>
+    <t xml:space="preserve">3.25023198127747</t>
   </si>
   <si>
     <t xml:space="preserve">3.09591865539551</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05734014511108</t>
+    <t xml:space="preserve">3.05734038352966</t>
   </si>
   <si>
     <t xml:space="preserve">2.92231559753418</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.90302634239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88373732566833</t>
+    <t xml:space="preserve">2.88373708724976</t>
   </si>
   <si>
     <t xml:space="preserve">2.86444807052612</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">2.84515881538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80658054351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">2.80658030509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
@@ -1445,31 +1445,31 @@
     <t xml:space="preserve">3.59743809700012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67459464073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71317338943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79033041000366</t>
+    <t xml:space="preserve">3.67459511756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71317315101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79033017158508</t>
   </si>
   <si>
     <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95428824424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94464421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9832227230072</t>
+    <t xml:space="preserve">3.95428848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9446439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98322248458862</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507345199585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97357773780823</t>
+    <t xml:space="preserve">3.97357797622681</t>
   </si>
   <si>
     <t xml:space="preserve">4.07002353668213</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">4.34971761703491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34007263183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39794015884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42687463760376</t>
+    <t xml:space="preserve">4.3400731086731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39794063568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4268741607666</t>
   </si>
   <si>
     <t xml:space="preserve">4.45580768585205</t>
@@ -1508,19 +1508,19 @@
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144502639771</t>
+    <t xml:space="preserve">4.03144550323486</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31113862991333</t>
+    <t xml:space="preserve">4.31113910675049</t>
   </si>
   <si>
     <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40758514404297</t>
+    <t xml:space="preserve">4.40758562088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36900663375854</t>
+    <t xml:space="preserve">4.3690071105957</t>
   </si>
   <si>
     <t xml:space="preserve">4.1278920173645</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1857590675354</t>
+    <t xml:space="preserve">4.18575954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.14718055725098</t>
@@ -1556,31 +1556,31 @@
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33042764663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51367568969727</t>
+    <t xml:space="preserve">4.17611455917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33042812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51367521286011</t>
   </si>
   <si>
     <t xml:space="preserve">4.46545267105103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37865114212036</t>
+    <t xml:space="preserve">4.37865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.48474168777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47509717941284</t>
+    <t xml:space="preserve">4.47509670257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.49438619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44616365432739</t>
+    <t xml:space="preserve">4.44616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">4.41722965240479</t>
@@ -1592,10 +1592,10 @@
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63905572891235</t>
+    <t xml:space="preserve">4.72585678100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6390552520752</t>
   </si>
   <si>
     <t xml:space="preserve">4.62941074371338</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">4.61012172698975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154321670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682458877563</t>
+    <t xml:space="preserve">4.57154273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682554244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45884704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5938720703125</t>
+    <t xml:space="preserve">5.45884656906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59387159347534</t>
   </si>
   <si>
     <t xml:space="preserve">5.4974250793457</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">5.42026853561401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38169002532959</t>
+    <t xml:space="preserve">5.38169050216675</t>
   </si>
   <si>
     <t xml:space="preserve">4.86088180541992</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">4.84159231185913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93803787231445</t>
+    <t xml:space="preserve">4.93803834915161</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
@@ -9376,7 +9376,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9428,7 +9428,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9454,7 +9454,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9480,7 +9480,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9506,7 +9506,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9532,7 +9532,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9558,7 +9558,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9584,7 +9584,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9610,7 +9610,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9688,7 +9688,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9714,7 +9714,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9792,7 +9792,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G273" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9818,7 +9818,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9870,7 +9870,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G277" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9922,7 +9922,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9948,7 +9948,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9974,7 +9974,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G280" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10052,7 +10052,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10078,7 +10078,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10130,7 +10130,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G286" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10156,7 +10156,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10208,7 +10208,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10286,7 +10286,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G292" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10312,7 +10312,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10364,7 +10364,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10416,7 +10416,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G297" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10442,7 +10442,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10494,7 +10494,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10546,7 +10546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10598,7 +10598,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10624,7 +10624,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10702,7 +10702,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10806,7 +10806,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G312" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10858,7 +10858,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G314" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10884,7 +10884,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10910,7 +10910,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G316" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10936,7 +10936,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10962,7 +10962,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G318" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -10988,7 +10988,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11040,7 +11040,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11066,7 +11066,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11092,7 +11092,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G323" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11144,7 +11144,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G325" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11170,7 +11170,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G326" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11196,7 +11196,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11222,7 +11222,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11352,7 +11352,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11378,7 +11378,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11404,7 +11404,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11508,7 +11508,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11534,7 +11534,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11560,7 +11560,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11586,7 +11586,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11846,7 +11846,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11872,7 +11872,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11898,7 +11898,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G354" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11924,7 +11924,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11950,7 +11950,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G356" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11976,7 +11976,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12002,7 +12002,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12028,7 +12028,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12054,7 +12054,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G360" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12080,7 +12080,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G361" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12106,7 +12106,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G362" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12132,7 +12132,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G363" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12158,7 +12158,7 @@
         <v>4.5</v>
       </c>
       <c r="G364" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12184,7 +12184,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G365" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12210,7 +12210,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G366" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12236,7 +12236,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G367" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12262,7 +12262,7 @@
         <v>4.42399978637695</v>
       </c>
       <c r="G368" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12288,7 +12288,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G369" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12314,7 +12314,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12340,7 +12340,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G371" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12366,7 +12366,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G372" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12392,7 +12392,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G373" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12418,7 +12418,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12444,7 +12444,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G375" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12470,7 +12470,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G376" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12496,7 +12496,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G377" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12522,7 +12522,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G378" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12548,7 +12548,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12574,7 +12574,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G380" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12600,7 +12600,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G381" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12626,7 +12626,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G382" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12652,7 +12652,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12678,7 +12678,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12704,7 +12704,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G385" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12730,7 +12730,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G386" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12756,7 +12756,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G387" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12782,7 +12782,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G388" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12808,7 +12808,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12834,7 +12834,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G390" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12860,7 +12860,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G391" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12886,7 +12886,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G392" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12912,7 +12912,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G393" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12938,7 +12938,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G394" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12964,7 +12964,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12990,7 +12990,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G396" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13016,7 +13016,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G397" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13042,7 +13042,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G398" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13068,7 +13068,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G399" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13094,7 +13094,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G400" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13120,7 +13120,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G401" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13146,7 +13146,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G402" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13172,7 +13172,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G403" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13198,7 +13198,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G404" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13224,7 +13224,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G405" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13250,7 +13250,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G406" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13276,7 +13276,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G407" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13302,7 +13302,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G408" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13328,7 +13328,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G409" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13354,7 +13354,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G410" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13380,7 +13380,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G411" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13406,7 +13406,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G412" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13432,7 +13432,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G413" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13458,7 +13458,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G414" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13484,7 +13484,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G415" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13510,7 +13510,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G416" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13536,7 +13536,7 @@
         <v>4.5</v>
       </c>
       <c r="G417" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13562,7 +13562,7 @@
         <v>4.5</v>
       </c>
       <c r="G418" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13588,7 +13588,7 @@
         <v>4.5</v>
       </c>
       <c r="G419" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13614,7 +13614,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G420" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13640,7 +13640,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G421" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13666,7 +13666,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G422" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13692,7 +13692,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G423" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13718,7 +13718,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G424" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13744,7 +13744,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G425" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13770,7 +13770,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G426" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13796,7 +13796,7 @@
         <v>4.5</v>
       </c>
       <c r="G427" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13822,7 +13822,7 @@
         <v>4.5</v>
       </c>
       <c r="G428" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13848,7 +13848,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G429" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13874,7 +13874,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G430" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13900,7 +13900,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G431" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13926,7 +13926,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G432" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13952,7 +13952,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G433" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13978,7 +13978,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G434" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14004,7 +14004,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G435" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14030,7 +14030,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G436" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14056,7 +14056,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G437" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14082,7 +14082,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G438" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14108,7 +14108,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G439" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14134,7 +14134,7 @@
         <v>4.46600008010864</v>
       </c>
       <c r="G440" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14160,7 +14160,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G441" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14186,7 +14186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G442" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14212,7 +14212,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G443" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14238,7 +14238,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G444" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14264,7 +14264,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G445" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14290,7 +14290,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G446" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14316,7 +14316,7 @@
         <v>4.5</v>
       </c>
       <c r="G447" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14342,7 +14342,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G448" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14368,7 +14368,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G449" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14394,7 +14394,7 @@
         <v>4.5</v>
       </c>
       <c r="G450" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14420,7 +14420,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G451" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14446,7 +14446,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G452" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14472,7 +14472,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G453" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14498,7 +14498,7 @@
         <v>4.42399978637695</v>
       </c>
       <c r="G454" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14524,7 +14524,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G455" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14550,7 +14550,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G456" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14576,7 +14576,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G457" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14602,7 +14602,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14628,7 +14628,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G459" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14654,7 +14654,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G460" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14680,7 +14680,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14706,7 +14706,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G462" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14732,7 +14732,7 @@
         <v>4.46600008010864</v>
       </c>
       <c r="G463" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14758,7 +14758,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G464" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14784,7 +14784,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G465" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14810,7 +14810,7 @@
         <v>4.42399978637695</v>
       </c>
       <c r="G466" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14836,7 +14836,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G467" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14862,7 +14862,7 @@
         <v>4.5</v>
       </c>
       <c r="G468" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14888,7 +14888,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G469" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14914,7 +14914,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14940,7 +14940,7 @@
         <v>4.5</v>
       </c>
       <c r="G471" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14966,7 +14966,7 @@
         <v>4.5</v>
       </c>
       <c r="G472" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14992,7 +14992,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G473" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15018,7 +15018,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G474" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15044,7 +15044,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G475" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15070,7 +15070,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G476" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15096,7 +15096,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G477" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15122,7 +15122,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G478" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15148,7 +15148,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G479" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15174,7 +15174,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G480" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15200,7 +15200,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G481" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15226,7 +15226,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G482" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15252,7 +15252,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G483" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15278,7 +15278,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G484" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15304,7 +15304,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G485" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15330,7 +15330,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15356,7 +15356,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G487" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15382,7 +15382,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15408,7 +15408,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G489" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15434,7 +15434,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G490" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15460,7 +15460,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G491" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15486,7 +15486,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G492" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15512,7 +15512,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G493" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15538,7 +15538,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G494" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15564,7 +15564,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G495" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15590,7 +15590,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G496" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15616,7 +15616,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G497" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15642,7 +15642,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G498" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15668,7 +15668,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G499" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15694,7 +15694,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G500" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15720,7 +15720,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G501" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15746,7 +15746,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G502" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15772,7 +15772,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G503" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15798,7 +15798,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G504" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15824,7 +15824,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G505" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15850,7 +15850,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G506" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15876,7 +15876,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G507" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15902,7 +15902,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G508" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15928,7 +15928,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G509" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15954,7 +15954,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G510" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15980,7 +15980,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G511" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16006,7 +16006,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16032,7 +16032,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G513" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16058,7 +16058,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G514" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16084,7 +16084,7 @@
         <v>4.5</v>
       </c>
       <c r="G515" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16110,7 +16110,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G516" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16136,7 +16136,7 @@
         <v>4.5</v>
       </c>
       <c r="G517" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16162,7 +16162,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G518" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16188,7 +16188,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G519" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16214,7 +16214,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G520" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16240,7 +16240,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G521" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16266,7 +16266,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G522" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16292,7 +16292,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G523" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16318,7 +16318,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G524" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16344,7 +16344,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G525" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16370,7 +16370,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G526" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16396,7 +16396,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G527" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16422,7 +16422,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G528" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16448,7 +16448,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G529" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16474,7 +16474,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G530" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16500,7 +16500,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G531" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16526,7 +16526,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16552,7 +16552,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G533" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16578,7 +16578,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16604,7 +16604,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G535" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16630,7 +16630,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G536" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16656,7 +16656,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G537" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16682,7 +16682,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16708,7 +16708,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G539" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16734,7 +16734,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16760,7 +16760,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G541" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16786,7 +16786,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G542" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16812,7 +16812,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G543" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16838,7 +16838,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16864,7 +16864,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16890,7 +16890,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16916,7 +16916,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16942,7 +16942,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G548" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16968,7 +16968,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G549" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17020,7 +17020,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17046,7 +17046,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17072,7 +17072,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G553" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17098,7 +17098,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G554" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17124,7 +17124,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G555" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17150,7 +17150,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G556" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17176,7 +17176,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G557" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17202,7 +17202,7 @@
         <v>4.25</v>
       </c>
       <c r="G558" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17228,7 +17228,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G559" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17254,7 +17254,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G560" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17280,7 +17280,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G561" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17306,7 +17306,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17332,7 +17332,7 @@
         <v>4.25</v>
       </c>
       <c r="G563" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17358,7 +17358,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G564" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17384,7 +17384,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17410,7 +17410,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17436,7 +17436,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17462,7 +17462,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G568" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17488,7 +17488,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G569" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17514,7 +17514,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G570" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17540,7 +17540,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17566,7 +17566,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G572" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17592,7 +17592,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17618,7 +17618,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G574" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17644,7 +17644,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G575" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17670,7 +17670,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G576" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17696,7 +17696,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G577" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17722,7 +17722,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G578" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17748,7 +17748,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G579" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17774,7 +17774,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G580" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17800,7 +17800,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G581" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17826,7 +17826,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G582" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17852,7 +17852,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17878,7 +17878,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17904,7 +17904,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G585" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17930,7 +17930,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G586" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17956,7 +17956,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17982,7 +17982,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18008,7 +18008,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18034,7 +18034,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G590" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18060,7 +18060,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G591" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18086,7 +18086,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18112,7 +18112,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18138,7 +18138,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G594" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18164,7 +18164,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G595" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18190,7 +18190,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G596" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18216,7 +18216,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18242,7 +18242,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18268,7 +18268,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G599" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18294,7 +18294,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G600" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18320,7 +18320,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18346,7 +18346,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G602" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18372,7 +18372,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18398,7 +18398,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18424,7 +18424,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G605" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18450,7 +18450,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G606" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18502,7 +18502,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G608" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18528,7 +18528,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G609" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18554,7 +18554,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18580,7 +18580,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G611" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18606,7 +18606,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G612" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18632,7 +18632,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18658,7 +18658,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G614" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18684,7 +18684,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G615" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18710,7 +18710,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G616" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18736,7 +18736,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G617" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18762,7 +18762,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G618" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18788,7 +18788,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18814,7 +18814,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G620" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18840,7 +18840,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G621" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18866,7 +18866,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G622" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18892,7 +18892,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G623" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18918,7 +18918,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G624" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18944,7 +18944,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G625" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18970,7 +18970,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G626" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18996,7 +18996,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19022,7 +19022,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19074,7 +19074,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19100,7 +19100,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19152,7 +19152,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G633" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19178,7 +19178,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G634" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19204,7 +19204,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19230,7 +19230,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19256,7 +19256,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G637" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19282,7 +19282,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G638" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19308,7 +19308,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G639" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19334,7 +19334,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G640" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19360,7 +19360,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G641" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19386,7 +19386,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G642" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19412,7 +19412,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G643" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19438,7 +19438,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G644" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19464,7 +19464,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G645" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19490,7 +19490,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G646" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G647" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19568,7 +19568,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19594,7 +19594,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19620,7 +19620,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19646,7 +19646,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19672,7 +19672,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19724,7 +19724,7 @@
         <v>4.25</v>
       </c>
       <c r="G655" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19776,7 +19776,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G657" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19802,7 +19802,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19828,7 +19828,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G659" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19854,7 +19854,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G660" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19880,7 +19880,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19906,7 +19906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19958,7 +19958,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20036,7 +20036,7 @@
         <v>4.25</v>
       </c>
       <c r="G667" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20062,7 +20062,7 @@
         <v>4.25</v>
       </c>
       <c r="G668" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20088,7 +20088,7 @@
         <v>4.25</v>
       </c>
       <c r="G669" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20114,7 +20114,7 @@
         <v>4.25</v>
       </c>
       <c r="G670" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20140,7 +20140,7 @@
         <v>4.25</v>
       </c>
       <c r="G671" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20166,7 +20166,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G672" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20192,7 +20192,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G673" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20218,7 +20218,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G674" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20244,7 +20244,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20270,7 +20270,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20296,7 +20296,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G677" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20322,7 +20322,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20348,7 +20348,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G679" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20374,7 +20374,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20400,7 +20400,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20426,7 +20426,7 @@
         <v>4.25</v>
       </c>
       <c r="G682" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20452,7 +20452,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20478,7 +20478,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20504,7 +20504,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20530,7 +20530,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G686" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20556,7 +20556,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G687" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20582,7 +20582,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G688" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20608,7 +20608,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G689" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20634,7 +20634,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20660,7 +20660,7 @@
         <v>4.25</v>
       </c>
       <c r="G691" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20686,7 +20686,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G692" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20712,7 +20712,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G693" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20738,7 +20738,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G694" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20764,7 +20764,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20790,7 +20790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20816,7 +20816,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G697" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20842,7 +20842,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G698" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20868,7 +20868,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G699" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20894,7 +20894,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G700" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20920,7 +20920,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G701" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20946,7 +20946,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G702" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20972,7 +20972,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G703" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20998,7 +20998,7 @@
         <v>4.25</v>
       </c>
       <c r="G704" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21024,7 +21024,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21050,7 +21050,7 @@
         <v>4.25</v>
       </c>
       <c r="G706" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21076,7 +21076,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G707" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21102,7 +21102,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G708" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21128,7 +21128,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21154,7 +21154,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21180,7 +21180,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G711" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21206,7 +21206,7 @@
         <v>4</v>
       </c>
       <c r="G712" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21232,7 +21232,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G713" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21258,7 +21258,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21284,7 +21284,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G715" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21310,7 +21310,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G716" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21336,7 +21336,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G717" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21362,7 +21362,7 @@
         <v>3.75</v>
       </c>
       <c r="G718" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21388,7 +21388,7 @@
         <v>3.75</v>
       </c>
       <c r="G719" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21414,7 +21414,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21440,7 +21440,7 @@
         <v>3.5</v>
       </c>
       <c r="G721" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21466,7 +21466,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G722" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21492,7 +21492,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G723" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21518,7 +21518,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G724" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21544,7 +21544,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G725" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21570,7 +21570,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G726" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21596,7 +21596,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G727" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21622,7 +21622,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G728" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21648,7 +21648,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G729" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21674,7 +21674,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G730" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21700,7 +21700,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21726,7 +21726,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G732" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21752,7 +21752,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G733" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21778,7 +21778,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21804,7 +21804,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G735" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21830,7 +21830,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G736" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21856,7 +21856,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G737" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21882,7 +21882,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21908,7 +21908,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G739" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21934,7 +21934,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G740" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21960,7 +21960,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G741" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21986,7 +21986,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G742" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22012,7 +22012,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G743" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22038,7 +22038,7 @@
         <v>3.75</v>
       </c>
       <c r="G744" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22064,7 +22064,7 @@
         <v>3.75</v>
       </c>
       <c r="G745" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22090,7 +22090,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22116,7 +22116,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G747" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22142,7 +22142,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22168,7 +22168,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G749" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22194,7 +22194,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G750" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22220,7 +22220,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G751" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22246,7 +22246,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G752" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22272,7 +22272,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G753" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22298,7 +22298,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G754" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22324,7 +22324,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G755" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22350,7 +22350,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G756" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22376,7 +22376,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G757" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22402,7 +22402,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G758" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22428,7 +22428,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22454,7 +22454,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G760" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22480,7 +22480,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22506,7 +22506,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22532,7 +22532,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G763" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22558,7 +22558,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G764" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22584,7 +22584,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G765" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22610,7 +22610,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G766" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22636,7 +22636,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G767" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22662,7 +22662,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G768" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22688,7 +22688,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G769" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22714,7 +22714,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G770" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22740,7 +22740,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G771" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22766,7 +22766,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22792,7 +22792,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22818,7 +22818,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G774" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22844,7 +22844,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G775" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22870,7 +22870,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G776" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22896,7 +22896,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G777" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22922,7 +22922,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G778" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22948,7 +22948,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G779" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22974,7 +22974,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G780" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23000,7 +23000,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G781" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23026,7 +23026,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G782" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23052,7 +23052,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G783" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23078,7 +23078,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G784" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23104,7 +23104,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G785" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23130,7 +23130,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G786" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23156,7 +23156,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G787" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23182,7 +23182,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23208,7 +23208,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G789" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23234,7 +23234,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23260,7 +23260,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G791" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23286,7 +23286,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G792" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23312,7 +23312,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G793" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23338,7 +23338,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G794" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23364,7 +23364,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G795" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23390,7 +23390,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G796" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23416,7 +23416,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23442,7 +23442,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G798" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23468,7 +23468,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G799" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23494,7 +23494,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G800" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23520,7 +23520,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23546,7 +23546,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G802" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23572,7 +23572,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G803" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23598,7 +23598,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G804" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23624,7 +23624,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G805" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23650,7 +23650,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G806" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23676,7 +23676,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G807" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23702,7 +23702,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G808" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23728,7 +23728,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G809" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23754,7 +23754,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G810" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23780,7 +23780,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G811" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23806,7 +23806,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G812" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23832,7 +23832,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G813" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23858,7 +23858,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G814" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23884,7 +23884,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G815" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23910,7 +23910,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G816" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23936,7 +23936,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23962,7 +23962,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G818" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23988,7 +23988,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G819" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24014,7 +24014,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G820" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24040,7 +24040,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G821" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24066,7 +24066,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G822" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24092,7 +24092,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24118,7 +24118,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G824" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24144,7 +24144,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24170,7 +24170,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G826" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24196,7 +24196,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G827" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24222,7 +24222,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G828" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24248,7 +24248,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G829" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24274,7 +24274,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G830" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24300,7 +24300,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24326,7 +24326,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G832" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24352,7 +24352,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G833" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24378,7 +24378,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24404,7 +24404,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G835" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24430,7 +24430,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G836" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24456,7 +24456,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G837" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24482,7 +24482,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G838" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24508,7 +24508,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G839" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24534,7 +24534,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G840" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24560,7 +24560,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G841" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24586,7 +24586,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24612,7 +24612,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G843" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24638,7 +24638,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G844" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24664,7 +24664,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G845" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24690,7 +24690,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G846" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24716,7 +24716,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G847" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24742,7 +24742,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G848" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24768,7 +24768,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G849" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24794,7 +24794,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G850" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24820,7 +24820,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G851" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24846,7 +24846,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G852" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24872,7 +24872,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G853" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24898,7 +24898,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G854" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24924,7 +24924,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G855" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24950,7 +24950,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G856" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24976,7 +24976,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G857" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25002,7 +25002,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25028,7 +25028,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G859" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25054,7 +25054,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G860" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25080,7 +25080,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G861" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25106,7 +25106,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G862" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25132,7 +25132,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G863" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25158,7 +25158,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G864" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25184,7 +25184,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G865" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25210,7 +25210,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G866" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25236,7 +25236,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G867" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25262,7 +25262,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G868" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25288,7 +25288,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G869" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25314,7 +25314,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G870" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25340,7 +25340,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G871" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25366,7 +25366,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25392,7 +25392,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G873" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25418,7 +25418,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G874" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25444,7 +25444,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G875" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25470,7 +25470,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G876" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25496,7 +25496,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G877" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25522,7 +25522,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G878" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25548,7 +25548,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G879" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25574,7 +25574,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G880" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25600,7 +25600,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G881" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25626,7 +25626,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G882" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25652,7 +25652,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G883" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25678,7 +25678,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G884" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25704,7 +25704,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G885" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25730,7 +25730,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G886" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25756,7 +25756,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G887" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25782,7 +25782,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G888" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25808,7 +25808,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G889" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25834,7 +25834,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G890" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25860,7 +25860,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G891" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25886,7 +25886,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G892" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25912,7 +25912,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G893" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25938,7 +25938,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G894" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25964,7 +25964,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25990,7 +25990,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G896" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26016,7 +26016,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G897" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26042,7 +26042,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G898" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26068,7 +26068,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26094,7 +26094,7 @@
         <v>4</v>
       </c>
       <c r="G900" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26120,7 +26120,7 @@
         <v>4</v>
       </c>
       <c r="G901" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26146,7 +26146,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G902" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26172,7 +26172,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G903" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26198,7 +26198,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26224,7 +26224,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26250,7 +26250,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G906" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26276,7 +26276,7 @@
         <v>4</v>
       </c>
       <c r="G907" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26302,7 +26302,7 @@
         <v>4</v>
       </c>
       <c r="G908" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26328,7 +26328,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G909" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26354,7 +26354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G910" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26380,7 +26380,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G911" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26406,7 +26406,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26432,7 +26432,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G913" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26458,7 +26458,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G914" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26484,7 +26484,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26510,7 +26510,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G916" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26536,7 +26536,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G917" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26588,7 +26588,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G919" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26614,7 +26614,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G920" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26640,7 +26640,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G921" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26666,7 +26666,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G922" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26692,7 +26692,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G923" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26718,7 +26718,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G924" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26770,7 +26770,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G926" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26796,7 +26796,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G927" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26822,7 +26822,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G928" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26848,7 +26848,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G929" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26874,7 +26874,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G930" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26900,7 +26900,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G931" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26926,7 +26926,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G932" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26952,7 +26952,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G933" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26978,7 +26978,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G934" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27004,7 +27004,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G935" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27056,7 +27056,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27082,7 +27082,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G938" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27108,7 +27108,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G939" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -42396,7 +42396,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1527" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42422,7 +42422,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1528" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42448,7 +42448,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1529" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42526,7 +42526,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1532" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -67572,7 +67572,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.5797800926</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>1510</v>
@@ -67593,6 +67593,32 @@
         <v>744</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494444444</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>3402</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>749</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="784">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282133102417</t>
+    <t xml:space="preserve">3.87282085418701</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105965614319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458229064941</t>
+    <t xml:space="preserve">3.87105941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458252906799</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577653884888</t>
@@ -56,40 +56,40 @@
     <t xml:space="preserve">3.8640148639679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78652381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74249482154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79532885551453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771759033203</t>
+    <t xml:space="preserve">3.78652358055115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7424943447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79532933235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771782875061</t>
   </si>
   <si>
     <t xml:space="preserve">3.62977933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67733073234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443587303162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66324162483215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6438684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040639877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68965911865234</t>
+    <t xml:space="preserve">3.677330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443563461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66324138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64386868476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4871244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040616035461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68965935707092</t>
   </si>
   <si>
     <t xml:space="preserve">3.66676378250122</t>
@@ -98,103 +98,103 @@
     <t xml:space="preserve">3.6033616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53995895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915227890015</t>
+    <t xml:space="preserve">3.68085241317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637692451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.539959192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568999290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915204048157</t>
   </si>
   <si>
     <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210772514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455537796021</t>
+    <t xml:space="preserve">3.65091371536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210724830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455513954163</t>
   </si>
   <si>
     <t xml:space="preserve">3.71431517601013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.751300573349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294131278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79356861114502</t>
+    <t xml:space="preserve">3.75130033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294107437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79356837272644</t>
   </si>
   <si>
     <t xml:space="preserve">3.86225414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.814701795578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941867828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368763923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7372100353241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255421638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891255378723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74953889846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74601697921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73016571998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6984646320343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613648414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488236427307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350826263428</t>
+    <t xml:space="preserve">3.81470203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721098899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255445480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192715644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72135972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76539015769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74953842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74601650238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016619682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846439361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350850105286</t>
   </si>
   <si>
     <t xml:space="preserve">3.95383501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91861152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446183204651</t>
+    <t xml:space="preserve">3.91861200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446254730225</t>
   </si>
   <si>
     <t xml:space="preserve">3.98377537727356</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">3.9432680606842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91508936882019</t>
+    <t xml:space="preserve">3.91508960723877</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855363368988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395546913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087980270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8921947479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622326850891</t>
+    <t xml:space="preserve">3.91332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395451545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96088004112244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219427108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622303009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.92741799354553</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">4.0261287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97220802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018144607544</t>
+    <t xml:space="preserve">3.97220826148987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018120765686</t>
   </si>
   <si>
     <t xml:space="preserve">3.97759985923767</t>
@@ -248,55 +248,55 @@
     <t xml:space="preserve">4.04410266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98299169540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95423364639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625950813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233828544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92727208137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8913254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8194305896759</t>
+    <t xml:space="preserve">3.98299217224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95423340797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625998497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9272723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367815971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560681343079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89132499694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256670951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81942987442017</t>
   </si>
   <si>
     <t xml:space="preserve">3.70799279212952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76550889015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59475779533386</t>
+    <t xml:space="preserve">3.7655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59475755691528</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273121833801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67923450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63070487976074</t>
+    <t xml:space="preserve">3.67923426628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070559501648</t>
   </si>
   <si>
     <t xml:space="preserve">3.62171840667725</t>
@@ -314,34 +314,34 @@
     <t xml:space="preserve">3.57318949699402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61632633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60374450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64688181877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69181609153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675084114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652146339417</t>
+    <t xml:space="preserve">3.61632657051086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60374474525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64688158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6918158531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675107955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652122497559</t>
   </si>
   <si>
     <t xml:space="preserve">3.80325365066528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86616253852844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81763243675232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044244766235</t>
+    <t xml:space="preserve">3.86616158485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81763339042664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044292449951</t>
   </si>
   <si>
     <t xml:space="preserve">3.79246926307678</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">3.74394011497498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77449536323547</t>
+    <t xml:space="preserve">3.77449560165405</t>
   </si>
   <si>
     <t xml:space="preserve">3.79067182540894</t>
@@ -365,64 +365,64 @@
     <t xml:space="preserve">3.74753499031067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75112962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80145597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7331554889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348278999329</t>
+    <t xml:space="preserve">3.75112915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80145645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348255157471</t>
   </si>
   <si>
     <t xml:space="preserve">3.72416925430298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057437896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371121406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978975296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70260071754456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854804039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956156730652</t>
+    <t xml:space="preserve">3.77090048789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978951454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70260047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956109046936</t>
   </si>
   <si>
     <t xml:space="preserve">3.72237181663513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72776365280151</t>
+    <t xml:space="preserve">3.72776317596436</t>
   </si>
   <si>
     <t xml:space="preserve">3.75292706489563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75831937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541096687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68462681770325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6936137676239</t>
+    <t xml:space="preserve">3.75831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68462657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69361352920532</t>
   </si>
   <si>
     <t xml:space="preserve">3.66485571861267</t>
@@ -434,88 +434,88 @@
     <t xml:space="preserve">3.73135828971863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7133846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380913734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224083900452</t>
+    <t xml:space="preserve">3.71338438987732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168559074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380889892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224036216736</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82661938667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841753959656</t>
+    <t xml:space="preserve">3.82661914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8284170627594</t>
   </si>
   <si>
     <t xml:space="preserve">3.92547535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92188024520874</t>
+    <t xml:space="preserve">3.92188000679016</t>
   </si>
   <si>
     <t xml:space="preserve">3.90031218528748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87335085868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639143943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740401268005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87514901161194</t>
+    <t xml:space="preserve">3.87335181236267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639096260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8751482963562</t>
   </si>
   <si>
     <t xml:space="preserve">3.94165205955505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90929913520813</t>
+    <t xml:space="preserve">3.90929889678955</t>
   </si>
   <si>
     <t xml:space="preserve">3.95243620872498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98119401931763</t>
+    <t xml:space="preserve">3.98119354248047</t>
   </si>
   <si>
     <t xml:space="preserve">3.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88413596153259</t>
+    <t xml:space="preserve">3.88413572311401</t>
   </si>
   <si>
     <t xml:space="preserve">3.9488410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87874341011047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01534414291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02073669433594</t>
+    <t xml:space="preserve">3.87874364852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01534461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02073621749878</t>
   </si>
   <si>
     <t xml:space="preserve">4.00815534591675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04050779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05308961868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01714181900024</t>
+    <t xml:space="preserve">4.04050731658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0530891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01714134216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207609176636</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">4.07106351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14295864105225</t>
+    <t xml:space="preserve">4.14295816421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.06926584243774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08903741836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40357780456543</t>
+    <t xml:space="preserve">4.08903694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40357828140259</t>
   </si>
   <si>
     <t xml:space="preserve">4.37661743164062</t>
@@ -545,49 +545,49 @@
     <t xml:space="preserve">4.34785938262939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32808828353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27237033843994</t>
+    <t xml:space="preserve">4.32808780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27236938476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.11599731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03691339492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9847891330719</t>
+    <t xml:space="preserve">4.03691291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98478841781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.04230499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008280754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828608512878</t>
+    <t xml:space="preserve">3.95603108406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828584671021</t>
   </si>
   <si>
     <t xml:space="preserve">3.94704389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93266534805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099864959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795902252197</t>
+    <t xml:space="preserve">3.93266439437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099841117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795926094055</t>
   </si>
   <si>
     <t xml:space="preserve">3.90390682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524645805359</t>
+    <t xml:space="preserve">3.94524669647217</t>
   </si>
   <si>
     <t xml:space="preserve">3.9635968208313</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">3.99112153053284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98194646835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06819152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524693489075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89019656181335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87184596061707</t>
+    <t xml:space="preserve">3.98194670677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06819105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524621963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89019632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87184643745422</t>
   </si>
   <si>
     <t xml:space="preserve">3.92689681053162</t>
@@ -617,28 +617,28 @@
     <t xml:space="preserve">4.06452083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12874603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17462110519409</t>
+    <t xml:space="preserve">4.128746509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
     <t xml:space="preserve">4.12691116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10672664642334</t>
+    <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.05901622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03699684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99479126930237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05351209640503</t>
+    <t xml:space="preserve">4.03699636459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99479150772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05351161956787</t>
   </si>
   <si>
     <t xml:space="preserve">4.08287143707275</t>
@@ -647,28 +647,28 @@
     <t xml:space="preserve">4.03332662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07369709014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09204578399658</t>
+    <t xml:space="preserve">4.07369661331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0920467376709</t>
   </si>
   <si>
     <t xml:space="preserve">4.08103656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05534648895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09021186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0626859664917</t>
+    <t xml:space="preserve">4.05534744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09021139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06268644332886</t>
   </si>
   <si>
     <t xml:space="preserve">4.15260124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15627145767212</t>
+    <t xml:space="preserve">4.15627193450928</t>
   </si>
   <si>
     <t xml:space="preserve">4.16544628143311</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.11039638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09388113021851</t>
+    <t xml:space="preserve">4.09388160705566</t>
   </si>
   <si>
     <t xml:space="preserve">4.20948600769043</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.15443658828735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13792181015015</t>
+    <t xml:space="preserve">4.13792133331299</t>
   </si>
   <si>
     <t xml:space="preserve">4.12507629394531</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">4.15076637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10305690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17278575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11223077774048</t>
+    <t xml:space="preserve">4.10305643081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17278671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
     <t xml:space="preserve">4.07002639770508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10122156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16911697387695</t>
+    <t xml:space="preserve">4.10122108459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16911602020264</t>
   </si>
   <si>
     <t xml:space="preserve">4.18379640579224</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">4.0975513458252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05167675018311</t>
+    <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
     <t xml:space="preserve">4.01864671707153</t>
@@ -737,22 +737,22 @@
     <t xml:space="preserve">4.07920122146606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13425207138062</t>
+    <t xml:space="preserve">4.13425159454346</t>
   </si>
   <si>
     <t xml:space="preserve">4.21866130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13241624832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12140703201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11590099334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11773681640625</t>
+    <t xml:space="preserve">4.13241672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12140655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11590147018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11773633956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.14709615707397</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">4.1489315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19113636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19297170639038</t>
+    <t xml:space="preserve">4.1911358833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19297218322754</t>
   </si>
   <si>
     <t xml:space="preserve">3.99662661552429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04433584213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341158866882</t>
+    <t xml:space="preserve">4.04433631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561644554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341111183167</t>
   </si>
   <si>
     <t xml:space="preserve">4.02048110961914</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">3.92322659492493</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03516101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08654165267944</t>
+    <t xml:space="preserve">4.03516149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
     <t xml:space="preserve">4.04800653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96726608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506146430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772127151489</t>
+    <t xml:space="preserve">3.96726584434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
     <t xml:space="preserve">4.0002965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97277188301086</t>
+    <t xml:space="preserve">3.97277140617371</t>
   </si>
   <si>
     <t xml:space="preserve">3.93790650367737</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">3.99846124649048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04617118835449</t>
+    <t xml:space="preserve">4.04617166519165</t>
   </si>
   <si>
     <t xml:space="preserve">3.88102173805237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85349678993225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442128181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854716300964</t>
+    <t xml:space="preserve">3.85349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514618873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89937138557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854668617249</t>
   </si>
   <si>
     <t xml:space="preserve">3.93607139587402</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">3.86267161369324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82597208023071</t>
+    <t xml:space="preserve">3.82597184181213</t>
   </si>
   <si>
     <t xml:space="preserve">3.78927206993103</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">3.807621717453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04857397079468</t>
+    <t xml:space="preserve">4.02039432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04857492446899</t>
   </si>
   <si>
     <t xml:space="preserve">4.03918075561523</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">3.97342705726624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99221420288086</t>
+    <t xml:space="preserve">3.9922137260437</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">3.89827942848206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91706609725952</t>
+    <t xml:space="preserve">3.91706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70101714134216</t>
+    <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.75737762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73859071731567</t>
+    <t xml:space="preserve">3.73859095573425</t>
   </si>
   <si>
     <t xml:space="preserve">3.71980404853821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71041059494019</t>
+    <t xml:space="preserve">3.71041083335876</t>
   </si>
   <si>
     <t xml:space="preserve">3.63526272773743</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">3.42860722541809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770565986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35345959663391</t>
+    <t xml:space="preserve">3.28770542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35345983505249</t>
   </si>
   <si>
     <t xml:space="preserve">3.33467292785645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37224650382996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38163995742798</t>
+    <t xml:space="preserve">3.37224626541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3816397190094</t>
   </si>
   <si>
     <t xml:space="preserve">3.45678758621216</t>
@@ -929,40 +929,40 @@
     <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36285281181335</t>
+    <t xml:space="preserve">3.36285305023193</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800067901611</t>
+    <t xml:space="preserve">3.43800091743469</t>
   </si>
   <si>
     <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47557473182678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49436116218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3158860206604</t>
+    <t xml:space="preserve">3.4755744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49436140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31588578224182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50375485420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65404963493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48496747016907</t>
+    <t xml:space="preserve">3.56950879096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50375461578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65404987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48496770858765</t>
   </si>
   <si>
     <t xml:space="preserve">3.68223023414612</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">3.58829569816589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55072212219238</t>
+    <t xml:space="preserve">3.5507218837738</t>
   </si>
   <si>
     <t xml:space="preserve">3.53193497657776</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">3.56011533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57890200614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64465665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6728367805481</t>
+    <t xml:space="preserve">3.57890224456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67283654212952</t>
   </si>
   <si>
     <t xml:space="preserve">3.51314806938171</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">3.62637186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58779335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495013237</t>
+    <t xml:space="preserve">3.58779358863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495037078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79997491836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210739135742</t>
+    <t xml:space="preserve">3.7999746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210715293884</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855319023132</t>
+    <t xml:space="preserve">3.8385534286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1043,40 +1043,40 @@
     <t xml:space="preserve">3.72281789779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64566135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56850457191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52992582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47205829620361</t>
+    <t xml:space="preserve">3.64566111564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56850433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52992606163025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47205805778503</t>
   </si>
   <si>
     <t xml:space="preserve">3.51063656806946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41419053077698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43347954750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45276880264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37561225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39490151405334</t>
+    <t xml:space="preserve">3.41419076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43347978591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4527690410614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37561202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39490127563477</t>
   </si>
   <si>
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916598320007</t>
+    <t xml:space="preserve">3.27916622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">3.14414167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2020092010498</t>
+    <t xml:space="preserve">3.20200896263123</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0669846534729</t>
+    <t xml:space="preserve">3.06698489189148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
+    <t xml:space="preserve">2.91267108917236</t>
   </si>
   <si>
     <t xml:space="preserve">2.85480356216431</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">2.71977877616882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83551406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.970538854599</t>
+    <t xml:space="preserve">2.83551430702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97053861618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">2.98982763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95124959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81622505187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75835704803467</t>
+    <t xml:space="preserve">2.95124936103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8162248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79693579673767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75835728645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.77764678001404</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.5847544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50759768486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46901893615723</t>
+    <t xml:space="preserve">2.50759744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46901917457581</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110255241394</t>
+    <t xml:space="preserve">2.14110279083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.23754858970642</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">2.26648235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41115140914917</t>
+    <t xml:space="preserve">2.41115164756775</t>
   </si>
   <si>
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044090270996</t>
+    <t xml:space="preserve">2.43044066429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.27612709999084</t>
@@ -1232,19 +1232,19 @@
     <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22790384292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24719309806824</t>
+    <t xml:space="preserve">2.2279040813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24719333648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.35328412055969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32435011863708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17968106269836</t>
+    <t xml:space="preserve">2.32434988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17968082427979</t>
   </si>
   <si>
     <t xml:space="preserve">2.18932557106018</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">2.17003631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13145804405212</t>
+    <t xml:space="preserve">2.1314582824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.08323502540588</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">1.98678886890411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92409884929657</t>
+    <t xml:space="preserve">1.92409896850586</t>
   </si>
   <si>
     <t xml:space="preserve">1.92892122268677</t>
@@ -1286,34 +1286,34 @@
     <t xml:space="preserve">1.95785510540009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15074706077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37257289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38221764564514</t>
+    <t xml:space="preserve">2.20861458778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15074729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37257313728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38221788406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66191124916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64262199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59439921379089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68120050430298</t>
+    <t xml:space="preserve">2.87409257888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66191148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64262223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6812002658844</t>
   </si>
   <si>
     <t xml:space="preserve">2.65226674079895</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">2.61368823051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53653144836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52688670158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51724219322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70048975944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71013426780701</t>
+    <t xml:space="preserve">2.53653168678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52688694000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51724195480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70048952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71013402938843</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98018288612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9608941078186</t>
+    <t xml:space="preserve">2.98018312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089386940002</t>
   </si>
   <si>
     <t xml:space="preserve">3.03805112838745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21165370941162</t>
+    <t xml:space="preserve">3.16343092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21165347099304</t>
   </si>
   <si>
     <t xml:space="preserve">3.23094296455383</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">3.17307543754578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952171325684</t>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378618240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952147483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
@@ -1394,28 +1394,28 @@
     <t xml:space="preserve">3.30809998512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32738900184631</t>
+    <t xml:space="preserve">3.32738924026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.25023221969604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766294002533</t>
+    <t xml:space="preserve">3.09591841697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07662916183472</t>
   </si>
   <si>
     <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05734014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.931960105896</t>
+    <t xml:space="preserve">3.05734038352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92231583595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93196034431458</t>
   </si>
   <si>
     <t xml:space="preserve">2.90302634239197</t>
@@ -1433,34 +1433,34 @@
     <t xml:space="preserve">2.80658054351807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67459464073181</t>
+    <t xml:space="preserve">3.59743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
     <t xml:space="preserve">3.71317338943481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79033041000366</t>
+    <t xml:space="preserve">3.79033017158508</t>
   </si>
   <si>
     <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95428824424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94464421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9832227230072</t>
+    <t xml:space="preserve">3.95428848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9446439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98322248458862</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507345199585</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">4.20504856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26291608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30149412155151</t>
+    <t xml:space="preserve">4.26291656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30149459838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.23398208618164</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">4.42687463760376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45580768585205</t>
+    <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
     <t xml:space="preserve">4.22433757781982</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40758514404297</t>
+    <t xml:space="preserve">4.40758562088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36900663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1278920173645</t>
+    <t xml:space="preserve">4.3690071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25327157974243</t>
+    <t xml:space="preserve">4.25327110290527</t>
   </si>
   <si>
     <t xml:space="preserve">4.1857590675354</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180051803589</t>
+    <t xml:space="preserve">4.02180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
+    <t xml:space="preserve">4.17611455917358</t>
   </si>
   <si>
     <t xml:space="preserve">4.33042764663696</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">4.47509717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49438619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44616365432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41722965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64870023727417</t>
+    <t xml:space="preserve">4.49438667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41722917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64869976043701</t>
   </si>
   <si>
     <t xml:space="preserve">4.80301380157471</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682458877563</t>
+    <t xml:space="preserve">4.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682554244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372430801392</t>
+    <t xml:space="preserve">4.78372478485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1634,118 +1634,121 @@
     <t xml:space="preserve">4.97661638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01519536972046</t>
+    <t xml:space="preserve">5.0151948928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5938720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28524398803711</t>
+    <t xml:space="preserve">5.59387159347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49742555618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28524446487427</t>
   </si>
   <si>
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026853561401</t>
+    <t xml:space="preserve">5.42026805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84159231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93803787231445</t>
+    <t xml:space="preserve">4.86088132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84159183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93803834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73550128936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70608854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86295795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87276268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96100187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13748025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0198278427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1963062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07865381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94139337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00021886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432725906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78452348709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67667579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61784934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6276535987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75511026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84334945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89237117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72569704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413246154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76491498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92178392410278</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70608854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86295795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87276220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9610013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13747978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0198278427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1963062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07865381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94139337539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90217542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78452348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67667531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61784934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6276535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75511026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84334945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89237117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413198471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76491498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92178440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687154769897</t>
+    <t xml:space="preserve">4.83354520797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687107086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1775,16 +1778,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000165939331</t>
+    <t xml:space="preserve">4.74530649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59824085235596</t>
+    <t xml:space="preserve">4.5982403755188</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1793,7 +1796,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921865463257</t>
+    <t xml:space="preserve">4.54921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1820,40 +1823,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254499435425</t>
+    <t xml:space="preserve">4.38254451751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3237190246582</t>
+    <t xml:space="preserve">4.32371854782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508880615234</t>
+    <t xml:space="preserve">4.26489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587133407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508832931519</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13743591308594</t>
+    <t xml:space="preserve">4.1374363899231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117568969727</t>
+    <t xml:space="preserve">4.33352375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117521286011</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1862,7 +1865,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274026870728</t>
+    <t xml:space="preserve">4.37274074554443</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1877,10 +1880,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1668496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1962628364563</t>
+    <t xml:space="preserve">4.16684913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19626235961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -46397,7 +46400,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1681" t="s">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46553,7 +46556,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46631,7 +46634,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1690" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46657,7 +46660,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46683,7 +46686,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1692" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46735,7 +46738,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1694" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46761,7 +46764,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1695" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46813,7 +46816,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46839,7 +46842,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1698" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46865,7 +46868,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1699" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46891,7 +46894,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1700" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46917,7 +46920,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1701" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46943,7 +46946,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47073,7 +47076,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47099,7 +47102,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1708" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47125,7 +47128,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1709" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47151,7 +47154,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1710" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47203,7 +47206,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47229,7 +47232,7 @@
         <v>4.5</v>
       </c>
       <c r="G1713" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47255,7 +47258,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47281,7 +47284,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47307,7 +47310,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47333,7 +47336,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47359,7 +47362,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1718" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47411,7 +47414,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1720" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47437,7 +47440,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47463,7 +47466,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1722" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47541,7 +47544,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1725" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47567,7 +47570,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1726" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47593,7 +47596,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47619,7 +47622,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1728" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47645,7 +47648,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1729" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47671,7 +47674,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47697,7 +47700,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1731" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47723,7 +47726,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1732" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47749,7 +47752,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1733" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47827,7 +47830,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1736" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47853,7 +47856,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1737" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47879,7 +47882,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1738" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47931,7 +47934,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1740" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47957,7 +47960,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1741" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47983,7 +47986,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1742" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48061,7 +48064,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1745" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48087,7 +48090,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1746" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48139,7 +48142,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1748" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48165,7 +48168,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1749" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48191,7 +48194,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1750" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48217,7 +48220,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1751" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48243,7 +48246,7 @@
         <v>4.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48269,7 +48272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48295,7 +48298,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1754" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48321,7 +48324,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1755" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48347,7 +48350,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1756" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48373,7 +48376,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1757" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48399,7 +48402,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48425,7 +48428,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1759" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48451,7 +48454,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1760" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48477,7 +48480,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1761" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48503,7 +48506,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1762" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48529,7 +48532,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1763" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48555,7 +48558,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48581,7 +48584,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1765" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48607,7 +48610,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1766" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48633,7 +48636,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1767" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48659,7 +48662,7 @@
         <v>4.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48685,7 +48688,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1769" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48711,7 +48714,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1770" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48737,7 +48740,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1771" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48763,7 +48766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1772" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48789,7 +48792,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1773" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48815,7 +48818,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1774" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48841,7 +48844,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1775" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48867,7 +48870,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48893,7 +48896,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1777" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48919,7 +48922,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1778" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48945,7 +48948,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1779" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48971,7 +48974,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1780" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48997,7 +49000,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1781" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49023,7 +49026,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1782" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49049,7 +49052,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49075,7 +49078,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49101,7 +49104,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1785" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49127,7 +49130,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49153,7 +49156,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1787" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49179,7 +49182,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1788" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49205,7 +49208,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49231,7 +49234,7 @@
         <v>4.5</v>
       </c>
       <c r="G1790" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49257,7 +49260,7 @@
         <v>4.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49283,7 +49286,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49309,7 +49312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49335,7 +49338,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49361,7 +49364,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1795" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49387,7 +49390,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1796" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49413,7 +49416,7 @@
         <v>4.75</v>
       </c>
       <c r="G1797" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49439,7 +49442,7 @@
         <v>4.75</v>
       </c>
       <c r="G1798" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49465,7 +49468,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1799" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49491,7 +49494,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49543,7 +49546,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1802" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49569,7 +49572,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1803" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49595,7 +49598,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1804" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49621,7 +49624,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1805" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49647,7 +49650,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1806" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49673,7 +49676,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1807" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49699,7 +49702,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1808" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49725,7 +49728,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1809" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49751,7 +49754,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1810" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49777,7 +49780,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1811" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49803,7 +49806,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1812" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49829,7 +49832,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1813" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49855,7 +49858,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1814" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49881,7 +49884,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1815" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49907,7 +49910,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1816" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49933,7 +49936,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1817" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49959,7 +49962,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49985,7 +49988,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1819" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50011,7 +50014,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1820" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50037,7 +50040,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1821" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50063,7 +50066,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1822" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50089,7 +50092,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1823" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50115,7 +50118,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1824" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50193,7 +50196,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50349,7 +50352,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50375,7 +50378,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1834" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50401,7 +50404,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1835" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50427,7 +50430,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1836" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50453,7 +50456,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1837" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50531,7 +50534,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1840" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50583,7 +50586,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1842" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50635,7 +50638,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1844" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50687,7 +50690,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1846" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50713,7 +50716,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1847" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50739,7 +50742,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1848" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50765,7 +50768,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1849" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50791,7 +50794,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1850" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50817,7 +50820,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1851" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50843,7 +50846,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50869,7 +50872,7 @@
         <v>4.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50895,7 +50898,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1854" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50921,7 +50924,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1855" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50947,7 +50950,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1856" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50973,7 +50976,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50999,7 +51002,7 @@
         <v>4.5</v>
       </c>
       <c r="G1858" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51025,7 +51028,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1859" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51051,7 +51054,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51077,7 +51080,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1861" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51103,7 +51106,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51129,7 +51132,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1863" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51155,7 +51158,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1864" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51181,7 +51184,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1865" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51207,7 +51210,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1866" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51233,7 +51236,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51259,7 +51262,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1868" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51285,7 +51288,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1869" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51311,7 +51314,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51337,7 +51340,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1871" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51363,7 +51366,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1872" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51389,7 +51392,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1873" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51415,7 +51418,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1874" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51441,7 +51444,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1875" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51467,7 +51470,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1876" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51493,7 +51496,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1877" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51519,7 +51522,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51545,7 +51548,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1879" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51571,7 +51574,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1880" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51597,7 +51600,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1881" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51623,7 +51626,7 @@
         <v>4.5</v>
       </c>
       <c r="G1882" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51649,7 +51652,7 @@
         <v>4.5</v>
       </c>
       <c r="G1883" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51675,7 +51678,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51701,7 +51704,7 @@
         <v>4.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51727,7 +51730,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1886" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51753,7 +51756,7 @@
         <v>4.5</v>
       </c>
       <c r="G1887" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51779,7 +51782,7 @@
         <v>4.5</v>
       </c>
       <c r="G1888" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51805,7 +51808,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51831,7 +51834,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1890" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51857,7 +51860,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1891" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51883,7 +51886,7 @@
         <v>4.5</v>
       </c>
       <c r="G1892" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51909,7 +51912,7 @@
         <v>4.5</v>
       </c>
       <c r="G1893" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51935,7 +51938,7 @@
         <v>4.5</v>
       </c>
       <c r="G1894" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51961,7 +51964,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51987,7 +51990,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52013,7 +52016,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1897" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52039,7 +52042,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1898" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52065,7 +52068,7 @@
         <v>4.5</v>
       </c>
       <c r="G1899" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52091,7 +52094,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1900" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52117,7 +52120,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1901" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52143,7 +52146,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1902" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52169,7 +52172,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52195,7 +52198,7 @@
         <v>4.5</v>
       </c>
       <c r="G1904" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52221,7 +52224,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1905" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52247,7 +52250,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1906" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52273,7 +52276,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1907" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52299,7 +52302,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1908" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52325,7 +52328,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1909" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52351,7 +52354,7 @@
         <v>4.75</v>
       </c>
       <c r="G1910" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52377,7 +52380,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52403,7 +52406,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1912" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52429,7 +52432,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1913" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52455,7 +52458,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1914" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52481,7 +52484,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1915" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52507,7 +52510,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1916" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52533,7 +52536,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1917" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52559,7 +52562,7 @@
         <v>4.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52585,7 +52588,7 @@
         <v>4.75</v>
       </c>
       <c r="G1919" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52611,7 +52614,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1920" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52637,7 +52640,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1921" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52663,7 +52666,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1922" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52689,7 +52692,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52715,7 +52718,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1924" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52741,7 +52744,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52767,7 +52770,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1926" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52793,7 +52796,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1927" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52819,7 +52822,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1928" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52845,7 +52848,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1929" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52871,7 +52874,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1930" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52897,7 +52900,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1931" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52923,7 +52926,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1932" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52949,7 +52952,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1933" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52975,7 +52978,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1934" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53001,7 +53004,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1935" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53027,7 +53030,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1936" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53053,7 +53056,7 @@
         <v>4.5</v>
       </c>
       <c r="G1937" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53079,7 +53082,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1938" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53105,7 +53108,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1939" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53131,7 +53134,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1940" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53157,7 +53160,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53183,7 +53186,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1942" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53209,7 +53212,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1943" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53235,7 +53238,7 @@
         <v>4.5</v>
       </c>
       <c r="G1944" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53261,7 +53264,7 @@
         <v>4.5</v>
       </c>
       <c r="G1945" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53287,7 +53290,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1946" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53313,7 +53316,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1947" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53339,7 +53342,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1948" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53365,7 +53368,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1949" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53391,7 +53394,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1950" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53417,7 +53420,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1951" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53443,7 +53446,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1952" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53469,7 +53472,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1953" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53495,7 +53498,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1954" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53521,7 +53524,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53547,7 +53550,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1956" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53573,7 +53576,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1957" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53599,7 +53602,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1958" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53625,7 +53628,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1959" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53651,7 +53654,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1960" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53677,7 +53680,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1961" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53703,7 +53706,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53729,7 +53732,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1963" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53755,7 +53758,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1964" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53781,7 +53784,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1965" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53807,7 +53810,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1966" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53833,7 +53836,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1967" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53859,7 +53862,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1968" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53885,7 +53888,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1969" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53911,7 +53914,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1970" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53937,7 +53940,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53963,7 +53966,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1972" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53989,7 +53992,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54015,7 +54018,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1974" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54041,7 +54044,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1975" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54067,7 +54070,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54093,7 +54096,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54119,7 +54122,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1978" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54145,7 +54148,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1979" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54171,7 +54174,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54197,7 +54200,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54223,7 +54226,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1982" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54249,7 +54252,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1983" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54275,7 +54278,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1984" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54301,7 +54304,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1985" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54327,7 +54330,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1986" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54353,7 +54356,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54379,7 +54382,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1988" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54405,7 +54408,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1989" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54431,7 +54434,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54457,7 +54460,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1991" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54483,7 +54486,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54509,7 +54512,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1993" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54535,7 +54538,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54561,7 +54564,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1995" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54587,7 +54590,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1996" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54613,7 +54616,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54639,7 +54642,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54665,7 +54668,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1999" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54691,7 +54694,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2000" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54717,7 +54720,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2001" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54743,7 +54746,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2002" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54769,7 +54772,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2003" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54795,7 +54798,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2004" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54821,7 +54824,7 @@
         <v>4.75</v>
       </c>
       <c r="G2005" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54847,7 +54850,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2006" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54873,7 +54876,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2007" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54899,7 +54902,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2008" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54925,7 +54928,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2009" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54951,7 +54954,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2010" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54977,7 +54980,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2011" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55003,7 +55006,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2012" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55029,7 +55032,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55055,7 +55058,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55081,7 +55084,7 @@
         <v>4.5</v>
       </c>
       <c r="G2015" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55107,7 +55110,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2016" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55133,7 +55136,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2017" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55159,7 +55162,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2018" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55185,7 +55188,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2019" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55211,7 +55214,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2020" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55237,7 +55240,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2021" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55263,7 +55266,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2022" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55289,7 +55292,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2023" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55315,7 +55318,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2024" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55341,7 +55344,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2025" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55367,7 +55370,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2026" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55393,7 +55396,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2027" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55419,7 +55422,7 @@
         <v>4.75</v>
       </c>
       <c r="G2028" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55445,7 +55448,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2029" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55471,7 +55474,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2030" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55497,7 +55500,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2031" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55523,7 +55526,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2032" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55549,7 +55552,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2033" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55575,7 +55578,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2034" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55601,7 +55604,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2035" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55627,7 +55630,7 @@
         <v>5</v>
       </c>
       <c r="G2036" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55653,7 +55656,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55679,7 +55682,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2038" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55705,7 +55708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2039" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55731,7 +55734,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55757,7 +55760,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55783,7 +55786,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2042" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55809,7 +55812,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2043" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55835,7 +55838,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2044" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55861,7 +55864,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2045" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55887,7 +55890,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2046" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55913,7 +55916,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55939,7 +55942,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2048" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55965,7 +55968,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2049" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55991,7 +55994,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2050" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56017,7 +56020,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2051" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56043,7 +56046,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2052" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56069,7 +56072,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2053" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56095,7 +56098,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2054" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56121,7 +56124,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56147,7 +56150,7 @@
         <v>5</v>
       </c>
       <c r="G2056" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56173,7 +56176,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56199,7 +56202,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56225,7 +56228,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2059" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56251,7 +56254,7 @@
         <v>5</v>
       </c>
       <c r="G2060" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56277,7 +56280,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2061" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56303,7 +56306,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2062" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56329,7 +56332,7 @@
         <v>5</v>
       </c>
       <c r="G2063" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56355,7 +56358,7 @@
         <v>5</v>
       </c>
       <c r="G2064" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56381,7 +56384,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2065" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56407,7 +56410,7 @@
         <v>5</v>
       </c>
       <c r="G2066" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56433,7 +56436,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2067" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56459,7 +56462,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2068" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56485,7 +56488,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2069" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56511,7 +56514,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2070" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56537,7 +56540,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2071" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56563,7 +56566,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2072" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56589,7 +56592,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2073" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56615,7 +56618,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2074" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56641,7 +56644,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2075" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56667,7 +56670,7 @@
         <v>5.5</v>
       </c>
       <c r="G2076" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56693,7 +56696,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56719,7 +56722,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56745,7 +56748,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2079" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56771,7 +56774,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2080" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56797,7 +56800,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56823,7 +56826,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2082" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56849,7 +56852,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2083" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56875,7 +56878,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2084" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56901,7 +56904,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2085" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56927,7 +56930,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2086" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56953,7 +56956,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2087" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56979,7 +56982,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2088" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57005,7 +57008,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2089" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57031,7 +57034,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2090" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57057,7 +57060,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57083,7 +57086,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2092" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57109,7 +57112,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2093" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57135,7 +57138,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2094" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57161,7 +57164,7 @@
         <v>5</v>
       </c>
       <c r="G2095" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57187,7 +57190,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2096" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57213,7 +57216,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2097" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57239,7 +57242,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57265,7 +57268,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2099" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57291,7 +57294,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2100" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57317,7 +57320,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2101" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57343,7 +57346,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57369,7 +57372,7 @@
         <v>5</v>
       </c>
       <c r="G2103" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57395,7 +57398,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57421,7 +57424,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2105" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57447,7 +57450,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2106" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57473,7 +57476,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2107" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57499,7 +57502,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2108" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57525,7 +57528,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2109" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57551,7 +57554,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57577,7 +57580,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57603,7 +57606,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2112" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57629,7 +57632,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2113" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57655,7 +57658,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2114" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57681,7 +57684,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2115" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57707,7 +57710,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57733,7 +57736,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2117" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57759,7 +57762,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2118" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57785,7 +57788,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2119" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57811,7 +57814,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2120" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57837,7 +57840,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2121" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57863,7 +57866,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2122" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57889,7 +57892,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57915,7 +57918,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57941,7 +57944,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57967,7 +57970,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2126" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57993,7 +57996,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2127" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58019,7 +58022,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2128" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58045,7 +58048,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2129" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58071,7 +58074,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58097,7 +58100,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2131" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58123,7 +58126,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2132" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58149,7 +58152,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2133" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58175,7 +58178,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2134" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58201,7 +58204,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2135" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58227,7 +58230,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2136" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58253,7 +58256,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58279,7 +58282,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2138" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58305,7 +58308,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2139" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58331,7 +58334,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2140" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58357,7 +58360,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2141" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58383,7 +58386,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2142" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58409,7 +58412,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2143" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58435,7 +58438,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2144" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58461,7 +58464,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2145" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58487,7 +58490,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2146" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58513,7 +58516,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2147" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58539,7 +58542,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2148" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58565,7 +58568,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2149" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58591,7 +58594,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58617,7 +58620,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2151" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58643,7 +58646,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2152" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58669,7 +58672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2153" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58695,7 +58698,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2154" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58721,7 +58724,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2155" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58747,7 +58750,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2156" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58773,7 +58776,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2157" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58799,7 +58802,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2158" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58825,7 +58828,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58851,7 +58854,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2160" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58877,7 +58880,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58903,7 +58906,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2162" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58929,7 +58932,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2163" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58955,7 +58958,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2164" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58981,7 +58984,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2165" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59007,7 +59010,7 @@
         <v>4.75</v>
       </c>
       <c r="G2166" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59033,7 +59036,7 @@
         <v>4.75</v>
       </c>
       <c r="G2167" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59059,7 +59062,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2168" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59085,7 +59088,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59111,7 +59114,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2170" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59137,7 +59140,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59163,7 +59166,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2172" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59189,7 +59192,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2173" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59215,7 +59218,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2174" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59241,7 +59244,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2175" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59267,7 +59270,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59293,7 +59296,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2177" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59319,7 +59322,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2178" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59345,7 +59348,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2179" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59371,7 +59374,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2180" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59397,7 +59400,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2181" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59423,7 +59426,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2182" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59449,7 +59452,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2183" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59475,7 +59478,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2184" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59501,7 +59504,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2185" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59527,7 +59530,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2186" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59553,7 +59556,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2187" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59579,7 +59582,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2188" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59605,7 +59608,7 @@
         <v>4.25</v>
       </c>
       <c r="G2189" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59631,7 +59634,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2190" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59657,7 +59660,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2191" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59683,7 +59686,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2192" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59709,7 +59712,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2193" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59735,7 +59738,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2194" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59761,7 +59764,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2195" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59787,7 +59790,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2196" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59813,7 +59816,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59839,7 +59842,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2198" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59865,7 +59868,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59891,7 +59894,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2200" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59917,7 +59920,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2201" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59943,7 +59946,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2202" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59969,7 +59972,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59995,7 +59998,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60021,7 +60024,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2205" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60047,7 +60050,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2206" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60073,7 +60076,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2207" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60099,7 +60102,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60125,7 +60128,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2209" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60151,7 +60154,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2210" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60177,7 +60180,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2211" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60203,7 +60206,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60229,7 +60232,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2213" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60255,7 +60258,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2214" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60281,7 +60284,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60307,7 +60310,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2216" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60333,7 +60336,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2217" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60359,7 +60362,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2218" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60385,7 +60388,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2219" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60411,7 +60414,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2220" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60437,7 +60440,7 @@
         <v>4.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60463,7 +60466,7 @@
         <v>4.5</v>
       </c>
       <c r="G2222" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60489,7 +60492,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2223" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60515,7 +60518,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60541,7 +60544,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2225" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60567,7 +60570,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2226" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60593,7 +60596,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2227" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60619,7 +60622,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2228" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60645,7 +60648,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2229" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60671,7 +60674,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2230" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60697,7 +60700,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2231" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60723,7 +60726,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2232" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60749,7 +60752,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60775,7 +60778,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60801,7 +60804,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2235" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60827,7 +60830,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2236" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60853,7 +60856,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2237" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60879,7 +60882,7 @@
         <v>4.5</v>
       </c>
       <c r="G2238" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60905,7 +60908,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2239" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60931,7 +60934,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2240" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60957,7 +60960,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2241" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60983,7 +60986,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2242" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61009,7 +61012,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2243" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61035,7 +61038,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2244" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61061,7 +61064,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2245" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61087,7 +61090,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2246" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61113,7 +61116,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2247" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61139,7 +61142,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2248" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61165,7 +61168,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2249" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61191,7 +61194,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2250" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61217,7 +61220,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2251" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61243,7 +61246,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2252" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61269,7 +61272,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61295,7 +61298,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2254" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61321,7 +61324,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2255" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61347,7 +61350,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2256" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61373,7 +61376,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2257" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61399,7 +61402,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2258" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61425,7 +61428,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2259" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61451,7 +61454,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2260" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61477,7 +61480,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61503,7 +61506,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61529,7 +61532,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2263" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61555,7 +61558,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2264" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61581,7 +61584,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2265" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61607,7 +61610,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2266" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61633,7 +61636,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2267" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61659,7 +61662,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61685,7 +61688,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2269" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61711,7 +61714,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2270" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61737,7 +61740,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2271" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61763,7 +61766,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2272" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61789,7 +61792,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2273" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61815,7 +61818,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2274" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61841,7 +61844,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2275" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61867,7 +61870,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2276" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61893,7 +61896,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2277" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61919,7 +61922,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2278" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61945,7 +61948,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2279" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61971,7 +61974,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2280" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61997,7 +62000,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2281" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62023,7 +62026,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2282" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62049,7 +62052,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2283" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62075,7 +62078,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2284" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62101,7 +62104,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2285" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62127,7 +62130,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62153,7 +62156,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2287" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62179,7 +62182,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2288" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62205,7 +62208,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2289" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62231,7 +62234,7 @@
         <v>4.5</v>
       </c>
       <c r="G2290" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62257,7 +62260,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2291" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62283,7 +62286,7 @@
         <v>4.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62309,7 +62312,7 @@
         <v>4.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62335,7 +62338,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2294" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62361,7 +62364,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2295" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62387,7 +62390,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2296" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62413,7 +62416,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2297" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62439,7 +62442,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2298" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62465,7 +62468,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2299" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62491,7 +62494,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2300" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62517,7 +62520,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2301" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62543,7 +62546,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2302" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62569,7 +62572,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2303" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62595,7 +62598,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62621,7 +62624,7 @@
         <v>4.5</v>
       </c>
       <c r="G2305" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62647,7 +62650,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2306" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62673,7 +62676,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2307" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62699,7 +62702,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2308" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62725,7 +62728,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62751,7 +62754,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2310" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62777,7 +62780,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2311" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62803,7 +62806,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2312" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62829,7 +62832,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2313" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62855,7 +62858,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2314" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62881,7 +62884,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2315" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62907,7 +62910,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2316" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62933,7 +62936,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2317" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62959,7 +62962,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62985,7 +62988,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2319" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63011,7 +63014,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2320" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63037,7 +63040,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63063,7 +63066,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2322" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63089,7 +63092,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2323" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63115,7 +63118,7 @@
         <v>4.25</v>
       </c>
       <c r="G2324" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63141,7 +63144,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2325" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63167,7 +63170,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2326" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63193,7 +63196,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2327" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63219,7 +63222,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2328" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63245,7 +63248,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63271,7 +63274,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2330" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63297,7 +63300,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2331" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63323,7 +63326,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2332" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63349,7 +63352,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2333" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63375,7 +63378,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2334" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63401,7 +63404,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2335" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63427,7 +63430,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2336" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63453,7 +63456,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2337" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63479,7 +63482,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2338" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63505,7 +63508,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2339" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63531,7 +63534,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2340" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63557,7 +63560,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2341" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63583,7 +63586,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2342" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63609,7 +63612,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2343" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63635,7 +63638,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2344" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63661,7 +63664,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2345" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63687,7 +63690,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2346" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63713,7 +63716,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2347" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63739,7 +63742,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2348" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63765,7 +63768,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63791,7 +63794,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2350" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63817,7 +63820,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2351" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63843,7 +63846,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2352" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63869,7 +63872,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2353" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63895,7 +63898,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2354" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63921,7 +63924,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2355" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63947,7 +63950,7 @@
         <v>4</v>
       </c>
       <c r="G2356" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63973,7 +63976,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2357" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63999,7 +64002,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2358" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64025,7 +64028,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2359" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64051,7 +64054,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2360" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64077,7 +64080,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2361" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64103,7 +64106,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2362" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64129,7 +64132,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2363" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64155,7 +64158,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2364" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64181,7 +64184,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2365" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64207,7 +64210,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2366" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64233,7 +64236,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2367" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64259,7 +64262,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2368" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64285,7 +64288,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2369" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64311,7 +64314,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2370" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64337,7 +64340,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2371" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64363,7 +64366,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2372" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64389,7 +64392,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2373" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64415,7 +64418,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2374" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64441,7 +64444,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2375" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64467,7 +64470,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64493,7 +64496,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2377" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64519,7 +64522,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2378" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64545,7 +64548,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2379" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64571,7 +64574,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2380" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64597,7 +64600,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2381" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64623,7 +64626,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2382" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64649,7 +64652,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2383" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64675,7 +64678,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64701,7 +64704,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64727,7 +64730,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64753,7 +64756,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64779,7 +64782,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2388" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64805,7 +64808,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2389" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64831,7 +64834,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2390" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64857,7 +64860,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2391" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64883,7 +64886,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2392" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64909,7 +64912,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2393" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64935,7 +64938,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2394" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64961,7 +64964,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2395" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64987,7 +64990,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2396" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65013,7 +65016,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65039,7 +65042,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2398" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65065,7 +65068,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2399" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65091,7 +65094,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2400" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65117,7 +65120,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2401" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65143,7 +65146,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2402" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65169,7 +65172,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2403" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65195,7 +65198,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2404" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65221,7 +65224,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2405" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65247,7 +65250,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65273,7 +65276,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2407" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65299,7 +65302,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2408" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65325,7 +65328,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2409" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65351,7 +65354,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65377,7 +65380,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65403,7 +65406,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2412" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65429,7 +65432,7 @@
         <v>4</v>
       </c>
       <c r="G2413" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65455,7 +65458,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2414" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65481,7 +65484,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2415" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65507,7 +65510,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2416" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65533,7 +65536,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65559,7 +65562,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2418" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65585,7 +65588,7 @@
         <v>4</v>
       </c>
       <c r="G2419" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65611,7 +65614,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2420" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65637,7 +65640,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2421" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65663,7 +65666,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2422" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65689,7 +65692,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2423" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65715,7 +65718,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65741,7 +65744,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2425" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65767,7 +65770,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2426" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65793,7 +65796,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2427" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65819,7 +65822,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2428" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65845,7 +65848,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65871,7 +65874,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2430" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65897,7 +65900,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2431" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65923,7 +65926,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2432" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65949,7 +65952,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2433" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65975,7 +65978,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2434" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66001,7 +66004,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2435" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66027,7 +66030,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2436" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66053,7 +66056,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2437" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66079,7 +66082,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2438" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66105,7 +66108,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2439" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66131,7 +66134,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66157,7 +66160,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66183,7 +66186,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2442" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66209,7 +66212,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2443" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66235,7 +66238,7 @@
         <v>4</v>
       </c>
       <c r="G2444" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66261,7 +66264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2445" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66287,7 +66290,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2446" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66313,7 +66316,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2447" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66339,7 +66342,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66365,7 +66368,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2449" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66391,7 +66394,7 @@
         <v>4</v>
       </c>
       <c r="G2450" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66417,7 +66420,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2451" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66443,7 +66446,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2452" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66469,7 +66472,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2453" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66495,7 +66498,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2454" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66521,7 +66524,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2455" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66547,7 +66550,7 @@
         <v>4</v>
       </c>
       <c r="G2456" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66573,7 +66576,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2457" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66599,7 +66602,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2458" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66625,7 +66628,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2459" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66651,7 +66654,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2460" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66677,7 +66680,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2461" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66703,7 +66706,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2462" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66729,7 +66732,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66755,7 +66758,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2464" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66781,7 +66784,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2465" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66807,7 +66810,7 @@
         <v>4</v>
       </c>
       <c r="G2466" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66833,7 +66836,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2467" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66859,7 +66862,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2468" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66885,7 +66888,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2469" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66911,7 +66914,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2470" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66937,7 +66940,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2471" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66963,7 +66966,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2472" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66989,7 +66992,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2473" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67015,7 +67018,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2474" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67041,7 +67044,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67067,7 +67070,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67093,7 +67096,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2477" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67119,7 +67122,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2478" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67145,7 +67148,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2479" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67171,7 +67174,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2480" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67197,7 +67200,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2481" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67223,7 +67226,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2482" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67249,7 +67252,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2483" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67275,7 +67278,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2484" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67301,7 +67304,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67327,7 +67330,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2486" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67353,7 +67356,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2487" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67379,7 +67382,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67405,7 +67408,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2489" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67431,7 +67434,7 @@
         <v>4.25</v>
       </c>
       <c r="G2490" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67457,7 +67460,7 @@
         <v>4.25</v>
       </c>
       <c r="G2491" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67483,7 +67486,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2492" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67509,7 +67512,7 @@
         <v>4.25</v>
       </c>
       <c r="G2493" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67535,7 +67538,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67561,7 +67564,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2495" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67587,7 +67590,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2496" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67613,7 +67616,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2497" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67639,7 +67642,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2498" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67665,7 +67668,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2499" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67673,7 +67676,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6813657407</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>11041</v>
@@ -67691,9 +67694,35 @@
         <v>4.25</v>
       </c>
       <c r="G2500" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6686574074</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>3102</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>4.19999980926514</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>748</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458252906799</t>
+    <t xml:space="preserve">3.87105965614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577653884888</t>
@@ -59,142 +59,142 @@
     <t xml:space="preserve">3.78652358055115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7424943447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79532933235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771782875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.677330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443563461304</t>
+    <t xml:space="preserve">3.74249410629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79532885551453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67733120918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443539619446</t>
   </si>
   <si>
     <t xml:space="preserve">3.66324138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64386868476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4871244430542</t>
+    <t xml:space="preserve">3.64386892318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712420463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68965935707092</t>
+    <t xml:space="preserve">3.68965911865234</t>
   </si>
   <si>
     <t xml:space="preserve">3.66676378250122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6033616065979</t>
+    <t xml:space="preserve">3.60336112976074</t>
   </si>
   <si>
     <t xml:space="preserve">3.68085241317749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56637692451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568999290466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915204048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65267419815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65091371536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210724830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455513954163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431517601013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75130033493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79356837272644</t>
+    <t xml:space="preserve">3.56637716293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568975448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6491527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65267395973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65091276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210772514343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.751300573349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294083595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79356861114502</t>
   </si>
   <si>
     <t xml:space="preserve">3.86225414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941963195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73721098899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192715644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135972976685</t>
+    <t xml:space="preserve">3.81470227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721075057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255373954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192739486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.721360206604</t>
   </si>
   <si>
     <t xml:space="preserve">3.76891231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76539015769958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74953842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74601650238037</t>
+    <t xml:space="preserve">3.76538920402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74953866004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74601697921753</t>
   </si>
   <si>
     <t xml:space="preserve">3.73016619682312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6861367225647</t>
+    <t xml:space="preserve">3.69846487045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68613624572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.72488260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82350850105286</t>
+    <t xml:space="preserve">3.82350826263428</t>
   </si>
   <si>
     <t xml:space="preserve">3.95383501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91861200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446254730225</t>
+    <t xml:space="preserve">3.91861152648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446230888367</t>
   </si>
   <si>
     <t xml:space="preserve">3.98377537727356</t>
@@ -203,31 +203,31 @@
     <t xml:space="preserve">3.9432680606842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91508960723877</t>
+    <t xml:space="preserve">3.91508936882019</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855363368988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395451545715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96088004112244</t>
+    <t xml:space="preserve">3.91332840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395499229431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96088027954102</t>
   </si>
   <si>
     <t xml:space="preserve">3.89219427108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93622303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741799354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338780403137</t>
+    <t xml:space="preserve">3.93622279167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741751670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338828086853</t>
   </si>
   <si>
     <t xml:space="preserve">3.99916791915894</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">4.0261287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97220826148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759985923767</t>
+    <t xml:space="preserve">3.97220754623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759938240051</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410266876221</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">3.98299217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95423340797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625998497009</t>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93626046180725</t>
   </si>
   <si>
     <t xml:space="preserve">3.88233852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9272723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367815971375</t>
+    <t xml:space="preserve">3.92727255821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
   </si>
   <si>
     <t xml:space="preserve">3.83560681343079</t>
@@ -272,22 +272,22 @@
     <t xml:space="preserve">3.89132499694824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86436414718628</t>
+    <t xml:space="preserve">3.86436438560486</t>
   </si>
   <si>
     <t xml:space="preserve">3.86256670951843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81942987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799279212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59475755691528</t>
+    <t xml:space="preserve">3.81942963600159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76550889015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59475779533386</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273121833801</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">3.67923426628113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63070559501648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62171840667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65766596794128</t>
+    <t xml:space="preserve">3.63070511817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62171864509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65766620635986</t>
   </si>
   <si>
     <t xml:space="preserve">3.63789486885071</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">3.68103218078613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57318949699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632657051086</t>
+    <t xml:space="preserve">3.57318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632633209229</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
@@ -323,25 +323,25 @@
     <t xml:space="preserve">3.64688158035278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6918158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675107955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616158485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81763339042664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044292449951</t>
+    <t xml:space="preserve">3.69181632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675084114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652098655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80325388908386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8176326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044268608093</t>
   </si>
   <si>
     <t xml:space="preserve">3.79246926307678</t>
@@ -353,34 +353,34 @@
     <t xml:space="preserve">3.77449560165405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79067182540894</t>
+    <t xml:space="preserve">3.79067206382751</t>
   </si>
   <si>
     <t xml:space="preserve">3.77629327774048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78887462615967</t>
+    <t xml:space="preserve">3.78887414932251</t>
   </si>
   <si>
     <t xml:space="preserve">3.74753499031067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75112915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80145645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348255157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72416925430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090048789978</t>
+    <t xml:space="preserve">3.75112962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80145621299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7331554889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348231315613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72416973114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77090096473694</t>
   </si>
   <si>
     <t xml:space="preserve">3.72057390213013</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">3.76371145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72596645355225</t>
+    <t xml:space="preserve">3.72596597671509</t>
   </si>
   <si>
     <t xml:space="preserve">3.70978951454163</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">3.72237181663513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72776317596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292706489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831985473633</t>
+    <t xml:space="preserve">3.72776341438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831913948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.69541072845459</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">3.73135828971863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71338438987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168559074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224036216736</t>
+    <t xml:space="preserve">3.71338510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380913734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224083900452</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
@@ -452,67 +452,70 @@
     <t xml:space="preserve">3.82661914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8284170627594</t>
+    <t xml:space="preserve">3.82841753959656</t>
   </si>
   <si>
     <t xml:space="preserve">3.92547535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92188000679016</t>
+    <t xml:space="preserve">3.93446278572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188024520874</t>
   </si>
   <si>
     <t xml:space="preserve">3.90031218528748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87335181236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639096260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8751482963562</t>
+    <t xml:space="preserve">3.87335085868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8374035358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87514877319336</t>
   </si>
   <si>
     <t xml:space="preserve">3.94165205955505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90929889678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243620872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98119354248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413572311401</t>
+    <t xml:space="preserve">3.90929913520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243573188782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98119401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9793963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413548469543</t>
   </si>
   <si>
     <t xml:space="preserve">3.9488410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87874364852905</t>
+    <t xml:space="preserve">3.87874341011047</t>
   </si>
   <si>
     <t xml:space="preserve">4.01534461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02073621749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00815534591675</t>
+    <t xml:space="preserve">4.0207371711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00815486907959</t>
   </si>
   <si>
     <t xml:space="preserve">4.04050731658936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0530891418457</t>
+    <t xml:space="preserve">4.05309009552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.01714134216309</t>
@@ -524,70 +527,70 @@
     <t xml:space="preserve">4.07106351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14295816421509</t>
+    <t xml:space="preserve">4.14295864105225</t>
   </si>
   <si>
     <t xml:space="preserve">4.06926584243774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08903694152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40357828140259</t>
+    <t xml:space="preserve">4.08903741836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40357780456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34606218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785938262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32808780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27236938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98478841781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603108406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828584671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266439437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099841117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795926094055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90390682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524669647217</t>
+    <t xml:space="preserve">4.34606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785890579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32808876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27236986160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599779129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03691339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9847891330719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04230546951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603132247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008328437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828608512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93266487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795878410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90390729904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524645805359</t>
   </si>
   <si>
     <t xml:space="preserve">3.9635968208313</t>
@@ -596,52 +599,49 @@
     <t xml:space="preserve">3.99112153053284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98194670677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06819105148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524621963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89019632339478</t>
+    <t xml:space="preserve">3.98194646835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06819152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8901960849762</t>
   </si>
   <si>
     <t xml:space="preserve">3.87184643745422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92689681053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.128746509552</t>
+    <t xml:space="preserve">3.92689728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691116333008</t>
+    <t xml:space="preserve">4.12691164016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05901622772217</t>
+    <t xml:space="preserve">4.05901575088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.03699636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99479150772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05351161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08287143707275</t>
+    <t xml:space="preserve">3.99479174613953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05351114273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08287191390991</t>
   </si>
   <si>
     <t xml:space="preserve">4.03332662582397</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">4.07369661331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0920467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08103656768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534744262695</t>
+    <t xml:space="preserve">4.09204626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08103609085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534648895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.09021139144897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06268644332886</t>
+    <t xml:space="preserve">4.0626859664917</t>
   </si>
   <si>
     <t xml:space="preserve">4.15260124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15627193450928</t>
+    <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
     <t xml:space="preserve">4.16544628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11039638519287</t>
+    <t xml:space="preserve">4.11039686203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.09388160705566</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">4.15443658828735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13792133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507629394531</t>
+    <t xml:space="preserve">4.1379222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507581710815</t>
   </si>
   <si>
     <t xml:space="preserve">4.11957120895386</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">4.13608646392822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15076637268066</t>
+    <t xml:space="preserve">4.15076589584351</t>
   </si>
   <si>
     <t xml:space="preserve">4.10305643081665</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">4.10122108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16911602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18379640579224</t>
+    <t xml:space="preserve">4.16911697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18379592895508</t>
   </si>
   <si>
     <t xml:space="preserve">4.21132135391235</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01864671707153</t>
+    <t xml:space="preserve">4.01864719390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.07920122146606</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">4.13241672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12140655517578</t>
+    <t xml:space="preserve">4.12140703201294</t>
   </si>
   <si>
     <t xml:space="preserve">4.11590147018433</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">4.14709615707397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1489315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1911358833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19297218322754</t>
+    <t xml:space="preserve">4.14893102645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19113636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19297170639038</t>
   </si>
   <si>
     <t xml:space="preserve">3.99662661552429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04433631896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561644554138</t>
+    <t xml:space="preserve">4.04433679580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561668395996</t>
   </si>
   <si>
     <t xml:space="preserve">3.94341111183167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02048110961914</t>
+    <t xml:space="preserve">4.0204815864563</t>
   </si>
   <si>
     <t xml:space="preserve">3.92322659492493</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726584434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772150993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0002965927124</t>
+    <t xml:space="preserve">4.04800701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506194114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772127151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00029706954956</t>
   </si>
   <si>
     <t xml:space="preserve">3.97277140617371</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">3.85349655151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95442199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514618873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89937138557434</t>
+    <t xml:space="preserve">3.95442128181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514595031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89937162399292</t>
   </si>
   <si>
     <t xml:space="preserve">3.90854668617249</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">3.807621717453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04857492446899</t>
+    <t xml:space="preserve">4.02039480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04857444763184</t>
   </si>
   <si>
     <t xml:space="preserve">4.03918075561523</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">3.71980404853821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71041083335876</t>
+    <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
     <t xml:space="preserve">3.63526272773743</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">3.42860722541809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770542144775</t>
+    <t xml:space="preserve">3.28770565986633</t>
   </si>
   <si>
     <t xml:space="preserve">3.35345983505249</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">3.37224626541138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3816397190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45678758621216</t>
+    <t xml:space="preserve">3.38163995742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45678734779358</t>
   </si>
   <si>
     <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36285305023193</t>
+    <t xml:space="preserve">3.36285281181335</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800091743469</t>
+    <t xml:space="preserve">3.43800067901611</t>
   </si>
   <si>
     <t xml:space="preserve">3.40042662620544</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">3.56950879096985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50375461578369</t>
+    <t xml:space="preserve">3.50375485420227</t>
   </si>
   <si>
     <t xml:space="preserve">3.65404987335205</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">3.59768915176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61647605895996</t>
+    <t xml:space="preserve">3.61647582054138</t>
   </si>
   <si>
     <t xml:space="preserve">3.66344332695007</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">3.64465641975403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67283654212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51314806938171</t>
+    <t xml:space="preserve">3.6728367805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51314830780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54921507835388</t>
+    <t xml:space="preserve">3.5492148399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.62637186050415</t>
@@ -1046,31 +1046,34 @@
     <t xml:space="preserve">3.64566111564636</t>
   </si>
   <si>
+    <t xml:space="preserve">3.60708284378052</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52992606163025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47205805778503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51063656806946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41419076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43347978591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4527690410614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37561202049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39490127563477</t>
+    <t xml:space="preserve">3.52992582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47205829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51063680648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41419053077698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43347954750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45276880264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37561225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39490151405334</t>
   </si>
   <si>
     <t xml:space="preserve">3.33703374862671</t>
@@ -1088,7 +1091,7 @@
     <t xml:space="preserve">3.14414167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20200896263123</t>
+    <t xml:space="preserve">3.2020092010498</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556316375732</t>
@@ -1109,7 +1112,7 @@
     <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71977877616882</t>
+    <t xml:space="preserve">2.7197790145874</t>
   </si>
   <si>
     <t xml:space="preserve">2.83551430702209</t>
@@ -1133,22 +1136,22 @@
     <t xml:space="preserve">2.98982763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95124936103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8162248134613</t>
+    <t xml:space="preserve">2.95124959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81622505187988</t>
   </si>
   <si>
     <t xml:space="preserve">2.79693579673767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75835728645325</t>
+    <t xml:space="preserve">2.75835704803467</t>
   </si>
   <si>
     <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73906803131104</t>
+    <t xml:space="preserve">2.73906779289246</t>
   </si>
   <si>
     <t xml:space="preserve">2.54617595672607</t>
@@ -1157,13 +1160,13 @@
     <t xml:space="preserve">2.62333297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60404372215271</t>
+    <t xml:space="preserve">2.60404396057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.5847544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50759744644165</t>
+    <t xml:space="preserve">2.50759768486023</t>
   </si>
   <si>
     <t xml:space="preserve">2.46901917457581</t>
@@ -1172,7 +1175,7 @@
     <t xml:space="preserve">2.33399486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16039180755615</t>
+    <t xml:space="preserve">2.16039204597473</t>
   </si>
   <si>
     <t xml:space="preserve">2.04465627670288</t>
@@ -1181,7 +1184,7 @@
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110279083252</t>
+    <t xml:space="preserve">2.14110255241394</t>
   </si>
   <si>
     <t xml:space="preserve">2.23754858970642</t>
@@ -1205,10 +1208,10 @@
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648235321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41115164756775</t>
+    <t xml:space="preserve">2.26648211479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41115140914917</t>
   </si>
   <si>
     <t xml:space="preserve">2.47866368293762</t>
@@ -1226,22 +1229,22 @@
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292862892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.36292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506110191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.2279040813446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24719333648682</t>
+    <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.35328412055969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32434988021851</t>
+    <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
     <t xml:space="preserve">2.17968082427979</t>
@@ -1253,7 +1256,7 @@
     <t xml:space="preserve">2.17003631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1314582824707</t>
+    <t xml:space="preserve">2.13145804405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.08323502540588</t>
@@ -1262,7 +1265,7 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216878890991</t>
+    <t xml:space="preserve">2.11216902732849</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
@@ -1274,7 +1277,7 @@
     <t xml:space="preserve">1.98678886890411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92409896850586</t>
+    <t xml:space="preserve">1.92409884929657</t>
   </si>
   <si>
     <t xml:space="preserve">1.92892122268677</t>
@@ -1286,10 +1289,10 @@
     <t xml:space="preserve">1.95785510540009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861458778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15074729919434</t>
+    <t xml:space="preserve">2.20861482620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15074706077576</t>
   </si>
   <si>
     <t xml:space="preserve">2.37257313728333</t>
@@ -1304,16 +1307,16 @@
     <t xml:space="preserve">2.87409257888794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66191148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64262223243713</t>
+    <t xml:space="preserve">2.66191124916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64262199401855</t>
   </si>
   <si>
     <t xml:space="preserve">2.59439897537231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6812002658844</t>
+    <t xml:space="preserve">2.68120050430298</t>
   </si>
   <si>
     <t xml:space="preserve">2.65226674079895</t>
@@ -1322,16 +1325,16 @@
     <t xml:space="preserve">2.61368823051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53653168678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52688694000244</t>
+    <t xml:space="preserve">2.53653144836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52688670158386</t>
   </si>
   <si>
     <t xml:space="preserve">2.51724195480347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70048952102661</t>
+    <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
     <t xml:space="preserve">2.71013402938843</t>
@@ -1349,7 +1352,7 @@
     <t xml:space="preserve">2.94160485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99947237968445</t>
+    <t xml:space="preserve">2.99947261810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.98018312454224</t>
@@ -1358,13 +1361,13 @@
     <t xml:space="preserve">2.96089386940002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03805112838745</t>
+    <t xml:space="preserve">3.03805088996887</t>
   </si>
   <si>
     <t xml:space="preserve">3.16343092918396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21165347099304</t>
+    <t xml:space="preserve">3.21165370941162</t>
   </si>
   <si>
     <t xml:space="preserve">3.23094296455383</t>
@@ -1379,10 +1382,10 @@
     <t xml:space="preserve">3.17307543754578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13449716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378618240356</t>
+    <t xml:space="preserve">3.13449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378594398499</t>
   </si>
   <si>
     <t xml:space="preserve">3.26952147483826</t>
@@ -1394,31 +1397,31 @@
     <t xml:space="preserve">3.30809998512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32738924026489</t>
+    <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
     <t xml:space="preserve">3.25023221969604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591841697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07662916183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01876187324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05734038352966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92231583595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93196034431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90302634239197</t>
+    <t xml:space="preserve">3.09591865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766294002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01876163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05734014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.931960105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90302658081055</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373732566833</t>
@@ -1433,31 +1436,31 @@
     <t xml:space="preserve">2.80658054351807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11520767211914</t>
+    <t xml:space="preserve">3.11520791053772</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743785858154</t>
+    <t xml:space="preserve">3.59743809700012</t>
   </si>
   <si>
     <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71317338943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79033017158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88677644729614</t>
+    <t xml:space="preserve">3.71317315101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79033041000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88677668571472</t>
   </si>
   <si>
     <t xml:space="preserve">3.95428848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9446439743042</t>
+    <t xml:space="preserve">3.94464421272278</t>
   </si>
   <si>
     <t xml:space="preserve">3.98322248458862</t>
@@ -1475,16 +1478,16 @@
     <t xml:space="preserve">4.20504856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26291656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30149459838867</t>
+    <t xml:space="preserve">4.26291608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30149412155151</t>
   </si>
   <si>
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971761703491</t>
+    <t xml:space="preserve">4.34971809387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1493,19 +1496,19 @@
     <t xml:space="preserve">4.39794015884399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42687463760376</t>
+    <t xml:space="preserve">4.4268741607666</t>
   </si>
   <si>
     <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22433757781982</t>
+    <t xml:space="preserve">4.22433805465698</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144502639771</t>
+    <t xml:space="preserve">4.03144454956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1514,31 +1517,31 @@
     <t xml:space="preserve">4.31113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2918496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40758562088013</t>
+    <t xml:space="preserve">4.29185009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40758514404297</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5329647064209</t>
+    <t xml:space="preserve">4.53296422958374</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3690071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12789154052734</t>
+    <t xml:space="preserve">4.36900663375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1278920173645</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25327110290527</t>
+    <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
     <t xml:space="preserve">4.1857590675354</t>
@@ -1553,7 +1556,7 @@
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611455917358</t>
+    <t xml:space="preserve">4.17611408233643</t>
   </si>
   <si>
     <t xml:space="preserve">4.33042764663696</t>
@@ -1568,28 +1571,28 @@
     <t xml:space="preserve">4.37865114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48474168777466</t>
+    <t xml:space="preserve">4.48474216461182</t>
   </si>
   <si>
     <t xml:space="preserve">4.47509717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49438667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41722917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64869976043701</t>
+    <t xml:space="preserve">4.49438619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44616365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41722965240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64870023727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585725784302</t>
+    <t xml:space="preserve">4.72585678100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.63905572891235</t>
@@ -1598,7 +1601,7 @@
     <t xml:space="preserve">4.62941074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61012172698975</t>
+    <t xml:space="preserve">4.6101222038269</t>
   </si>
   <si>
     <t xml:space="preserve">4.57154321670532</t>
@@ -1610,13 +1613,13 @@
     <t xml:space="preserve">4.11824655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15682554244995</t>
+    <t xml:space="preserve">4.15682506561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260921478271</t>
+    <t xml:space="preserve">4.54260969161987</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1634,7 +1637,7 @@
     <t xml:space="preserve">4.97661638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0151948928833</t>
+    <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
     <t xml:space="preserve">5.45884704589844</t>
@@ -1646,7 +1649,7 @@
     <t xml:space="preserve">5.49742555618286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28524446487427</t>
+    <t xml:space="preserve">5.28524398803711</t>
   </si>
   <si>
     <t xml:space="preserve">5.3045334815979</t>
@@ -1661,13 +1664,13 @@
     <t xml:space="preserve">4.86088132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84159183502197</t>
+    <t xml:space="preserve">4.84159231185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.93803834915161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73550128936768</t>
+    <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
     <t xml:space="preserve">4.70608854293823</t>
@@ -1740,9 +1743,6 @@
   </si>
   <si>
     <t xml:space="preserve">4.92178392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
     <t xml:space="preserve">4.83354520797729</t>
@@ -9376,7 +9376,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9428,7 +9428,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9454,7 +9454,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9480,7 +9480,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9506,7 +9506,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9532,7 +9532,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9558,7 +9558,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9584,7 +9584,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9610,7 +9610,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9688,7 +9688,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9714,7 +9714,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9792,7 +9792,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G273" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9818,7 +9818,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9870,7 +9870,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G277" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9922,7 +9922,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9948,7 +9948,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9974,7 +9974,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G280" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10052,7 +10052,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10078,7 +10078,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10130,7 +10130,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G286" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10156,7 +10156,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10208,7 +10208,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10286,7 +10286,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G292" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10312,7 +10312,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10364,7 +10364,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10416,7 +10416,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G297" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10442,7 +10442,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10494,7 +10494,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10546,7 +10546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10598,7 +10598,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10624,7 +10624,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10702,7 +10702,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10806,7 +10806,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G312" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10858,7 +10858,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G314" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10884,7 +10884,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10910,7 +10910,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G316" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10936,7 +10936,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10962,7 +10962,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G318" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -10988,7 +10988,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11040,7 +11040,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11066,7 +11066,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11092,7 +11092,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G323" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11144,7 +11144,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G325" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11170,7 +11170,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G326" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11196,7 +11196,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11222,7 +11222,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11352,7 +11352,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11378,7 +11378,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11404,7 +11404,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11508,7 +11508,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11534,7 +11534,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11560,7 +11560,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11586,7 +11586,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11846,7 +11846,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11872,7 +11872,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11898,7 +11898,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G354" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11924,7 +11924,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11950,7 +11950,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G356" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11976,7 +11976,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12002,7 +12002,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12028,7 +12028,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12314,7 +12314,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15330,7 +15330,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15382,7 +15382,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16552,7 +16552,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G533" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16578,7 +16578,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16682,7 +16682,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16864,7 +16864,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16890,7 +16890,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16916,7 +16916,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17020,7 +17020,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17046,7 +17046,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17306,7 +17306,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17384,7 +17384,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17410,7 +17410,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17436,7 +17436,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17956,7 +17956,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18372,7 +18372,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18398,7 +18398,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18788,7 +18788,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19022,7 +19022,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19152,7 +19152,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G633" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G647" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19568,7 +19568,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19594,7 +19594,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19620,7 +19620,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19646,7 +19646,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19672,7 +19672,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19880,7 +19880,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19906,7 +19906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19958,7 +19958,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20244,7 +20244,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20270,7 +20270,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20764,7 +20764,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20790,7 +20790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -26536,7 +26536,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G917" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26562,7 +26562,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G918" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26744,7 +26744,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G925" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27030,7 +27030,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G936" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27056,7 +27056,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27134,7 +27134,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G940" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27160,7 +27160,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G941" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27186,7 +27186,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G942" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27212,7 +27212,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G943" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27238,7 +27238,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G944" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27264,7 +27264,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G945" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27290,7 +27290,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G946" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27316,7 +27316,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27342,7 +27342,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G948" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27368,7 +27368,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27394,7 +27394,7 @@
         <v>3.5</v>
       </c>
       <c r="G950" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27420,7 +27420,7 @@
         <v>3.5</v>
       </c>
       <c r="G951" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27446,7 +27446,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27472,7 +27472,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G953" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27498,7 +27498,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27524,7 +27524,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G955" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27550,7 +27550,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G956" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27576,7 +27576,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G957" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27602,7 +27602,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G958" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27628,7 +27628,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G959" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27654,7 +27654,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G960" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27680,7 +27680,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G961" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27706,7 +27706,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G962" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27732,7 +27732,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G963" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27758,7 +27758,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G964" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27784,7 +27784,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27810,7 +27810,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G966" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27836,7 +27836,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G967" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27862,7 +27862,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G968" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27888,7 +27888,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G969" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27914,7 +27914,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27940,7 +27940,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G971" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27966,7 +27966,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G972" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27992,7 +27992,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G973" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28018,7 +28018,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G974" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28044,7 +28044,7 @@
         <v>3</v>
       </c>
       <c r="G975" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28070,7 +28070,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G976" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28096,7 +28096,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G977" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28122,7 +28122,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G978" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28148,7 +28148,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G979" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28174,7 +28174,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G980" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28200,7 +28200,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G981" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28226,7 +28226,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G982" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28252,7 +28252,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G983" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28278,7 +28278,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G984" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28304,7 +28304,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G985" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28330,7 +28330,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G986" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28356,7 +28356,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G987" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28382,7 +28382,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G988" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28408,7 +28408,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G989" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28434,7 +28434,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G990" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28460,7 +28460,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G991" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28486,7 +28486,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G992" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28512,7 +28512,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28538,7 +28538,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G994" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28564,7 +28564,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G995" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28590,7 +28590,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G996" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28616,7 +28616,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G997" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28642,7 +28642,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G998" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28668,7 +28668,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G999" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28694,7 +28694,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1000" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28720,7 +28720,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1001" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28746,7 +28746,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1002" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28772,7 +28772,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1003" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28798,7 +28798,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1004" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28824,7 +28824,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1005" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28850,7 +28850,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28876,7 +28876,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1007" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28902,7 +28902,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1008" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28928,7 +28928,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28954,7 +28954,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28980,7 +28980,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1011" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29006,7 +29006,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29032,7 +29032,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1013" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29058,7 +29058,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29084,7 +29084,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1015" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29110,7 +29110,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1016" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29136,7 +29136,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1017" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29162,7 +29162,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1018" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29188,7 +29188,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1019" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29214,7 +29214,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1020" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29240,7 +29240,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1021" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29266,7 +29266,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1022" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29292,7 +29292,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1023" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29318,7 +29318,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1024" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29344,7 +29344,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1025" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29370,7 +29370,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1026" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29396,7 +29396,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1027" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29422,7 +29422,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1028" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29448,7 +29448,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1029" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29474,7 +29474,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1030" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29500,7 +29500,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1031" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29526,7 +29526,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1032" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29552,7 +29552,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1033" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29578,7 +29578,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1034" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29604,7 +29604,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1035" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29630,7 +29630,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1036" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29656,7 +29656,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1037" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29682,7 +29682,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1038" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29708,7 +29708,7 @@
         <v>3</v>
       </c>
       <c r="G1039" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29734,7 +29734,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1040" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29760,7 +29760,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1041" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29786,7 +29786,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29812,7 +29812,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1043" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29838,7 +29838,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1044" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29864,7 +29864,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1045" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29890,7 +29890,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1046" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29916,7 +29916,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1047" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29942,7 +29942,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1048" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29968,7 +29968,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1049" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29994,7 +29994,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1050" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30020,7 +30020,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1051" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30046,7 +30046,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1052" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30072,7 +30072,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1053" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30098,7 +30098,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1054" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30124,7 +30124,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1055" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30150,7 +30150,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1056" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30176,7 +30176,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1057" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30202,7 +30202,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1058" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30228,7 +30228,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1059" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30254,7 +30254,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1060" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30280,7 +30280,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1061" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30306,7 +30306,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1062" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30332,7 +30332,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1063" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30358,7 +30358,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30384,7 +30384,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1065" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30410,7 +30410,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1066" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30436,7 +30436,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1067" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30462,7 +30462,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1068" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30488,7 +30488,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1069" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30514,7 +30514,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1070" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30540,7 +30540,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1071" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30566,7 +30566,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1072" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30592,7 +30592,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1073" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30618,7 +30618,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1074" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30644,7 +30644,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1075" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30670,7 +30670,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30696,7 +30696,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1077" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30722,7 +30722,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1078" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30748,7 +30748,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1079" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30774,7 +30774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1080" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30800,7 +30800,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1081" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30826,7 +30826,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1082" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30852,7 +30852,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30878,7 +30878,7 @@
         <v>2.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30904,7 +30904,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1085" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30930,7 +30930,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1086" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30956,7 +30956,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1087" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30982,7 +30982,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1088" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31008,7 +31008,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31034,7 +31034,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1090" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31060,7 +31060,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31086,7 +31086,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1092" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31112,7 +31112,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1093" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31138,7 +31138,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1094" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31164,7 +31164,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1095" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31190,7 +31190,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1096" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31216,7 +31216,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1097" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31242,7 +31242,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1098" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31268,7 +31268,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31294,7 +31294,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1100" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31320,7 +31320,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1101" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31346,7 +31346,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1102" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31372,7 +31372,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1103" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31398,7 +31398,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1104" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31424,7 +31424,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1105" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31450,7 +31450,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1106" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31476,7 +31476,7 @@
         <v>2.5</v>
       </c>
       <c r="G1107" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31502,7 +31502,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1108" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31528,7 +31528,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1109" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31554,7 +31554,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1110" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31580,7 +31580,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1111" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31606,7 +31606,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1112" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31632,7 +31632,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31658,7 +31658,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1114" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31684,7 +31684,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31710,7 +31710,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1116" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31736,7 +31736,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1117" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31762,7 +31762,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1118" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31788,7 +31788,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1119" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31814,7 +31814,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1120" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31840,7 +31840,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31866,7 +31866,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1122" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31892,7 +31892,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1123" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31918,7 +31918,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1124" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31944,7 +31944,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1125" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31970,7 +31970,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1126" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31996,7 +31996,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1127" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32022,7 +32022,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1128" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32048,7 +32048,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1129" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32074,7 +32074,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1130" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32100,7 +32100,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1131" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32126,7 +32126,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1132" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32152,7 +32152,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1133" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32178,7 +32178,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1134" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32204,7 +32204,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32230,7 +32230,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1136" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32256,7 +32256,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1137" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32282,7 +32282,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1138" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32308,7 +32308,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32334,7 +32334,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1140" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32360,7 +32360,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1141" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32386,7 +32386,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32412,7 +32412,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1143" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32438,7 +32438,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1144" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32464,7 +32464,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1145" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32490,7 +32490,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1146" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32516,7 +32516,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1147" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32542,7 +32542,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1148" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32568,7 +32568,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32594,7 +32594,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1150" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32620,7 +32620,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32646,7 +32646,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1152" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32672,7 +32672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1153" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32698,7 +32698,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1154" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32724,7 +32724,7 @@
         <v>2.25</v>
       </c>
       <c r="G1155" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32750,7 +32750,7 @@
         <v>2.25</v>
       </c>
       <c r="G1156" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32776,7 +32776,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1157" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32802,7 +32802,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32828,7 +32828,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1159" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32854,7 +32854,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1160" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32880,7 +32880,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1161" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32906,7 +32906,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1162" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32932,7 +32932,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32958,7 +32958,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1164" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32984,7 +32984,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1165" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33010,7 +33010,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1166" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33036,7 +33036,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1167" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33062,7 +33062,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1168" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33088,7 +33088,7 @@
         <v>2</v>
       </c>
       <c r="G1169" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33114,7 +33114,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1170" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33140,7 +33140,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1171" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33166,7 +33166,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1172" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33192,7 +33192,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1173" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33218,7 +33218,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1174" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33244,7 +33244,7 @@
         <v>2.25</v>
       </c>
       <c r="G1175" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33270,7 +33270,7 @@
         <v>2.25</v>
       </c>
       <c r="G1176" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33296,7 +33296,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1177" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33322,7 +33322,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1178" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33348,7 +33348,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1179" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33374,7 +33374,7 @@
         <v>2.25</v>
       </c>
       <c r="G1180" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33400,7 +33400,7 @@
         <v>2.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33426,7 +33426,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1182" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33452,7 +33452,7 @@
         <v>2.25</v>
       </c>
       <c r="G1183" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33478,7 +33478,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1184" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33504,7 +33504,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1185" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33530,7 +33530,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1186" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33556,7 +33556,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1187" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33582,7 +33582,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1188" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33608,7 +33608,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1189" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33634,7 +33634,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1190" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33660,7 +33660,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33686,7 +33686,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1192" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33712,7 +33712,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33738,7 +33738,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1194" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33764,7 +33764,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1195" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33790,7 +33790,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1196" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33816,7 +33816,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1197" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33842,7 +33842,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1198" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33868,7 +33868,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1199" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33894,7 +33894,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1200" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33920,7 +33920,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33946,7 +33946,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33972,7 +33972,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33998,7 +33998,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1204" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34024,7 +34024,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1205" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34050,7 +34050,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34076,7 +34076,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34102,7 +34102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1208" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34128,7 +34128,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1209" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34154,7 +34154,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34180,7 +34180,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1211" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34206,7 +34206,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1212" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34232,7 +34232,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34258,7 +34258,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1214" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34284,7 +34284,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1215" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34310,7 +34310,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34336,7 +34336,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1217" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34362,7 +34362,7 @@
         <v>2.25</v>
       </c>
       <c r="G1218" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34388,7 +34388,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34414,7 +34414,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1220" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34440,7 +34440,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34466,7 +34466,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34492,7 +34492,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1223" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34518,7 +34518,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1224" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34544,7 +34544,7 @@
         <v>2.25</v>
       </c>
       <c r="G1225" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34570,7 +34570,7 @@
         <v>2.25</v>
       </c>
       <c r="G1226" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34596,7 +34596,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34622,7 +34622,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1228" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34648,7 +34648,7 @@
         <v>2.25</v>
       </c>
       <c r="G1229" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34674,7 +34674,7 @@
         <v>2.25</v>
       </c>
       <c r="G1230" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34700,7 +34700,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1231" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34726,7 +34726,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34752,7 +34752,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34778,7 +34778,7 @@
         <v>2.25</v>
       </c>
       <c r="G1234" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34804,7 +34804,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1235" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34830,7 +34830,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1236" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34856,7 +34856,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34882,7 +34882,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1238" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34908,7 +34908,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34934,7 +34934,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1240" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34960,7 +34960,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1241" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34986,7 +34986,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1242" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35012,7 +35012,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1243" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35038,7 +35038,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1244" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35064,7 +35064,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1245" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35090,7 +35090,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1246" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35116,7 +35116,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1247" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35142,7 +35142,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35168,7 +35168,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1249" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35194,7 +35194,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1250" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35220,7 +35220,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1251" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35246,7 +35246,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1252" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35272,7 +35272,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1253" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35298,7 +35298,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1254" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35324,7 +35324,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35350,7 +35350,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1256" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35376,7 +35376,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1257" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35402,7 +35402,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35428,7 +35428,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1259" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35454,7 +35454,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1260" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35480,7 +35480,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1261" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35506,7 +35506,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1262" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35532,7 +35532,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1263" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35558,7 +35558,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1264" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35584,7 +35584,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1265" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35610,7 +35610,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1266" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35636,7 +35636,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1267" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35662,7 +35662,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1268" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35688,7 +35688,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35714,7 +35714,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1270" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35740,7 +35740,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1271" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35766,7 +35766,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35792,7 +35792,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1273" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35818,7 +35818,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1274" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35844,7 +35844,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1275" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35870,7 +35870,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1276" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35896,7 +35896,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1277" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35922,7 +35922,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1278" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35948,7 +35948,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1279" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35974,7 +35974,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1280" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36000,7 +36000,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1281" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36026,7 +36026,7 @@
         <v>2.75</v>
       </c>
       <c r="G1282" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36052,7 +36052,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1283" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36078,7 +36078,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1284" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36104,7 +36104,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1285" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36130,7 +36130,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1286" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36156,7 +36156,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1287" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36182,7 +36182,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1288" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36208,7 +36208,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1289" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36234,7 +36234,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1290" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36260,7 +36260,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1291" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36286,7 +36286,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1292" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36312,7 +36312,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1293" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36338,7 +36338,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1294" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36364,7 +36364,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1295" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36390,7 +36390,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36416,7 +36416,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1297" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36442,7 +36442,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1298" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36468,7 +36468,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1299" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36494,7 +36494,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1300" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36520,7 +36520,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1301" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36546,7 +36546,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1302" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36572,7 +36572,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1303" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36598,7 +36598,7 @@
         <v>2.75</v>
       </c>
       <c r="G1304" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36624,7 +36624,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1305" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36650,7 +36650,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36676,7 +36676,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1307" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36702,7 +36702,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1308" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36728,7 +36728,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1309" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36754,7 +36754,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1310" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36780,7 +36780,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1311" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36806,7 +36806,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1312" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36832,7 +36832,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1313" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36858,7 +36858,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1314" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36884,7 +36884,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36910,7 +36910,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36936,7 +36936,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36962,7 +36962,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1318" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36988,7 +36988,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1319" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37014,7 +37014,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37040,7 +37040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1321" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37066,7 +37066,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37092,7 +37092,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1323" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37118,7 +37118,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1324" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37144,7 +37144,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1325" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37170,7 +37170,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1326" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37196,7 +37196,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37222,7 +37222,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1328" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37248,7 +37248,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1329" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37274,7 +37274,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1330" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37300,7 +37300,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37326,7 +37326,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1332" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37352,7 +37352,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1333" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37378,7 +37378,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1334" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37404,7 +37404,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1335" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37430,7 +37430,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1336" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37456,7 +37456,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37482,7 +37482,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1338" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37508,7 +37508,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37534,7 +37534,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1340" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37560,7 +37560,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1341" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37586,7 +37586,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1342" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37612,7 +37612,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1343" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37638,7 +37638,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1344" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37664,7 +37664,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37690,7 +37690,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1346" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37716,7 +37716,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1347" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37742,7 +37742,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37768,7 +37768,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1349" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37794,7 +37794,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1350" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37820,7 +37820,7 @@
         <v>3.25</v>
       </c>
       <c r="G1351" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37846,7 +37846,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37872,7 +37872,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1353" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37898,7 +37898,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37924,7 +37924,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37950,7 +37950,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1356" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37976,7 +37976,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1357" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38002,7 +38002,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38028,7 +38028,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1359" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38054,7 +38054,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1360" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38080,7 +38080,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1361" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38106,7 +38106,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1362" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38132,7 +38132,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1363" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38158,7 +38158,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38184,7 +38184,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1365" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38210,7 +38210,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1366" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38236,7 +38236,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1367" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38262,7 +38262,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1368" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38288,7 +38288,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1369" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38314,7 +38314,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1370" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38340,7 +38340,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1371" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38366,7 +38366,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1372" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38392,7 +38392,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1373" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38418,7 +38418,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1374" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38444,7 +38444,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1375" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38470,7 +38470,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1376" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38496,7 +38496,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1377" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38522,7 +38522,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38548,7 +38548,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38574,7 +38574,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1380" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38600,7 +38600,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38626,7 +38626,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1382" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38652,7 +38652,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1383" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38678,7 +38678,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1384" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38704,7 +38704,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38730,7 +38730,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1386" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38756,7 +38756,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1387" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38782,7 +38782,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1388" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38808,7 +38808,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1389" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38834,7 +38834,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1390" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38860,7 +38860,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1391" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38886,7 +38886,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1392" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38912,7 +38912,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38938,7 +38938,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1394" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38964,7 +38964,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1395" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38990,7 +38990,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1396" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39016,7 +39016,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1397" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39042,7 +39042,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1398" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39068,7 +39068,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1399" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39094,7 +39094,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1400" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39120,7 +39120,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1401" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39146,7 +39146,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1402" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39172,7 +39172,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39198,7 +39198,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1404" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39224,7 +39224,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1405" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39250,7 +39250,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1406" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39276,7 +39276,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1407" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39302,7 +39302,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1408" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39328,7 +39328,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1409" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39354,7 +39354,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39380,7 +39380,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39406,7 +39406,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1412" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39432,7 +39432,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1413" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39458,7 +39458,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1414" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39484,7 +39484,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39510,7 +39510,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39536,7 +39536,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1417" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39562,7 +39562,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1418" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39588,7 +39588,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1419" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39614,7 +39614,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1420" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39640,7 +39640,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39666,7 +39666,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39692,7 +39692,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39718,7 +39718,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1424" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39744,7 +39744,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1425" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39770,7 +39770,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1426" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39796,7 +39796,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1427" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39822,7 +39822,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1428" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39848,7 +39848,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1429" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39874,7 +39874,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1430" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39900,7 +39900,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1431" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39926,7 +39926,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1432" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39952,7 +39952,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1433" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39978,7 +39978,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1434" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40004,7 +40004,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1435" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40030,7 +40030,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1436" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40056,7 +40056,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40082,7 +40082,7 @@
         <v>3</v>
       </c>
       <c r="G1438" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40108,7 +40108,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1439" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40134,7 +40134,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1440" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40160,7 +40160,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1441" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40186,7 +40186,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1442" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40212,7 +40212,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1443" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40238,7 +40238,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1444" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40264,7 +40264,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1445" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40290,7 +40290,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1446" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40316,7 +40316,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1447" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40342,7 +40342,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1448" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40368,7 +40368,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1449" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40394,7 +40394,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40420,7 +40420,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1451" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40446,7 +40446,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40472,7 +40472,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1453" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40498,7 +40498,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1454" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40524,7 +40524,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1455" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40550,7 +40550,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1456" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40576,7 +40576,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1457" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40602,7 +40602,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1458" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40628,7 +40628,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1459" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40654,7 +40654,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1460" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40680,7 +40680,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1461" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40706,7 +40706,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1462" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40732,7 +40732,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1463" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40758,7 +40758,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40784,7 +40784,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40810,7 +40810,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1466" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40836,7 +40836,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1467" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40862,7 +40862,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40888,7 +40888,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1469" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40914,7 +40914,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1470" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40940,7 +40940,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1471" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40966,7 +40966,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40992,7 +40992,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41018,7 +41018,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41044,7 +41044,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1475" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41070,7 +41070,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1476" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41096,7 +41096,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1477" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41122,7 +41122,7 @@
         <v>3</v>
       </c>
       <c r="G1478" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41148,7 +41148,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1479" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41174,7 +41174,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1480" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41200,7 +41200,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1481" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41226,7 +41226,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1482" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41252,7 +41252,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1483" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41278,7 +41278,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1484" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41304,7 +41304,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41330,7 +41330,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1486" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41356,7 +41356,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1487" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41382,7 +41382,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1488" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41408,7 +41408,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1489" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41434,7 +41434,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1490" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41460,7 +41460,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1491" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41486,7 +41486,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1492" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41512,7 +41512,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1493" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41538,7 +41538,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41564,7 +41564,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1495" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41590,7 +41590,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1496" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41616,7 +41616,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1497" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41642,7 +41642,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1498" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41668,7 +41668,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1499" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41694,7 +41694,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1500" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41720,7 +41720,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1501" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41746,7 +41746,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1502" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41772,7 +41772,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1503" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41798,7 +41798,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1504" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41824,7 +41824,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1505" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41850,7 +41850,7 @@
         <v>3.25</v>
       </c>
       <c r="G1506" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41876,7 +41876,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1507" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41902,7 +41902,7 @@
         <v>3.25</v>
       </c>
       <c r="G1508" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41928,7 +41928,7 @@
         <v>3.25</v>
       </c>
       <c r="G1509" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41954,7 +41954,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1510" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41980,7 +41980,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1511" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42006,7 +42006,7 @@
         <v>3.25</v>
       </c>
       <c r="G1512" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42032,7 +42032,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1513" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42058,7 +42058,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1514" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42084,7 +42084,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1515" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42110,7 +42110,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1516" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42136,7 +42136,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1517" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42162,7 +42162,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42188,7 +42188,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1519" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42214,7 +42214,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42240,7 +42240,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42266,7 +42266,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42292,7 +42292,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42318,7 +42318,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1524" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42344,7 +42344,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1525" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42370,7 +42370,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1526" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42474,7 +42474,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1530" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42500,7 +42500,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1531" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42552,7 +42552,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1533" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42578,7 +42578,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1534" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42604,7 +42604,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1535" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42630,7 +42630,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1536" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42656,7 +42656,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42682,7 +42682,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1538" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42708,7 +42708,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42734,7 +42734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1540" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42760,7 +42760,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1541" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42786,7 +42786,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42812,7 +42812,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1543" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42838,7 +42838,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1544" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42864,7 +42864,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1545" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42890,7 +42890,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1546" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42916,7 +42916,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1547" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42942,7 +42942,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1548" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42968,7 +42968,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1549" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42994,7 +42994,7 @@
         <v>4.5</v>
       </c>
       <c r="G1550" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43020,7 +43020,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1551" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43046,7 +43046,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43072,7 +43072,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1553" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43098,7 +43098,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1554" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43124,7 +43124,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1555" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43150,7 +43150,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1556" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43176,7 +43176,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1557" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43202,7 +43202,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1558" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43228,7 +43228,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1559" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43254,7 +43254,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1560" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43280,7 +43280,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43306,7 +43306,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43332,7 +43332,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1563" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43358,7 +43358,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1564" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43384,7 +43384,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1565" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43410,7 +43410,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1566" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43436,7 +43436,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1567" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43462,7 +43462,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1568" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43488,7 +43488,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1569" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43514,7 +43514,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1570" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43540,7 +43540,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43566,7 +43566,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1572" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43592,7 +43592,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1573" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43618,7 +43618,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1574" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43644,7 +43644,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1575" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43670,7 +43670,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1576" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43696,7 +43696,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1577" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43722,7 +43722,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1578" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43748,7 +43748,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1579" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43774,7 +43774,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1580" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43800,7 +43800,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1581" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43826,7 +43826,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1582" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43852,7 +43852,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1583" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43878,7 +43878,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43904,7 +43904,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43930,7 +43930,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1586" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43956,7 +43956,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1587" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43982,7 +43982,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1588" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44008,7 +44008,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44034,7 +44034,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1590" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44060,7 +44060,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1591" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44086,7 +44086,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1592" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44112,7 +44112,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1593" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44138,7 +44138,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1594" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44164,7 +44164,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1595" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44190,7 +44190,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44216,7 +44216,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1597" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44242,7 +44242,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1598" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44268,7 +44268,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1599" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44294,7 +44294,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1600" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44320,7 +44320,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1601" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44346,7 +44346,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1602" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44372,7 +44372,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1603" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44398,7 +44398,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1604" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44424,7 +44424,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1605" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44450,7 +44450,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1606" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44476,7 +44476,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1607" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44502,7 +44502,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1608" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44528,7 +44528,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1609" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44554,7 +44554,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1610" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44580,7 +44580,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1611" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44606,7 +44606,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1612" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44632,7 +44632,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1613" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44658,7 +44658,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1614" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44684,7 +44684,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1615" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44710,7 +44710,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1616" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44736,7 +44736,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1617" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44762,7 +44762,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44788,7 +44788,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44814,7 +44814,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1620" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44840,7 +44840,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1621" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44866,7 +44866,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1622" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44892,7 +44892,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1623" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44918,7 +44918,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1624" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44944,7 +44944,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44970,7 +44970,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44996,7 +44996,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1627" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45022,7 +45022,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45048,7 +45048,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45074,7 +45074,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1630" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45100,7 +45100,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1631" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45126,7 +45126,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45152,7 +45152,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1633" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45178,7 +45178,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1634" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45204,7 +45204,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45230,7 +45230,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45256,7 +45256,7 @@
         <v>5.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45282,7 +45282,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1638" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45308,7 +45308,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1639" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45334,7 +45334,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45360,7 +45360,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1641" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45386,7 +45386,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1642" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45412,7 +45412,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1643" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45438,7 +45438,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1644" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45464,7 +45464,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45490,7 +45490,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1646" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45516,7 +45516,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1647" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45542,7 +45542,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1648" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45568,7 +45568,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1649" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45594,7 +45594,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1650" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45620,7 +45620,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1651" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45646,7 +45646,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1652" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45672,7 +45672,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1653" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45698,7 +45698,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1654" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45724,7 +45724,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1655" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45750,7 +45750,7 @@
         <v>5</v>
       </c>
       <c r="G1656" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45776,7 +45776,7 @@
         <v>5</v>
       </c>
       <c r="G1657" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45802,7 +45802,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1658" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45828,7 +45828,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1659" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45854,7 +45854,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1660" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45880,7 +45880,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1661" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45906,7 +45906,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1662" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45932,7 +45932,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1663" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45958,7 +45958,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1664" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45984,7 +45984,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1665" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46010,7 +46010,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46036,7 +46036,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1667" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46062,7 +46062,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1668" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46088,7 +46088,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1669" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46114,7 +46114,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1670" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46140,7 +46140,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1671" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46166,7 +46166,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1672" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46192,7 +46192,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1673" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46218,7 +46218,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1674" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46244,7 +46244,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1675" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46270,7 +46270,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1676" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46296,7 +46296,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1677" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46322,7 +46322,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1678" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46348,7 +46348,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1679" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46374,7 +46374,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1680" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46400,7 +46400,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1681" t="s">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46426,7 +46426,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46452,7 +46452,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46478,7 +46478,7 @@
         <v>5</v>
       </c>
       <c r="G1684" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46504,7 +46504,7 @@
         <v>5</v>
       </c>
       <c r="G1685" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46530,7 +46530,7 @@
         <v>5</v>
       </c>
       <c r="G1686" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46582,7 +46582,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1688" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46608,7 +46608,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1689" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46712,7 +46712,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1693" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46790,7 +46790,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1696" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46972,7 +46972,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1703" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46998,7 +46998,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1704" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47024,7 +47024,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1705" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47050,7 +47050,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1706" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47180,7 +47180,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1711" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47388,7 +47388,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1719" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47492,7 +47492,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1723" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47518,7 +47518,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1724" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47778,7 +47778,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1734" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47804,7 +47804,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1735" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47908,7 +47908,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1739" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48012,7 +48012,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1743" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48038,7 +48038,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1744" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48116,7 +48116,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1747" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49520,7 +49520,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1801" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50144,7 +50144,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1825" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50170,7 +50170,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1826" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50222,7 +50222,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1828" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50248,7 +50248,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1829" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50274,7 +50274,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1830" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50300,7 +50300,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50326,7 +50326,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1832" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50482,7 +50482,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50508,7 +50508,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1839" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50560,7 +50560,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1841" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50612,7 +50612,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1843" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50664,7 +50664,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1845" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -67702,7 +67702,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6686574074</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>3102</v>
@@ -67723,6 +67723,32 @@
         <v>748</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.5501273148</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282085418701</t>
+    <t xml:space="preserve">3.87282109260559</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
@@ -50,184 +50,184 @@
     <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86577653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8640148639679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652358055115</t>
+    <t xml:space="preserve">3.86577677726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401510238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652381896973</t>
   </si>
   <si>
     <t xml:space="preserve">3.74249410629272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79532885551453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771759033203</t>
+    <t xml:space="preserve">3.79532957077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771782875061</t>
   </si>
   <si>
     <t xml:space="preserve">3.62977886199951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67733120918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443539619446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66324138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64386892318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712420463562</t>
+    <t xml:space="preserve">3.67733025550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443587303162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.663241147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6438684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712396621704</t>
   </si>
   <si>
     <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68965911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66676378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60336112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53995895385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6491527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65267395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65091276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210772514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431541442871</t>
+    <t xml:space="preserve">3.68965888023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66676330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336136817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637668609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6156895160675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915204048157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65267443656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65091300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210724830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455513954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431493759155</t>
   </si>
   <si>
     <t xml:space="preserve">3.751300573349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81294083595276</t>
+    <t xml:space="preserve">3.8129415512085</t>
   </si>
   <si>
     <t xml:space="preserve">3.79356861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86225414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81470227241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941915512085</t>
+    <t xml:space="preserve">3.86225438117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941963195801</t>
   </si>
   <si>
     <t xml:space="preserve">3.73368787765503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73721075057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255373954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.721360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538920402527</t>
+    <t xml:space="preserve">3.73721051216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192715644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72135996818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891207695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538944244385</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953866004944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74601697921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73016619682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846487045288</t>
+    <t xml:space="preserve">3.74601650238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016595840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846439361572</t>
   </si>
   <si>
     <t xml:space="preserve">3.68613624572754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72488260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350826263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91861152648926</t>
+    <t xml:space="preserve">3.72488212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350850105286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383429527283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9186110496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446230888367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98377537727356</t>
+    <t xml:space="preserve">3.98377513885498</t>
   </si>
   <si>
     <t xml:space="preserve">3.9432680606842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91508936882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9855363368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91332840919495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395499229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96088027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219427108765</t>
+    <t xml:space="preserve">3.91508913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98553586006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91332817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395475387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96087956428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219403266907</t>
   </si>
   <si>
     <t xml:space="preserve">3.93622279167175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92741751670837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338828086853</t>
+    <t xml:space="preserve">3.92741727828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338780403137</t>
   </si>
   <si>
     <t xml:space="preserve">3.99916791915894</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">3.97220754623413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759938240051</t>
+    <t xml:space="preserve">3.9901807308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759985923767</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98299217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95423364639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93626046180725</t>
+    <t xml:space="preserve">3.98299145698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95423340797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625974655151</t>
   </si>
   <si>
     <t xml:space="preserve">3.88233852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92727255821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367839813232</t>
+    <t xml:space="preserve">3.9272723197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367792129517</t>
   </si>
   <si>
     <t xml:space="preserve">3.83560681343079</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">3.89132499694824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86436438560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81942963600159</t>
+    <t xml:space="preserve">3.86436486244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256647109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81943011283875</t>
   </si>
   <si>
     <t xml:space="preserve">3.70799255371094</t>
@@ -290,25 +290,25 @@
     <t xml:space="preserve">3.59475779533386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273121833801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67923426628113</t>
+    <t xml:space="preserve">3.61273169517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67923450469971</t>
   </si>
   <si>
     <t xml:space="preserve">3.63070511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62171864509583</t>
+    <t xml:space="preserve">3.62171840667725</t>
   </si>
   <si>
     <t xml:space="preserve">3.65766620635986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63789486885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103218078613</t>
+    <t xml:space="preserve">3.63789463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103241920471</t>
   </si>
   <si>
     <t xml:space="preserve">3.57318925857544</t>
@@ -323,34 +323,34 @@
     <t xml:space="preserve">3.64688158035278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69181632995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675084114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652098655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325388908386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616230010986</t>
+    <t xml:space="preserve">3.69181609153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652170181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80325365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616182327271</t>
   </si>
   <si>
     <t xml:space="preserve">3.8176326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81044268608093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246926307678</t>
+    <t xml:space="preserve">3.81044292449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246950149536</t>
   </si>
   <si>
     <t xml:space="preserve">3.74394011497498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77449560165405</t>
+    <t xml:space="preserve">3.77449512481689</t>
   </si>
   <si>
     <t xml:space="preserve">3.79067206382751</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">3.77629327774048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78887414932251</t>
+    <t xml:space="preserve">3.78887462615967</t>
   </si>
   <si>
     <t xml:space="preserve">3.74753499031067</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80145621299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7331554889679</t>
+    <t xml:space="preserve">3.80145597457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
   </si>
   <si>
     <t xml:space="preserve">3.78348231315613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72416973114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090096473694</t>
+    <t xml:space="preserve">3.72416925430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77090120315552</t>
   </si>
   <si>
     <t xml:space="preserve">3.72057390213013</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">3.76371145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72596597671509</t>
+    <t xml:space="preserve">3.72596621513367</t>
   </si>
   <si>
     <t xml:space="preserve">3.70978951454163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70260047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854780197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956109046936</t>
+    <t xml:space="preserve">3.70260071754456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854756355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956132888794</t>
   </si>
   <si>
     <t xml:space="preserve">3.72237181663513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72776341438293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292730331421</t>
+    <t xml:space="preserve">3.72776365280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292682647705</t>
   </si>
   <si>
     <t xml:space="preserve">3.75831913948059</t>
@@ -422,43 +422,40 @@
     <t xml:space="preserve">3.68462657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69361352920532</t>
+    <t xml:space="preserve">3.69361329078674</t>
   </si>
   <si>
     <t xml:space="preserve">3.66485571861267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68822145462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135828971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338510513306</t>
+    <t xml:space="preserve">3.68822121620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338486671448</t>
   </si>
   <si>
     <t xml:space="preserve">3.78168535232544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83380913734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224083900452</t>
+    <t xml:space="preserve">3.83380842208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224060058594</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82661914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841753959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547535896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446278572083</t>
+    <t xml:space="preserve">3.82661938667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82841730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547583580017</t>
   </si>
   <si>
     <t xml:space="preserve">3.92188024520874</t>
@@ -467,34 +464,34 @@
     <t xml:space="preserve">3.90031218528748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87335085868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639120101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8374035358429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87514877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165205955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929913520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243573188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98119401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9793963432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413548469543</t>
+    <t xml:space="preserve">3.87335133552551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639096260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87514853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94165229797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929937362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243620872498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98119425773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97939610481262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413572311401</t>
   </si>
   <si>
     <t xml:space="preserve">3.9488410949707</t>
@@ -506,19 +503,19 @@
     <t xml:space="preserve">4.01534461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0207371711731</t>
+    <t xml:space="preserve">4.02073669433594</t>
   </si>
   <si>
     <t xml:space="preserve">4.00815486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04050731658936</t>
+    <t xml:space="preserve">4.04050779342651</t>
   </si>
   <si>
     <t xml:space="preserve">4.05309009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01714134216309</t>
+    <t xml:space="preserve">4.01714086532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207609176636</t>
@@ -527,16 +524,16 @@
     <t xml:space="preserve">4.07106351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14295864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06926584243774</t>
+    <t xml:space="preserve">4.14295816421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06926536560059</t>
   </si>
   <si>
     <t xml:space="preserve">4.08903741836548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40357780456543</t>
+    <t xml:space="preserve">4.40357828140259</t>
   </si>
   <si>
     <t xml:space="preserve">4.37661743164062</t>
@@ -545,13 +542,13 @@
     <t xml:space="preserve">4.34606170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34785890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32808876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27236986160278</t>
+    <t xml:space="preserve">4.34785985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32808828353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27236938476562</t>
   </si>
   <si>
     <t xml:space="preserve">4.11599779129028</t>
@@ -563,22 +560,22 @@
     <t xml:space="preserve">3.9847891330719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04230546951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603132247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008328437805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828608512878</t>
+    <t xml:space="preserve">4.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828584671021</t>
   </si>
   <si>
     <t xml:space="preserve">3.94704437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93266487121582</t>
+    <t xml:space="preserve">3.9326651096344</t>
   </si>
   <si>
     <t xml:space="preserve">3.84099912643433</t>
@@ -587,7 +584,7 @@
     <t xml:space="preserve">3.86795878410339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90390729904175</t>
+    <t xml:space="preserve">3.90390682220459</t>
   </si>
   <si>
     <t xml:space="preserve">3.94524645805359</t>
@@ -596,67 +593,70 @@
     <t xml:space="preserve">3.9635968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99112153053284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194646835327</t>
+    <t xml:space="preserve">3.99112176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194670677185</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8901960849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87184643745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92689728736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12874603271484</t>
+    <t xml:space="preserve">3.94524693489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89019632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87184691429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689657211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.128746509552</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691164016724</t>
+    <t xml:space="preserve">4.12691116333008</t>
   </si>
   <si>
     <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05901575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03699636459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99479174613953</t>
+    <t xml:space="preserve">4.05901622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03699684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99479150772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.05351114273071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08287191390991</t>
+    <t xml:space="preserve">4.0828709602356</t>
   </si>
   <si>
     <t xml:space="preserve">4.03332662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07369661331177</t>
+    <t xml:space="preserve">4.07369565963745</t>
   </si>
   <si>
     <t xml:space="preserve">4.09204626083374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08103609085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534648895264</t>
+    <t xml:space="preserve">4.08103704452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534696578979</t>
   </si>
   <si>
     <t xml:space="preserve">4.09021139144897</t>
@@ -665,52 +665,52 @@
     <t xml:space="preserve">4.0626859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15260124206543</t>
+    <t xml:space="preserve">4.15260171890259</t>
   </si>
   <si>
     <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16544628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11039686203003</t>
+    <t xml:space="preserve">4.16544580459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11039638519287</t>
   </si>
   <si>
     <t xml:space="preserve">4.09388160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20948600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15443658828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1379222869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507581710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11957120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13608646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15076589584351</t>
+    <t xml:space="preserve">4.20948553085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1544361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13792181015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507677078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1195707321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13608598709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15076684951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.10305643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278671264648</t>
+    <t xml:space="preserve">4.17278623580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002639770508</t>
+    <t xml:space="preserve">4.07002592086792</t>
   </si>
   <si>
     <t xml:space="preserve">4.10122108459473</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">4.16911697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18379592895508</t>
+    <t xml:space="preserve">4.18379640579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.21132135391235</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01864719390869</t>
+    <t xml:space="preserve">4.01864671707153</t>
   </si>
   <si>
     <t xml:space="preserve">4.07920122146606</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">4.13241672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12140703201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11590147018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11773633956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14709615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14893102645874</t>
+    <t xml:space="preserve">4.12140655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11590194702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11773586273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14709663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1489315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.19113636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19297170639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662661552429</t>
+    <t xml:space="preserve">4.19297122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662613868713</t>
   </si>
   <si>
     <t xml:space="preserve">4.04433679580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98561668395996</t>
+    <t xml:space="preserve">3.98561644554138</t>
   </si>
   <si>
     <t xml:space="preserve">3.94341111183167</t>
@@ -791,49 +791,49 @@
     <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506194114685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772127151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00029706954956</t>
+    <t xml:space="preserve">4.04800653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726632118225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772103309631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0002965927124</t>
   </si>
   <si>
     <t xml:space="preserve">3.97277140617371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93790650367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99846124649048</t>
+    <t xml:space="preserve">3.93790698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846148490906</t>
   </si>
   <si>
     <t xml:space="preserve">4.04617166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88102173805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442128181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514595031738</t>
+    <t xml:space="preserve">3.88102149963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349631309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442175865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514642715454</t>
   </si>
   <si>
     <t xml:space="preserve">3.89937162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90854668617249</t>
+    <t xml:space="preserve">3.90854692459106</t>
   </si>
   <si>
     <t xml:space="preserve">3.93607139587402</t>
@@ -845,40 +845,40 @@
     <t xml:space="preserve">3.82597184181213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78927206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.807621717453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039480209351</t>
+    <t xml:space="preserve">3.78927183151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80762195587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039432525635</t>
   </si>
   <si>
     <t xml:space="preserve">4.04857444763184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03918075561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97342705726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9922137260437</t>
+    <t xml:space="preserve">4.03918123245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97342681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99221396446228</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403336524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827942848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91706657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616453170776</t>
+    <t xml:space="preserve">3.96403360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827966690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9170663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616477012634</t>
   </si>
   <si>
     <t xml:space="preserve">3.70101690292358</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63526272773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62586951255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52254176139832</t>
+    <t xml:space="preserve">3.63526296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62586903572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52254152297974</t>
   </si>
   <si>
     <t xml:space="preserve">3.42860722541809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770565986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35345983505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33467292785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37224626541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38163995742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45678734779358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46618103981018</t>
+    <t xml:space="preserve">3.28770542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35345959663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33467268943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37224650382996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3816397190094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45678758621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4661808013916</t>
   </si>
   <si>
     <t xml:space="preserve">3.36285281181335</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40042662620544</t>
+    <t xml:space="preserve">3.43800091743469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40042686462402</t>
   </si>
   <si>
     <t xml:space="preserve">3.4755744934082</t>
@@ -950,106 +950,106 @@
     <t xml:space="preserve">3.31588578224182</t>
   </si>
   <si>
+    <t xml:space="preserve">3.60708236694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56950879096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50375485420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65404987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48496794700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68223023414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5976893901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66344332695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58829569816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55072212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56011533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57890200614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6728367805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51314806938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70352864265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54921507835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62637186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58779335021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68423938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068566322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79997491836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81926417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83855319023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85784244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76139640808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72281789779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64566135406494</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950879096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50375485420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65404987335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68223023414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59768915176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647582054138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66344332695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58829569816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5507218837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193497657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56011533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57890224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6728367805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51314830780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70352864265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5492148399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62637186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58779358863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68423938751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068566322327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7999746799469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210715293884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81926417350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8385534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85784244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76139640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72281789779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64566111564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708284378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56850433349609</t>
+    <t xml:space="preserve">3.56850457191467</t>
   </si>
   <si>
     <t xml:space="preserve">3.52992582321167</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">3.47205829620361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51063680648804</t>
+    <t xml:space="preserve">3.51063656806946</t>
   </si>
   <si>
     <t xml:space="preserve">3.41419053077698</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916622161865</t>
+    <t xml:space="preserve">3.27916598320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06698489189148</t>
+    <t xml:space="preserve">3.0669846534729</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1106,19 +1106,19 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267108917236</t>
+    <t xml:space="preserve">2.91267085075378</t>
   </si>
   <si>
     <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7197790145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83551430702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97053861618042</t>
+    <t xml:space="preserve">2.71977877616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83551406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.970538854599</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">2.81622505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79693579673767</t>
+    <t xml:space="preserve">2.79693603515625</t>
   </si>
   <si>
     <t xml:space="preserve">2.75835704803467</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73906779289246</t>
+    <t xml:space="preserve">2.73906803131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.54617595672607</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">2.62333297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60404396057129</t>
+    <t xml:space="preserve">2.60404372215271</t>
   </si>
   <si>
     <t xml:space="preserve">2.5847544670105</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">2.50759768486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46901917457581</t>
+    <t xml:space="preserve">2.46901893615723</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16039204597473</t>
+    <t xml:space="preserve">2.16039180755615</t>
   </si>
   <si>
     <t xml:space="preserve">2.04465627670288</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648211479187</t>
+    <t xml:space="preserve">2.26648235321045</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044066429138</t>
+    <t xml:space="preserve">2.43044090270996</t>
   </si>
   <si>
     <t xml:space="preserve">2.27612709999084</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506110191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2279040813446</t>
+    <t xml:space="preserve">2.36292862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506086349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22790384292603</t>
   </si>
   <si>
     <t xml:space="preserve">2.24719309806824</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17968082427979</t>
+    <t xml:space="preserve">2.17968106269836</t>
   </si>
   <si>
     <t xml:space="preserve">2.18932557106018</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216902732849</t>
+    <t xml:space="preserve">2.11216878890991</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">2.15074706077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37257313728333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38221788406372</t>
+    <t xml:space="preserve">2.37257289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38221764564514</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409257888794</t>
+    <t xml:space="preserve">2.87409281730652</t>
   </si>
   <si>
     <t xml:space="preserve">2.66191124916077</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">2.64262199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59439897537231</t>
+    <t xml:space="preserve">2.59439921379089</t>
   </si>
   <si>
     <t xml:space="preserve">2.68120050430298</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">2.52688670158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51724195480347</t>
+    <t xml:space="preserve">2.51724219322205</t>
   </si>
   <si>
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013402938843</t>
+    <t xml:space="preserve">2.71013426780701</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">2.94160485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99947261810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98018312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96089386940002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03805088996887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16343092918396</t>
+    <t xml:space="preserve">2.99947237968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98018288612366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9608941078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03805112838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16343069076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">3.15378594398499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26952147483826</t>
+    <t xml:space="preserve">3.26952171325684</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">3.0766294002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01876163482666</t>
+    <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
     <t xml:space="preserve">3.05734014511108</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90302658081055</t>
+    <t xml:space="preserve">2.90302634239197</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373732566833</t>
@@ -1445,25 +1445,25 @@
     <t xml:space="preserve">3.59743809700012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67459487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71317315101624</t>
+    <t xml:space="preserve">3.67459464073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71317338943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88677668571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95428848266602</t>
+    <t xml:space="preserve">3.88677644729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95428824424744</t>
   </si>
   <si>
     <t xml:space="preserve">3.94464421272278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98322248458862</t>
+    <t xml:space="preserve">3.9832227230072</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507345199585</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971809387207</t>
+    <t xml:space="preserve">4.34971761703491</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">4.39794015884399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4268741607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45580816268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22433805465698</t>
+    <t xml:space="preserve">4.42687463760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45580768585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22433757781982</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144454956055</t>
+    <t xml:space="preserve">4.03144502639771</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">4.31113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29185009002686</t>
+    <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
     <t xml:space="preserve">4.40758514404297</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53296422958374</t>
+    <t xml:space="preserve">4.5329647064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180099487305</t>
+    <t xml:space="preserve">4.02180051803589</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">4.37865114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48474216461182</t>
+    <t xml:space="preserve">4.48474168777466</t>
   </si>
   <si>
     <t xml:space="preserve">4.47509717941284</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585678100586</t>
+    <t xml:space="preserve">4.72585725784302</t>
   </si>
   <si>
     <t xml:space="preserve">4.63905572891235</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">4.62941074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6101222038269</t>
+    <t xml:space="preserve">4.61012172698975</t>
   </si>
   <si>
     <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682506561279</t>
+    <t xml:space="preserve">4.27256059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682458877563</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372478485107</t>
+    <t xml:space="preserve">4.78372430801392</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59387159347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49742555618286</t>
+    <t xml:space="preserve">5.5938720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.28524398803711</t>
@@ -1655,19 +1655,19 @@
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026805877686</t>
+    <t xml:space="preserve">5.42026853561401</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088132858276</t>
+    <t xml:space="preserve">4.86088180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.84159231185913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93803834915161</t>
+    <t xml:space="preserve">4.93803787231445</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96100187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13748025894165</t>
+    <t xml:space="preserve">4.87276220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9610013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432725906372</t>
+    <t xml:space="preserve">5.00021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432773590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667579650879</t>
+    <t xml:space="preserve">4.67667531967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413246154785</t>
+    <t xml:space="preserve">4.72569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413198471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687107086182</t>
+    <t xml:space="preserve">4.92178440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687154769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000118255615</t>
+    <t xml:space="preserve">4.74530601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000165939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5982403755188</t>
+    <t xml:space="preserve">4.59824085235596</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921913146973</t>
+    <t xml:space="preserve">4.54921865463257</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1823,40 +1823,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254451751709</t>
+    <t xml:space="preserve">4.38254499435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32371854782104</t>
+    <t xml:space="preserve">4.3237190246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508832931519</t>
+    <t xml:space="preserve">4.264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508880615234</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1374363899231</t>
+    <t xml:space="preserve">4.13743591308594</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352375030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117521286011</t>
+    <t xml:space="preserve">4.33352327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117568969727</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274074554443</t>
+    <t xml:space="preserve">4.37274026870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16684913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19626235961914</t>
+    <t xml:space="preserve">4.1668496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1962628364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -9376,7 +9376,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9428,7 +9428,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9454,7 +9454,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9480,7 +9480,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9506,7 +9506,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9532,7 +9532,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9558,7 +9558,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9584,7 +9584,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9610,7 +9610,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9688,7 +9688,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9714,7 +9714,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9792,7 +9792,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G273" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9818,7 +9818,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9870,7 +9870,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G277" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9922,7 +9922,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9948,7 +9948,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G279" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9974,7 +9974,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G280" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10052,7 +10052,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10078,7 +10078,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10130,7 +10130,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G286" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10156,7 +10156,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10208,7 +10208,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10286,7 +10286,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G292" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10312,7 +10312,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10364,7 +10364,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10416,7 +10416,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G297" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10442,7 +10442,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G298" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10494,7 +10494,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10546,7 +10546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10598,7 +10598,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10624,7 +10624,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10702,7 +10702,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10806,7 +10806,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G312" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10858,7 +10858,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G314" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10884,7 +10884,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10910,7 +10910,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G316" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10936,7 +10936,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10962,7 +10962,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G318" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -10988,7 +10988,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11040,7 +11040,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G321" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11066,7 +11066,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11092,7 +11092,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G323" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11144,7 +11144,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G325" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11170,7 +11170,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G326" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11196,7 +11196,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11222,7 +11222,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11352,7 +11352,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11378,7 +11378,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11404,7 +11404,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11508,7 +11508,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11534,7 +11534,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11560,7 +11560,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G341" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11586,7 +11586,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11846,7 +11846,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11872,7 +11872,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11898,7 +11898,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G354" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11924,7 +11924,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11950,7 +11950,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G356" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11976,7 +11976,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12002,7 +12002,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12028,7 +12028,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12314,7 +12314,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15330,7 +15330,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15382,7 +15382,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16552,7 +16552,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G533" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16578,7 +16578,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16682,7 +16682,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16864,7 +16864,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16890,7 +16890,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16916,7 +16916,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17020,7 +17020,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17046,7 +17046,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17306,7 +17306,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17384,7 +17384,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17410,7 +17410,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17436,7 +17436,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17956,7 +17956,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18372,7 +18372,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18398,7 +18398,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18788,7 +18788,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19022,7 +19022,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19152,7 +19152,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G633" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G647" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19568,7 +19568,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19594,7 +19594,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19620,7 +19620,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19646,7 +19646,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19672,7 +19672,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19880,7 +19880,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19906,7 +19906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19958,7 +19958,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20244,7 +20244,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20270,7 +20270,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20764,7 +20764,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20790,7 +20790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -67728,7 +67728,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.5501273148</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>3300</v>
@@ -67749,6 +67749,32 @@
         <v>725</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6858796296</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282109260559</t>
+    <t xml:space="preserve">3.87282085418701</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
@@ -47,451 +47,454 @@
     <t xml:space="preserve">3.87105965614319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87458229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86577677726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401510238647</t>
+    <t xml:space="preserve">3.87458252906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86577653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401462554932</t>
   </si>
   <si>
     <t xml:space="preserve">3.78652381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74249410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79532957077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771782875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67733025550842</t>
+    <t xml:space="preserve">3.74249458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79532909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977910041809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.677330493927</t>
   </si>
   <si>
     <t xml:space="preserve">3.65443587303162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.663241147995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6438684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040616035461</t>
+    <t xml:space="preserve">3.66324138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64386868476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040592193604</t>
   </si>
   <si>
     <t xml:space="preserve">3.68965888023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66676330566406</t>
+    <t xml:space="preserve">3.66676378250122</t>
   </si>
   <si>
     <t xml:space="preserve">3.60336136817932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637668609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53995943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6156895160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915204048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65267443656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65091300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210724830627</t>
+    <t xml:space="preserve">3.68085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637692451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.539959192276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568975448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915227890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65267419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65091276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210748672485</t>
   </si>
   <si>
     <t xml:space="preserve">3.59455513954163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71431493759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.751300573349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8129415512085</t>
+    <t xml:space="preserve">3.71431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75130033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294131278992</t>
   </si>
   <si>
     <t xml:space="preserve">3.79356861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86225438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81470251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941963195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368787765503</t>
+    <t xml:space="preserve">3.86225414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941939353943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368835449219</t>
   </si>
   <si>
     <t xml:space="preserve">3.73721051216125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71255397796631</t>
+    <t xml:space="preserve">3.71255445480347</t>
   </si>
   <si>
     <t xml:space="preserve">3.73192715644836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72135996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891207695007</t>
+    <t xml:space="preserve">3.72136044502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891231536865</t>
   </si>
   <si>
     <t xml:space="preserve">3.76538944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74953866004944</t>
+    <t xml:space="preserve">3.74953842163086</t>
   </si>
   <si>
     <t xml:space="preserve">3.74601650238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73016595840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613624572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350850105286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383429527283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9186110496521</t>
+    <t xml:space="preserve">3.7301664352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846415519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68613600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488284111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91861128807068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446278572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98377537727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9432680606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9855363368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395451545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96088027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219379425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622231483459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741751670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338828086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02612829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220754623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759938240051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04410266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98299169540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93626046180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92727208137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560681343079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8913254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436486244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256718635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8194305896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7655086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59475755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273121833801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67923426628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070511817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62171864509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65766620635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63789463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318902015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60374474525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64688158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69181632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675084114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80325365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8176326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044268608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246950149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449536323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067206382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7762930393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887486457825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753475189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75112962722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80145645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348207473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72416949272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7709014415741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596621513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978951454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70260047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854756355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956156730652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72237181663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72776365280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831913948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541096687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68462634086609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69361352920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66485548019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68822145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135828971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8338086605072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224083900452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81583547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82661914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82841753959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547535896301</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446230888367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98377513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9432680606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98553586006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087956428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219403266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622279167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741727828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338780403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0261287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220754623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9901807308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759985923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04410266876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98299145698547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95423340797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625974655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9272723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367792129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560681343079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89132499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436486244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256647109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81943011283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76550889015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59475779533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273169517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67923450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63070511817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62171840667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65766620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103241920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60374474525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64688158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69181609153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652170181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616182327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8176326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044292449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394011497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449512481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067206382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77629327774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753499031067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75112962722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80145597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348231315613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72416925430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090120315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057390213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978951454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70260071754456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854756355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72237181663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72776365280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292682647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831913948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68462657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69361329078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66485571861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68822121620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380842208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81583499908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82661938667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841730117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547583580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188024520874</t>
+    <t xml:space="preserve">3.9218807220459</t>
   </si>
   <si>
     <t xml:space="preserve">3.90031218528748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87335133552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639096260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740329742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87514853477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929937362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243620872498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98119425773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97939610481262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413572311401</t>
+    <t xml:space="preserve">3.87335085868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8374035358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8751482963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94165253639221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929865837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243573188782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98119401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9793963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413596153259</t>
   </si>
   <si>
     <t xml:space="preserve">3.9488410949707</t>
@@ -500,22 +503,22 @@
     <t xml:space="preserve">3.87874341011047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01534461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02073669433594</t>
+    <t xml:space="preserve">4.01534414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0207371711731</t>
   </si>
   <si>
     <t xml:space="preserve">4.00815486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04050779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05309009552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01714086532593</t>
+    <t xml:space="preserve">4.04050731658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05308961868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01714134216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207609176636</t>
@@ -524,25 +527,25 @@
     <t xml:space="preserve">4.07106351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14295816421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06926536560059</t>
+    <t xml:space="preserve">4.14295864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06926584243774</t>
   </si>
   <si>
     <t xml:space="preserve">4.08903741836548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40357828140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37661743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34606170654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785985946655</t>
+    <t xml:space="preserve">4.40357780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37661790847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34606218338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785890579224</t>
   </si>
   <si>
     <t xml:space="preserve">4.32808828353882</t>
@@ -557,25 +560,25 @@
     <t xml:space="preserve">4.03691339492798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9847891330719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04230499267578</t>
+    <t xml:space="preserve">3.98478865623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04230546951294</t>
   </si>
   <si>
     <t xml:space="preserve">3.95603084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92008376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828584671021</t>
+    <t xml:space="preserve">3.92008328437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828608512878</t>
   </si>
   <si>
     <t xml:space="preserve">3.94704437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9326651096344</t>
+    <t xml:space="preserve">3.93266487121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.84099912643433</t>
@@ -593,70 +596,67 @@
     <t xml:space="preserve">3.9635968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99112176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194670677185</t>
+    <t xml:space="preserve">3.99112153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194646835327</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524693489075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89019632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87184691429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92689657211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.128746509552</t>
+    <t xml:space="preserve">3.8901960849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87184643745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691116333008</t>
+    <t xml:space="preserve">4.12691164016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05901622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03699684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99479150772095</t>
+    <t xml:space="preserve">4.05901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03699636459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99479174613953</t>
   </si>
   <si>
     <t xml:space="preserve">4.05351114273071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0828709602356</t>
+    <t xml:space="preserve">4.08287191390991</t>
   </si>
   <si>
     <t xml:space="preserve">4.03332662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07369565963745</t>
+    <t xml:space="preserve">4.07369661331177</t>
   </si>
   <si>
     <t xml:space="preserve">4.09204626083374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08103704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534696578979</t>
+    <t xml:space="preserve">4.08103609085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534648895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.09021139144897</t>
@@ -665,52 +665,52 @@
     <t xml:space="preserve">4.0626859664917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15260171890259</t>
+    <t xml:space="preserve">4.15260124206543</t>
   </si>
   <si>
     <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16544580459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11039638519287</t>
+    <t xml:space="preserve">4.16544628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11039686203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.09388160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20948553085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1544361114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1195707321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13608598709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15076684951782</t>
+    <t xml:space="preserve">4.20948600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15443658828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1379222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507581710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11957120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13608646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15076589584351</t>
   </si>
   <si>
     <t xml:space="preserve">4.10305643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278623580933</t>
+    <t xml:space="preserve">4.17278671264648</t>
   </si>
   <si>
     <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002592086792</t>
+    <t xml:space="preserve">4.07002639770508</t>
   </si>
   <si>
     <t xml:space="preserve">4.10122108459473</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">4.16911697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18379640579224</t>
+    <t xml:space="preserve">4.18379592895508</t>
   </si>
   <si>
     <t xml:space="preserve">4.21132135391235</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01864671707153</t>
+    <t xml:space="preserve">4.01864719390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.07920122146606</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">4.13241672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12140655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11590194702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11773586273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14709663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1489315032959</t>
+    <t xml:space="preserve">4.12140703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11590147018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11773633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14709615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14893102645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.19113636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19297122955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662613868713</t>
+    <t xml:space="preserve">4.19297170639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662661552429</t>
   </si>
   <si>
     <t xml:space="preserve">4.04433679580688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98561644554138</t>
+    <t xml:space="preserve">3.98561668395996</t>
   </si>
   <si>
     <t xml:space="preserve">3.94341111183167</t>
@@ -791,49 +791,49 @@
     <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726632118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772103309631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0002965927124</t>
+    <t xml:space="preserve">4.04800701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506194114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772127151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00029706954956</t>
   </si>
   <si>
     <t xml:space="preserve">3.97277140617371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93790698051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99846148490906</t>
+    <t xml:space="preserve">3.93790650367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846124649048</t>
   </si>
   <si>
     <t xml:space="preserve">4.04617166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88102149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349631309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442175865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514642715454</t>
+    <t xml:space="preserve">3.88102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442128181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514595031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.89937162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90854692459106</t>
+    <t xml:space="preserve">3.90854668617249</t>
   </si>
   <si>
     <t xml:space="preserve">3.93607139587402</t>
@@ -845,40 +845,40 @@
     <t xml:space="preserve">3.82597184181213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78927183151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80762195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039432525635</t>
+    <t xml:space="preserve">3.78927206993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.807621717453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039480209351</t>
   </si>
   <si>
     <t xml:space="preserve">4.04857444763184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03918123245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97342681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221396446228</t>
+    <t xml:space="preserve">4.03918075561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97342705726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922137260437</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9170663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616477012634</t>
+    <t xml:space="preserve">3.96403336524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827942848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91706657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.70101690292358</t>
@@ -896,37 +896,37 @@
     <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63526296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62586903572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52254152297974</t>
+    <t xml:space="preserve">3.63526272773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62586951255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52254176139832</t>
   </si>
   <si>
     <t xml:space="preserve">3.42860722541809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35345959663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33467268943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37224650382996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3816397190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45678758621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4661808013916</t>
+    <t xml:space="preserve">3.28770565986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35345983505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33467292785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37224626541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38163995742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45678734779358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
     <t xml:space="preserve">3.36285281181335</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800091743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40042686462402</t>
+    <t xml:space="preserve">3.43800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
     <t xml:space="preserve">3.4755744934082</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">3.31588578224182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60708236694336</t>
+    <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
     <t xml:space="preserve">3.56950879096985</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">3.65404987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48496794700623</t>
+    <t xml:space="preserve">3.48496770858765</t>
   </si>
   <si>
     <t xml:space="preserve">3.68223023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5976893901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647605895996</t>
+    <t xml:space="preserve">3.59768915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647582054138</t>
   </si>
   <si>
     <t xml:space="preserve">3.66344332695007</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">3.58829569816589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55072212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193473815918</t>
+    <t xml:space="preserve">3.5507218837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193497657776</t>
   </si>
   <si>
     <t xml:space="preserve">3.56011533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57890200614929</t>
+    <t xml:space="preserve">3.57890224456787</t>
   </si>
   <si>
     <t xml:space="preserve">3.64465641975403</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">3.6728367805481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51314806938171</t>
+    <t xml:space="preserve">3.51314830780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54921507835388</t>
+    <t xml:space="preserve">3.5492148399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.62637186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58779335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495013237</t>
+    <t xml:space="preserve">3.58779358863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495037078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79997491836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210739135742</t>
+    <t xml:space="preserve">3.7999746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210715293884</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855319023132</t>
+    <t xml:space="preserve">3.8385534286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">3.72281789779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64566135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708260536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56850457191467</t>
+    <t xml:space="preserve">3.64566111564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60708284378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">3.52992582321167</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">3.47205829620361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51063656806946</t>
+    <t xml:space="preserve">3.51063680648804</t>
   </si>
   <si>
     <t xml:space="preserve">3.41419053077698</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916598320007</t>
+    <t xml:space="preserve">3.27916622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0669846534729</t>
+    <t xml:space="preserve">3.06698489189148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1106,19 +1106,19 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
+    <t xml:space="preserve">2.91267108917236</t>
   </si>
   <si>
     <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71977877616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83551406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.970538854599</t>
+    <t xml:space="preserve">2.7197790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83551430702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97053861618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">2.81622505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79693603515625</t>
+    <t xml:space="preserve">2.79693579673767</t>
   </si>
   <si>
     <t xml:space="preserve">2.75835704803467</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73906803131104</t>
+    <t xml:space="preserve">2.73906779289246</t>
   </si>
   <si>
     <t xml:space="preserve">2.54617595672607</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">2.62333297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60404372215271</t>
+    <t xml:space="preserve">2.60404396057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.5847544670105</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">2.50759768486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46901893615723</t>
+    <t xml:space="preserve">2.46901917457581</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16039180755615</t>
+    <t xml:space="preserve">2.16039204597473</t>
   </si>
   <si>
     <t xml:space="preserve">2.04465627670288</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648235321045</t>
+    <t xml:space="preserve">2.26648211479187</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044090270996</t>
+    <t xml:space="preserve">2.43044066429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.27612709999084</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292862892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22790384292603</t>
+    <t xml:space="preserve">2.36292839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506110191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2279040813446</t>
   </si>
   <si>
     <t xml:space="preserve">2.24719309806824</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17968106269836</t>
+    <t xml:space="preserve">2.17968082427979</t>
   </si>
   <si>
     <t xml:space="preserve">2.18932557106018</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216878890991</t>
+    <t xml:space="preserve">2.11216902732849</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">2.15074706077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37257289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38221764564514</t>
+    <t xml:space="preserve">2.37257313728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38221788406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409281730652</t>
+    <t xml:space="preserve">2.87409257888794</t>
   </si>
   <si>
     <t xml:space="preserve">2.66191124916077</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">2.64262199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59439921379089</t>
+    <t xml:space="preserve">2.59439897537231</t>
   </si>
   <si>
     <t xml:space="preserve">2.68120050430298</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">2.52688670158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51724219322205</t>
+    <t xml:space="preserve">2.51724195480347</t>
   </si>
   <si>
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013426780701</t>
+    <t xml:space="preserve">2.71013402938843</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">2.94160485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99947237968445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98018288612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9608941078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03805112838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16343069076538</t>
+    <t xml:space="preserve">2.99947261810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98018312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089386940002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03805088996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16343092918396</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">3.15378594398499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26952171325684</t>
+    <t xml:space="preserve">3.26952147483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">3.0766294002533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01876187324524</t>
+    <t xml:space="preserve">3.01876163482666</t>
   </si>
   <si>
     <t xml:space="preserve">3.05734014511108</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90302634239197</t>
+    <t xml:space="preserve">2.90302658081055</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373732566833</t>
@@ -1445,25 +1445,25 @@
     <t xml:space="preserve">3.59743809700012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67459464073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71317338943481</t>
+    <t xml:space="preserve">3.67459487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71317315101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88677644729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95428824424744</t>
+    <t xml:space="preserve">3.88677668571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95428848266602</t>
   </si>
   <si>
     <t xml:space="preserve">3.94464421272278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9832227230072</t>
+    <t xml:space="preserve">3.98322248458862</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507345199585</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971761703491</t>
+    <t xml:space="preserve">4.34971809387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">4.39794015884399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42687463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45580768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22433757781982</t>
+    <t xml:space="preserve">4.4268741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45580816268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22433805465698</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144502639771</t>
+    <t xml:space="preserve">4.03144454956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">4.31113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2918496131897</t>
+    <t xml:space="preserve">4.29185009002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.40758514404297</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5329647064209</t>
+    <t xml:space="preserve">4.53296422958374</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180051803589</t>
+    <t xml:space="preserve">4.02180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">4.37865114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48474168777466</t>
+    <t xml:space="preserve">4.48474216461182</t>
   </si>
   <si>
     <t xml:space="preserve">4.47509717941284</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585725784302</t>
+    <t xml:space="preserve">4.72585678100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.63905572891235</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">4.62941074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61012172698975</t>
+    <t xml:space="preserve">4.6101222038269</t>
   </si>
   <si>
     <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682458877563</t>
+    <t xml:space="preserve">4.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682506561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372430801392</t>
+    <t xml:space="preserve">4.78372478485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5938720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4974250793457</t>
+    <t xml:space="preserve">5.59387159347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49742555618286</t>
   </si>
   <si>
     <t xml:space="preserve">5.28524398803711</t>
@@ -1655,19 +1655,19 @@
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026853561401</t>
+    <t xml:space="preserve">5.42026805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088180541992</t>
+    <t xml:space="preserve">4.86088132858276</t>
   </si>
   <si>
     <t xml:space="preserve">4.84159231185913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93803787231445</t>
+    <t xml:space="preserve">4.93803834915161</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9610013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13747978210449</t>
+    <t xml:space="preserve">4.87276268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96100187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13748025894165</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432773590088</t>
+    <t xml:space="preserve">5.00021886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432725906372</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667531967163</t>
+    <t xml:space="preserve">4.67667579650879</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413198471069</t>
+    <t xml:space="preserve">4.72569704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413246154785</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687154769897</t>
+    <t xml:space="preserve">4.92178392410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354520797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687107086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000165939331</t>
+    <t xml:space="preserve">4.74530649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59824085235596</t>
+    <t xml:space="preserve">4.5982403755188</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921865463257</t>
+    <t xml:space="preserve">4.54921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1823,40 +1823,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254499435425</t>
+    <t xml:space="preserve">4.38254451751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3237190246582</t>
+    <t xml:space="preserve">4.32371854782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508880615234</t>
+    <t xml:space="preserve">4.26489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587133407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508832931519</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13743591308594</t>
+    <t xml:space="preserve">4.1374363899231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117568969727</t>
+    <t xml:space="preserve">4.33352375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117521286011</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274026870728</t>
+    <t xml:space="preserve">4.37274074554443</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1668496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1962628364563</t>
+    <t xml:space="preserve">4.16684913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19626235961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -9376,7 +9376,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9428,7 +9428,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9454,7 +9454,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9480,7 +9480,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9506,7 +9506,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9532,7 +9532,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9558,7 +9558,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9584,7 +9584,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9610,7 +9610,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9688,7 +9688,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9714,7 +9714,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9792,7 +9792,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G273" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9818,7 +9818,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9870,7 +9870,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G277" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9922,7 +9922,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9948,7 +9948,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9974,7 +9974,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G280" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10052,7 +10052,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10078,7 +10078,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10130,7 +10130,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G286" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10156,7 +10156,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10208,7 +10208,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10286,7 +10286,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G292" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10312,7 +10312,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10364,7 +10364,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10416,7 +10416,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G297" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10442,7 +10442,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10494,7 +10494,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10546,7 +10546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10598,7 +10598,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10624,7 +10624,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10702,7 +10702,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10806,7 +10806,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G312" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10858,7 +10858,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G314" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10884,7 +10884,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10910,7 +10910,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G316" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10936,7 +10936,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10962,7 +10962,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G318" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -10988,7 +10988,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11040,7 +11040,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11066,7 +11066,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11092,7 +11092,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G323" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11144,7 +11144,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G325" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11170,7 +11170,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G326" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11196,7 +11196,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11222,7 +11222,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11352,7 +11352,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11378,7 +11378,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11404,7 +11404,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11508,7 +11508,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11534,7 +11534,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11560,7 +11560,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11586,7 +11586,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11846,7 +11846,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11872,7 +11872,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11898,7 +11898,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G354" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11924,7 +11924,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11950,7 +11950,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G356" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11976,7 +11976,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12002,7 +12002,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12028,7 +12028,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12314,7 +12314,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15330,7 +15330,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15382,7 +15382,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16552,7 +16552,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G533" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16578,7 +16578,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16682,7 +16682,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16864,7 +16864,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16890,7 +16890,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16916,7 +16916,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17020,7 +17020,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17046,7 +17046,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17306,7 +17306,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17384,7 +17384,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17410,7 +17410,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17436,7 +17436,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17956,7 +17956,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18372,7 +18372,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18398,7 +18398,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18788,7 +18788,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19022,7 +19022,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19152,7 +19152,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G633" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G647" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19568,7 +19568,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19594,7 +19594,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19620,7 +19620,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19646,7 +19646,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19672,7 +19672,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19880,7 +19880,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19906,7 +19906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19958,7 +19958,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20244,7 +20244,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20270,7 +20270,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20764,7 +20764,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20790,7 +20790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -67754,7 +67754,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6858796296</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>2200</v>
@@ -67775,6 +67775,32 @@
         <v>725</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6177546296</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>5945</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87106037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458205223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8657763004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401534080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652334213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74249410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79532980918884</t>
+    <t xml:space="preserve">3.87105989456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458276748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86577558517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74249458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79532957077026</t>
   </si>
   <si>
     <t xml:space="preserve">3.77771782875061</t>
@@ -71,43 +71,43 @@
     <t xml:space="preserve">3.62977957725525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67733097076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66324090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64386868476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040616035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68965911865234</t>
+    <t xml:space="preserve">3.677330493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443587303162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66324138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6438684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040663719177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68965935707092</t>
   </si>
   <si>
     <t xml:space="preserve">3.6667640209198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60336136817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6156895160675</t>
+    <t xml:space="preserve">3.6033616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637692451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568975448608</t>
   </si>
   <si>
     <t xml:space="preserve">3.64915204048157</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">3.65267443656921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091347694397</t>
+    <t xml:space="preserve">3.65091323852539</t>
   </si>
   <si>
     <t xml:space="preserve">3.64210748672485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59455537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431541442871</t>
+    <t xml:space="preserve">3.59455561637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431517601013</t>
   </si>
   <si>
     <t xml:space="preserve">3.75130081176758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81294083595276</t>
+    <t xml:space="preserve">3.81294131278992</t>
   </si>
   <si>
     <t xml:space="preserve">3.79356837272644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86225390434265</t>
+    <t xml:space="preserve">3.86225438117981</t>
   </si>
   <si>
     <t xml:space="preserve">3.81470203399658</t>
@@ -149,142 +149,142 @@
     <t xml:space="preserve">3.73368787765503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73721075057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255421638489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538896560669</t>
+    <t xml:space="preserve">3.73721027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72135972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891160011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538968086243</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953842163086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74601697921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73016619682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6984646320343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613624572754</t>
+    <t xml:space="preserve">3.74601650238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016571998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846439361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68613696098328</t>
   </si>
   <si>
     <t xml:space="preserve">3.72488236427307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82350850105286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9186110496521</t>
+    <t xml:space="preserve">3.82350826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383477210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91861176490784</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446207046509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9837749004364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94326853752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508936882019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98553681373596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395499229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96088004112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219450950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741799354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338780403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0261287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220778465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9901807308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759938240051</t>
+    <t xml:space="preserve">3.98377561569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94326782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98553609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91332769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96087980270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219427108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741751670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338756561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916815757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02612829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220754623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759985923767</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98299169540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95423340797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625950813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233828544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92727327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367815971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89132475852966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436414718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81942987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799231529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655086517334</t>
+    <t xml:space="preserve">3.98299193382263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9542338848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625974655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92727208137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367792129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560705184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89132523536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436486244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256766319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81943035125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76550912857056</t>
   </si>
   <si>
     <t xml:space="preserve">3.59475755691528</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">3.6307053565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62171840667725</t>
+    <t xml:space="preserve">3.62171864509583</t>
   </si>
   <si>
     <t xml:space="preserve">3.65766596794128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63789439201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103194236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318902015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632633209229</t>
+    <t xml:space="preserve">3.63789463043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632657051086</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
@@ -323,58 +323,58 @@
     <t xml:space="preserve">3.64688158035278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69181561470032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652146339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325317382812</t>
+    <t xml:space="preserve">3.69181632995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675084114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8032534122467</t>
   </si>
   <si>
     <t xml:space="preserve">3.86616206169128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81763291358948</t>
+    <t xml:space="preserve">3.81763243675232</t>
   </si>
   <si>
     <t xml:space="preserve">3.81044268608093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79246950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449536323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067182540894</t>
+    <t xml:space="preserve">3.79246878623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74394011497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449512481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067158699036</t>
   </si>
   <si>
     <t xml:space="preserve">3.77629327774048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78887462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753499031067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7511293888092</t>
+    <t xml:space="preserve">3.78887438774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753522872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
     <t xml:space="preserve">3.80145621299744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348278999329</t>
+    <t xml:space="preserve">3.73315596580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348207473755</t>
   </si>
   <si>
     <t xml:space="preserve">3.7241690158844</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">3.77090096473694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72057437896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371169090271</t>
+    <t xml:space="preserve">3.72057390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371145248413</t>
   </si>
   <si>
     <t xml:space="preserve">3.72596645355225</t>
@@ -398,40 +398,40 @@
     <t xml:space="preserve">3.70260047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73854756355286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956085205078</t>
+    <t xml:space="preserve">3.73854804039001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956132888794</t>
   </si>
   <si>
     <t xml:space="preserve">3.72237157821655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72776365280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292730331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831937789917</t>
+    <t xml:space="preserve">3.72776389122009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831913948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.69541096687317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68462657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69361352920532</t>
+    <t xml:space="preserve">3.68462705612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6936137676239</t>
   </si>
   <si>
     <t xml:space="preserve">3.66485548019409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68822121620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135828971863</t>
+    <t xml:space="preserve">3.68822193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135876655579</t>
   </si>
   <si>
     <t xml:space="preserve">3.7133846282959</t>
@@ -440,52 +440,52 @@
     <t xml:space="preserve">3.78168511390686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83380889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224083900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81583547592163</t>
+    <t xml:space="preserve">3.83380913734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224036216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81583499908447</t>
   </si>
   <si>
     <t xml:space="preserve">3.82661914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82841753959656</t>
+    <t xml:space="preserve">3.82841777801514</t>
   </si>
   <si>
     <t xml:space="preserve">3.92547535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93446254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188048362732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90031218528748</t>
+    <t xml:space="preserve">3.93446230888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031242370605</t>
   </si>
   <si>
     <t xml:space="preserve">3.87335157394409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84639120101929</t>
+    <t xml:space="preserve">3.84639048576355</t>
   </si>
   <si>
     <t xml:space="preserve">3.83740401268005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8751482963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9416515827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929865837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243573188782</t>
+    <t xml:space="preserve">3.87514853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94165205955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929841995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243549346924</t>
   </si>
   <si>
     <t xml:space="preserve">3.98119449615479</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">3.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88413548469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94884157180786</t>
+    <t xml:space="preserve">3.88413596153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94884085655212</t>
   </si>
   <si>
     <t xml:space="preserve">3.87874364852905</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">4.01534414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0207371711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00815534591675</t>
+    <t xml:space="preserve">4.02073669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00815486907959</t>
   </si>
   <si>
     <t xml:space="preserve">4.04050779342651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05308961868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01714134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06207656860352</t>
+    <t xml:space="preserve">4.0530891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01714181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06207609176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.07106304168701</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.14295864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06926584243774</t>
+    <t xml:space="preserve">4.0692663192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.08903694152832</t>
@@ -545,79 +545,79 @@
     <t xml:space="preserve">4.34606218338013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34785985946655</t>
+    <t xml:space="preserve">4.34785938262939</t>
   </si>
   <si>
     <t xml:space="preserve">4.32808780670166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27236938476562</t>
+    <t xml:space="preserve">4.27236986160278</t>
   </si>
   <si>
     <t xml:space="preserve">4.11599731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98478889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04230546951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603108406067</t>
+    <t xml:space="preserve">4.03691339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98478865623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603013038635</t>
   </si>
   <si>
     <t xml:space="preserve">3.92008280754089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91828632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099864959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795902252197</t>
+    <t xml:space="preserve">3.91828608512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704413414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9326651096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099888801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795926094055</t>
   </si>
   <si>
     <t xml:space="preserve">3.90390682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96359658241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99112129211426</t>
+    <t xml:space="preserve">3.94524574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9635968208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99112153053284</t>
   </si>
   <si>
     <t xml:space="preserve">3.98194670677185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06819152832031</t>
+    <t xml:space="preserve">4.06819105148315</t>
   </si>
   <si>
     <t xml:space="preserve">3.94524621963501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8901960849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8718466758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9268970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452178955078</t>
+    <t xml:space="preserve">3.89019632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87184643745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689681053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452083587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.128746509552</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691164016724</t>
+    <t xml:space="preserve">4.12691116333008</t>
   </si>
   <si>
     <t xml:space="preserve">4.10672616958618</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">3.99479150772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05351114273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0828709602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07369613647461</t>
+    <t xml:space="preserve">4.05351161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08287143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03332662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07369661331177</t>
   </si>
   <si>
     <t xml:space="preserve">4.0920467376709</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">4.08103656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05534696578979</t>
+    <t xml:space="preserve">4.05534744262695</t>
   </si>
   <si>
     <t xml:space="preserve">4.09021139144897</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.06268644332886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15260171890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15627145767212</t>
+    <t xml:space="preserve">4.15260124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15627193450928</t>
   </si>
   <si>
     <t xml:space="preserve">4.16544628143311</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">4.11039638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09388113021851</t>
+    <t xml:space="preserve">4.09388160705566</t>
   </si>
   <si>
     <t xml:space="preserve">4.20948600769043</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">4.15443658828735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13792181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507677078247</t>
+    <t xml:space="preserve">4.13792133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507629394531</t>
   </si>
   <si>
     <t xml:space="preserve">4.11957120895386</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">4.10305643081665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11223173141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07002592086792</t>
+    <t xml:space="preserve">4.17278671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11223125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07002639770508</t>
   </si>
   <si>
     <t xml:space="preserve">4.10122108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16911697387695</t>
+    <t xml:space="preserve">4.16911602020264</t>
   </si>
   <si>
     <t xml:space="preserve">4.18379640579224</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01864624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07920169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1342511177063</t>
+    <t xml:space="preserve">4.01864671707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07920122146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13425159454346</t>
   </si>
   <si>
     <t xml:space="preserve">4.21866130828857</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">4.11590147018433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11773586273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14709663391113</t>
+    <t xml:space="preserve">4.11773633956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14709615707397</t>
   </si>
   <si>
     <t xml:space="preserve">4.1489315032959</t>
@@ -767,124 +767,124 @@
     <t xml:space="preserve">4.1911358833313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19297170639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662613868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04433679580688</t>
+    <t xml:space="preserve">4.19297218322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662661552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04433631896973</t>
   </si>
   <si>
     <t xml:space="preserve">3.98561644554138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94341135025024</t>
+    <t xml:space="preserve">3.94341111183167</t>
   </si>
   <si>
     <t xml:space="preserve">4.02048110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92322611808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03516101837158</t>
+    <t xml:space="preserve">3.92322659492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03516149520874</t>
   </si>
   <si>
     <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726679801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772174835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00029706954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97277116775513</t>
+    <t xml:space="preserve">4.04800653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726584434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772150993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0002965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97277140617371</t>
   </si>
   <si>
     <t xml:space="preserve">3.93790650367737</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99846148490906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04617118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88102149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349631309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442175865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514642715454</t>
+    <t xml:space="preserve">3.99846124649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04617166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514618873596</t>
   </si>
   <si>
     <t xml:space="preserve">3.89937138557434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90854716300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267185211182</t>
+    <t xml:space="preserve">3.90854668617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93607139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267161369324</t>
   </si>
   <si>
     <t xml:space="preserve">3.82597184181213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78927183151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80762147903442</t>
+    <t xml:space="preserve">3.78927206993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.807621717453</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04857444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03918123245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97342681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221348762512</t>
+    <t xml:space="preserve">4.04857492446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03918075561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97342705726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922137260437</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9170663356781</t>
+    <t xml:space="preserve">3.96403336524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827942848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91706657409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70101714134216</t>
+    <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.75737762451172</t>
@@ -893,43 +893,43 @@
     <t xml:space="preserve">3.73859095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71041059494019</t>
+    <t xml:space="preserve">3.71980404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71041083335876</t>
   </si>
   <si>
     <t xml:space="preserve">3.63526272773743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6258692741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52254152297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28770518302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35345959663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33467245101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37224650382996</t>
+    <t xml:space="preserve">3.62586951255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52254176139832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860722541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28770542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35345983505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33467292785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37224626541138</t>
   </si>
   <si>
     <t xml:space="preserve">3.3816397190094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45678782463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4661808013916</t>
+    <t xml:space="preserve">3.45678758621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
     <t xml:space="preserve">3.36285305023193</t>
@@ -944,55 +944,55 @@
     <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47557425498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49436116218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3158860206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708236694336</t>
+    <t xml:space="preserve">3.4755744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49436140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31588578224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
     <t xml:space="preserve">3.56950879096985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50375485420227</t>
+    <t xml:space="preserve">3.50375461578369</t>
   </si>
   <si>
     <t xml:space="preserve">3.65404987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48496794700623</t>
+    <t xml:space="preserve">3.48496770858765</t>
   </si>
   <si>
     <t xml:space="preserve">3.68223023414612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5976893901825</t>
+    <t xml:space="preserve">3.59768915176392</t>
   </si>
   <si>
     <t xml:space="preserve">3.61647605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66344356536865</t>
+    <t xml:space="preserve">3.66344332695007</t>
   </si>
   <si>
     <t xml:space="preserve">3.58829569816589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55072212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193473815918</t>
+    <t xml:space="preserve">3.5507218837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193497657776</t>
   </si>
   <si>
     <t xml:space="preserve">3.56011533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57890200614929</t>
+    <t xml:space="preserve">3.57890224456787</t>
   </si>
   <si>
     <t xml:space="preserve">3.64465641975403</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">3.62637186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58779335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495013237</t>
+    <t xml:space="preserve">3.58779358863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495037078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79997491836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210739135742</t>
+    <t xml:space="preserve">3.7999746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210715293884</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855319023132</t>
+    <t xml:space="preserve">3.8385534286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1046,43 +1046,40 @@
     <t xml:space="preserve">3.72281789779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64566135406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708260536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56850457191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52992582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47205829620361</t>
+    <t xml:space="preserve">3.64566111564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56850433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52992606163025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47205805778503</t>
   </si>
   <si>
     <t xml:space="preserve">3.51063656806946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41419053077698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43347954750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45276880264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37561225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39490151405334</t>
+    <t xml:space="preserve">3.41419076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43347978591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4527690410614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37561202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39490127563477</t>
   </si>
   <si>
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916598320007</t>
+    <t xml:space="preserve">3.27916622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1094,13 +1091,13 @@
     <t xml:space="preserve">3.14414167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2020092010498</t>
+    <t xml:space="preserve">3.20200896263123</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0669846534729</t>
+    <t xml:space="preserve">3.06698489189148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1109,7 +1106,7 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
+    <t xml:space="preserve">2.91267108917236</t>
   </si>
   <si>
     <t xml:space="preserve">2.85480356216431</t>
@@ -1118,10 +1115,10 @@
     <t xml:space="preserve">2.71977877616882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83551406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.970538854599</t>
+    <t xml:space="preserve">2.83551430702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97053861618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1139,16 +1136,16 @@
     <t xml:space="preserve">2.98982763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95124959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81622505187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75835704803467</t>
+    <t xml:space="preserve">2.95124936103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8162248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79693579673767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75835728645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.77764678001404</t>
@@ -1169,10 +1166,10 @@
     <t xml:space="preserve">2.5847544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50759768486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46901893615723</t>
+    <t xml:space="preserve">2.50759744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46901917457581</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
@@ -1187,7 +1184,7 @@
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110255241394</t>
+    <t xml:space="preserve">2.14110279083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.23754858970642</t>
@@ -1214,13 +1211,13 @@
     <t xml:space="preserve">2.26648235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41115140914917</t>
+    <t xml:space="preserve">2.41115164756775</t>
   </si>
   <si>
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044090270996</t>
+    <t xml:space="preserve">2.43044066429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.27612709999084</t>
@@ -1238,19 +1235,19 @@
     <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22790384292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24719309806824</t>
+    <t xml:space="preserve">2.2279040813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24719333648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.35328412055969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32435011863708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17968106269836</t>
+    <t xml:space="preserve">2.32434988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17968082427979</t>
   </si>
   <si>
     <t xml:space="preserve">2.18932557106018</t>
@@ -1259,7 +1256,7 @@
     <t xml:space="preserve">2.17003631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13145804405212</t>
+    <t xml:space="preserve">2.1314582824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.08323502540588</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">1.98678886890411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92409884929657</t>
+    <t xml:space="preserve">1.92409896850586</t>
   </si>
   <si>
     <t xml:space="preserve">1.92892122268677</t>
@@ -1292,34 +1289,34 @@
     <t xml:space="preserve">1.95785510540009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15074706077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37257289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38221764564514</t>
+    <t xml:space="preserve">2.20861458778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15074729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37257313728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38221788406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66191124916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64262199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59439921379089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68120050430298</t>
+    <t xml:space="preserve">2.87409257888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66191148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64262223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6812002658844</t>
   </si>
   <si>
     <t xml:space="preserve">2.65226674079895</t>
@@ -1328,19 +1325,19 @@
     <t xml:space="preserve">2.61368823051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53653144836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52688670158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51724219322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70048975944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71013426780701</t>
+    <t xml:space="preserve">2.53653168678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52688694000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51724195480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70048952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71013402938843</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
@@ -1358,19 +1355,19 @@
     <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98018288612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9608941078186</t>
+    <t xml:space="preserve">2.98018312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089386940002</t>
   </si>
   <si>
     <t xml:space="preserve">3.03805112838745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21165370941162</t>
+    <t xml:space="preserve">3.16343092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21165347099304</t>
   </si>
   <si>
     <t xml:space="preserve">3.23094296455383</t>
@@ -1385,13 +1382,13 @@
     <t xml:space="preserve">3.17307543754578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952171325684</t>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378618240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952147483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
@@ -1400,28 +1397,28 @@
     <t xml:space="preserve">3.30809998512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32738900184631</t>
+    <t xml:space="preserve">3.32738924026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.25023221969604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766294002533</t>
+    <t xml:space="preserve">3.09591841697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07662916183472</t>
   </si>
   <si>
     <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05734014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.931960105896</t>
+    <t xml:space="preserve">3.05734038352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92231583595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93196034431458</t>
   </si>
   <si>
     <t xml:space="preserve">2.90302634239197</t>
@@ -1439,34 +1436,34 @@
     <t xml:space="preserve">2.80658054351807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67459464073181</t>
+    <t xml:space="preserve">3.59743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
     <t xml:space="preserve">3.71317338943481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79033041000366</t>
+    <t xml:space="preserve">3.79033017158508</t>
   </si>
   <si>
     <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95428824424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94464421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9832227230072</t>
+    <t xml:space="preserve">3.95428848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9446439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98322248458862</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507345199585</t>
@@ -1481,10 +1478,10 @@
     <t xml:space="preserve">4.20504856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26291608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30149412155151</t>
+    <t xml:space="preserve">4.26291656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30149459838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.23398208618164</t>
@@ -1502,7 +1499,7 @@
     <t xml:space="preserve">4.42687463760376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45580768585205</t>
+    <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
     <t xml:space="preserve">4.22433757781982</t>
@@ -1523,7 +1520,7 @@
     <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40758514404297</t>
+    <t xml:space="preserve">4.40758562088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
@@ -1535,16 +1532,16 @@
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36900663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1278920173645</t>
+    <t xml:space="preserve">4.3690071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25327157974243</t>
+    <t xml:space="preserve">4.25327110290527</t>
   </si>
   <si>
     <t xml:space="preserve">4.1857590675354</t>
@@ -1553,13 +1550,13 @@
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180051803589</t>
+    <t xml:space="preserve">4.02180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
+    <t xml:space="preserve">4.17611455917358</t>
   </si>
   <si>
     <t xml:space="preserve">4.33042764663696</t>
@@ -1580,16 +1577,16 @@
     <t xml:space="preserve">4.47509717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49438619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44616365432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41722965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64870023727417</t>
+    <t xml:space="preserve">4.49438667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41722917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64869976043701</t>
   </si>
   <si>
     <t xml:space="preserve">4.80301380157471</t>
@@ -1610,19 +1607,19 @@
     <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682458877563</t>
+    <t xml:space="preserve">4.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682554244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1631,7 +1628,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372430801392</t>
+    <t xml:space="preserve">4.78372478485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1640,118 +1637,121 @@
     <t xml:space="preserve">4.97661638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01519536972046</t>
+    <t xml:space="preserve">5.0151948928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5938720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28524398803711</t>
+    <t xml:space="preserve">5.59387159347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49742555618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28524446487427</t>
   </si>
   <si>
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026853561401</t>
+    <t xml:space="preserve">5.42026805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84159231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93803787231445</t>
+    <t xml:space="preserve">4.86088132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84159183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93803834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73550128936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70608854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86295795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87276268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96100187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13748025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0198278427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1963062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07865381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94139337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00021886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432725906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78452348709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67667579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61784934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6276535987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75511026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84334945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89237117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72569704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413246154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76491498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92178392410278</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70608854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86295795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87276220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9610013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13747978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0198278427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1963062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07865381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94139337539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90217542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78452348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67667531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61784934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6276535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75511026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84334945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89237117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413198471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76491498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92178440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687154769897</t>
+    <t xml:space="preserve">4.83354520797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687107086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000165939331</t>
+    <t xml:space="preserve">4.74530649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59824085235596</t>
+    <t xml:space="preserve">4.5982403755188</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921865463257</t>
+    <t xml:space="preserve">4.54921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254499435425</t>
+    <t xml:space="preserve">4.38254451751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3237190246582</t>
+    <t xml:space="preserve">4.32371854782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508880615234</t>
+    <t xml:space="preserve">4.26489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587133407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508832931519</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13743591308594</t>
+    <t xml:space="preserve">4.1374363899231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117568969727</t>
+    <t xml:space="preserve">4.33352375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117521286011</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274026870728</t>
+    <t xml:space="preserve">4.37274074554443</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1668496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1962628364563</t>
+    <t xml:space="preserve">4.16684913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19626235961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -26539,7 +26539,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G917" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G918" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G925" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G936" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G937" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27137,7 +27137,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G940" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G941" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27189,7 +27189,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G942" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27215,7 +27215,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G943" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G944" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G945" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G946" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G948" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G949" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>3.5</v>
       </c>
       <c r="G950" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>3.5</v>
       </c>
       <c r="G951" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G953" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27527,7 +27527,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G955" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27553,7 +27553,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G956" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G957" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G958" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G959" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G960" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G961" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G962" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G963" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G964" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G965" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G966" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G967" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G968" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G969" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G971" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G972" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27995,7 +27995,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G973" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G974" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>3</v>
       </c>
       <c r="G975" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G976" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G977" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G978" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G979" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G980" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G981" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G982" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G983" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G984" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G985" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G986" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G987" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G988" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G989" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G990" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G991" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G992" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G993" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G994" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G995" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G996" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G997" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G998" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G999" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1000" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1001" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1002" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1003" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1004" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1005" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1007" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1008" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1009" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1010" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1011" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1012" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1013" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1015" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1016" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1017" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1018" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1019" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1020" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1021" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1022" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1023" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1024" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1025" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1026" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1027" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1028" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1029" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1030" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1031" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1032" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1033" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1034" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1035" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1036" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1037" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1038" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>3</v>
       </c>
       <c r="G1039" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1040" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1041" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1042" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1043" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1044" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1045" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1046" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1047" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1048" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1049" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1050" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1051" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1052" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1053" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1054" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1055" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1056" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1057" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1058" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1059" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1060" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1061" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1062" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1063" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1064" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1065" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1066" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1067" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1068" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1069" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1070" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1071" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1072" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1073" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1074" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1075" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1077" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1078" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1079" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1080" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1081" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1082" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>2.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1085" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1086" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1087" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1088" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1090" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1091" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1092" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1093" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1094" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1095" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1096" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1097" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1098" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1099" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1100" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1101" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1102" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1103" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1104" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1105" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1106" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>2.5</v>
       </c>
       <c r="G1107" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1108" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1109" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1110" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1111" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1112" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1113" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1114" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1115" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31713,7 +31713,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1116" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31739,7 +31739,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1117" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1118" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31791,7 +31791,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1119" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1120" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1121" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1122" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1123" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1124" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1125" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1126" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1127" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1128" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1129" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32077,7 +32077,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1130" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1131" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1132" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32155,7 +32155,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1133" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1134" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1135" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32233,7 +32233,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1136" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1137" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1138" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1139" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32337,7 +32337,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1140" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32363,7 +32363,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1141" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1142" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1143" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1144" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32467,7 +32467,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1145" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32493,7 +32493,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32519,7 +32519,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1147" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32545,7 +32545,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1148" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32571,7 +32571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1149" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32597,7 +32597,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1150" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32623,7 +32623,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32649,7 +32649,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1152" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32675,7 +32675,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1153" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32701,7 +32701,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1154" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32727,7 +32727,7 @@
         <v>2.25</v>
       </c>
       <c r="G1155" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32753,7 +32753,7 @@
         <v>2.25</v>
       </c>
       <c r="G1156" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32779,7 +32779,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1157" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32805,7 +32805,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32831,7 +32831,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1159" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32857,7 +32857,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1160" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32883,7 +32883,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1161" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32909,7 +32909,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1162" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1163" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1164" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32987,7 +32987,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1165" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1166" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1167" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1168" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>2</v>
       </c>
       <c r="G1169" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1170" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1171" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1172" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1173" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1174" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>2.25</v>
       </c>
       <c r="G1175" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>2.25</v>
       </c>
       <c r="G1176" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1177" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1178" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1179" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>2.25</v>
       </c>
       <c r="G1180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>2.25</v>
       </c>
       <c r="G1181" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1182" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>2.25</v>
       </c>
       <c r="G1183" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1184" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1185" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1186" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1187" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1188" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1189" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1190" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1191" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1192" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33715,7 +33715,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1194" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33767,7 +33767,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1195" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1196" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33819,7 +33819,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1197" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1198" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1199" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1200" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1201" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1202" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1203" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1204" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1205" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1207" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1208" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1209" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1211" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1212" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34235,7 +34235,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1214" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1215" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34313,7 +34313,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1217" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>2.25</v>
       </c>
       <c r="G1218" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1219" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1220" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1221" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1223" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1224" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>2.25</v>
       </c>
       <c r="G1225" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>2.25</v>
       </c>
       <c r="G1226" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1228" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>2.25</v>
       </c>
       <c r="G1229" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>2.25</v>
       </c>
       <c r="G1230" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1231" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1232" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1233" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>2.25</v>
       </c>
       <c r="G1234" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1235" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1236" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1238" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1240" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1241" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1242" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1243" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1244" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1245" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1246" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1247" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35145,7 +35145,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1249" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1250" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35223,7 +35223,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1251" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1252" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1253" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1254" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1255" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1256" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1257" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1258" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1259" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1260" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1261" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1262" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1263" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1264" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35587,7 +35587,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1265" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35613,7 +35613,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1266" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1267" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1268" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1269" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1270" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1271" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1272" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1273" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1274" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1275" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1276" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1277" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1278" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35951,7 +35951,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G1279" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35977,7 +35977,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1280" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36003,7 +36003,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1281" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36029,7 +36029,7 @@
         <v>2.75</v>
       </c>
       <c r="G1282" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36055,7 +36055,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1283" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36081,7 +36081,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1284" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1285" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36133,7 +36133,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1286" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36159,7 +36159,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1287" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36185,7 +36185,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1288" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36211,7 +36211,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1289" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1290" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36263,7 +36263,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1291" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1292" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36315,7 +36315,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1293" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36341,7 +36341,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1294" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36367,7 +36367,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1295" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36393,7 +36393,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1296" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36419,7 +36419,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1297" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36445,7 +36445,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1298" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36471,7 +36471,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1299" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36497,7 +36497,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1300" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36523,7 +36523,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1301" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36549,7 +36549,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1302" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36575,7 +36575,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1303" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36601,7 +36601,7 @@
         <v>2.75</v>
       </c>
       <c r="G1304" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36627,7 +36627,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1305" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36653,7 +36653,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1306" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36679,7 +36679,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1307" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36705,7 +36705,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1308" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36731,7 +36731,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1309" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36757,7 +36757,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1310" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36783,7 +36783,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1311" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36809,7 +36809,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1312" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36835,7 +36835,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1313" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36861,7 +36861,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1314" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36887,7 +36887,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36913,7 +36913,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1316" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36939,7 +36939,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1317" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36965,7 +36965,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1318" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36991,7 +36991,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1319" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37017,7 +37017,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37043,7 +37043,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1321" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37069,7 +37069,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37095,7 +37095,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1323" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37121,7 +37121,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1324" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37147,7 +37147,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1325" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37173,7 +37173,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1326" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37199,7 +37199,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1327" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37225,7 +37225,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1328" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37251,7 +37251,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G1329" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37277,7 +37277,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1330" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37303,7 +37303,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37329,7 +37329,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1332" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37355,7 +37355,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1333" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37381,7 +37381,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1334" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37407,7 +37407,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1335" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37433,7 +37433,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1336" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37459,7 +37459,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37485,7 +37485,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1338" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37511,7 +37511,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37537,7 +37537,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1340" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37563,7 +37563,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1341" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37589,7 +37589,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1342" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37615,7 +37615,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1343" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37641,7 +37641,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1344" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37667,7 +37667,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1345" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37693,7 +37693,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1346" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37719,7 +37719,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1347" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37745,7 +37745,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37771,7 +37771,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1349" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37797,7 +37797,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1350" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37823,7 +37823,7 @@
         <v>3.25</v>
       </c>
       <c r="G1351" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37849,7 +37849,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37875,7 +37875,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1353" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37901,7 +37901,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37927,7 +37927,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37953,7 +37953,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1356" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37979,7 +37979,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1357" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38005,7 +38005,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38031,7 +38031,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1359" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38057,7 +38057,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1360" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38083,7 +38083,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1361" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38109,7 +38109,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1362" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38135,7 +38135,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1363" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38161,7 +38161,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38187,7 +38187,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1365" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38213,7 +38213,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1366" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38239,7 +38239,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1367" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38265,7 +38265,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1368" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38291,7 +38291,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1369" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38317,7 +38317,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1370" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38343,7 +38343,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1371" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38369,7 +38369,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1372" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38395,7 +38395,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1373" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38421,7 +38421,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1374" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38447,7 +38447,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1375" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38473,7 +38473,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1376" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38499,7 +38499,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1377" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38525,7 +38525,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1378" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38551,7 +38551,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1379" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38577,7 +38577,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1380" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38603,7 +38603,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1381" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38629,7 +38629,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1382" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38655,7 +38655,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1383" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38681,7 +38681,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1384" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38707,7 +38707,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1385" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38733,7 +38733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1386" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38759,7 +38759,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1387" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38785,7 +38785,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1388" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38811,7 +38811,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1389" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38837,7 +38837,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1390" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38863,7 +38863,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1391" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38889,7 +38889,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1392" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38915,7 +38915,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38941,7 +38941,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1394" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38967,7 +38967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1395" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38993,7 +38993,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1396" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39019,7 +39019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1397" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39045,7 +39045,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1398" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39071,7 +39071,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1399" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39097,7 +39097,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1400" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39123,7 +39123,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1401" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39149,7 +39149,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1402" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39175,7 +39175,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1403" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39201,7 +39201,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1404" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39227,7 +39227,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1405" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39253,7 +39253,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1406" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39279,7 +39279,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1407" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39305,7 +39305,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1408" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39331,7 +39331,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1409" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39357,7 +39357,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1410" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39383,7 +39383,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1411" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39409,7 +39409,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1412" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39435,7 +39435,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1413" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39461,7 +39461,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1414" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39487,7 +39487,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1415" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39513,7 +39513,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1416" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39539,7 +39539,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1417" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39565,7 +39565,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1418" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39591,7 +39591,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1419" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39617,7 +39617,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1420" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39643,7 +39643,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1421" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39669,7 +39669,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1422" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39695,7 +39695,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1423" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39721,7 +39721,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1424" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39747,7 +39747,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1425" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39773,7 +39773,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1426" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39799,7 +39799,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1427" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39825,7 +39825,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1428" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39851,7 +39851,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1429" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39877,7 +39877,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1430" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39903,7 +39903,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1431" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39929,7 +39929,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1432" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39955,7 +39955,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1433" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39981,7 +39981,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1434" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40007,7 +40007,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1435" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40033,7 +40033,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1436" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40059,7 +40059,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1437" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40085,7 +40085,7 @@
         <v>3</v>
       </c>
       <c r="G1438" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40111,7 +40111,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1439" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40137,7 +40137,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1440" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40163,7 +40163,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1441" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40189,7 +40189,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1442" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40215,7 +40215,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1443" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40241,7 +40241,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1444" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40267,7 +40267,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1445" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40293,7 +40293,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1446" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40319,7 +40319,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1447" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40345,7 +40345,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1448" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40371,7 +40371,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1449" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40397,7 +40397,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40423,7 +40423,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1451" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40449,7 +40449,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1452" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40475,7 +40475,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1453" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40501,7 +40501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1454" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40527,7 +40527,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1455" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40553,7 +40553,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1456" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40579,7 +40579,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1457" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40605,7 +40605,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1458" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40631,7 +40631,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1459" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40657,7 +40657,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1460" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40683,7 +40683,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1461" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40709,7 +40709,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1462" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40735,7 +40735,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1463" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40761,7 +40761,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1464" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40787,7 +40787,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40813,7 +40813,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1466" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40839,7 +40839,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G1467" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40865,7 +40865,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40891,7 +40891,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1469" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40917,7 +40917,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1470" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40943,7 +40943,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1471" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40969,7 +40969,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1472" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40995,7 +40995,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1473" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41021,7 +41021,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1474" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41047,7 +41047,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1475" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41073,7 +41073,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1476" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41099,7 +41099,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1477" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41125,7 +41125,7 @@
         <v>3</v>
       </c>
       <c r="G1478" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41151,7 +41151,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1479" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41177,7 +41177,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1480" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41203,7 +41203,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1481" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41229,7 +41229,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1482" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41255,7 +41255,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1483" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41281,7 +41281,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1484" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41307,7 +41307,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41333,7 +41333,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1486" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41359,7 +41359,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1487" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41385,7 +41385,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1488" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41411,7 +41411,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1489" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41437,7 +41437,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1490" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41463,7 +41463,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1491" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41489,7 +41489,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1492" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41515,7 +41515,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1493" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41541,7 +41541,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1494" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41567,7 +41567,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1495" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41593,7 +41593,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1496" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41619,7 +41619,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1497" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41645,7 +41645,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1498" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41671,7 +41671,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1499" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41697,7 +41697,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1500" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41723,7 +41723,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1501" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41749,7 +41749,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1502" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41775,7 +41775,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1503" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41801,7 +41801,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1504" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41827,7 +41827,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1505" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41853,7 +41853,7 @@
         <v>3.25</v>
       </c>
       <c r="G1506" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41879,7 +41879,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1507" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41905,7 +41905,7 @@
         <v>3.25</v>
       </c>
       <c r="G1508" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41931,7 +41931,7 @@
         <v>3.25</v>
       </c>
       <c r="G1509" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41957,7 +41957,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1510" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41983,7 +41983,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1511" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42009,7 +42009,7 @@
         <v>3.25</v>
       </c>
       <c r="G1512" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42035,7 +42035,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1513" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42061,7 +42061,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1514" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42087,7 +42087,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1515" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42113,7 +42113,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1516" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42139,7 +42139,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1517" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42165,7 +42165,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1518" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42191,7 +42191,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1519" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42217,7 +42217,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1520" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42243,7 +42243,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1521" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42269,7 +42269,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1522" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42295,7 +42295,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42321,7 +42321,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1524" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42347,7 +42347,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1525" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42373,7 +42373,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1526" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42477,7 +42477,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1530" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42503,7 +42503,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1531" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42555,7 +42555,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1533" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42581,7 +42581,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1534" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42607,7 +42607,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1535" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42633,7 +42633,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1536" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42659,7 +42659,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1537" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42685,7 +42685,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1538" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42711,7 +42711,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1539" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42737,7 +42737,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1540" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42763,7 +42763,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1541" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42789,7 +42789,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1542" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42815,7 +42815,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1543" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42841,7 +42841,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1544" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42867,7 +42867,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1545" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42893,7 +42893,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1546" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42919,7 +42919,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1547" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42945,7 +42945,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1548" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42971,7 +42971,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1549" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42997,7 +42997,7 @@
         <v>4.5</v>
       </c>
       <c r="G1550" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43023,7 +43023,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1551" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43049,7 +43049,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1552" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43075,7 +43075,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1553" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43101,7 +43101,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1554" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43127,7 +43127,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1555" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43153,7 +43153,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1556" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43179,7 +43179,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1557" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43205,7 +43205,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1558" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43231,7 +43231,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1559" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43257,7 +43257,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1560" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43283,7 +43283,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1561" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43309,7 +43309,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1562" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43335,7 +43335,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1563" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43361,7 +43361,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1564" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43387,7 +43387,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1565" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43413,7 +43413,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1566" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43439,7 +43439,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1567" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43465,7 +43465,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1568" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43491,7 +43491,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1569" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43517,7 +43517,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1570" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43543,7 +43543,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1571" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43569,7 +43569,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1572" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43595,7 +43595,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1573" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43621,7 +43621,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1574" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43647,7 +43647,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1575" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43673,7 +43673,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1576" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43699,7 +43699,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1577" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43725,7 +43725,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1578" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43751,7 +43751,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1579" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43777,7 +43777,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1580" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43803,7 +43803,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1581" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43829,7 +43829,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1582" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43855,7 +43855,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1583" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43881,7 +43881,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43907,7 +43907,7 @@
         <v>4.5</v>
       </c>
       <c r="G1585" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43933,7 +43933,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1586" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43959,7 +43959,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1587" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43985,7 +43985,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1588" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44011,7 +44011,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44037,7 +44037,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1590" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44063,7 +44063,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1591" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44089,7 +44089,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1592" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44115,7 +44115,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1593" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44141,7 +44141,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1594" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44167,7 +44167,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1595" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44193,7 +44193,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44219,7 +44219,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1597" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44245,7 +44245,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1598" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44271,7 +44271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1599" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44297,7 +44297,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1600" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44323,7 +44323,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1601" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44349,7 +44349,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1602" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44375,7 +44375,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1603" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44401,7 +44401,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1604" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44427,7 +44427,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1605" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44453,7 +44453,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1606" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44479,7 +44479,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1607" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44505,7 +44505,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1608" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44531,7 +44531,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1609" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44557,7 +44557,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1610" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44583,7 +44583,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1611" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44609,7 +44609,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1612" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44635,7 +44635,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1613" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44661,7 +44661,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1614" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44687,7 +44687,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1615" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44713,7 +44713,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1616" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44739,7 +44739,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1617" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44765,7 +44765,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1618" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44791,7 +44791,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44817,7 +44817,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1620" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44843,7 +44843,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1621" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44869,7 +44869,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1622" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44895,7 +44895,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1623" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44921,7 +44921,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1624" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44947,7 +44947,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44973,7 +44973,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44999,7 +44999,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1627" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45025,7 +45025,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45051,7 +45051,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45077,7 +45077,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1630" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45103,7 +45103,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1631" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45129,7 +45129,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1632" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45155,7 +45155,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1633" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45181,7 +45181,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1634" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45207,7 +45207,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45233,7 +45233,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45259,7 +45259,7 @@
         <v>5.5</v>
       </c>
       <c r="G1637" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45285,7 +45285,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1638" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45311,7 +45311,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1639" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45337,7 +45337,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1640" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45363,7 +45363,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1641" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45389,7 +45389,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1642" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45415,7 +45415,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1643" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45441,7 +45441,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1644" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45467,7 +45467,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45493,7 +45493,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1646" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45519,7 +45519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1647" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45545,7 +45545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1648" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45571,7 +45571,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1649" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45597,7 +45597,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1650" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45623,7 +45623,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1651" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45649,7 +45649,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1652" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45675,7 +45675,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1653" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45701,7 +45701,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1654" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45727,7 +45727,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1655" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45753,7 +45753,7 @@
         <v>5</v>
       </c>
       <c r="G1656" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45779,7 +45779,7 @@
         <v>5</v>
       </c>
       <c r="G1657" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45805,7 +45805,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1658" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45831,7 +45831,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1659" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45857,7 +45857,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1660" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45883,7 +45883,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1661" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45909,7 +45909,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1662" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45935,7 +45935,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1663" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45961,7 +45961,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1664" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45987,7 +45987,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1665" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46013,7 +46013,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46039,7 +46039,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1667" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46065,7 +46065,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1668" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46091,7 +46091,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1669" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46117,7 +46117,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G1670" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46143,7 +46143,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1671" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46169,7 +46169,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1672" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46195,7 +46195,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1673" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46221,7 +46221,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1674" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46247,7 +46247,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1675" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46273,7 +46273,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1676" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46299,7 +46299,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1677" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46325,7 +46325,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1678" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46351,7 +46351,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1679" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46377,7 +46377,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1680" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46403,7 +46403,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1681" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46429,7 +46429,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46455,7 +46455,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1683" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46481,7 +46481,7 @@
         <v>5</v>
       </c>
       <c r="G1684" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46507,7 +46507,7 @@
         <v>5</v>
       </c>
       <c r="G1685" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46533,7 +46533,7 @@
         <v>5</v>
       </c>
       <c r="G1686" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46585,7 +46585,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1688" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46611,7 +46611,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1689" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46715,7 +46715,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1693" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46793,7 +46793,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1696" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46975,7 +46975,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1703" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47001,7 +47001,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1704" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47027,7 +47027,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1705" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47053,7 +47053,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1706" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47183,7 +47183,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1711" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47391,7 +47391,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1719" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47495,7 +47495,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1723" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47521,7 +47521,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1724" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47781,7 +47781,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1734" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47807,7 +47807,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1735" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47911,7 +47911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1739" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48015,7 +48015,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1743" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48041,7 +48041,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1744" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48119,7 +48119,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1747" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49523,7 +49523,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1801" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50147,7 +50147,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1825" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50173,7 +50173,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G1826" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50225,7 +50225,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1828" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50251,7 +50251,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1829" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50277,7 +50277,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1830" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50303,7 +50303,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50329,7 +50329,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1832" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50485,7 +50485,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1838" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50511,7 +50511,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1839" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50563,7 +50563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1841" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50615,7 +50615,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1843" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50667,7 +50667,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1845" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -68017,7 +68017,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6647337963</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>400</v>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282061576843</t>
+    <t xml:space="preserve">3.87282085418701</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87106013298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458205223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86577582359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401534080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652358055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74249386787415</t>
+    <t xml:space="preserve">3.87105965614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458252906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8657763004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74249410629272</t>
   </si>
   <si>
     <t xml:space="preserve">3.79532933235168</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">3.67733073234558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65443515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.663241147995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6438684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040639877319</t>
+    <t xml:space="preserve">3.65443587303162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66324090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64386892318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
     <t xml:space="preserve">3.68965911865234</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">3.66676378250122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60336136817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637692451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6156895160675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915227890015</t>
+    <t xml:space="preserve">3.60336112976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637740135193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568975448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915204048157</t>
   </si>
   <si>
     <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210724830627</t>
+    <t xml:space="preserve">3.65091276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210748672485</t>
   </si>
   <si>
     <t xml:space="preserve">3.59455537796021</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">3.71431517601013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.751300573349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79356837272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86225414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81470227241516</t>
+    <t xml:space="preserve">3.75130033493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294131278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79356861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86225438117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470274925232</t>
   </si>
   <si>
     <t xml:space="preserve">3.80941891670227</t>
@@ -149,100 +149,100 @@
     <t xml:space="preserve">3.73368811607361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73721075057983</t>
+    <t xml:space="preserve">3.73721098899841</t>
   </si>
   <si>
     <t xml:space="preserve">3.71255397796631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73192715644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.721360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891183853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538944244385</t>
+    <t xml:space="preserve">3.73192739486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72135996818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538920402527</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953866004944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74601650238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7301664352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6861367225647</t>
+    <t xml:space="preserve">3.74601674079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016595840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6984646320343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68613624572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.72488260269165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82350873947144</t>
+    <t xml:space="preserve">3.8235080242157</t>
   </si>
   <si>
     <t xml:space="preserve">3.95383501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9186110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446230888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98377466201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9432680606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508913040161</t>
+    <t xml:space="preserve">3.91861176490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446183204651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9837749004364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508936882019</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855363368988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332769393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395546913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087956428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219427108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622350692749</t>
+    <t xml:space="preserve">3.91332840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96088027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219403266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622303009033</t>
   </si>
   <si>
     <t xml:space="preserve">3.92741751670837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88338828086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02612829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759938240051</t>
+    <t xml:space="preserve">3.88338875770569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0261287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220754623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759985923767</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410219192505</t>
@@ -251,31 +251,31 @@
     <t xml:space="preserve">3.98299193382263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9542338848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625950813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233828544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92727279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367815971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560633659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8913254737854</t>
+    <t xml:space="preserve">3.95423340797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93626046180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92727255821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367792129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560681343079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89132499694824</t>
   </si>
   <si>
     <t xml:space="preserve">3.86436462402344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86256694793701</t>
+    <t xml:space="preserve">3.86256670951843</t>
   </si>
   <si>
     <t xml:space="preserve">3.81943011283875</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">3.7655086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59475755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61273169517517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67923450469971</t>
+    <t xml:space="preserve">3.59475779533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61273145675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67923426628113</t>
   </si>
   <si>
     <t xml:space="preserve">3.63070511817932</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">3.62171864509583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65766644477844</t>
+    <t xml:space="preserve">3.65766572952271</t>
   </si>
   <si>
     <t xml:space="preserve">3.63789463043213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68103241920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632633209229</t>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318902015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632657051086</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
@@ -323,55 +323,55 @@
     <t xml:space="preserve">3.64688181877136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6918158531189</t>
+    <t xml:space="preserve">3.69181609153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.73675060272217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75652170181274</t>
+    <t xml:space="preserve">3.75652146339417</t>
   </si>
   <si>
     <t xml:space="preserve">3.80325365066528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86616158485413</t>
+    <t xml:space="preserve">3.86616206169128</t>
   </si>
   <si>
     <t xml:space="preserve">3.8176326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81044292449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246878623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394011497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449584007263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7762930393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887438774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753475189209</t>
+    <t xml:space="preserve">3.81044268608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246950149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449512481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067206382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77629351615906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887486457825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753499031067</t>
   </si>
   <si>
     <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80145621299744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7331554889679</t>
+    <t xml:space="preserve">3.80145597457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
   </si>
   <si>
     <t xml:space="preserve">3.78348255157471</t>
@@ -380,94 +380,94 @@
     <t xml:space="preserve">3.7241690158844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090048789978</t>
+    <t xml:space="preserve">3.77090096473694</t>
   </si>
   <si>
     <t xml:space="preserve">3.72057390213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76371145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978975296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7026002407074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854756355286</t>
+    <t xml:space="preserve">3.76371169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596597671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978951454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70260047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854804039001</t>
   </si>
   <si>
     <t xml:space="preserve">3.72956132888794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72237157821655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72776365280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292730331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831913948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541072845459</t>
+    <t xml:space="preserve">3.72237181663513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72776341438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831890106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541096687317</t>
   </si>
   <si>
     <t xml:space="preserve">3.68462657928467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6936137676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68822145462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135876655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7133846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8338086605072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224060058594</t>
+    <t xml:space="preserve">3.69361352920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66485571861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68822121620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168511390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380913734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224083900452</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82661938667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841753959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547535896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90031266212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335181236267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639072418213</t>
+    <t xml:space="preserve">3.82661914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8284170627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547583580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9003119468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335133552551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
   </si>
   <si>
     <t xml:space="preserve">3.83740377426147</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">3.87514877319336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94165229797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929865837097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243549346924</t>
+    <t xml:space="preserve">3.94165205955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929913520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243620872498</t>
   </si>
   <si>
     <t xml:space="preserve">3.98119378089905</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">3.97939658164978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88413524627686</t>
+    <t xml:space="preserve">3.88413572311401</t>
   </si>
   <si>
     <t xml:space="preserve">3.94884133338928</t>
@@ -500,37 +500,37 @@
     <t xml:space="preserve">3.87874341011047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01534414291382</t>
+    <t xml:space="preserve">4.01534461975098</t>
   </si>
   <si>
     <t xml:space="preserve">4.02073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00815486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04050731658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0530891418457</t>
+    <t xml:space="preserve">4.00815439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04050779342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05309009552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.01714181900024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06207609176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07106351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14295864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06926536560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08903741836548</t>
+    <t xml:space="preserve">4.06207656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07106304168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14295816421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0692663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08903694152832</t>
   </si>
   <si>
     <t xml:space="preserve">4.40357828140259</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34606266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785890579224</t>
+    <t xml:space="preserve">4.34606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785938262939</t>
   </si>
   <si>
     <t xml:space="preserve">4.32808828353882</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">4.27236986160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11599779129028</t>
+    <t xml:space="preserve">4.11599731445312</t>
   </si>
   <si>
     <t xml:space="preserve">4.03691339492798</t>
@@ -563,55 +563,55 @@
     <t xml:space="preserve">4.04230546951294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008376121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828584671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704461097717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266439437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099888801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795949935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90390682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524621963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9635968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99112129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194718360901</t>
+    <t xml:space="preserve">3.95603060722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008352279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828560829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704413414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93266487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795878410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90390729904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96359634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99112176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194646835327</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89019656181335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87184596061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92689657211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452131271362</t>
+    <t xml:space="preserve">3.8901960849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8718466758728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452178955078</t>
   </si>
   <si>
     <t xml:space="preserve">4.128746509552</t>
@@ -623,31 +623,31 @@
     <t xml:space="preserve">4.12691164016724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10672616958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05901670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03699684143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99479150772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05351161956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0828709602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03332662582397</t>
+    <t xml:space="preserve">4.10672569274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05901622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03699588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99479198455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05351114273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08287143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03332614898682</t>
   </si>
   <si>
     <t xml:space="preserve">4.07369613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09204626083374</t>
+    <t xml:space="preserve">4.0920467376709</t>
   </si>
   <si>
     <t xml:space="preserve">4.08103656768799</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">4.05534696578979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09021091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06268644332886</t>
+    <t xml:space="preserve">4.09021139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0626859664917</t>
   </si>
   <si>
     <t xml:space="preserve">4.15260171890259</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">4.16544628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11039638519287</t>
+    <t xml:space="preserve">4.11039686203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.09388160705566</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">4.20948600769043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1544361114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507629394531</t>
+    <t xml:space="preserve">4.15443658828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13792181015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507677078247</t>
   </si>
   <si>
     <t xml:space="preserve">4.11957120895386</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">4.15076637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10305595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17278671264648</t>
+    <t xml:space="preserve">4.10305643081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17278623580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10122156143188</t>
+    <t xml:space="preserve">4.07002592086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10122108459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.16911697387695</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01864624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07920169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1342511177063</t>
+    <t xml:space="preserve">4.01864671707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07920122146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13425159454346</t>
   </si>
   <si>
     <t xml:space="preserve">4.21866130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13241720199585</t>
+    <t xml:space="preserve">4.13241672515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.12140655517578</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">4.11773633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14709615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14893198013306</t>
+    <t xml:space="preserve">4.14709663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1489315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.19113636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19297170639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662613868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04433679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341135025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02048206329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92322611808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03516101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08654069900513</t>
+    <t xml:space="preserve">4.19297122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662637710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04433631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02048110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92322635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03516149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
     <t xml:space="preserve">4.04800701141357</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0002965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97277164459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93790650367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99846196174622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04617118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88102173805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349678993225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442175865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514642715454</t>
+    <t xml:space="preserve">4.00029611587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97277116775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93790698051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846124649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04617166519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88102149963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349631309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514666557312</t>
   </si>
   <si>
     <t xml:space="preserve">3.8993718624115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90854716300964</t>
+    <t xml:space="preserve">3.90854692459106</t>
   </si>
   <si>
     <t xml:space="preserve">3.9360716342926</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">3.86267161369324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82597160339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78927206993103</t>
+    <t xml:space="preserve">3.82597184181213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78927183151245</t>
   </si>
   <si>
     <t xml:space="preserve">3.80762195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039432525635</t>
+    <t xml:space="preserve">4.02039480209351</t>
   </si>
   <si>
     <t xml:space="preserve">4.04857444763184</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">4.03918123245239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97342705726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221396446228</t>
+    <t xml:space="preserve">3.97342658042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922137260437</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403288841248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827942848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91706609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616477012634</t>
+    <t xml:space="preserve">3.96403360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827990531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9170663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75737762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73859047889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980404853821</t>
+    <t xml:space="preserve">3.7573778629303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73859095573425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980428695679</t>
   </si>
   <si>
     <t xml:space="preserve">3.71041059494019</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">3.6258692741394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52254176139832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28770542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35345935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33467268943787</t>
+    <t xml:space="preserve">3.52254152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860722541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28770565986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35345959663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33467292785645</t>
   </si>
   <si>
     <t xml:space="preserve">3.37224650382996</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">3.38163995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45678782463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4661808013916</t>
+    <t xml:space="preserve">3.45678758621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
     <t xml:space="preserve">3.36285281181335</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">3.43800067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40042662620544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47557425498962</t>
+    <t xml:space="preserve">3.40042686462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4755744934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.49436140060425</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">3.31588578224182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60708236694336</t>
+    <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
     <t xml:space="preserve">3.56950879096985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50375461578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65405011177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48496794700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68223023414612</t>
+    <t xml:space="preserve">3.50375485420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65404987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48496770858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68222999572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.59768915176392</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">3.61647605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58829569816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5507218837738</t>
+    <t xml:space="preserve">3.66344332695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58829545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55072212219238</t>
   </si>
   <si>
     <t xml:space="preserve">3.53193497657776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56011533737183</t>
+    <t xml:space="preserve">3.56011557579041</t>
   </si>
   <si>
     <t xml:space="preserve">3.57890224456787</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">3.64465641975403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67283654212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51314806938171</t>
+    <t xml:space="preserve">3.67283701896667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51314830780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54921531677246</t>
+    <t xml:space="preserve">3.5492148399353</t>
   </si>
   <si>
     <t xml:space="preserve">3.62637186050415</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">3.58779358863831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66495013237</t>
+    <t xml:space="preserve">3.66495037078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">3.7999746799469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210739135742</t>
+    <t xml:space="preserve">3.74210715293884</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855295181274</t>
+    <t xml:space="preserve">3.8385534286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">3.64566111564636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60708260536194</t>
+    <t xml:space="preserve">3.60708284378052</t>
   </si>
   <si>
     <t xml:space="preserve">3.56850433349609</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.41419053077698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43347978591919</t>
+    <t xml:space="preserve">3.43347954750061</t>
   </si>
   <si>
     <t xml:space="preserve">3.45276880264282</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916598320007</t>
+    <t xml:space="preserve">3.27916622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71977877616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83551406860352</t>
+    <t xml:space="preserve">2.7197790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83551430702209</t>
   </si>
   <si>
     <t xml:space="preserve">2.97053861618042</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">3.12485241889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98982787132263</t>
+    <t xml:space="preserve">2.98982763290405</t>
   </si>
   <si>
     <t xml:space="preserve">2.95124959945679</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73906803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54617619514465</t>
+    <t xml:space="preserve">2.73906779289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54617595672607</t>
   </si>
   <si>
     <t xml:space="preserve">2.62333297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60404372215271</t>
+    <t xml:space="preserve">2.60404396057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.5847544670105</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">2.33399486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16039180755615</t>
+    <t xml:space="preserve">2.16039204597473</t>
   </si>
   <si>
     <t xml:space="preserve">2.04465627670288</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">2.14110255241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23754835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02536749839783</t>
+    <t xml:space="preserve">2.23754858970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02536725997925</t>
   </si>
   <si>
     <t xml:space="preserve">2.198970079422</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">2.25683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29541635513306</t>
+    <t xml:space="preserve">2.29541611671448</t>
   </si>
   <si>
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648259162903</t>
+    <t xml:space="preserve">2.26648211479187</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044090270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27612686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577136993408</t>
+    <t xml:space="preserve">2.43044066429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27612709999084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577160835266</t>
   </si>
   <si>
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292862892151</t>
+    <t xml:space="preserve">2.36292839050293</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506110191345</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35328388214111</t>
+    <t xml:space="preserve">2.35328412055969</t>
   </si>
   <si>
     <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17968106269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18932580947876</t>
+    <t xml:space="preserve">2.17968082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18932557106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.17003631591797</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216855049133</t>
+    <t xml:space="preserve">2.11216902732849</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03501152992249</t>
+    <t xml:space="preserve">2.03501176834106</t>
   </si>
   <si>
     <t xml:space="preserve">1.98678886890411</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">1.92892122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93856585025787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9578549861908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20861458778381</t>
+    <t xml:space="preserve">1.93856573104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95785510540009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20861482620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.15074706077576</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">2.37257313728333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38221764564514</t>
+    <t xml:space="preserve">2.38221788406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">2.65226674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61368846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53653168678284</t>
+    <t xml:space="preserve">2.61368823051453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53653144836426</t>
   </si>
   <si>
     <t xml:space="preserve">2.52688670158386</t>
@@ -1334,40 +1334,40 @@
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013450622559</t>
+    <t xml:space="preserve">2.71013402938843</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72942328453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78729152679443</t>
+    <t xml:space="preserve">2.72942352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78729128837585</t>
   </si>
   <si>
     <t xml:space="preserve">2.94160485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99947237968445</t>
+    <t xml:space="preserve">2.99947261810303</t>
   </si>
   <si>
     <t xml:space="preserve">2.98018312454224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9608941078186</t>
+    <t xml:space="preserve">2.96089386940002</t>
   </si>
   <si>
     <t xml:space="preserve">3.03805088996887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343069076538</t>
+    <t xml:space="preserve">3.16343092918396</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23094320297241</t>
+    <t xml:space="preserve">3.23094296455383</t>
   </si>
   <si>
     <t xml:space="preserve">3.24058747291565</t>
@@ -1376,40 +1376,40 @@
     <t xml:space="preserve">3.19236469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1730751991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13449716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378618240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952171325684</t>
+    <t xml:space="preserve">3.17307543754578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378594398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952147483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30810022354126</t>
+    <t xml:space="preserve">3.30809998512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25023198127747</t>
+    <t xml:space="preserve">3.25023221969604</t>
   </si>
   <si>
     <t xml:space="preserve">3.09591865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07662916183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01876187324524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05734038352966</t>
+    <t xml:space="preserve">3.0766294002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01876163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05734014511108</t>
   </si>
   <si>
     <t xml:space="preserve">2.92231559753418</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90302634239197</t>
+    <t xml:space="preserve">2.90302658081055</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373732566833</t>
@@ -1430,46 +1430,46 @@
     <t xml:space="preserve">2.84515881538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80658030509949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11520767211914</t>
+    <t xml:space="preserve">2.80658054351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11520791053772</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743785858154</t>
+    <t xml:space="preserve">3.59743809700012</t>
   </si>
   <si>
     <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71317338943481</t>
+    <t xml:space="preserve">3.71317315101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88677644729614</t>
+    <t xml:space="preserve">3.88677668571472</t>
   </si>
   <si>
     <t xml:space="preserve">3.95428848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94464373588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9832227230072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073499679565</t>
+    <t xml:space="preserve">3.94464421272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98322248458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507345199585</t>
   </si>
   <si>
     <t xml:space="preserve">3.97357773780823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002305984497</t>
+    <t xml:space="preserve">4.07002353668213</t>
   </si>
   <si>
     <t xml:space="preserve">4.20504856109619</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971714019775</t>
+    <t xml:space="preserve">4.34971809387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22433710098267</t>
+    <t xml:space="preserve">4.22433805465698</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144550323486</t>
+    <t xml:space="preserve">4.03144454956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">4.31113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2918496131897</t>
+    <t xml:space="preserve">4.29185009002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.40758514404297</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53296518325806</t>
+    <t xml:space="preserve">4.53296422958374</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">4.36900663375854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12789154052734</t>
+    <t xml:space="preserve">4.1278920173645</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
@@ -1541,37 +1541,37 @@
     <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18575954437256</t>
+    <t xml:space="preserve">4.1857590675354</t>
   </si>
   <si>
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180051803589</t>
+    <t xml:space="preserve">4.02180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611455917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33042812347412</t>
+    <t xml:space="preserve">4.17611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33042764663696</t>
   </si>
   <si>
     <t xml:space="preserve">4.51367568969727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46545314788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37865161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48474168777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47509670257568</t>
+    <t xml:space="preserve">4.46545267105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37865114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48474216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47509717941284</t>
   </si>
   <si>
     <t xml:space="preserve">4.49438619613647</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">4.44616365432739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41722917556763</t>
+    <t xml:space="preserve">4.41722965240479</t>
   </si>
   <si>
     <t xml:space="preserve">4.64870023727417</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585725784302</t>
+    <t xml:space="preserve">4.72585678100586</t>
   </si>
   <si>
     <t xml:space="preserve">4.63905572891235</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">4.6101222038269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154273986816</t>
+    <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.27256011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11824703216553</t>
+    <t xml:space="preserve">4.11824655532837</t>
   </si>
   <si>
     <t xml:space="preserve">4.15682506561279</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260921478271</t>
+    <t xml:space="preserve">4.54260969161987</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372430801392</t>
+    <t xml:space="preserve">4.78372478485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45884656906128</t>
+    <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
     <t xml:space="preserve">5.59387159347534</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026901245117</t>
+    <t xml:space="preserve">5.42026805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088180541992</t>
+    <t xml:space="preserve">4.86088132858276</t>
   </si>
   <si>
     <t xml:space="preserve">4.84159231185913</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9610013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13747978210449</t>
+    <t xml:space="preserve">4.87276268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96100187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13748025894165</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432773590088</t>
+    <t xml:space="preserve">5.00021886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432725906372</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667531967163</t>
+    <t xml:space="preserve">4.67667579650879</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1730,22 +1730,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413198471069</t>
+    <t xml:space="preserve">4.72569704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413246154785</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687154769897</t>
+    <t xml:space="preserve">4.92178392410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354520797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687107086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000165939331</t>
+    <t xml:space="preserve">4.74530649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59824085235596</t>
+    <t xml:space="preserve">4.5982403755188</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921865463257</t>
+    <t xml:space="preserve">4.54921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1820,40 +1820,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254499435425</t>
+    <t xml:space="preserve">4.38254451751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3237190246582</t>
+    <t xml:space="preserve">4.32371854782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508880615234</t>
+    <t xml:space="preserve">4.26489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587133407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508832931519</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13743591308594</t>
+    <t xml:space="preserve">4.1374363899231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117568969727</t>
+    <t xml:space="preserve">4.33352375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117521286011</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274026870728</t>
+    <t xml:space="preserve">4.37274074554443</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1668496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1962628364563</t>
+    <t xml:space="preserve">4.16684913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19626235961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -68115,7 +68115,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6346296296</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>1100</v>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105989456177</t>
+    <t xml:space="preserve">3.87106013298035</t>
   </si>
   <si>
     <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86577582359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401510238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652358055115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74249386787415</t>
+    <t xml:space="preserve">3.8657763004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401534080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652334213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74249410629272</t>
   </si>
   <si>
     <t xml:space="preserve">3.79532957077026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77771782875061</t>
+    <t xml:space="preserve">3.77771759033203</t>
   </si>
   <si>
     <t xml:space="preserve">3.62977933883667</t>
@@ -74,40 +74,40 @@
     <t xml:space="preserve">3.67733097076416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65443563461304</t>
+    <t xml:space="preserve">3.65443539619446</t>
   </si>
   <si>
     <t xml:space="preserve">3.663241147995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6438684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712396621704</t>
+    <t xml:space="preserve">3.64386868476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712420463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68965911865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66676354408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6033616065979</t>
+    <t xml:space="preserve">3.68965935707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66676378250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336136817932</t>
   </si>
   <si>
     <t xml:space="preserve">3.68085312843323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56637716293335</t>
+    <t xml:space="preserve">3.56637692451477</t>
   </si>
   <si>
     <t xml:space="preserve">3.539959192276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61568927764893</t>
+    <t xml:space="preserve">3.61568975448608</t>
   </si>
   <si>
     <t xml:space="preserve">3.64915204048157</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">3.65091323852539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64210748672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431517601013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.751300573349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294131278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79356837272644</t>
+    <t xml:space="preserve">3.6421070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75130009651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294107437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79356861114502</t>
   </si>
   <si>
     <t xml:space="preserve">3.86225414276123</t>
@@ -143,148 +143,148 @@
     <t xml:space="preserve">3.81470227241516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80941939353943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73721075057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891207695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538920402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74953866004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74601650238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73016571998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613600730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350850105286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383477210999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9186110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446135520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98377537727356</t>
+    <t xml:space="preserve">3.80941915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721051216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255421638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192715644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.721360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538944244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74953889846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74601626396179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016595840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846487045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68613648414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383501052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91861081123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446183204651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98377466201782</t>
   </si>
   <si>
     <t xml:space="preserve">3.94326829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91508960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9855363368988</t>
+    <t xml:space="preserve">3.91508984565735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98553681373596</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332769393921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89395499229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96088004112244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219403266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622279167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741751670837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9991672039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02612829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220754623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9901807308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759890556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04410266876221</t>
+    <t xml:space="preserve">3.89395546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96087956428528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219355583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622374534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741703987122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338780403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0261287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220683097839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018120765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759938240051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04410219192505</t>
   </si>
   <si>
     <t xml:space="preserve">3.98299193382263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95423340797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625974655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233828544617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9272735118866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367792129517</t>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625950813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92727303504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
   </si>
   <si>
     <t xml:space="preserve">3.83560633659363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89132499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436438560486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81942963600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799231529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655086517334</t>
+    <t xml:space="preserve">3.89132523536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256718635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81942987442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799255371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76550889015198</t>
   </si>
   <si>
     <t xml:space="preserve">3.59475779533386</t>
@@ -293,19 +293,19 @@
     <t xml:space="preserve">3.61273145675659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67923426628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6307053565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62171840667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65766572952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63789486885071</t>
+    <t xml:space="preserve">3.67923474311829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070511817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62171864509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65766620635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63789463043213</t>
   </si>
   <si>
     <t xml:space="preserve">3.68103194236755</t>
@@ -314,52 +314,52 @@
     <t xml:space="preserve">3.57318925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61632657051086</t>
+    <t xml:space="preserve">3.61632680892944</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64688158035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6918158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675084114075</t>
+    <t xml:space="preserve">3.64688205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69181561470032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675107955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.75652146339417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80325317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616230010986</t>
+    <t xml:space="preserve">3.80325365066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616134643555</t>
   </si>
   <si>
     <t xml:space="preserve">3.8176326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81044268608093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394011497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449512481689</t>
+    <t xml:space="preserve">3.81044316291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246926307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74394035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449560165405</t>
   </si>
   <si>
     <t xml:space="preserve">3.79067206382751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77629375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887438774109</t>
+    <t xml:space="preserve">3.77629327774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887462615967</t>
   </si>
   <si>
     <t xml:space="preserve">3.74753499031067</t>
@@ -368,43 +368,43 @@
     <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80145597457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73315596580505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348302841187</t>
+    <t xml:space="preserve">3.80145573616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348255157471</t>
   </si>
   <si>
     <t xml:space="preserve">3.72416877746582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090096473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057414054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978975296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70260047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854780197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956109046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72237157821655</t>
+    <t xml:space="preserve">3.77090072631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978951454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7026002407074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854756355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72237181663513</t>
   </si>
   <si>
     <t xml:space="preserve">3.72776365280151</t>
@@ -425,91 +425,91 @@
     <t xml:space="preserve">3.69361352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66485524177551</t>
+    <t xml:space="preserve">3.66485571861267</t>
   </si>
   <si>
     <t xml:space="preserve">3.68822121620178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73135852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338510513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380889892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224083900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81583571434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82661914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841730117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547535896301</t>
+    <t xml:space="preserve">3.73135828971863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8338086605072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81583523750305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82661962509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8284170627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547512054443</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446230888367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9003119468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639096260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740401268005</t>
+    <t xml:space="preserve">3.92188024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335157394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740377426147</t>
   </si>
   <si>
     <t xml:space="preserve">3.87514853477478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9416515827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929841995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9524359703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98119401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94884133338928</t>
+    <t xml:space="preserve">3.94165182113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929913520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243573188782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98119425773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97939658164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413548469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94884157180786</t>
   </si>
   <si>
     <t xml:space="preserve">3.87874364852905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01534366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0207371711731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00815486907959</t>
+    <t xml:space="preserve">4.01534414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02073621749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00815439224243</t>
   </si>
   <si>
     <t xml:space="preserve">4.04050731658936</t>
@@ -518,28 +518,28 @@
     <t xml:space="preserve">4.05308961868286</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01714134216309</t>
+    <t xml:space="preserve">4.01714181900024</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207656860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07106351852417</t>
+    <t xml:space="preserve">4.07106304168701</t>
   </si>
   <si>
     <t xml:space="preserve">4.14295816421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0692663192749</t>
+    <t xml:space="preserve">4.06926536560059</t>
   </si>
   <si>
     <t xml:space="preserve">4.08903694152832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40357875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37661790847778</t>
+    <t xml:space="preserve">4.40357828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
     <t xml:space="preserve">4.34606218338013</t>
@@ -557,82 +557,82 @@
     <t xml:space="preserve">4.11599731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03691291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98478865623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04230546951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603060722351</t>
+    <t xml:space="preserve">4.03691339492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9847891330719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603084564209</t>
   </si>
   <si>
     <t xml:space="preserve">3.92008280754089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91828608512878</t>
+    <t xml:space="preserve">3.91828656196594</t>
   </si>
   <si>
     <t xml:space="preserve">3.94704413414001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93266463279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099888801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795878410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90390729904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524621963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9635968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99112105369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194622993469</t>
+    <t xml:space="preserve">3.9326651096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099841117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795949935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90390706062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524645805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96359658241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99112129211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194670677185</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819105148315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8901960849762</t>
+    <t xml:space="preserve">3.89019656181335</t>
   </si>
   <si>
     <t xml:space="preserve">3.8718466758728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92689728736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.128746509552</t>
+    <t xml:space="preserve">3.92689681053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874698638916</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10672664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05901575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03699636459351</t>
+    <t xml:space="preserve">4.12691164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10672616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05901622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03699684143066</t>
   </si>
   <si>
     <t xml:space="preserve">3.99479150772095</t>
@@ -641,40 +641,40 @@
     <t xml:space="preserve">4.05351161956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08287048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07369613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920467376709</t>
+    <t xml:space="preserve">4.0828709602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03332662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07369661331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09204626083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.08103656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05534696578979</t>
+    <t xml:space="preserve">4.05534648895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.09021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06268692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15260124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15627098083496</t>
+    <t xml:space="preserve">4.06268644332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15260171890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
     <t xml:space="preserve">4.16544580459595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11039638519287</t>
+    <t xml:space="preserve">4.11039590835571</t>
   </si>
   <si>
     <t xml:space="preserve">4.09388113021851</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">4.20948600769043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15443706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792181015015</t>
+    <t xml:space="preserve">4.15443658828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13792133331299</t>
   </si>
   <si>
     <t xml:space="preserve">4.12507629394531</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">4.11957120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13608598709106</t>
+    <t xml:space="preserve">4.13608646392822</t>
   </si>
   <si>
     <t xml:space="preserve">4.15076637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10305595397949</t>
+    <t xml:space="preserve">4.10305643081665</t>
   </si>
   <si>
     <t xml:space="preserve">4.17278623580933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11223125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07002639770508</t>
+    <t xml:space="preserve">4.11223173141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07002592086792</t>
   </si>
   <si>
     <t xml:space="preserve">4.10122156143188</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.16911697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18379688262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21132135391235</t>
+    <t xml:space="preserve">4.18379640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21132183074951</t>
   </si>
   <si>
     <t xml:space="preserve">4.0975513458252</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">4.07920122146606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13425159454346</t>
+    <t xml:space="preserve">4.1342511177063</t>
   </si>
   <si>
     <t xml:space="preserve">4.21866130828857</t>
@@ -758,49 +758,49 @@
     <t xml:space="preserve">4.14709663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14893102645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1911358833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19297218322754</t>
+    <t xml:space="preserve">4.1489315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19113636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19297170639038</t>
   </si>
   <si>
     <t xml:space="preserve">3.99662613868713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04433584213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341111183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02048063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92322659492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03516054153442</t>
+    <t xml:space="preserve">4.04433631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561644554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341135025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02048110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92322635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03516101837158</t>
   </si>
   <si>
     <t xml:space="preserve">4.08654165267944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726632118225</t>
+    <t xml:space="preserve">4.04800653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726679801941</t>
   </si>
   <si>
     <t xml:space="preserve">3.92506170272827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91772198677063</t>
+    <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029706954956</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">3.97277140617371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93790602684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99846124649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04617166519165</t>
+    <t xml:space="preserve">3.93790578842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846148490906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04617118835449</t>
   </si>
   <si>
     <t xml:space="preserve">3.88102126121521</t>
@@ -827,76 +827,76 @@
     <t xml:space="preserve">3.95442152023315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83514618873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854716300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93607139587402</t>
+    <t xml:space="preserve">3.83514642715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89937138557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854692459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93607187271118</t>
   </si>
   <si>
     <t xml:space="preserve">3.86267185211182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82597184181213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78927183151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.807621717453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039480209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04857444763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03918075561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97342658042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02978754043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96403360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827942848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9170663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616429328918</t>
+    <t xml:space="preserve">3.82597160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78927206993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80762147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04857397079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03918123245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97342681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99221348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02978801727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96403336524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91706609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.70101714134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7573778629303</t>
+    <t xml:space="preserve">3.75737762451172</t>
   </si>
   <si>
     <t xml:space="preserve">3.73859095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980404853821</t>
+    <t xml:space="preserve">3.71980381011963</t>
   </si>
   <si>
     <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63526248931885</t>
+    <t xml:space="preserve">3.63526272773743</t>
   </si>
   <si>
     <t xml:space="preserve">3.62586951255798</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">3.52254152297974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42860698699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28770542144775</t>
+    <t xml:space="preserve">3.42860722541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28770518302917</t>
   </si>
   <si>
     <t xml:space="preserve">3.35345959663391</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">3.37224650382996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38163995742798</t>
+    <t xml:space="preserve">3.3816397190094</t>
   </si>
   <si>
     <t xml:space="preserve">3.45678758621216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46618103981018</t>
+    <t xml:space="preserve">3.4661808013916</t>
   </si>
   <si>
     <t xml:space="preserve">3.36285305023193</t>
@@ -941,114 +941,114 @@
     <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47557425498962</t>
+    <t xml:space="preserve">3.4755744934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.49436116218567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3158860206604</t>
+    <t xml:space="preserve">3.31588578224182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60708236694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56950879096985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50375485420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65404987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48496794700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68223023414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5976893901825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66344356536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58829569816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5507218837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193497657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56011557579041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57890200614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64465641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6728367805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51314806938171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70352864265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54921531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62637186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58779358863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68423938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068566322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7999746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210739135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81926417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83855295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85784244537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76139640808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72281789779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64566111564636</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950879096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50375485420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65404987335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48496794700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68222999572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59768915176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58829545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55072212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193497657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56011557579041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57890224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6728367805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51314830780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70352864265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5492148399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62637186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58779358863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68423938751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068566322327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7999746799469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210715293884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81926417350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8385534286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85784244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76139640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72281789779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64566111564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60708284378052</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">3.41419053077698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43347954750061</t>
+    <t xml:space="preserve">3.43347978591919</t>
   </si>
   <si>
     <t xml:space="preserve">3.45276880264282</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916622161865</t>
+    <t xml:space="preserve">3.27916598320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7197790145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83551430702209</t>
+    <t xml:space="preserve">2.71977877616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83551406860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.97053861618042</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">3.12485241889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98982763290405</t>
+    <t xml:space="preserve">2.98982787132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.95124959945679</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73906779289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54617595672607</t>
+    <t xml:space="preserve">2.73906803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54617619514465</t>
   </si>
   <si>
     <t xml:space="preserve">2.62333297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60404396057129</t>
+    <t xml:space="preserve">2.60404372215271</t>
   </si>
   <si>
     <t xml:space="preserve">2.5847544670105</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">2.33399486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16039204597473</t>
+    <t xml:space="preserve">2.16039180755615</t>
   </si>
   <si>
     <t xml:space="preserve">2.04465627670288</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">2.14110255241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23754858970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02536725997925</t>
+    <t xml:space="preserve">2.23754835128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02536749839783</t>
   </si>
   <si>
     <t xml:space="preserve">2.198970079422</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">2.25683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29541611671448</t>
+    <t xml:space="preserve">2.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648211479187</t>
+    <t xml:space="preserve">2.26648259162903</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1217,19 +1217,19 @@
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044066429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27612709999084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577160835266</t>
+    <t xml:space="preserve">2.43044090270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27612686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577136993408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292839050293</t>
+    <t xml:space="preserve">2.36292862892151</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506110191345</t>
@@ -1241,16 +1241,16 @@
     <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35328412055969</t>
+    <t xml:space="preserve">2.35328388214111</t>
   </si>
   <si>
     <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17968082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18932557106018</t>
+    <t xml:space="preserve">2.17968106269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18932580947876</t>
   </si>
   <si>
     <t xml:space="preserve">2.17003631591797</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216902732849</t>
+    <t xml:space="preserve">2.11216855049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03501176834106</t>
+    <t xml:space="preserve">2.03501152992249</t>
   </si>
   <si>
     <t xml:space="preserve">1.98678886890411</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">1.92892122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93856573104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95785510540009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20861482620239</t>
+    <t xml:space="preserve">1.93856585025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9578549861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20861458778381</t>
   </si>
   <si>
     <t xml:space="preserve">2.15074706077576</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">2.37257313728333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38221788406372</t>
+    <t xml:space="preserve">2.38221764564514</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">2.65226674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61368823051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53653144836426</t>
+    <t xml:space="preserve">2.61368846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53653168678284</t>
   </si>
   <si>
     <t xml:space="preserve">2.52688670158386</t>
@@ -1337,40 +1337,40 @@
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013402938843</t>
+    <t xml:space="preserve">2.71013450622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78729128837585</t>
+    <t xml:space="preserve">2.72942328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78729152679443</t>
   </si>
   <si>
     <t xml:space="preserve">2.94160485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99947261810303</t>
+    <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
     <t xml:space="preserve">2.98018312454224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96089386940002</t>
+    <t xml:space="preserve">2.9608941078186</t>
   </si>
   <si>
     <t xml:space="preserve">3.03805088996887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343092918396</t>
+    <t xml:space="preserve">3.16343069076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23094296455383</t>
+    <t xml:space="preserve">3.23094320297241</t>
   </si>
   <si>
     <t xml:space="preserve">3.24058747291565</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">3.19236469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17307543754578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952147483826</t>
+    <t xml:space="preserve">3.1730751991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378618240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952171325684</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30809998512268</t>
+    <t xml:space="preserve">3.30810022354126</t>
   </si>
   <si>
     <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25023221969604</t>
+    <t xml:space="preserve">3.25023198127747</t>
   </si>
   <si>
     <t xml:space="preserve">3.09591865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0766294002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05734014511108</t>
+    <t xml:space="preserve">3.07662916183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01876187324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05734038352966</t>
   </si>
   <si>
     <t xml:space="preserve">2.92231559753418</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90302658081055</t>
+    <t xml:space="preserve">2.90302634239197</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373732566833</t>
@@ -1433,46 +1433,46 @@
     <t xml:space="preserve">2.84515881538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80658054351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">2.80658030509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
+    <t xml:space="preserve">3.59743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71317315101624</t>
+    <t xml:space="preserve">3.71317338943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88677668571472</t>
+    <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
     <t xml:space="preserve">3.95428848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94464421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98322248458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507345199585</t>
+    <t xml:space="preserve">3.94464373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9832227230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073499679565</t>
   </si>
   <si>
     <t xml:space="preserve">3.97357773780823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002353668213</t>
+    <t xml:space="preserve">4.07002305984497</t>
   </si>
   <si>
     <t xml:space="preserve">4.20504856109619</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971809387207</t>
+    <t xml:space="preserve">4.34971714019775</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1502,13 +1502,13 @@
     <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22433805465698</t>
+    <t xml:space="preserve">4.22433710098267</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144454956055</t>
+    <t xml:space="preserve">4.03144550323486</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">4.31113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29185009002686</t>
+    <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
     <t xml:space="preserve">4.40758514404297</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53296422958374</t>
+    <t xml:space="preserve">4.53296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">4.36900663375854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1278920173645</t>
+    <t xml:space="preserve">4.12789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
@@ -1544,37 +1544,37 @@
     <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1857590675354</t>
+    <t xml:space="preserve">4.18575954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180099487305</t>
+    <t xml:space="preserve">4.02180051803589</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33042764663696</t>
+    <t xml:space="preserve">4.17611455917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33042812347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.51367568969727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46545267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37865114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48474216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47509717941284</t>
+    <t xml:space="preserve">4.46545314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37865161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48474168777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47509670257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.49438619613647</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">4.44616365432739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41722965240479</t>
+    <t xml:space="preserve">4.41722917556763</t>
   </si>
   <si>
     <t xml:space="preserve">4.64870023727417</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585678100586</t>
+    <t xml:space="preserve">4.72585725784302</t>
   </si>
   <si>
     <t xml:space="preserve">4.63905572891235</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">4.6101222038269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154321670532</t>
+    <t xml:space="preserve">4.57154273986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.27256011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11824655532837</t>
+    <t xml:space="preserve">4.11824703216553</t>
   </si>
   <si>
     <t xml:space="preserve">4.15682506561279</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372478485107</t>
+    <t xml:space="preserve">4.78372430801392</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45884704589844</t>
+    <t xml:space="preserve">5.45884656906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.59387159347534</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026805877686</t>
+    <t xml:space="preserve">5.42026901245117</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088132858276</t>
+    <t xml:space="preserve">4.86088180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.84159231185913</t>
@@ -1679,13 +1679,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96100187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13748025894165</t>
+    <t xml:space="preserve">4.87276220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9610013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432725906372</t>
+    <t xml:space="preserve">5.00021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432773590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667579650879</t>
+    <t xml:space="preserve">4.67667531967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413246154785</t>
+    <t xml:space="preserve">4.72569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413198471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687107086182</t>
+    <t xml:space="preserve">4.92178440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687154769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000118255615</t>
+    <t xml:space="preserve">4.74530601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000165939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5982403755188</t>
+    <t xml:space="preserve">4.59824085235596</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921913146973</t>
+    <t xml:space="preserve">4.54921865463257</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1823,40 +1823,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254451751709</t>
+    <t xml:space="preserve">4.38254499435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32371854782104</t>
+    <t xml:space="preserve">4.3237190246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508832931519</t>
+    <t xml:space="preserve">4.264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508880615234</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1374363899231</t>
+    <t xml:space="preserve">4.13743591308594</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352375030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117521286011</t>
+    <t xml:space="preserve">4.33352327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117568969727</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274074554443</t>
+    <t xml:space="preserve">4.37274026870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16684913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19626235961914</t>
+    <t xml:space="preserve">4.1668496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1962628364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -68196,7 +68196,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.5849884259</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>175</v>
@@ -68217,6 +68217,32 @@
         <v>743</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6845717593</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>800</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>4.44000005722046</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>737</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,70 +38,70 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282109260559</t>
+    <t xml:space="preserve">3.87282133102417</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105989456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458276748657</t>
+    <t xml:space="preserve">3.87105965614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86401557922363</t>
+    <t xml:space="preserve">3.86401510238647</t>
   </si>
   <si>
     <t xml:space="preserve">3.78652405738831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74249386787415</t>
+    <t xml:space="preserve">3.74249458312988</t>
   </si>
   <si>
     <t xml:space="preserve">3.79532957077026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77771735191345</t>
+    <t xml:space="preserve">3.77771782875061</t>
   </si>
   <si>
     <t xml:space="preserve">3.62977933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67733073234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443563461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66324162483215</t>
+    <t xml:space="preserve">3.67733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443587303162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.663241147995</t>
   </si>
   <si>
     <t xml:space="preserve">3.64386868476868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48712420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040592193604</t>
+    <t xml:space="preserve">3.4871244430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
     <t xml:space="preserve">3.68965935707092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6667640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60336136817932</t>
+    <t xml:space="preserve">3.66676378250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6033616065979</t>
   </si>
   <si>
     <t xml:space="preserve">3.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56637716293335</t>
+    <t xml:space="preserve">3.56637740135193</t>
   </si>
   <si>
     <t xml:space="preserve">3.539959192276</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">3.61568975448608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64915204048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65267395973206</t>
+    <t xml:space="preserve">3.64915227890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
     <t xml:space="preserve">3.65091300010681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64210724830627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431565284729</t>
+    <t xml:space="preserve">3.64210748672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431493759155</t>
   </si>
   <si>
     <t xml:space="preserve">3.751300573349</t>
@@ -137,106 +137,106 @@
     <t xml:space="preserve">3.79356837272644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86225414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81470227241516</t>
+    <t xml:space="preserve">3.86225390434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470203399658</t>
   </si>
   <si>
     <t xml:space="preserve">3.80941915512085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73368835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73721075057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255397796631</t>
+    <t xml:space="preserve">3.73368763923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721051216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255421638489</t>
   </si>
   <si>
     <t xml:space="preserve">3.73192715644836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.721360206604</t>
+    <t xml:space="preserve">3.72135972976685</t>
   </si>
   <si>
     <t xml:space="preserve">3.76891231536865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76538944244385</t>
+    <t xml:space="preserve">3.76538991928101</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953866004944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74601674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73016595840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6984646320343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613696098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488307952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350778579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9186110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446159362793</t>
+    <t xml:space="preserve">3.74601721763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016571998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846439361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488236427307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8235080242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91861128807068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446230888367</t>
   </si>
   <si>
     <t xml:space="preserve">3.98377537727356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94326782226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98553586006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087980270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219403266907</t>
+    <t xml:space="preserve">3.94326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508984565735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98553681373596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9608793258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219450950623</t>
   </si>
   <si>
     <t xml:space="preserve">3.93622303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92741775512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338804244995</t>
+    <t xml:space="preserve">3.92741799354553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338756561279</t>
   </si>
   <si>
     <t xml:space="preserve">3.99916791915894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0261287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220706939697</t>
+    <t xml:space="preserve">4.02612829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220754623413</t>
   </si>
   <si>
     <t xml:space="preserve">3.99018144607544</t>
@@ -254,37 +254,37 @@
     <t xml:space="preserve">3.95423340797424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93626022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233780860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92727279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9236786365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560609817505</t>
+    <t xml:space="preserve">3.93625950813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92727255821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560657501221</t>
   </si>
   <si>
     <t xml:space="preserve">3.8913254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86436486244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256718635559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81943011283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799231529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76550912857056</t>
+    <t xml:space="preserve">3.86436462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256766319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8194305896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799279212952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7655086517334</t>
   </si>
   <si>
     <t xml:space="preserve">3.59475779533386</t>
@@ -293,67 +293,67 @@
     <t xml:space="preserve">3.61273121833801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67923426628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6307053565979</t>
+    <t xml:space="preserve">3.67923450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070511817932</t>
   </si>
   <si>
     <t xml:space="preserve">3.62171840667725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65766620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103194236755</t>
+    <t xml:space="preserve">3.65766596794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63789486885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103218078613</t>
   </si>
   <si>
     <t xml:space="preserve">3.57318925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61632633209229</t>
+    <t xml:space="preserve">3.61632657051086</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64688205718994</t>
+    <t xml:space="preserve">3.64688181877136</t>
   </si>
   <si>
     <t xml:space="preserve">3.69181609153748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73675084114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652122497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616182327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81763291358948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044292449951</t>
+    <t xml:space="preserve">3.73675060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652146339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8032534122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81763243675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044244766235</t>
   </si>
   <si>
     <t xml:space="preserve">3.79246926307678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7439398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449584007263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067230224609</t>
+    <t xml:space="preserve">3.74394011497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449536323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067158699036</t>
   </si>
   <si>
     <t xml:space="preserve">3.77629327774048</t>
@@ -368,34 +368,34 @@
     <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80145645141602</t>
+    <t xml:space="preserve">3.80145597457886</t>
   </si>
   <si>
     <t xml:space="preserve">3.7331554889679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78348255157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72416925430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090096473694</t>
+    <t xml:space="preserve">3.78348278999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7241690158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77090072631836</t>
   </si>
   <si>
     <t xml:space="preserve">3.72057414054871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76371169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596597671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978951454163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70260000228882</t>
+    <t xml:space="preserve">3.76371121406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978975296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70260047912598</t>
   </si>
   <si>
     <t xml:space="preserve">3.73854804039001</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">3.72956109046936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72237229347229</t>
+    <t xml:space="preserve">3.72237205505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.72776341438293</t>
@@ -416,52 +416,52 @@
     <t xml:space="preserve">3.75831913948059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69541072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68462657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69361352920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68822169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135876655579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338438987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168559074402</t>
+    <t xml:space="preserve">3.69541096687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68462681770325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6936137676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66485571861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68822145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338486671448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168511390686</t>
   </si>
   <si>
     <t xml:space="preserve">3.83380913734436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81224036216736</t>
+    <t xml:space="preserve">3.81224060058594</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82661938667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841753959656</t>
+    <t xml:space="preserve">3.82661914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82841730117798</t>
   </si>
   <si>
     <t xml:space="preserve">3.92547535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93446207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188048362732</t>
+    <t xml:space="preserve">3.93446183204651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188024520874</t>
   </si>
   <si>
     <t xml:space="preserve">3.90031218528748</t>
@@ -470,46 +470,46 @@
     <t xml:space="preserve">3.87335109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84639096260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83740377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8751482963562</t>
+    <t xml:space="preserve">3.84639143943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740401268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87514877319336</t>
   </si>
   <si>
     <t xml:space="preserve">3.94165205955505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90929889678955</t>
+    <t xml:space="preserve">3.90929913520813</t>
   </si>
   <si>
     <t xml:space="preserve">3.95243620872498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98119330406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97939658164978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413572311401</t>
+    <t xml:space="preserve">3.98119378089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97939705848694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413548469543</t>
   </si>
   <si>
     <t xml:space="preserve">3.94884133338928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87874293327332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01534414291382</t>
+    <t xml:space="preserve">3.87874364852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01534461975098</t>
   </si>
   <si>
     <t xml:space="preserve">4.02073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00815439224243</t>
+    <t xml:space="preserve">4.00815486907959</t>
   </si>
   <si>
     <t xml:space="preserve">4.04050779342651</t>
@@ -524,79 +524,79 @@
     <t xml:space="preserve">4.0620756149292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07106351852417</t>
+    <t xml:space="preserve">4.07106304168701</t>
   </si>
   <si>
     <t xml:space="preserve">4.14295816421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0692663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08903694152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40357875823975</t>
+    <t xml:space="preserve">4.06926584243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08903646469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40357780456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34606122970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785890579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32808876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27236986160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599731445312</t>
+    <t xml:space="preserve">4.34606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32808828353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27237033843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599683761597</t>
   </si>
   <si>
     <t xml:space="preserve">4.03691291809082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98478865623474</t>
+    <t xml:space="preserve">3.98478960990906</t>
   </si>
   <si>
     <t xml:space="preserve">4.04230546951294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603060722351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008352279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704461097717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099864959717</t>
+    <t xml:space="preserve">3.95603013038635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828608512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704413414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93266534805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099888801575</t>
   </si>
   <si>
     <t xml:space="preserve">3.86795902252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90390658378601</t>
+    <t xml:space="preserve">3.90390682220459</t>
   </si>
   <si>
     <t xml:space="preserve">3.94524645805359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96359634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99112129211426</t>
+    <t xml:space="preserve">3.9635968208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9911208152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.98194646835327</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">3.87184619903564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92689681053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.128746509552</t>
+    <t xml:space="preserve">3.92689728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05901670455933</t>
+    <t xml:space="preserve">4.05901622772217</t>
   </si>
   <si>
     <t xml:space="preserve">4.03699684143066</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99479150772095</t>
+    <t xml:space="preserve">3.99479198455811</t>
   </si>
   <si>
     <t xml:space="preserve">4.05351161956787</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">4.03332662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07369661331177</t>
+    <t xml:space="preserve">4.07369709014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.09204626083374</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">4.09021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06268644332886</t>
+    <t xml:space="preserve">4.0626859664917</t>
   </si>
   <si>
     <t xml:space="preserve">4.15260124206543</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16544675827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11039638519287</t>
+    <t xml:space="preserve">4.16544628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11039686203003</t>
   </si>
   <si>
     <t xml:space="preserve">4.09388113021851</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">4.15443658828735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13792133331299</t>
+    <t xml:space="preserve">4.13792181015015</t>
   </si>
   <si>
     <t xml:space="preserve">4.12507677078247</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">4.07002639770508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10122108459473</t>
+    <t xml:space="preserve">4.10122156143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.16911697387695</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">4.0975513458252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05167675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01864671707153</t>
+    <t xml:space="preserve">4.05167627334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01864624023438</t>
   </si>
   <si>
     <t xml:space="preserve">4.07920122146606</t>
@@ -746,16 +746,16 @@
     <t xml:space="preserve">4.21866130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13241672515869</t>
+    <t xml:space="preserve">4.13241624832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.12140655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11590147018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11773633956909</t>
+    <t xml:space="preserve">4.11590099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11773681640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.14709663391113</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">4.19113636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19297218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662637710571</t>
+    <t xml:space="preserve">4.19297170639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662685394287</t>
   </si>
   <si>
     <t xml:space="preserve">4.04433631896973</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">4.02048110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92322635650635</t>
+    <t xml:space="preserve">3.92322683334351</t>
   </si>
   <si>
     <t xml:space="preserve">4.03516101837158</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">3.97277164459229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93790674209595</t>
+    <t xml:space="preserve">3.93790650367737</t>
   </si>
   <si>
     <t xml:space="preserve">3.99846124649048</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">3.88102173805237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442152023315</t>
+    <t xml:space="preserve">3.85349678993225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.954421043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.83514642715454</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">3.89937162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90854716300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93607139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267161369324</t>
+    <t xml:space="preserve">3.90854692459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9360716342926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267185211182</t>
   </si>
   <si>
     <t xml:space="preserve">3.82597184181213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78927206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.807621717453</t>
+    <t xml:space="preserve">3.78927183151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80762147903442</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039480209351</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">4.03918123245239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97342705726624</t>
+    <t xml:space="preserve">3.97342658042908</t>
   </si>
   <si>
     <t xml:space="preserve">3.9922137260437</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">3.96403360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89827966690063</t>
+    <t xml:space="preserve">3.89827990531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.9170663356781</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75737762451172</t>
+    <t xml:space="preserve">3.7573778629303</t>
   </si>
   <si>
     <t xml:space="preserve">3.73859095573425</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">3.63526272773743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62586951255798</t>
+    <t xml:space="preserve">3.6258692741394</t>
   </si>
   <si>
     <t xml:space="preserve">3.52254152297974</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">3.28770565986633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35345983505249</t>
+    <t xml:space="preserve">3.35345959663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.33467292785645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37224626541138</t>
+    <t xml:space="preserve">3.37224650382996</t>
   </si>
   <si>
     <t xml:space="preserve">3.38163995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45678734779358</t>
+    <t xml:space="preserve">3.45678758621216</t>
   </si>
   <si>
     <t xml:space="preserve">3.46618103981018</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">3.36285281181335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44739437103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43800044059753</t>
+    <t xml:space="preserve">3.44739413261414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43800067901611</t>
   </si>
   <si>
     <t xml:space="preserve">3.40042686462402</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">3.49436140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31588554382324</t>
+    <t xml:space="preserve">3.31588578224182</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708260536194</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">3.48496770858765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68223023414612</t>
+    <t xml:space="preserve">3.68222999572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.59768915176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61647582054138</t>
+    <t xml:space="preserve">3.61647605895996</t>
   </si>
   <si>
     <t xml:space="preserve">3.66344332695007</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">3.58829545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5507218837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193521499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56011533737183</t>
+    <t xml:space="preserve">3.55072212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193497657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56011557579041</t>
   </si>
   <si>
     <t xml:space="preserve">3.57890224456787</t>
@@ -68251,7 +68251,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6869907407</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>2028</v>
@@ -68272,6 +68272,32 @@
         <v>725</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6911574074</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>4402</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>4.44999980926514</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282109260559</t>
+    <t xml:space="preserve">3.87282061576843</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105989456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458252906799</t>
+    <t xml:space="preserve">3.87105965614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577653884888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86401534080505</t>
+    <t xml:space="preserve">3.86401581764221</t>
   </si>
   <si>
     <t xml:space="preserve">3.78652381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74249458312988</t>
+    <t xml:space="preserve">3.74249410629272</t>
   </si>
   <si>
     <t xml:space="preserve">3.79532933235168</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">3.77771759033203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62977886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.677330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443587303162</t>
+    <t xml:space="preserve">3.62977957725525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443563461304</t>
   </si>
   <si>
     <t xml:space="preserve">3.66324138641357</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">3.64386868476868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4871244430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68965888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66676378250122</t>
+    <t xml:space="preserve">3.48712420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040616035461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68965911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6667640209198</t>
   </si>
   <si>
     <t xml:space="preserve">3.60336112976074</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">3.68085289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56637716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568975448608</t>
+    <t xml:space="preserve">3.56637692451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6156895160675</t>
   </si>
   <si>
     <t xml:space="preserve">3.64915227890015</t>
@@ -116,34 +116,34 @@
     <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210772514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.751300573349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294083595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7935688495636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86225438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81470227241516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941915512085</t>
+    <t xml:space="preserve">3.65091276168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210724830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431517601013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75130081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8129415512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79356837272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86225390434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941891670227</t>
   </si>
   <si>
     <t xml:space="preserve">3.73368811607361</t>
@@ -152,181 +152,181 @@
     <t xml:space="preserve">3.73721051216125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71255445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72136044502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891207695007</t>
+    <t xml:space="preserve">3.71255421638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192715644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.721360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891231536865</t>
   </si>
   <si>
     <t xml:space="preserve">3.76538944244385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74953866004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74601650238037</t>
+    <t xml:space="preserve">3.74953842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74601674079895</t>
   </si>
   <si>
     <t xml:space="preserve">3.73016619682312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613624572754</t>
+    <t xml:space="preserve">3.6984646320343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68613696098328</t>
   </si>
   <si>
     <t xml:space="preserve">3.72488284111023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82350873947144</t>
+    <t xml:space="preserve">3.8235080242157</t>
   </si>
   <si>
     <t xml:space="preserve">3.95383501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91861152648926</t>
+    <t xml:space="preserve">3.9186110496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446207046509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98377466201782</t>
+    <t xml:space="preserve">3.98377513885498</t>
   </si>
   <si>
     <t xml:space="preserve">3.9432680606842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91508889198303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9855363368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91332793235779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395475387573</t>
+    <t xml:space="preserve">3.91508913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98553586006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91332769393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395546913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.96088004112244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89219403266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622326850891</t>
+    <t xml:space="preserve">3.89219379425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622350692749</t>
   </si>
   <si>
     <t xml:space="preserve">3.92741703987122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88338828086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0261287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220730781555</t>
+    <t xml:space="preserve">3.88338780403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02612829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220706939697</t>
   </si>
   <si>
     <t xml:space="preserve">3.99018120765686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97759938240051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04410171508789</t>
+    <t xml:space="preserve">3.97759985923767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04410219192505</t>
   </si>
   <si>
     <t xml:space="preserve">3.98299193382263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9542338848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93626046180725</t>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625950813293</t>
   </si>
   <si>
     <t xml:space="preserve">3.88233828544617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92727184295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367815971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560681343079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89132499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436462402344</t>
+    <t xml:space="preserve">3.92727279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367792129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89132571220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436486244202</t>
   </si>
   <si>
     <t xml:space="preserve">3.86256694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81943035125732</t>
+    <t xml:space="preserve">3.81942987442017</t>
   </si>
   <si>
     <t xml:space="preserve">3.70799255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7655086517334</t>
+    <t xml:space="preserve">3.76550889015198</t>
   </si>
   <si>
     <t xml:space="preserve">3.59475779533386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61273145675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67923450469971</t>
+    <t xml:space="preserve">3.61273169517517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67923426628113</t>
   </si>
   <si>
     <t xml:space="preserve">3.63070511817932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62171840667725</t>
+    <t xml:space="preserve">3.62171864509583</t>
   </si>
   <si>
     <t xml:space="preserve">3.65766620635986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63789486885071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103218078613</t>
+    <t xml:space="preserve">3.63789510726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103241920471</t>
   </si>
   <si>
     <t xml:space="preserve">3.57318925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61632657051086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60374450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64688181877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69181609153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675060272217</t>
+    <t xml:space="preserve">3.61632633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6037449836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64688205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6918158531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675036430359</t>
   </si>
   <si>
     <t xml:space="preserve">3.75652122497559</t>
@@ -338,88 +338,88 @@
     <t xml:space="preserve">3.86616182327271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81763243675232</t>
+    <t xml:space="preserve">3.81763291358948</t>
   </si>
   <si>
     <t xml:space="preserve">3.81044292449951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79246926307678</t>
+    <t xml:space="preserve">3.7924690246582</t>
   </si>
   <si>
     <t xml:space="preserve">3.74394011497498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77449512481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067206382751</t>
+    <t xml:space="preserve">3.77449536323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067182540894</t>
   </si>
   <si>
     <t xml:space="preserve">3.7762930393219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78887486457825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753475189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75112962722778</t>
+    <t xml:space="preserve">3.78887462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753499031067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7511293888092</t>
   </si>
   <si>
     <t xml:space="preserve">3.80145645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73315572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348231315613</t>
+    <t xml:space="preserve">3.7331554889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348278999329</t>
   </si>
   <si>
     <t xml:space="preserve">3.72416925430298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77090120315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057437896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371169090271</t>
+    <t xml:space="preserve">3.77090096473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057414054871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371145248413</t>
   </si>
   <si>
     <t xml:space="preserve">3.72596597671509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70978975296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70260047912598</t>
+    <t xml:space="preserve">3.70978951454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70260000228882</t>
   </si>
   <si>
     <t xml:space="preserve">3.73854780197144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72956132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72237181663513</t>
+    <t xml:space="preserve">3.72956109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72237205505371</t>
   </si>
   <si>
     <t xml:space="preserve">3.72776341438293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75292682647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68462634086609</t>
+    <t xml:space="preserve">3.75292706489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831961631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541096687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68462657928467</t>
   </si>
   <si>
     <t xml:space="preserve">3.69361352920532</t>
@@ -431,40 +431,37 @@
     <t xml:space="preserve">3.68822121620178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73135805130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338510513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380913734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224083900452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81583523750305</t>
+    <t xml:space="preserve">3.73135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338438987732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380889892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81583476066589</t>
   </si>
   <si>
     <t xml:space="preserve">3.82661938667297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82841730117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547535896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446183204651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9003119468689</t>
+    <t xml:space="preserve">3.82841777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547488212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188048362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031218528748</t>
   </si>
   <si>
     <t xml:space="preserve">3.87335133552551</t>
@@ -476,31 +473,31 @@
     <t xml:space="preserve">3.83740377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8751482963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165205955505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929913520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243620872498</t>
+    <t xml:space="preserve">3.87514853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9416515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929865837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243573188782</t>
   </si>
   <si>
     <t xml:space="preserve">3.98119378089905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97939658164978</t>
+    <t xml:space="preserve">3.97939705848694</t>
   </si>
   <si>
     <t xml:space="preserve">3.88413572311401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94884085655212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87874341011047</t>
+    <t xml:space="preserve">3.9488410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87874317169189</t>
   </si>
   <si>
     <t xml:space="preserve">4.01534414291382</t>
@@ -521,7 +518,7 @@
     <t xml:space="preserve">4.01714134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06207609176636</t>
+    <t xml:space="preserve">4.0620756149292</t>
   </si>
   <si>
     <t xml:space="preserve">4.07106351852417</t>
@@ -536,16 +533,16 @@
     <t xml:space="preserve">4.08903741836548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40357780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37661790847778</t>
+    <t xml:space="preserve">4.40357828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
     <t xml:space="preserve">4.34606170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34785890579224</t>
+    <t xml:space="preserve">4.34785938262939</t>
   </si>
   <si>
     <t xml:space="preserve">4.32808876037598</t>
@@ -560,61 +557,64 @@
     <t xml:space="preserve">4.03691339492798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98478865623474</t>
+    <t xml:space="preserve">3.98478817939758</t>
   </si>
   <si>
     <t xml:space="preserve">4.04230546951294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603084564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008352279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828560829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099888801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86795902252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90390658378601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524669647217</t>
+    <t xml:space="preserve">3.95603132247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828584671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704413414001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9326651096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099912643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86795949935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90390729904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524645805359</t>
   </si>
   <si>
     <t xml:space="preserve">3.96359658241272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99112176895142</t>
+    <t xml:space="preserve">3.99112129211426</t>
   </si>
   <si>
     <t xml:space="preserve">3.98194670677185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06819152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8901960849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8718466758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9268970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452178955078</t>
+    <t xml:space="preserve">4.06819105148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524693489075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89019632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87184619903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689681053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452131271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.128746509552</t>
@@ -629,43 +629,43 @@
     <t xml:space="preserve">4.10672569274902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05901622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03699636459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99479198455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05351114273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08287143707275</t>
+    <t xml:space="preserve">4.05901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03699684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99479150772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05351161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0828709602356</t>
   </si>
   <si>
     <t xml:space="preserve">4.03332662582397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07369565963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920467376709</t>
+    <t xml:space="preserve">4.07369661331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09204626083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.08103656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05534696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09021091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0626859664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15260171890259</t>
+    <t xml:space="preserve">4.05534648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09021186828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06268644332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15260124206543</t>
   </si>
   <si>
     <t xml:space="preserve">4.15627145767212</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.16544628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11039686203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09388160705566</t>
+    <t xml:space="preserve">4.11039638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09388113021851</t>
   </si>
   <si>
     <t xml:space="preserve">4.20948600769043</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">4.11957120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13608646392822</t>
+    <t xml:space="preserve">4.13608598709106</t>
   </si>
   <si>
     <t xml:space="preserve">4.15076637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10305643081665</t>
+    <t xml:space="preserve">4.10305690765381</t>
   </si>
   <si>
     <t xml:space="preserve">4.17278623580933</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">4.07002592086792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10122108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16911697387695</t>
+    <t xml:space="preserve">4.10122156143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16911649703979</t>
   </si>
   <si>
     <t xml:space="preserve">4.18379640579224</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01864671707153</t>
+    <t xml:space="preserve">4.01864624023438</t>
   </si>
   <si>
     <t xml:space="preserve">4.07920122146606</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">4.21866130828857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13241720199585</t>
+    <t xml:space="preserve">4.13241624832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.12140655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11590194702148</t>
+    <t xml:space="preserve">4.11590147018433</t>
   </si>
   <si>
     <t xml:space="preserve">4.11773586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14709663391113</t>
+    <t xml:space="preserve">4.14709615707397</t>
   </si>
   <si>
     <t xml:space="preserve">4.14893198013306</t>
@@ -764,52 +764,52 @@
     <t xml:space="preserve">4.19113636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19297170639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662613868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04433679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561644554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02048110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92322611808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03516149520874</t>
+    <t xml:space="preserve">4.19297218322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662661552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04433631896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98561692237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341135025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0204815864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92322635650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03516101837158</t>
   </si>
   <si>
     <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04800701141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96726632118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772127151489</t>
+    <t xml:space="preserve">4.04800653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96726679801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
     <t xml:space="preserve">4.0002965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97277116775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93790698051453</t>
+    <t xml:space="preserve">3.97277188301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93790674209595</t>
   </si>
   <si>
     <t xml:space="preserve">3.99846148490906</t>
@@ -818,28 +818,28 @@
     <t xml:space="preserve">4.04617118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88102149963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349631309509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442175865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8993718624115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854716300964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267161369324</t>
+    <t xml:space="preserve">3.88102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83514618873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89937138557434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854740142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93607139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267185211182</t>
   </si>
   <si>
     <t xml:space="preserve">3.82597184181213</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">3.78927183151245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80762195587158</t>
+    <t xml:space="preserve">3.807621717453</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04857444763184</t>
+    <t xml:space="preserve">4.04857397079468</t>
   </si>
   <si>
     <t xml:space="preserve">4.03918123245239</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">3.97342681884766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99221396446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02978754043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96403360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9170663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616477012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101690292358</t>
+    <t xml:space="preserve">3.99221348762512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02978801727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96403336524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91706609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70101714134216</t>
   </si>
   <si>
     <t xml:space="preserve">3.75737762451172</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">3.73859095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980404853821</t>
+    <t xml:space="preserve">3.71980381011963</t>
   </si>
   <si>
     <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63526296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62586903572083</t>
+    <t xml:space="preserve">3.63526272773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62586951255798</t>
   </si>
   <si>
     <t xml:space="preserve">3.52254152297974</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">3.42860722541809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770542144775</t>
+    <t xml:space="preserve">3.28770518302917</t>
   </si>
   <si>
     <t xml:space="preserve">3.35345959663391</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">3.4661808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36285281181335</t>
+    <t xml:space="preserve">3.36285305023193</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800091743469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40042686462402</t>
+    <t xml:space="preserve">3.43800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
     <t xml:space="preserve">3.4755744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49436140060425</t>
+    <t xml:space="preserve">3.49436116218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.31588578224182</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">3.61647605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66344332695007</t>
+    <t xml:space="preserve">3.66344356536865</t>
   </si>
   <si>
     <t xml:space="preserve">3.58829569816589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55072212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56011533737183</t>
+    <t xml:space="preserve">3.5507218837738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193497657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56011557579041</t>
   </si>
   <si>
     <t xml:space="preserve">3.57890200614929</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54921507835388</t>
+    <t xml:space="preserve">3.54921531677246</t>
   </si>
   <si>
     <t xml:space="preserve">3.62637186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58779335021973</t>
+    <t xml:space="preserve">3.58779358863831</t>
   </si>
   <si>
     <t xml:space="preserve">3.66495013237</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79997491836548</t>
+    <t xml:space="preserve">3.7999746799469</t>
   </si>
   <si>
     <t xml:space="preserve">3.74210739135742</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855319023132</t>
+    <t xml:space="preserve">3.83855295181274</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">3.72281789779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64566135406494</t>
+    <t xml:space="preserve">3.64566111564636</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56850457191467</t>
+    <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">3.52992582321167</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">3.47205829620361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51063656806946</t>
+    <t xml:space="preserve">3.51063680648804</t>
   </si>
   <si>
     <t xml:space="preserve">3.41419053077698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43347954750061</t>
+    <t xml:space="preserve">3.43347978591919</t>
   </si>
   <si>
     <t xml:space="preserve">3.45276880264282</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0669846534729</t>
+    <t xml:space="preserve">3.06698489189148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
+    <t xml:space="preserve">2.91267108917236</t>
   </si>
   <si>
     <t xml:space="preserve">2.85480356216431</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.83551406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.970538854599</t>
+    <t xml:space="preserve">2.97053861618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">3.12485241889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98982763290405</t>
+    <t xml:space="preserve">2.98982787132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.95124959945679</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">2.81622505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79693603515625</t>
+    <t xml:space="preserve">2.79693579673767</t>
   </si>
   <si>
     <t xml:space="preserve">2.75835704803467</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.73906803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54617595672607</t>
+    <t xml:space="preserve">2.54617619514465</t>
   </si>
   <si>
     <t xml:space="preserve">2.62333297729492</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">2.50759768486023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46901893615723</t>
+    <t xml:space="preserve">2.46901917457581</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">2.14110255241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23754858970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02536725997925</t>
+    <t xml:space="preserve">2.23754835128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02536749839783</t>
   </si>
   <si>
     <t xml:space="preserve">2.198970079422</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">2.25683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29541611671448</t>
+    <t xml:space="preserve">2.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648235321045</t>
+    <t xml:space="preserve">2.26648259162903</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">2.43044090270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27612709999084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577160835266</t>
+    <t xml:space="preserve">2.27612686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577136993408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3436393737793</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">2.36292862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506086349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22790384292603</t>
+    <t xml:space="preserve">2.30506110191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2279040813446</t>
   </si>
   <si>
     <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35328412055969</t>
+    <t xml:space="preserve">2.35328388214111</t>
   </si>
   <si>
     <t xml:space="preserve">2.32435011863708</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">2.17968106269836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18932557106018</t>
+    <t xml:space="preserve">2.18932580947876</t>
   </si>
   <si>
     <t xml:space="preserve">2.17003631591797</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216878890991</t>
+    <t xml:space="preserve">2.11216855049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03501176834106</t>
+    <t xml:space="preserve">2.03501152992249</t>
   </si>
   <si>
     <t xml:space="preserve">1.98678886890411</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">1.92892122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93856573104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95785510540009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20861482620239</t>
+    <t xml:space="preserve">1.93856585025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9578549861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20861458778381</t>
   </si>
   <si>
     <t xml:space="preserve">2.15074706077576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37257289886475</t>
+    <t xml:space="preserve">2.37257313728333</t>
   </si>
   <si>
     <t xml:space="preserve">2.38221764564514</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409281730652</t>
+    <t xml:space="preserve">2.87409257888794</t>
   </si>
   <si>
     <t xml:space="preserve">2.66191124916077</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">2.64262199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59439921379089</t>
+    <t xml:space="preserve">2.59439897537231</t>
   </si>
   <si>
     <t xml:space="preserve">2.68120050430298</t>
@@ -1322,31 +1322,31 @@
     <t xml:space="preserve">2.65226674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61368823051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53653144836426</t>
+    <t xml:space="preserve">2.61368846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53653168678284</t>
   </si>
   <si>
     <t xml:space="preserve">2.52688670158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51724219322205</t>
+    <t xml:space="preserve">2.51724195480347</t>
   </si>
   <si>
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013426780701</t>
+    <t xml:space="preserve">2.71013450622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78729128837585</t>
+    <t xml:space="preserve">2.72942328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78729152679443</t>
   </si>
   <si>
     <t xml:space="preserve">2.94160485267639</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98018288612366</t>
+    <t xml:space="preserve">2.98018312454224</t>
   </si>
   <si>
     <t xml:space="preserve">2.9608941078186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03805112838745</t>
+    <t xml:space="preserve">3.03805088996887</t>
   </si>
   <si>
     <t xml:space="preserve">3.16343069076538</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">3.21165370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23094296455383</t>
+    <t xml:space="preserve">3.23094320297241</t>
   </si>
   <si>
     <t xml:space="preserve">3.24058747291565</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">3.19236469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17307543754578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
+    <t xml:space="preserve">3.1730751991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378618240356</t>
   </si>
   <si>
     <t xml:space="preserve">3.26952171325684</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">3.25987696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30809998512268</t>
+    <t xml:space="preserve">3.30810022354126</t>
   </si>
   <si>
     <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25023221969604</t>
+    <t xml:space="preserve">3.25023198127747</t>
   </si>
   <si>
     <t xml:space="preserve">3.09591865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0766294002533</t>
+    <t xml:space="preserve">3.07662916183472</t>
   </si>
   <si>
     <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05734014511108</t>
+    <t xml:space="preserve">3.05734038352966</t>
   </si>
   <si>
     <t xml:space="preserve">2.92231559753418</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">2.84515881538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80658054351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">2.80658030509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67459464073181</t>
+    <t xml:space="preserve">3.59743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
     <t xml:space="preserve">3.71317338943481</t>
@@ -1457,22 +1457,22 @@
     <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95428824424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94464421272278</t>
+    <t xml:space="preserve">3.95428848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94464373588562</t>
   </si>
   <si>
     <t xml:space="preserve">3.9832227230072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0507345199585</t>
+    <t xml:space="preserve">4.05073499679565</t>
   </si>
   <si>
     <t xml:space="preserve">3.97357773780823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002353668213</t>
+    <t xml:space="preserve">4.07002305984497</t>
   </si>
   <si>
     <t xml:space="preserve">4.20504856109619</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971761703491</t>
+    <t xml:space="preserve">4.34971714019775</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">4.39794015884399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42687463760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45580768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22433757781982</t>
+    <t xml:space="preserve">4.4268741607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45580816268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22433710098267</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144502639771</t>
+    <t xml:space="preserve">4.03144550323486</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5329647064209</t>
+    <t xml:space="preserve">4.53296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">4.36900663375854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1278920173645</t>
+    <t xml:space="preserve">4.12789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1857590675354</t>
+    <t xml:space="preserve">4.18575954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.14718055725098</t>
@@ -1556,25 +1556,25 @@
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33042764663696</t>
+    <t xml:space="preserve">4.17611455917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33042812347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.51367568969727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46545267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37865114212036</t>
+    <t xml:space="preserve">4.46545314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37865161895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.48474168777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47509717941284</t>
+    <t xml:space="preserve">4.47509670257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.49438619613647</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">4.44616365432739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41722965240479</t>
+    <t xml:space="preserve">4.41722917556763</t>
   </si>
   <si>
     <t xml:space="preserve">4.64870023727417</t>
@@ -1601,25 +1601,25 @@
     <t xml:space="preserve">4.62941074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61012172698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57154321670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27256059646606</t>
+    <t xml:space="preserve">4.6101222038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57154273986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27256011962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.11824703216553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15682458877563</t>
+    <t xml:space="preserve">4.15682506561279</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45884704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5938720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4974250793457</t>
+    <t xml:space="preserve">5.45884656906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59387159347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49742555618286</t>
   </si>
   <si>
     <t xml:space="preserve">5.28524398803711</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026853561401</t>
+    <t xml:space="preserve">5.42026901245117</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">4.84159231185913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93803787231445</t>
+    <t xml:space="preserve">4.93803834915161</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
@@ -9376,7 +9376,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9428,7 +9428,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9454,7 +9454,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9480,7 +9480,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9506,7 +9506,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9532,7 +9532,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9558,7 +9558,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9584,7 +9584,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9610,7 +9610,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9688,7 +9688,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9714,7 +9714,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9792,7 +9792,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G273" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9818,7 +9818,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9870,7 +9870,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G277" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9922,7 +9922,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9948,7 +9948,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G279" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9974,7 +9974,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G280" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10052,7 +10052,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10078,7 +10078,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10130,7 +10130,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G286" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10156,7 +10156,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10208,7 +10208,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10286,7 +10286,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G292" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10312,7 +10312,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10364,7 +10364,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10416,7 +10416,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G297" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10442,7 +10442,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G298" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10494,7 +10494,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10546,7 +10546,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10598,7 +10598,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10624,7 +10624,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10702,7 +10702,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10806,7 +10806,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G312" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10858,7 +10858,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G314" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10884,7 +10884,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10910,7 +10910,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G316" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10936,7 +10936,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10962,7 +10962,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G318" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -10988,7 +10988,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11014,7 +11014,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11040,7 +11040,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G321" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11066,7 +11066,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11092,7 +11092,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G323" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11144,7 +11144,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G325" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11170,7 +11170,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G326" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11196,7 +11196,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11222,7 +11222,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11352,7 +11352,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11378,7 +11378,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11404,7 +11404,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11508,7 +11508,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11534,7 +11534,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11560,7 +11560,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G341" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11586,7 +11586,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11664,7 +11664,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11846,7 +11846,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11872,7 +11872,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11898,7 +11898,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G354" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11924,7 +11924,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11950,7 +11950,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G356" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11976,7 +11976,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12002,7 +12002,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12028,7 +12028,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12314,7 +12314,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -15330,7 +15330,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15382,7 +15382,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16552,7 +16552,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G533" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16578,7 +16578,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16682,7 +16682,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16864,7 +16864,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16890,7 +16890,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16916,7 +16916,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16994,7 +16994,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17020,7 +17020,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17046,7 +17046,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17306,7 +17306,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17384,7 +17384,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17410,7 +17410,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17436,7 +17436,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17956,7 +17956,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18372,7 +18372,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18398,7 +18398,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18476,7 +18476,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18788,7 +18788,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19022,7 +19022,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19048,7 +19048,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19126,7 +19126,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19152,7 +19152,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G633" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19516,7 +19516,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G647" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19542,7 +19542,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19568,7 +19568,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19594,7 +19594,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19620,7 +19620,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19646,7 +19646,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19672,7 +19672,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19698,7 +19698,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19750,7 +19750,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19880,7 +19880,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19906,7 +19906,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19932,7 +19932,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19958,7 +19958,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19984,7 +19984,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20010,7 +20010,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20244,7 +20244,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20270,7 +20270,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20764,7 +20764,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20790,7 +20790,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -68430,7 +68430,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.478287037</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>1000</v>
@@ -68451,6 +68451,32 @@
         <v>725</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.3500115741</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>950</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>723</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="783">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,100 +38,100 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282133102417</t>
+    <t xml:space="preserve">3.87282037734985</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458205223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8657763004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401510238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652405738831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7424943447113</t>
+    <t xml:space="preserve">3.87105965614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8640148639679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74249458312988</t>
   </si>
   <si>
     <t xml:space="preserve">3.79532980918884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77771759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977957725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.677330493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6544361114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.663241147995</t>
+    <t xml:space="preserve">3.77771782875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67733097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443539619446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66324138641357</t>
   </si>
   <si>
     <t xml:space="preserve">3.64386868476868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48712396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040616035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68965888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6667640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60336136817932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637692451477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915204048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65267395973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65091371536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210772514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75130033493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294131278992</t>
+    <t xml:space="preserve">3.48712420463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040639877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68965911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66676378250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336184501648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085312843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637716293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995895385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61568999290466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915227890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65267419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65091300010681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455513954163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431565284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.751300573349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81294083595276</t>
   </si>
   <si>
     <t xml:space="preserve">3.79356861114502</t>
@@ -140,187 +140,187 @@
     <t xml:space="preserve">3.86225414276123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81470274925232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73721098899841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255469322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192715644836</t>
+    <t xml:space="preserve">3.81470227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368811607361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721051216125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192691802979</t>
   </si>
   <si>
     <t xml:space="preserve">3.72135996818542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76891183853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538968086243</t>
+    <t xml:space="preserve">3.76891231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538991928101</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953889846802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74601674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73016619682312</t>
+    <t xml:space="preserve">3.74601697921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73016571998596</t>
   </si>
   <si>
     <t xml:space="preserve">3.6984646320343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68613624572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488284111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350850105286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383524894714</t>
+    <t xml:space="preserve">3.68613648414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488236427307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350873947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383501052856</t>
   </si>
   <si>
     <t xml:space="preserve">3.91861152648926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93446278572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98377537727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94326782226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508960723877</t>
+    <t xml:space="preserve">3.93446230888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9837749004364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94326853752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508984565735</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855363368988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332864761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96088004112244</t>
+    <t xml:space="preserve">3.91332840919495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96087980270386</t>
   </si>
   <si>
     <t xml:space="preserve">3.89219427108765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93622279167175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741799354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338780403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916768074036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02612829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018168449402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759938240051</t>
+    <t xml:space="preserve">3.93622326850891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741751670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338828086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916791915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0261287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220754623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018144607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759985923767</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98299241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9542338848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625974655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233852386475</t>
+    <t xml:space="preserve">3.98299169540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625950813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233828544617</t>
   </si>
   <si>
     <t xml:space="preserve">3.92727255821228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92367839813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89132523536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436486244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81942987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799231529236</t>
+    <t xml:space="preserve">3.92367792129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560633659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89132499694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81943011283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799279212952</t>
   </si>
   <si>
     <t xml:space="preserve">3.76550889015198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59475779533386</t>
+    <t xml:space="preserve">3.59475755691528</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273121833801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67923426628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63070559501648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62171864509583</t>
+    <t xml:space="preserve">3.67923450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070511817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62171816825867</t>
   </si>
   <si>
     <t xml:space="preserve">3.65766596794128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63789463043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68103194236755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632633209229</t>
+    <t xml:space="preserve">3.63789486885071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318949699402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632657051086</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64688158035278</t>
+    <t xml:space="preserve">3.64688205718994</t>
   </si>
   <si>
     <t xml:space="preserve">3.69181609153748</t>
@@ -329,121 +329,121 @@
     <t xml:space="preserve">3.73675084114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75652146339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616158485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81763291358948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044316291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246950149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394011497498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449488639832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067206382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77629351615906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887486457825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753522872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75112986564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80145645141602</t>
+    <t xml:space="preserve">3.75652170181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80325317382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8176326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044292449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246926307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449536323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887438774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753499031067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75112915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80145597457886</t>
   </si>
   <si>
     <t xml:space="preserve">3.73315572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78348231315613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7241690158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090048789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057366371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596645355225</t>
+    <t xml:space="preserve">3.78348255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72416925430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77090096473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057437896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596621513367</t>
   </si>
   <si>
     <t xml:space="preserve">3.70978975296021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7026002407074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854804039001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956132888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72237181663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72776341438293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292706489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831913948059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69541049003601</t>
+    <t xml:space="preserve">3.70260071754456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956109046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72237157821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72776365280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69541096687317</t>
   </si>
   <si>
     <t xml:space="preserve">3.68462681770325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6936137676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66485524177551</t>
+    <t xml:space="preserve">3.69361400604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66485571861267</t>
   </si>
   <si>
     <t xml:space="preserve">3.68822169303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73135828971863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168559074402</t>
+    <t xml:space="preserve">3.73135852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7133846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168535232544</t>
   </si>
   <si>
     <t xml:space="preserve">3.8338086605072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81224036216736</t>
+    <t xml:space="preserve">3.81224083900452</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">3.82661962509155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82841730117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547535896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9003119468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335157394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8374035358429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87514853477478</t>
+    <t xml:space="preserve">3.82841753959656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547488212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031266212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335181236267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83740401268005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87514901161194</t>
   </si>
   <si>
     <t xml:space="preserve">3.94165205955505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90929937362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9524359703064</t>
+    <t xml:space="preserve">3.90929865837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243525505066</t>
   </si>
   <si>
     <t xml:space="preserve">3.98119449615479</t>
@@ -491,13 +491,13 @@
     <t xml:space="preserve">3.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88413619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94884133338928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87874364852905</t>
+    <t xml:space="preserve">3.88413596153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9488410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87874341011047</t>
   </si>
   <si>
     <t xml:space="preserve">4.01534461975098</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">4.02073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00815534591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04050779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0530891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01714134216309</t>
+    <t xml:space="preserve">4.00815486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04050731658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05308961868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01714181900024</t>
   </si>
   <si>
     <t xml:space="preserve">4.06207656860352</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">4.07106351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14295816421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0692663192749</t>
+    <t xml:space="preserve">4.14295864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06926536560059</t>
   </si>
   <si>
     <t xml:space="preserve">4.08903741836548</t>
@@ -545,16 +545,16 @@
     <t xml:space="preserve">4.34785890579224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32808828353882</t>
+    <t xml:space="preserve">4.32808780670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.27236986160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11599779129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03691339492798</t>
+    <t xml:space="preserve">4.11599731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03691291809082</t>
   </si>
   <si>
     <t xml:space="preserve">3.9847891330719</t>
@@ -563,22 +563,22 @@
     <t xml:space="preserve">4.04230499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603108406067</t>
+    <t xml:space="preserve">3.95603084564209</t>
   </si>
   <si>
     <t xml:space="preserve">3.92008328437805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91828608512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704413414001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9326651096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099841117859</t>
+    <t xml:space="preserve">3.91828560829163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93266487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099912643433</t>
   </si>
   <si>
     <t xml:space="preserve">3.86795926094055</t>
@@ -587,88 +587,88 @@
     <t xml:space="preserve">3.90390682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524621963501</t>
+    <t xml:space="preserve">3.94524598121643</t>
   </si>
   <si>
     <t xml:space="preserve">3.9635968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99112200737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194670677185</t>
+    <t xml:space="preserve">3.99112153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194646835327</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89019680023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87184691429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92689681053162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12874698638916</t>
+    <t xml:space="preserve">3.94524645805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89019656181335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87184643745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689728736877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10672664642334</t>
+    <t xml:space="preserve">4.12691164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.05901622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03699636459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99479150772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05351161956787</t>
+    <t xml:space="preserve">4.03699684143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99479126930237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05351209640503</t>
   </si>
   <si>
     <t xml:space="preserve">4.08287143707275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03332614898682</t>
+    <t xml:space="preserve">4.03332662582397</t>
   </si>
   <si>
     <t xml:space="preserve">4.07369661331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0920467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08103704452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09021186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06268644332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15260124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15627193450928</t>
+    <t xml:space="preserve">4.09204578399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08103609085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09021139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0626859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15260171890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15627145767212</t>
   </si>
   <si>
     <t xml:space="preserve">4.16544628143311</t>
@@ -677,37 +677,37 @@
     <t xml:space="preserve">4.11039638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09388160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20948648452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15443658828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11957168579102</t>
+    <t xml:space="preserve">4.09388113021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20948600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15443706512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1379222869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507581710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11957120895386</t>
   </si>
   <si>
     <t xml:space="preserve">4.13608646392822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15076684951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10305690765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17278671264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11223125457764</t>
+    <t xml:space="preserve">4.15076637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10305643081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17278623580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11223077774048</t>
   </si>
   <si>
     <t xml:space="preserve">4.07002687454224</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">4.10122108459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16911649703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18379688262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21132135391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0975513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05167675018311</t>
+    <t xml:space="preserve">4.16911697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18379640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21132183074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09755086898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05167627334595</t>
   </si>
   <si>
     <t xml:space="preserve">4.01864671707153</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">4.13425159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21866130828857</t>
+    <t xml:space="preserve">4.21866178512573</t>
   </si>
   <si>
     <t xml:space="preserve">4.13241672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12140655517578</t>
+    <t xml:space="preserve">4.12140703201294</t>
   </si>
   <si>
     <t xml:space="preserve">4.11590147018433</t>
@@ -755,52 +755,52 @@
     <t xml:space="preserve">4.11773633956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14709663391113</t>
+    <t xml:space="preserve">4.14709615707397</t>
   </si>
   <si>
     <t xml:space="preserve">4.1489315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1911358833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19297218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662661552429</t>
+    <t xml:space="preserve">4.19113636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19297122955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662613868713</t>
   </si>
   <si>
     <t xml:space="preserve">4.04433631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98561644554138</t>
+    <t xml:space="preserve">3.9856162071228</t>
   </si>
   <si>
     <t xml:space="preserve">3.94341111183167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02048110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92322707176208</t>
+    <t xml:space="preserve">4.0204815864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92322659492493</t>
   </si>
   <si>
     <t xml:space="preserve">4.03516149520874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08654165267944</t>
+    <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
     <t xml:space="preserve">4.04800701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96726632118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772150993347</t>
+    <t xml:space="preserve">3.96726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506194114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772127151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.0002965927124</t>
@@ -815,73 +815,73 @@
     <t xml:space="preserve">3.99846124649048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04617166519165</t>
+    <t xml:space="preserve">4.04617118835449</t>
   </si>
   <si>
     <t xml:space="preserve">3.88102173805237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85349607467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442199707031</t>
+    <t xml:space="preserve">3.85349631309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442128181458</t>
   </si>
   <si>
     <t xml:space="preserve">3.83514618873596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89937138557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854668617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93607139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267161369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82597184181213</t>
+    <t xml:space="preserve">3.89937162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854716300964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93607187271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267137527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82597160339355</t>
   </si>
   <si>
     <t xml:space="preserve">3.78927206993103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80762219429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02039432525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04857492446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03918123245239</t>
+    <t xml:space="preserve">3.80762195587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02039480209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04857397079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03918075561523</t>
   </si>
   <si>
     <t xml:space="preserve">3.97342705726624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9922137260437</t>
+    <t xml:space="preserve">3.99221420288086</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403384208679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827990531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91706657409668</t>
+    <t xml:space="preserve">3.96403336524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827942848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91706609725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.77616453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70101690292358</t>
+    <t xml:space="preserve">3.70101714134216</t>
   </si>
   <si>
     <t xml:space="preserve">3.75737762451172</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">3.62586951255798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52254199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42860746383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28770542144775</t>
+    <t xml:space="preserve">3.52254176139832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42860722541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28770565986633</t>
   </si>
   <si>
     <t xml:space="preserve">3.35345959663391</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">3.37224650382996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3816397190094</t>
+    <t xml:space="preserve">3.38163995742798</t>
   </si>
   <si>
     <t xml:space="preserve">3.45678758621216</t>
@@ -929,49 +929,49 @@
     <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36285305023193</t>
+    <t xml:space="preserve">3.36285281181335</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43800091743469</t>
+    <t xml:space="preserve">3.43800067901611</t>
   </si>
   <si>
     <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4755744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49436140060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31588578224182</t>
+    <t xml:space="preserve">3.47557473182678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49436116218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3158860206604</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950879096985</t>
+    <t xml:space="preserve">3.56950855255127</t>
   </si>
   <si>
     <t xml:space="preserve">3.50375485420227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65404987335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68222999572754</t>
+    <t xml:space="preserve">3.65404963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48496747016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68223023414612</t>
   </si>
   <si>
     <t xml:space="preserve">3.59768915176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61647582054138</t>
+    <t xml:space="preserve">3.61647605895996</t>
   </si>
   <si>
     <t xml:space="preserve">3.66344332695007</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">3.58829569816589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5507218837738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193521499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56011557579041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57890224456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67283654212952</t>
+    <t xml:space="preserve">3.55072212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193497657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56011533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57890200614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64465665817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6728367805481</t>
   </si>
   <si>
     <t xml:space="preserve">3.51314806938171</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">3.54921507835388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62637209892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58779358863831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495037078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68423962593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78068542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7999746799469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210715293884</t>
+    <t xml:space="preserve">3.62637186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58779335021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495013237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68423938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78068566322327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79997491836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210739135742</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
@@ -1043,16 +1043,16 @@
     <t xml:space="preserve">3.72281789779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64566111564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56850433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52992606163025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47205805778503</t>
+    <t xml:space="preserve">3.64566135406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56850457191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52992582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47205829620361</t>
   </si>
   <si>
     <t xml:space="preserve">3.51063656806946</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">3.41419053077698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43347978591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4527690410614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37561202049255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39490127563477</t>
+    <t xml:space="preserve">3.43347954750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45276880264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37561225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39490151405334</t>
   </si>
   <si>
     <t xml:space="preserve">3.33703374862671</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06698489189148</t>
+    <t xml:space="preserve">3.0669846534729</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">2.91267085075378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85480332374573</t>
+    <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
     <t xml:space="preserve">2.71977877616882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83551430702209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97053861618042</t>
+    <t xml:space="preserve">2.83551406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.970538854599</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">3.08627390861511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12485265731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98982787132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95124936103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8162248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79693579673767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75835728645325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77764654159546</t>
+    <t xml:space="preserve">3.12485241889954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98982763290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95124959945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81622505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75835704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
     <t xml:space="preserve">2.73906803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54617619514465</t>
+    <t xml:space="preserve">2.54617595672607</t>
   </si>
   <si>
     <t xml:space="preserve">2.62333297729492</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">2.5847544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50759744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46901917457581</t>
+    <t xml:space="preserve">2.50759768486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46901893615723</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
@@ -1175,28 +1175,28 @@
     <t xml:space="preserve">2.16039180755615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04465651512146</t>
+    <t xml:space="preserve">2.04465627670288</t>
   </si>
   <si>
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110279083252</t>
+    <t xml:space="preserve">2.14110255241394</t>
   </si>
   <si>
     <t xml:space="preserve">2.23754858970642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02536702156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19897031784058</t>
+    <t xml:space="preserve">2.02536725997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.198970079422</t>
   </si>
   <si>
     <t xml:space="preserve">2.12181329727173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25683760643005</t>
+    <t xml:space="preserve">2.25683784484863</t>
   </si>
   <si>
     <t xml:space="preserve">2.29541611671448</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">2.43044090270996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27612686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577136993408</t>
+    <t xml:space="preserve">2.27612709999084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577160835266</t>
   </si>
   <si>
     <t xml:space="preserve">2.3436393737793</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35328388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32434988021851</t>
+    <t xml:space="preserve">2.35328412055969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
     <t xml:space="preserve">2.17968106269836</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">2.18932557106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17003655433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1314582824707</t>
+    <t xml:space="preserve">2.17003631591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13145804405212</t>
   </si>
   <si>
     <t xml:space="preserve">2.08323502540588</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">2.11216878890991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07359051704407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03501200675964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98678874969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92409896850586</t>
+    <t xml:space="preserve">2.07359027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03501176834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98678886890411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92409884929657</t>
   </si>
   <si>
     <t xml:space="preserve">1.92892122268677</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">2.20861482620239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15074729919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37257313728333</t>
+    <t xml:space="preserve">2.15074706077576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37257289886475</t>
   </si>
   <si>
     <t xml:space="preserve">2.38221764564514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56546545028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87409257888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66191148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64262223243713</t>
+    <t xml:space="preserve">2.56546521186829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87409281730652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66191124916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64262199401855</t>
   </si>
   <si>
     <t xml:space="preserve">2.59439921379089</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">2.61368823051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53653168678284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52688694000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51724195480347</t>
+    <t xml:space="preserve">2.53653144836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52688670158386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51724219322205</t>
   </si>
   <si>
     <t xml:space="preserve">2.70048975944519</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">2.72942352294922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78729104995728</t>
+    <t xml:space="preserve">2.78729128837585</t>
   </si>
   <si>
     <t xml:space="preserve">2.94160485267639</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98018312454224</t>
+    <t xml:space="preserve">2.98018288612366</t>
   </si>
   <si>
     <t xml:space="preserve">2.9608941078186</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">3.03805112838745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343092918396</t>
+    <t xml:space="preserve">3.16343069076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
@@ -1379,25 +1379,25 @@
     <t xml:space="preserve">3.17307543754578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13449716567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378618240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952147483826</t>
+    <t xml:space="preserve">3.13449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378594398499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952171325684</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3080997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32738924026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25023198127747</t>
+    <t xml:space="preserve">3.30809998512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32738900184631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25023221969604</t>
   </si>
   <si>
     <t xml:space="preserve">3.09591865539551</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05734038352966</t>
+    <t xml:space="preserve">3.05734014511108</t>
   </si>
   <si>
     <t xml:space="preserve">2.92231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93196034431458</t>
+    <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
     <t xml:space="preserve">2.90302634239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88373708724976</t>
+    <t xml:space="preserve">2.88373732566833</t>
   </si>
   <si>
     <t xml:space="preserve">2.86444807052612</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">2.84515881538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80658030509949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11520767211914</t>
+    <t xml:space="preserve">2.80658054351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11520791053772</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
@@ -1442,43 +1442,43 @@
     <t xml:space="preserve">3.59743809700012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67459487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71317315101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79033017158508</t>
+    <t xml:space="preserve">3.67459464073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71317338943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
     <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95428848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9446439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98322248458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05073404312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97357749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07002401351929</t>
+    <t xml:space="preserve">3.95428824424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94464421272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9832227230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0507345199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97357773780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07002353668213</t>
   </si>
   <si>
     <t xml:space="preserve">4.20504856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26291656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30149459838867</t>
+    <t xml:space="preserve">4.26291608810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30149412155151</t>
   </si>
   <si>
     <t xml:space="preserve">4.23398208618164</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">4.34971761703491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3400731086731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39794063568115</t>
+    <t xml:space="preserve">4.34007263183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39794015884399</t>
   </si>
   <si>
     <t xml:space="preserve">4.42687463760376</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">4.22433757781982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08931303024292</t>
+    <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
     <t xml:space="preserve">4.03144502639771</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40758562088013</t>
+    <t xml:space="preserve">4.40758514404297</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
@@ -1529,37 +1529,37 @@
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3690071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12789154052734</t>
+    <t xml:space="preserve">4.36900663375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1278920173645</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25327110290527</t>
+    <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
     <t xml:space="preserve">4.1857590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14718103408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02180099487305</t>
+    <t xml:space="preserve">4.14718055725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02180051803589</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611455917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33042812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51367521286011</t>
+    <t xml:space="preserve">4.17611408233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33042764663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51367568969727</t>
   </si>
   <si>
     <t xml:space="preserve">4.46545267105103</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">4.49438619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44616317749023</t>
+    <t xml:space="preserve">4.44616365432739</t>
   </si>
   <si>
     <t xml:space="preserve">4.41722965240479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64869976043701</t>
+    <t xml:space="preserve">4.64870023727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.80301380157471</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">4.72585725784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6390552520752</t>
+    <t xml:space="preserve">4.63905572891235</t>
   </si>
   <si>
     <t xml:space="preserve">4.62941074371338</t>
@@ -1601,22 +1601,22 @@
     <t xml:space="preserve">4.61012172698975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154273986816</t>
+    <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.27256059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11824655532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682554244995</t>
+    <t xml:space="preserve">4.11824703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682458877563</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260921478271</t>
+    <t xml:space="preserve">4.54260969161987</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1634,19 +1634,19 @@
     <t xml:space="preserve">4.97661638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0151948928833</t>
+    <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
     <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59387159347534</t>
+    <t xml:space="preserve">5.5938720703125</t>
   </si>
   <si>
     <t xml:space="preserve">5.4974250793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28524446487427</t>
+    <t xml:space="preserve">5.28524398803711</t>
   </si>
   <si>
     <t xml:space="preserve">5.3045334815979</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">4.86088180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84159183502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93803834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73550128936768</t>
+    <t xml:space="preserve">4.84159231185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93803787231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
     <t xml:space="preserve">4.70608854293823</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96100187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13748025894165</t>
+    <t xml:space="preserve">4.87276220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9610013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432725906372</t>
+    <t xml:space="preserve">5.00021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432773590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667579650879</t>
+    <t xml:space="preserve">4.67667531967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1730,25 +1730,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413246154785</t>
+    <t xml:space="preserve">4.72569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413198471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73550176620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687107086182</t>
+    <t xml:space="preserve">4.92178440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687154769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1778,16 +1775,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000118255615</t>
+    <t xml:space="preserve">4.74530601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000165939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5982403755188</t>
+    <t xml:space="preserve">4.59824085235596</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1796,7 +1793,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921913146973</t>
+    <t xml:space="preserve">4.54921865463257</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1823,40 +1820,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254451751709</t>
+    <t xml:space="preserve">4.38254499435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32371854782104</t>
+    <t xml:space="preserve">4.3237190246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508832931519</t>
+    <t xml:space="preserve">4.264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508880615234</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1374363899231</t>
+    <t xml:space="preserve">4.13743591308594</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352375030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117521286011</t>
+    <t xml:space="preserve">4.33352327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117568969727</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1865,7 +1862,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274074554443</t>
+    <t xml:space="preserve">4.37274026870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1880,10 +1877,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16684913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19626235961914</t>
+    <t xml:space="preserve">4.1668496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1962628364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -46400,7 +46397,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1681" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46556,7 +46553,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46634,7 +46631,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1690" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46660,7 +46657,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46686,7 +46683,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1692" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46738,7 +46735,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1694" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46764,7 +46761,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1695" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46816,7 +46813,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46842,7 +46839,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1698" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46868,7 +46865,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1699" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46894,7 +46891,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1700" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46920,7 +46917,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1701" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46946,7 +46943,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47076,7 +47073,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47102,7 +47099,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1708" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47128,7 +47125,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1709" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47154,7 +47151,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1710" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47206,7 +47203,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47232,7 +47229,7 @@
         <v>4.5</v>
       </c>
       <c r="G1713" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47258,7 +47255,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47284,7 +47281,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47310,7 +47307,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47336,7 +47333,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47362,7 +47359,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1718" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47414,7 +47411,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1720" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47440,7 +47437,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47466,7 +47463,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1722" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47544,7 +47541,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1725" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47570,7 +47567,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1726" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47596,7 +47593,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47622,7 +47619,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1728" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47648,7 +47645,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1729" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47674,7 +47671,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47700,7 +47697,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1731" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47726,7 +47723,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1732" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47752,7 +47749,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1733" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47830,7 +47827,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1736" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47856,7 +47853,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1737" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47882,7 +47879,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1738" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47934,7 +47931,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1740" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47960,7 +47957,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1741" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47986,7 +47983,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1742" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48064,7 +48061,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1745" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48090,7 +48087,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1746" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48142,7 +48139,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1748" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48168,7 +48165,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1749" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48194,7 +48191,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1750" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48220,7 +48217,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1751" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48246,7 +48243,7 @@
         <v>4.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48272,7 +48269,7 @@
         <v>4.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48298,7 +48295,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1754" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48324,7 +48321,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1755" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48350,7 +48347,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1756" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48376,7 +48373,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1757" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48402,7 +48399,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48428,7 +48425,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1759" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48454,7 +48451,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1760" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48480,7 +48477,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1761" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48506,7 +48503,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1762" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48532,7 +48529,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1763" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48558,7 +48555,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48584,7 +48581,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1765" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48610,7 +48607,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1766" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48636,7 +48633,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1767" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48662,7 +48659,7 @@
         <v>4.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48688,7 +48685,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1769" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48714,7 +48711,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1770" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48740,7 +48737,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1771" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48766,7 +48763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1772" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48792,7 +48789,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1773" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48818,7 +48815,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1774" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48844,7 +48841,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1775" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48870,7 +48867,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48896,7 +48893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1777" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48922,7 +48919,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1778" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48948,7 +48945,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1779" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48974,7 +48971,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1780" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49000,7 +48997,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1781" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49026,7 +49023,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1782" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49052,7 +49049,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49078,7 +49075,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49104,7 +49101,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1785" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49130,7 +49127,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49156,7 +49153,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1787" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49182,7 +49179,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1788" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49208,7 +49205,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49234,7 +49231,7 @@
         <v>4.5</v>
       </c>
       <c r="G1790" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49260,7 +49257,7 @@
         <v>4.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49286,7 +49283,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49312,7 +49309,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49338,7 +49335,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49364,7 +49361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1795" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49390,7 +49387,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1796" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49416,7 +49413,7 @@
         <v>4.75</v>
       </c>
       <c r="G1797" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49442,7 +49439,7 @@
         <v>4.75</v>
       </c>
       <c r="G1798" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49468,7 +49465,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1799" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49494,7 +49491,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49546,7 +49543,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1802" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49572,7 +49569,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1803" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49598,7 +49595,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1804" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49624,7 +49621,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1805" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49650,7 +49647,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1806" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49676,7 +49673,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1807" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49702,7 +49699,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1808" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49728,7 +49725,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1809" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49754,7 +49751,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1810" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49780,7 +49777,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1811" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49806,7 +49803,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1812" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49832,7 +49829,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1813" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49858,7 +49855,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1814" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49884,7 +49881,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1815" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49910,7 +49907,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1816" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49936,7 +49933,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1817" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49962,7 +49959,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49988,7 +49985,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1819" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50014,7 +50011,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1820" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50040,7 +50037,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1821" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50066,7 +50063,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1822" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50092,7 +50089,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1823" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50118,7 +50115,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1824" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50196,7 +50193,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50352,7 +50349,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50378,7 +50375,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1834" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50404,7 +50401,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1835" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50430,7 +50427,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1836" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50456,7 +50453,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1837" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50534,7 +50531,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1840" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50586,7 +50583,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1842" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50638,7 +50635,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1844" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50690,7 +50687,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1846" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50716,7 +50713,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1847" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50742,7 +50739,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1848" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50768,7 +50765,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1849" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50794,7 +50791,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1850" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50820,7 +50817,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1851" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50846,7 +50843,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50872,7 +50869,7 @@
         <v>4.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50898,7 +50895,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1854" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50924,7 +50921,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1855" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50950,7 +50947,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1856" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50976,7 +50973,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51002,7 +50999,7 @@
         <v>4.5</v>
       </c>
       <c r="G1858" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51028,7 +51025,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1859" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51054,7 +51051,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51080,7 +51077,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1861" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51106,7 +51103,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51132,7 +51129,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1863" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51158,7 +51155,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1864" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51184,7 +51181,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1865" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51210,7 +51207,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1866" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51236,7 +51233,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51262,7 +51259,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1868" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51288,7 +51285,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1869" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51314,7 +51311,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51340,7 +51337,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1871" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51366,7 +51363,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1872" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51392,7 +51389,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1873" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51418,7 +51415,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1874" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51444,7 +51441,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1875" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51470,7 +51467,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1876" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51496,7 +51493,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1877" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51522,7 +51519,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51548,7 +51545,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1879" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51574,7 +51571,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1880" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51600,7 +51597,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1881" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51626,7 +51623,7 @@
         <v>4.5</v>
       </c>
       <c r="G1882" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51652,7 +51649,7 @@
         <v>4.5</v>
       </c>
       <c r="G1883" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51678,7 +51675,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51704,7 +51701,7 @@
         <v>4.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51730,7 +51727,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1886" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51756,7 +51753,7 @@
         <v>4.5</v>
       </c>
       <c r="G1887" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51782,7 +51779,7 @@
         <v>4.5</v>
       </c>
       <c r="G1888" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51808,7 +51805,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51834,7 +51831,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1890" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51860,7 +51857,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1891" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51886,7 +51883,7 @@
         <v>4.5</v>
       </c>
       <c r="G1892" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51912,7 +51909,7 @@
         <v>4.5</v>
       </c>
       <c r="G1893" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51938,7 +51935,7 @@
         <v>4.5</v>
       </c>
       <c r="G1894" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51964,7 +51961,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51990,7 +51987,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52016,7 +52013,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1897" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52042,7 +52039,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1898" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52068,7 +52065,7 @@
         <v>4.5</v>
       </c>
       <c r="G1899" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52094,7 +52091,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1900" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52120,7 +52117,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1901" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52146,7 +52143,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1902" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52172,7 +52169,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52198,7 +52195,7 @@
         <v>4.5</v>
       </c>
       <c r="G1904" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52224,7 +52221,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1905" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52250,7 +52247,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1906" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52276,7 +52273,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1907" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52302,7 +52299,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1908" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52328,7 +52325,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1909" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52354,7 +52351,7 @@
         <v>4.75</v>
       </c>
       <c r="G1910" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52380,7 +52377,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52406,7 +52403,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1912" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52432,7 +52429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1913" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52458,7 +52455,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1914" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52484,7 +52481,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1915" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52510,7 +52507,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1916" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52536,7 +52533,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1917" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52562,7 +52559,7 @@
         <v>4.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52588,7 +52585,7 @@
         <v>4.75</v>
       </c>
       <c r="G1919" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52614,7 +52611,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1920" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52640,7 +52637,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1921" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52666,7 +52663,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1922" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52692,7 +52689,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52718,7 +52715,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1924" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52744,7 +52741,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52770,7 +52767,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1926" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52796,7 +52793,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1927" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52822,7 +52819,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1928" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52848,7 +52845,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1929" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52874,7 +52871,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1930" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52900,7 +52897,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1931" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52926,7 +52923,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1932" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52952,7 +52949,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1933" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52978,7 +52975,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1934" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53004,7 +53001,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1935" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53030,7 +53027,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1936" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53056,7 +53053,7 @@
         <v>4.5</v>
       </c>
       <c r="G1937" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53082,7 +53079,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1938" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53108,7 +53105,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1939" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53134,7 +53131,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1940" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53160,7 +53157,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53186,7 +53183,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1942" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53212,7 +53209,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1943" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53238,7 +53235,7 @@
         <v>4.5</v>
       </c>
       <c r="G1944" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53264,7 +53261,7 @@
         <v>4.5</v>
       </c>
       <c r="G1945" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53290,7 +53287,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1946" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53316,7 +53313,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1947" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53342,7 +53339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1948" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53368,7 +53365,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1949" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53394,7 +53391,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1950" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53420,7 +53417,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1951" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53446,7 +53443,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1952" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53472,7 +53469,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1953" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53498,7 +53495,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1954" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53524,7 +53521,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53550,7 +53547,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1956" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53576,7 +53573,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1957" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53602,7 +53599,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1958" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53628,7 +53625,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1959" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53654,7 +53651,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1960" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53680,7 +53677,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1961" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53706,7 +53703,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53732,7 +53729,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1963" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53758,7 +53755,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1964" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53784,7 +53781,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1965" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53810,7 +53807,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1966" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53836,7 +53833,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1967" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53862,7 +53859,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1968" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53888,7 +53885,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1969" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53914,7 +53911,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1970" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53940,7 +53937,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53966,7 +53963,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1972" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53992,7 +53989,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54018,7 +54015,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1974" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54044,7 +54041,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1975" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54070,7 +54067,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54096,7 +54093,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54122,7 +54119,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1978" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54148,7 +54145,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1979" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54174,7 +54171,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54200,7 +54197,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54226,7 +54223,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1982" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54252,7 +54249,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1983" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54278,7 +54275,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1984" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54304,7 +54301,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1985" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54330,7 +54327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1986" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54356,7 +54353,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54382,7 +54379,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1988" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54408,7 +54405,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1989" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54434,7 +54431,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54460,7 +54457,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1991" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54486,7 +54483,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54512,7 +54509,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1993" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54538,7 +54535,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54564,7 +54561,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1995" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54590,7 +54587,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1996" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54616,7 +54613,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54642,7 +54639,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54668,7 +54665,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1999" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54694,7 +54691,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2000" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54720,7 +54717,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2001" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54746,7 +54743,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2002" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54772,7 +54769,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2003" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54798,7 +54795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2004" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54824,7 +54821,7 @@
         <v>4.75</v>
       </c>
       <c r="G2005" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54850,7 +54847,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2006" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54876,7 +54873,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2007" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54902,7 +54899,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2008" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54928,7 +54925,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2009" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54954,7 +54951,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2010" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54980,7 +54977,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2011" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55006,7 +55003,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2012" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55032,7 +55029,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55058,7 +55055,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55084,7 +55081,7 @@
         <v>4.5</v>
       </c>
       <c r="G2015" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55110,7 +55107,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2016" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55136,7 +55133,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2017" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55162,7 +55159,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2018" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55188,7 +55185,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2019" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55214,7 +55211,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2020" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55240,7 +55237,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2021" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55266,7 +55263,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2022" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55292,7 +55289,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2023" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55318,7 +55315,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2024" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55344,7 +55341,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2025" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55370,7 +55367,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2026" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55396,7 +55393,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2027" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55422,7 +55419,7 @@
         <v>4.75</v>
       </c>
       <c r="G2028" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55448,7 +55445,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2029" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55474,7 +55471,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2030" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55500,7 +55497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2031" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55526,7 +55523,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2032" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55552,7 +55549,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2033" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55578,7 +55575,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2034" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55604,7 +55601,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2035" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55630,7 +55627,7 @@
         <v>5</v>
       </c>
       <c r="G2036" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55656,7 +55653,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55682,7 +55679,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2038" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55708,7 +55705,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2039" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55734,7 +55731,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55760,7 +55757,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55786,7 +55783,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2042" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55812,7 +55809,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2043" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55838,7 +55835,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2044" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55864,7 +55861,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2045" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55890,7 +55887,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2046" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55916,7 +55913,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55942,7 +55939,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2048" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55968,7 +55965,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2049" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55994,7 +55991,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2050" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56020,7 +56017,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2051" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56046,7 +56043,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2052" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56072,7 +56069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2053" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56098,7 +56095,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2054" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56124,7 +56121,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56150,7 +56147,7 @@
         <v>5</v>
       </c>
       <c r="G2056" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56176,7 +56173,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56202,7 +56199,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56228,7 +56225,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2059" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56254,7 +56251,7 @@
         <v>5</v>
       </c>
       <c r="G2060" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56280,7 +56277,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2061" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56306,7 +56303,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2062" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56332,7 +56329,7 @@
         <v>5</v>
       </c>
       <c r="G2063" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56358,7 +56355,7 @@
         <v>5</v>
       </c>
       <c r="G2064" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56384,7 +56381,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2065" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56410,7 +56407,7 @@
         <v>5</v>
       </c>
       <c r="G2066" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56436,7 +56433,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2067" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56462,7 +56459,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2068" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56488,7 +56485,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2069" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56514,7 +56511,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2070" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56540,7 +56537,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2071" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56566,7 +56563,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2072" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56592,7 +56589,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2073" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56618,7 +56615,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2074" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56644,7 +56641,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2075" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56670,7 +56667,7 @@
         <v>5.5</v>
       </c>
       <c r="G2076" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56696,7 +56693,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56722,7 +56719,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56748,7 +56745,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2079" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56774,7 +56771,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2080" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56800,7 +56797,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56826,7 +56823,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2082" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56852,7 +56849,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2083" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56878,7 +56875,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2084" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56904,7 +56901,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2085" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56930,7 +56927,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2086" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56956,7 +56953,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2087" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56982,7 +56979,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2088" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57008,7 +57005,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2089" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57034,7 +57031,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2090" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57060,7 +57057,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57086,7 +57083,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2092" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57112,7 +57109,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2093" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57138,7 +57135,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2094" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57164,7 +57161,7 @@
         <v>5</v>
       </c>
       <c r="G2095" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57190,7 +57187,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2096" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57216,7 +57213,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2097" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57242,7 +57239,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57268,7 +57265,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2099" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57294,7 +57291,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2100" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57320,7 +57317,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2101" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57346,7 +57343,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57372,7 +57369,7 @@
         <v>5</v>
       </c>
       <c r="G2103" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57398,7 +57395,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57424,7 +57421,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2105" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57450,7 +57447,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2106" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57476,7 +57473,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2107" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57502,7 +57499,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2108" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57528,7 +57525,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2109" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57554,7 +57551,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57580,7 +57577,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57606,7 +57603,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2112" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57632,7 +57629,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2113" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57658,7 +57655,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2114" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57684,7 +57681,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2115" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57710,7 +57707,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57736,7 +57733,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2117" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57762,7 +57759,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2118" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57788,7 +57785,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2119" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57814,7 +57811,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2120" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57840,7 +57837,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2121" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57866,7 +57863,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2122" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57892,7 +57889,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57918,7 +57915,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57944,7 +57941,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57970,7 +57967,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2126" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57996,7 +57993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2127" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58022,7 +58019,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2128" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58048,7 +58045,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2129" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58074,7 +58071,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58100,7 +58097,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2131" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58126,7 +58123,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2132" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58152,7 +58149,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2133" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58178,7 +58175,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2134" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58204,7 +58201,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2135" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58230,7 +58227,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2136" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58256,7 +58253,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58282,7 +58279,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2138" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58308,7 +58305,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2139" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58334,7 +58331,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2140" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58360,7 +58357,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2141" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58386,7 +58383,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2142" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58412,7 +58409,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2143" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58438,7 +58435,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2144" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58464,7 +58461,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2145" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58490,7 +58487,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2146" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58516,7 +58513,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2147" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58542,7 +58539,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2148" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58568,7 +58565,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2149" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58594,7 +58591,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58620,7 +58617,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2151" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58646,7 +58643,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2152" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58672,7 +58669,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2153" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58698,7 +58695,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2154" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58724,7 +58721,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2155" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58750,7 +58747,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2156" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58776,7 +58773,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2157" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58802,7 +58799,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2158" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58828,7 +58825,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58854,7 +58851,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2160" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58880,7 +58877,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58906,7 +58903,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2162" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58932,7 +58929,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2163" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58958,7 +58955,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2164" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58984,7 +58981,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2165" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59010,7 +59007,7 @@
         <v>4.75</v>
       </c>
       <c r="G2166" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59036,7 +59033,7 @@
         <v>4.75</v>
       </c>
       <c r="G2167" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59062,7 +59059,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2168" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59088,7 +59085,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59114,7 +59111,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2170" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59140,7 +59137,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59166,7 +59163,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2172" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59192,7 +59189,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2173" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59218,7 +59215,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2174" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59244,7 +59241,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2175" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59270,7 +59267,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59296,7 +59293,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2177" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59322,7 +59319,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2178" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59348,7 +59345,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2179" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59374,7 +59371,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2180" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59400,7 +59397,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2181" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59426,7 +59423,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2182" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59452,7 +59449,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2183" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59478,7 +59475,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2184" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59504,7 +59501,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2185" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59530,7 +59527,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2186" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59556,7 +59553,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2187" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59582,7 +59579,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2188" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59608,7 +59605,7 @@
         <v>4.25</v>
       </c>
       <c r="G2189" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59634,7 +59631,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2190" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59660,7 +59657,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2191" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59686,7 +59683,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2192" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59712,7 +59709,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2193" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59738,7 +59735,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2194" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59764,7 +59761,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2195" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59790,7 +59787,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2196" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59816,7 +59813,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59842,7 +59839,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2198" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59868,7 +59865,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59894,7 +59891,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2200" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59920,7 +59917,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2201" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59946,7 +59943,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2202" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59972,7 +59969,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59998,7 +59995,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60024,7 +60021,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2205" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60050,7 +60047,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2206" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60076,7 +60073,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2207" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60102,7 +60099,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60128,7 +60125,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2209" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60154,7 +60151,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2210" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60180,7 +60177,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2211" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60206,7 +60203,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60232,7 +60229,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2213" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60258,7 +60255,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2214" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60284,7 +60281,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60310,7 +60307,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2216" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60336,7 +60333,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2217" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60362,7 +60359,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2218" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60388,7 +60385,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2219" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60414,7 +60411,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2220" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60440,7 +60437,7 @@
         <v>4.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60466,7 +60463,7 @@
         <v>4.5</v>
       </c>
       <c r="G2222" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60492,7 +60489,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2223" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60518,7 +60515,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60544,7 +60541,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2225" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60570,7 +60567,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2226" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60596,7 +60593,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2227" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60622,7 +60619,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2228" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60648,7 +60645,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2229" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60674,7 +60671,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2230" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60700,7 +60697,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2231" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60726,7 +60723,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2232" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60752,7 +60749,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60778,7 +60775,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60804,7 +60801,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2235" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60830,7 +60827,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2236" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60856,7 +60853,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2237" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60882,7 +60879,7 @@
         <v>4.5</v>
       </c>
       <c r="G2238" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60908,7 +60905,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2239" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60934,7 +60931,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2240" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60960,7 +60957,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2241" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60986,7 +60983,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2242" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61012,7 +61009,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2243" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61038,7 +61035,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2244" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61064,7 +61061,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2245" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61090,7 +61087,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2246" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61116,7 +61113,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2247" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61142,7 +61139,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2248" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61168,7 +61165,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2249" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61194,7 +61191,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2250" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61220,7 +61217,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2251" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61246,7 +61243,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2252" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61272,7 +61269,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61298,7 +61295,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2254" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61324,7 +61321,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2255" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61350,7 +61347,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2256" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61376,7 +61373,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2257" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61402,7 +61399,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2258" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61428,7 +61425,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2259" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61454,7 +61451,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2260" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61480,7 +61477,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61506,7 +61503,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61532,7 +61529,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2263" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61558,7 +61555,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2264" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61584,7 +61581,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2265" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61610,7 +61607,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2266" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61636,7 +61633,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2267" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61662,7 +61659,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61688,7 +61685,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2269" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61714,7 +61711,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2270" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61740,7 +61737,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2271" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61766,7 +61763,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2272" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61792,7 +61789,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2273" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61818,7 +61815,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2274" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61844,7 +61841,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2275" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61870,7 +61867,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2276" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61896,7 +61893,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2277" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61922,7 +61919,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2278" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61948,7 +61945,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2279" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61974,7 +61971,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2280" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62000,7 +61997,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2281" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62026,7 +62023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2282" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62052,7 +62049,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2283" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62078,7 +62075,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2284" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62104,7 +62101,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2285" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62130,7 +62127,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62156,7 +62153,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2287" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62182,7 +62179,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2288" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62208,7 +62205,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2289" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62234,7 +62231,7 @@
         <v>4.5</v>
       </c>
       <c r="G2290" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62260,7 +62257,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2291" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62286,7 +62283,7 @@
         <v>4.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62312,7 +62309,7 @@
         <v>4.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62338,7 +62335,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2294" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62364,7 +62361,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2295" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62390,7 +62387,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2296" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62416,7 +62413,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2297" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62442,7 +62439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2298" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62468,7 +62465,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2299" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62494,7 +62491,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2300" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62520,7 +62517,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2301" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62546,7 +62543,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2302" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62572,7 +62569,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2303" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62598,7 +62595,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62624,7 +62621,7 @@
         <v>4.5</v>
       </c>
       <c r="G2305" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62650,7 +62647,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2306" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62676,7 +62673,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2307" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62702,7 +62699,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2308" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62728,7 +62725,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62754,7 +62751,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2310" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62780,7 +62777,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2311" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62806,7 +62803,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2312" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62832,7 +62829,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2313" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62858,7 +62855,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2314" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62884,7 +62881,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2315" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62910,7 +62907,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2316" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62936,7 +62933,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2317" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62962,7 +62959,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62988,7 +62985,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2319" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63014,7 +63011,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2320" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63040,7 +63037,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63066,7 +63063,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2322" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63092,7 +63089,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2323" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63118,7 +63115,7 @@
         <v>4.25</v>
       </c>
       <c r="G2324" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63144,7 +63141,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2325" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63170,7 +63167,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2326" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63196,7 +63193,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2327" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63222,7 +63219,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2328" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63248,7 +63245,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63274,7 +63271,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2330" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63300,7 +63297,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2331" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63326,7 +63323,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2332" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63352,7 +63349,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2333" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63378,7 +63375,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2334" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63404,7 +63401,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2335" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63430,7 +63427,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2336" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63456,7 +63453,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2337" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63482,7 +63479,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2338" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63508,7 +63505,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2339" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63534,7 +63531,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2340" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63560,7 +63557,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2341" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63586,7 +63583,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2342" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63612,7 +63609,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2343" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63638,7 +63635,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2344" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63664,7 +63661,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2345" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63690,7 +63687,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2346" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63716,7 +63713,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2347" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63742,7 +63739,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2348" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63768,7 +63765,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63794,7 +63791,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2350" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63820,7 +63817,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2351" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63846,7 +63843,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2352" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63872,7 +63869,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2353" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63898,7 +63895,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2354" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63924,7 +63921,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2355" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63950,7 +63947,7 @@
         <v>4</v>
       </c>
       <c r="G2356" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63976,7 +63973,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2357" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64002,7 +63999,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2358" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64028,7 +64025,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2359" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64054,7 +64051,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2360" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64080,7 +64077,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2361" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64106,7 +64103,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2362" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64132,7 +64129,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2363" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64158,7 +64155,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2364" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64184,7 +64181,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2365" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64210,7 +64207,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2366" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64236,7 +64233,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2367" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64262,7 +64259,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2368" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64288,7 +64285,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2369" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64314,7 +64311,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2370" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64340,7 +64337,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2371" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64366,7 +64363,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2372" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64392,7 +64389,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2373" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64418,7 +64415,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2374" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64444,7 +64441,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2375" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64470,7 +64467,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64496,7 +64493,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2377" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64522,7 +64519,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2378" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64548,7 +64545,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2379" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64574,7 +64571,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2380" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64600,7 +64597,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2381" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64626,7 +64623,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2382" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64652,7 +64649,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2383" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64678,7 +64675,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64704,7 +64701,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64730,7 +64727,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64756,7 +64753,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64782,7 +64779,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2388" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64808,7 +64805,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2389" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64834,7 +64831,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2390" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64860,7 +64857,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2391" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64886,7 +64883,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2392" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64912,7 +64909,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2393" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64938,7 +64935,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2394" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64964,7 +64961,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2395" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64990,7 +64987,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2396" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65016,7 +65013,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65042,7 +65039,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2398" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65068,7 +65065,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2399" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65094,7 +65091,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2400" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65120,7 +65117,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2401" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65146,7 +65143,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2402" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65172,7 +65169,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2403" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65198,7 +65195,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2404" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65224,7 +65221,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2405" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65250,7 +65247,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65276,7 +65273,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2407" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65302,7 +65299,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2408" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65328,7 +65325,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2409" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65354,7 +65351,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65380,7 +65377,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65406,7 +65403,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2412" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65432,7 +65429,7 @@
         <v>4</v>
       </c>
       <c r="G2413" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65458,7 +65455,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2414" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65484,7 +65481,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2415" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65510,7 +65507,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2416" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65536,7 +65533,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65562,7 +65559,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2418" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65588,7 +65585,7 @@
         <v>4</v>
       </c>
       <c r="G2419" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65614,7 +65611,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2420" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65640,7 +65637,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2421" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65666,7 +65663,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2422" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65692,7 +65689,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2423" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65718,7 +65715,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65744,7 +65741,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2425" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65770,7 +65767,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2426" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65796,7 +65793,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2427" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65822,7 +65819,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2428" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65848,7 +65845,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65874,7 +65871,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2430" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65900,7 +65897,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2431" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65926,7 +65923,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2432" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65952,7 +65949,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2433" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65978,7 +65975,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2434" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66004,7 +66001,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2435" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66030,7 +66027,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2436" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66056,7 +66053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2437" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66082,7 +66079,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2438" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66108,7 +66105,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2439" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66134,7 +66131,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66160,7 +66157,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66186,7 +66183,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2442" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66212,7 +66209,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2443" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66238,7 +66235,7 @@
         <v>4</v>
       </c>
       <c r="G2444" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66264,7 +66261,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2445" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66290,7 +66287,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2446" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66316,7 +66313,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2447" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66342,7 +66339,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66368,7 +66365,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2449" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66394,7 +66391,7 @@
         <v>4</v>
       </c>
       <c r="G2450" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66420,7 +66417,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2451" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66446,7 +66443,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2452" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66472,7 +66469,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2453" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66498,7 +66495,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2454" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66524,7 +66521,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2455" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66550,7 +66547,7 @@
         <v>4</v>
       </c>
       <c r="G2456" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66576,7 +66573,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2457" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66602,7 +66599,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2458" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66628,7 +66625,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2459" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66654,7 +66651,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2460" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66680,7 +66677,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2461" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66706,7 +66703,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2462" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66732,7 +66729,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66758,7 +66755,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2464" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66784,7 +66781,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2465" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66810,7 +66807,7 @@
         <v>4</v>
       </c>
       <c r="G2466" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66836,7 +66833,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2467" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66862,7 +66859,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2468" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66888,7 +66885,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2469" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66914,7 +66911,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2470" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66940,7 +66937,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2471" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66966,7 +66963,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2472" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66992,7 +66989,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2473" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67018,7 +67015,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2474" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67044,7 +67041,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67070,7 +67067,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67096,7 +67093,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2477" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67122,7 +67119,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2478" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67148,7 +67145,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2479" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67174,7 +67171,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2480" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67200,7 +67197,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2481" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67226,7 +67223,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2482" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67252,7 +67249,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2483" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67278,7 +67275,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2484" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67304,7 +67301,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67330,7 +67327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2486" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67356,7 +67353,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2487" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67382,7 +67379,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67408,7 +67405,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2489" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67434,7 +67431,7 @@
         <v>4.25</v>
       </c>
       <c r="G2490" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67460,7 +67457,7 @@
         <v>4.25</v>
       </c>
       <c r="G2491" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67486,7 +67483,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2492" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67512,7 +67509,7 @@
         <v>4.25</v>
       </c>
       <c r="G2493" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67538,7 +67535,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67564,7 +67561,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2495" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67590,7 +67587,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2496" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67616,7 +67613,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2497" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67642,7 +67639,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2498" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67668,7 +67665,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2499" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67694,7 +67691,7 @@
         <v>4.25</v>
       </c>
       <c r="G2500" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67720,7 +67717,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2501" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67746,7 +67743,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2502" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67772,7 +67769,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2503" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67798,7 +67795,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2504" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67824,7 +67821,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2505" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67850,7 +67847,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2506" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67876,7 +67873,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2507" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67902,7 +67899,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2508" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67928,7 +67925,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2509" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67954,7 +67951,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2510" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67980,7 +67977,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2511" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68006,7 +68003,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2512" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68032,7 +68029,7 @@
         <v>4.25</v>
       </c>
       <c r="G2513" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68058,7 +68055,7 @@
         <v>4.25</v>
       </c>
       <c r="G2514" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68084,7 +68081,7 @@
         <v>4.25</v>
       </c>
       <c r="G2515" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68110,7 +68107,7 @@
         <v>4.25</v>
       </c>
       <c r="G2516" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68136,7 +68133,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2517" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68162,7 +68159,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2518" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68188,7 +68185,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2519" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68214,7 +68211,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2520" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68240,7 +68237,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2521" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68266,7 +68263,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2522" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68292,7 +68289,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2523" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68318,7 +68315,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2524" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68344,7 +68341,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2525" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68370,7 +68367,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2526" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68396,7 +68393,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2527" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68422,7 +68419,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2528" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68448,7 +68445,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2529" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68474,7 +68471,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2530" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68500,7 +68497,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2531" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68526,7 +68523,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2532" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68552,7 +68549,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2533" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68578,7 +68575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2534" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68604,7 +68601,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2535" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68630,7 +68627,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2536" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68656,7 +68653,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2537" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68682,7 +68679,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2538" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68690,7 +68687,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6082407407</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>920</v>
@@ -68708,7 +68705,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2539" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="786">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,133 +38,133 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282109260559</t>
+    <t xml:space="preserve">3.87282085418701</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105989456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87458205223083</t>
+    <t xml:space="preserve">3.87106037139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87458252906799</t>
   </si>
   <si>
     <t xml:space="preserve">3.86577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86401510238647</t>
+    <t xml:space="preserve">3.86401534080505</t>
   </si>
   <si>
     <t xml:space="preserve">3.78652381896973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74249458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79532909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771806716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977957725525</t>
+    <t xml:space="preserve">3.74249386787415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79532933235168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771735191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977933883667</t>
   </si>
   <si>
     <t xml:space="preserve">3.67733073234558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65443587303162</t>
+    <t xml:space="preserve">3.65443539619446</t>
   </si>
   <si>
     <t xml:space="preserve">3.663241147995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6438684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48712420463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61040639877319</t>
+    <t xml:space="preserve">3.64386868476868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712396621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61040592193604</t>
   </si>
   <si>
     <t xml:space="preserve">3.68965911865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66676378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6033616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56637716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.539959192276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61568975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64915227890015</t>
+    <t xml:space="preserve">3.6667640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336112976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085265159607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56637692451477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6156895160675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64915204048157</t>
   </si>
   <si>
     <t xml:space="preserve">3.65267419815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65091323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64210772514343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59455513954163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431517601013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75130081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81294131278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79356861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86225438117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80941891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368763923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73721027374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192691802979</t>
+    <t xml:space="preserve">3.65091252326965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64210724830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59455561637878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.751300573349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8129415512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79356837272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86225414276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81470227241516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80941963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721098899841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255421638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192715644836</t>
   </si>
   <si>
     <t xml:space="preserve">3.72135972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76891231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76539015769958</t>
+    <t xml:space="preserve">3.76891183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538968086243</t>
   </si>
   <si>
     <t xml:space="preserve">3.74953866004944</t>
@@ -173,52 +173,52 @@
     <t xml:space="preserve">3.74601697921753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73016548156738</t>
+    <t xml:space="preserve">3.7301664352417</t>
   </si>
   <si>
     <t xml:space="preserve">3.6984646320343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68613648414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488236427307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350826263428</t>
+    <t xml:space="preserve">3.6861367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488284111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8235080242157</t>
   </si>
   <si>
     <t xml:space="preserve">3.95383501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91861152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446230888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98377513885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94326853752136</t>
+    <t xml:space="preserve">3.9186110496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98377537727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9432680606842</t>
   </si>
   <si>
     <t xml:space="preserve">3.91508960723877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98553586006165</t>
+    <t xml:space="preserve">3.9855363368988</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89395546913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96087956428528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219427108765</t>
+    <t xml:space="preserve">3.89395523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96087980270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219403266907</t>
   </si>
   <si>
     <t xml:space="preserve">3.93622350692749</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">3.92741751670837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88338732719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02612829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97220754623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99018120765686</t>
+    <t xml:space="preserve">3.88338780403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0261287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97220706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99018144607544</t>
   </si>
   <si>
     <t xml:space="preserve">3.97759985923767</t>
@@ -260,100 +260,100 @@
     <t xml:space="preserve">3.88233828544617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9272723197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92367815971375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83560657501221</t>
+    <t xml:space="preserve">3.92727255821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92367839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83560633659363</t>
   </si>
   <si>
     <t xml:space="preserve">3.8913254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86436462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256718635559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8194305896759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799279212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59475779533386</t>
+    <t xml:space="preserve">3.86436486244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81942987442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799231529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76550889015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59475755691528</t>
   </si>
   <si>
     <t xml:space="preserve">3.61273145675659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67923450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63070487976074</t>
+    <t xml:space="preserve">3.67923426628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63070511817932</t>
   </si>
   <si>
     <t xml:space="preserve">3.62171864509583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65766620635986</t>
+    <t xml:space="preserve">3.65766596794128</t>
   </si>
   <si>
     <t xml:space="preserve">3.63789486885071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68103241920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57318949699402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60374450683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64688181877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6918158531189</t>
+    <t xml:space="preserve">3.68103218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632657051086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60374474525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64688205718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69181609153748</t>
   </si>
   <si>
     <t xml:space="preserve">3.73675060272217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75652146339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81763243675232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044244766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79246926307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74394035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449512481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067182540894</t>
+    <t xml:space="preserve">3.75652122497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8032534122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81763315200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044268608093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79246878623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7439398765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449536323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067206382751</t>
   </si>
   <si>
     <t xml:space="preserve">3.7762930393219</t>
@@ -368,40 +368,40 @@
     <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80145573616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7331554889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78348278999329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72416925430298</t>
+    <t xml:space="preserve">3.80145645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73315572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78348231315613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7241690158844</t>
   </si>
   <si>
     <t xml:space="preserve">3.77090072631836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72057437896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76371121406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72596621513367</t>
+    <t xml:space="preserve">3.72057390213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76371169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72596597671509</t>
   </si>
   <si>
     <t xml:space="preserve">3.70978975296021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70260047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73854780197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72956156730652</t>
+    <t xml:space="preserve">3.70260000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73854804039001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72956109046936</t>
   </si>
   <si>
     <t xml:space="preserve">3.72237205505371</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">3.72776341438293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75292682647705</t>
+    <t xml:space="preserve">3.75292706489563</t>
   </si>
   <si>
     <t xml:space="preserve">3.75831937789917</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">3.69541096687317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68462681770325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6936137676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66485548019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68822145462036</t>
+    <t xml:space="preserve">3.68462657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69361352920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66485571861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68822169303894</t>
   </si>
   <si>
     <t xml:space="preserve">3.73135852813721</t>
@@ -437,67 +437,67 @@
     <t xml:space="preserve">3.7133846282959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78168511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380913734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81224060058594</t>
+    <t xml:space="preserve">3.78168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83380961418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81224036216736</t>
   </si>
   <si>
     <t xml:space="preserve">3.81583499908447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82661962509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82841753959656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92547535896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93446183204651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92188024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90031242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335085868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639143943787</t>
+    <t xml:space="preserve">3.82661914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82841730117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92547488212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93446207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92188048362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031218528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639120101929</t>
   </si>
   <si>
     <t xml:space="preserve">3.83740377426147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87514877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94165182113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929913520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243644714355</t>
+    <t xml:space="preserve">3.87514853477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9416515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929865837097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243573188782</t>
   </si>
   <si>
     <t xml:space="preserve">3.98119378089905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97939705848694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94884133338928</t>
+    <t xml:space="preserve">3.97939658164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413548469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94884181022644</t>
   </si>
   <si>
     <t xml:space="preserve">3.87874341011047</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">4.01534414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02073669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00815534591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04050779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0530891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01714181900024</t>
+    <t xml:space="preserve">4.0207371711731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00815486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04050874710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05309009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01714134216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.0620756149292</t>
@@ -527,79 +527,79 @@
     <t xml:space="preserve">4.07106351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14295864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06926536560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08903741836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40357780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37661743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34606218338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34785938262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32808876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27236986160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11599731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03691339492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9847891330719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04230546951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95603036880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008280754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704365730286</t>
+    <t xml:space="preserve">4.14295816421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06926584243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08903694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40357828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37661695480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34606170654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34785890579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32808828353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27237033843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599779129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03691291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98478865623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95603108406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008376121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828584671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704413414001</t>
   </si>
   <si>
     <t xml:space="preserve">3.93266534805298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84099864959717</t>
+    <t xml:space="preserve">3.84099888801575</t>
   </si>
   <si>
     <t xml:space="preserve">3.86795926094055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90390682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94524621963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9635968208313</t>
+    <t xml:space="preserve">3.90390706062317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94524645805359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96359634399414</t>
   </si>
   <si>
     <t xml:space="preserve">3.99112129211426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98194670677185</t>
+    <t xml:space="preserve">3.98194646835327</t>
   </si>
   <si>
     <t xml:space="preserve">4.06819152832031</t>
@@ -608,34 +608,34 @@
     <t xml:space="preserve">3.94524669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89019656181335</t>
+    <t xml:space="preserve">3.8901960849762</t>
   </si>
   <si>
     <t xml:space="preserve">3.87184596061707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92689657211304</t>
+    <t xml:space="preserve">3.92689681053162</t>
   </si>
   <si>
     <t xml:space="preserve">4.06452083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.128746509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17462110519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12691116333008</t>
+    <t xml:space="preserve">4.12874603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17462158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12691164016724</t>
   </si>
   <si>
     <t xml:space="preserve">4.10672616958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05901670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03699684143066</t>
+    <t xml:space="preserve">4.05901622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03699636459351</t>
   </si>
   <si>
     <t xml:space="preserve">3.99479150772095</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">4.09204626083374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08103704452515</t>
+    <t xml:space="preserve">4.08103656768799</t>
   </si>
   <si>
     <t xml:space="preserve">4.05534648895264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09021139144897</t>
+    <t xml:space="preserve">4.09021186828613</t>
   </si>
   <si>
     <t xml:space="preserve">4.06268644332886</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">4.11039638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09388113021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20948600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1544361114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792133331299</t>
+    <t xml:space="preserve">4.09388160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20948648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15443658828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13792181015015</t>
   </si>
   <si>
     <t xml:space="preserve">4.12507677078247</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">4.11957120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13608646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15076637268066</t>
+    <t xml:space="preserve">4.13608598709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15076684951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.10305643081665</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">4.11223125457764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002592086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10122156143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16911745071411</t>
+    <t xml:space="preserve">4.07002639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10122108459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16911697387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.18379640579224</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">4.21132135391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0975513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05167675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01864671707153</t>
+    <t xml:space="preserve">4.09755182266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05167627334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01864624023438</t>
   </si>
   <si>
     <t xml:space="preserve">4.07920169830322</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">4.13425159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21866130828857</t>
+    <t xml:space="preserve">4.21866178512573</t>
   </si>
   <si>
     <t xml:space="preserve">4.13241672515869</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">4.14709615707397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14893198013306</t>
+    <t xml:space="preserve">4.1489315032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.19113636016846</t>
@@ -770,52 +770,52 @@
     <t xml:space="preserve">4.19297170639038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99662661552429</t>
+    <t xml:space="preserve">3.99662685394287</t>
   </si>
   <si>
     <t xml:space="preserve">4.04433631896973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98561692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341135025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02048110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92322635650635</t>
+    <t xml:space="preserve">3.98561668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341158866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0204815864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92322683334351</t>
   </si>
   <si>
     <t xml:space="preserve">4.03516101837158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08654117584229</t>
+    <t xml:space="preserve">4.08654165267944</t>
   </si>
   <si>
     <t xml:space="preserve">4.04800653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96726608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506122589111</t>
+    <t xml:space="preserve">3.96726655960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506146430969</t>
   </si>
   <si>
     <t xml:space="preserve">3.91772150993347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0002965927124</t>
+    <t xml:space="preserve">4.00029611587524</t>
   </si>
   <si>
     <t xml:space="preserve">3.97277164459229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93790650367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99846148490906</t>
+    <t xml:space="preserve">3.93790674209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846124649048</t>
   </si>
   <si>
     <t xml:space="preserve">4.04617118835449</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">3.88102173805237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85349678993225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442128181458</t>
+    <t xml:space="preserve">3.85349631309509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.954421043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.83514618873596</t>
@@ -839,70 +839,70 @@
     <t xml:space="preserve">3.90854716300964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9360716342926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86267185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82597208023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78927206993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.807621717453</t>
+    <t xml:space="preserve">3.93607115745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86267161369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82597160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78927159309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80762147903442</t>
   </si>
   <si>
     <t xml:space="preserve">4.02039480209351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04857397079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03918123245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97342705726624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221396446228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02978801727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96403336524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89827942848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91706609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616453170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101714134216</t>
+    <t xml:space="preserve">4.04857444763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03918075561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97342658042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9922137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02978754043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96403360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89827919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9170663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70101690292358</t>
   </si>
   <si>
     <t xml:space="preserve">3.75737762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73859071731567</t>
+    <t xml:space="preserve">3.73859095573425</t>
   </si>
   <si>
     <t xml:space="preserve">3.71980404853821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71041059494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63526272773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6258692741394</t>
+    <t xml:space="preserve">3.71041035652161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63526248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62586951255798</t>
   </si>
   <si>
     <t xml:space="preserve">3.52254176139832</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">3.42860722541809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35345935821533</t>
+    <t xml:space="preserve">3.28770565986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35345983505249</t>
   </si>
   <si>
     <t xml:space="preserve">3.33467292785645</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">3.37224650382996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38163995742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45678758621216</t>
+    <t xml:space="preserve">3.38164019584656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45678782463074</t>
   </si>
   <si>
     <t xml:space="preserve">3.46618103981018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36285281181335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44739413261414</t>
+    <t xml:space="preserve">3.36285305023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44739437103271</t>
   </si>
   <si>
     <t xml:space="preserve">3.43800067901611</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">3.4755744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49436116218567</t>
+    <t xml:space="preserve">3.49436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">3.31588578224182</t>
@@ -956,43 +956,43 @@
     <t xml:space="preserve">3.60708236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950879096985</t>
+    <t xml:space="preserve">3.56950855255127</t>
   </si>
   <si>
     <t xml:space="preserve">3.50375485420227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65404987335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48496770858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68223023414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5976893901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61647605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58829569816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55072212219238</t>
+    <t xml:space="preserve">3.65404963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48496794700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68222999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59768915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61647582054138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66344332695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58829545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5507218837738</t>
   </si>
   <si>
     <t xml:space="preserve">3.53193497657776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56011509895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57890200614929</t>
+    <t xml:space="preserve">3.56011533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57890224456787</t>
   </si>
   <si>
     <t xml:space="preserve">3.64465641975403</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">3.6728367805481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51314806938171</t>
+    <t xml:space="preserve">3.51314830780029</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">3.62637186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58779335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66495013237</t>
+    <t xml:space="preserve">3.58779358863831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66495037078857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">3.78068566322327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79997491836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210739135742</t>
+    <t xml:space="preserve">3.7999746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210715293884</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83855319023132</t>
+    <t xml:space="preserve">3.8385534286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1046,43 +1046,43 @@
     <t xml:space="preserve">3.72281789779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64566135406494</t>
+    <t xml:space="preserve">3.64566111564636</t>
   </si>
   <si>
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56850457191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52992582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47205829620361</t>
+    <t xml:space="preserve">3.56850433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52992606163025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47205805778503</t>
   </si>
   <si>
     <t xml:space="preserve">3.51063656806946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41419053077698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43347954750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45276880264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37561225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39490151405334</t>
+    <t xml:space="preserve">3.41419076919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43347978591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4527690410614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37561202049255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39490127563477</t>
   </si>
   <si>
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916598320007</t>
+    <t xml:space="preserve">3.27916622161865</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">3.14414167404175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2020092010498</t>
+    <t xml:space="preserve">3.20200896263123</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556316375732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0669846534729</t>
+    <t xml:space="preserve">3.06698489189148</t>
   </si>
   <si>
     <t xml:space="preserve">3.04769563674927</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">3.02840662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91267085075378</t>
+    <t xml:space="preserve">2.91267108917236</t>
   </si>
   <si>
     <t xml:space="preserve">2.85480356216431</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">2.71977877616882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83551406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.970538854599</t>
+    <t xml:space="preserve">2.83551430702209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97053861618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.89338183403015</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">2.98982763290405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95124959945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81622505187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79693603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75835704803467</t>
+    <t xml:space="preserve">2.95124936103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8162248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79693579673767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75835728645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.77764678001404</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">2.5847544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50759768486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46901893615723</t>
+    <t xml:space="preserve">2.50759744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46901917457581</t>
   </si>
   <si>
     <t xml:space="preserve">2.33399486541748</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.21825933456421</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14110255241394</t>
+    <t xml:space="preserve">2.14110279083252</t>
   </si>
   <si>
     <t xml:space="preserve">2.23754858970642</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.26648235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41115140914917</t>
+    <t xml:space="preserve">2.41115164756775</t>
   </si>
   <si>
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044090270996</t>
+    <t xml:space="preserve">2.43044066429138</t>
   </si>
   <si>
     <t xml:space="preserve">2.27612709999084</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22790384292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24719309806824</t>
+    <t xml:space="preserve">2.2279040813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24719333648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.35328412055969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32435011863708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17968106269836</t>
+    <t xml:space="preserve">2.32434988021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17968082427979</t>
   </si>
   <si>
     <t xml:space="preserve">2.18932557106018</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.17003631591797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13145804405212</t>
+    <t xml:space="preserve">2.1314582824707</t>
   </si>
   <si>
     <t xml:space="preserve">2.08323502540588</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">1.98678886890411</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92409884929657</t>
+    <t xml:space="preserve">1.92409896850586</t>
   </si>
   <si>
     <t xml:space="preserve">1.92892122268677</t>
@@ -1292,34 +1292,34 @@
     <t xml:space="preserve">1.95785510540009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20861482620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15074706077576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37257289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38221764564514</t>
+    <t xml:space="preserve">2.20861458778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15074729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37257313728333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38221788406372</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87409281730652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66191124916077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64262199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59439921379089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68120050430298</t>
+    <t xml:space="preserve">2.87409257888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66191148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64262223243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59439897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6812002658844</t>
   </si>
   <si>
     <t xml:space="preserve">2.65226674079895</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">2.61368823051453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53653144836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52688670158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51724219322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70048975944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71013426780701</t>
+    <t xml:space="preserve">2.53653168678284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52688694000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51724195480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70048952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71013402938843</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98018288612366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9608941078186</t>
+    <t xml:space="preserve">2.98018312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96089386940002</t>
   </si>
   <si>
     <t xml:space="preserve">3.03805112838745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21165370941162</t>
+    <t xml:space="preserve">3.16343092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21165347099304</t>
   </si>
   <si>
     <t xml:space="preserve">3.23094296455383</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">3.17307543754578</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952171325684</t>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378618240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952147483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
@@ -1400,28 +1400,28 @@
     <t xml:space="preserve">3.30809998512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32738900184631</t>
+    <t xml:space="preserve">3.32738924026489</t>
   </si>
   <si>
     <t xml:space="preserve">3.25023221969604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09591865539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766294002533</t>
+    <t xml:space="preserve">3.09591841697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07662916183472</t>
   </si>
   <si>
     <t xml:space="preserve">3.01876187324524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05734014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.931960105896</t>
+    <t xml:space="preserve">3.05734038352966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92231583595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93196034431458</t>
   </si>
   <si>
     <t xml:space="preserve">2.90302634239197</t>
@@ -1439,34 +1439,34 @@
     <t xml:space="preserve">2.80658054351807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67459464073181</t>
+    <t xml:space="preserve">3.59743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
     <t xml:space="preserve">3.71317338943481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79033041000366</t>
+    <t xml:space="preserve">3.79033017158508</t>
   </si>
   <si>
     <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95428824424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94464421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9832227230072</t>
+    <t xml:space="preserve">3.95428848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9446439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98322248458862</t>
   </si>
   <si>
     <t xml:space="preserve">4.0507345199585</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">4.20504856109619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26291608810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30149412155151</t>
+    <t xml:space="preserve">4.26291656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30149459838867</t>
   </si>
   <si>
     <t xml:space="preserve">4.23398208618164</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">4.42687463760376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45580768585205</t>
+    <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
     <t xml:space="preserve">4.22433757781982</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40758514404297</t>
+    <t xml:space="preserve">4.40758562088013</t>
   </si>
   <si>
     <t xml:space="preserve">4.50403070449829</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">4.43651866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36900663375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1278920173645</t>
+    <t xml:space="preserve">4.3690071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25327157974243</t>
+    <t xml:space="preserve">4.25327110290527</t>
   </si>
   <si>
     <t xml:space="preserve">4.1857590675354</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180051803589</t>
+    <t xml:space="preserve">4.02180099487305</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
+    <t xml:space="preserve">4.17611455917358</t>
   </si>
   <si>
     <t xml:space="preserve">4.33042764663696</t>
@@ -1580,16 +1580,16 @@
     <t xml:space="preserve">4.47509717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49438619613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44616365432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41722965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64870023727417</t>
+    <t xml:space="preserve">4.49438667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41722917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64869976043701</t>
   </si>
   <si>
     <t xml:space="preserve">4.80301380157471</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">4.57154321670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27256059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11824703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15682458877563</t>
+    <t xml:space="preserve">4.27256011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11824655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15682554244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372430801392</t>
+    <t xml:space="preserve">4.78372478485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1640,118 +1640,121 @@
     <t xml:space="preserve">4.97661638259888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01519536972046</t>
+    <t xml:space="preserve">5.0151948928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.45884704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5938720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28524398803711</t>
+    <t xml:space="preserve">5.59387159347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49742555618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28524446487427</t>
   </si>
   <si>
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026853561401</t>
+    <t xml:space="preserve">5.42026805877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84159231185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93803787231445</t>
+    <t xml:space="preserve">4.86088132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84159183502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93803834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73550128936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70608854293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86295795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87276268005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96100187301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13748025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0198278427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1963062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07865381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94139337539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90217542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00021886825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393623352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432725906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78452348709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67667579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61784934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6276535987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75511026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84334945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89237117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72569704055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413246154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76491498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92178392410278</t>
   </si>
   <si>
     <t xml:space="preserve">4.73550176620483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70608854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86295795440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87276220321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9610013961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13747978210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0198278427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1963062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07865381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94139337539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90217542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00021934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393671035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78452348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67667531967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61784934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6276535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75511026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84334945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89237117767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72569751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413198471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76491498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92178440093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687154769897</t>
+    <t xml:space="preserve">4.83354520797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687107086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1781,16 +1784,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000165939331</t>
+    <t xml:space="preserve">4.74530649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59824085235596</t>
+    <t xml:space="preserve">4.5982403755188</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1799,7 +1802,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921865463257</t>
+    <t xml:space="preserve">4.54921913146973</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1826,40 +1829,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254499435425</t>
+    <t xml:space="preserve">4.38254451751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3237190246582</t>
+    <t xml:space="preserve">4.32371854782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.264892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508880615234</t>
+    <t xml:space="preserve">4.26489305496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587133407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508832931519</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13743591308594</t>
+    <t xml:space="preserve">4.1374363899231</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352327346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117568969727</t>
+    <t xml:space="preserve">4.33352375030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117521286011</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1868,7 +1871,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274026870728</t>
+    <t xml:space="preserve">4.37274074554443</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1883,10 +1886,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1668496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1962628364563</t>
+    <t xml:space="preserve">4.16684913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19626235961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -46403,7 +46406,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1681" t="s">
-        <v>553</v>
+        <v>578</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46559,7 +46562,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1687" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46637,7 +46640,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1690" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46663,7 +46666,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46689,7 +46692,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1692" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46741,7 +46744,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1694" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46767,7 +46770,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1695" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46819,7 +46822,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1697" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46845,7 +46848,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1698" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46871,7 +46874,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1699" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46897,7 +46900,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1700" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46923,7 +46926,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1701" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46949,7 +46952,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47079,7 +47082,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1707" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47105,7 +47108,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1708" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47131,7 +47134,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1709" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47157,7 +47160,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1710" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47209,7 +47212,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1712" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47235,7 +47238,7 @@
         <v>4.5</v>
       </c>
       <c r="G1713" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47261,7 +47264,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1714" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47287,7 +47290,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1715" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47313,7 +47316,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1716" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47339,7 +47342,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47365,7 +47368,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1718" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47417,7 +47420,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1720" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47443,7 +47446,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47469,7 +47472,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1722" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47547,7 +47550,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1725" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47573,7 +47576,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1726" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47599,7 +47602,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47625,7 +47628,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1728" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47651,7 +47654,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1729" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47677,7 +47680,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47703,7 +47706,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1731" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47729,7 +47732,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1732" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47755,7 +47758,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1733" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47833,7 +47836,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1736" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47859,7 +47862,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1737" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47885,7 +47888,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1738" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47937,7 +47940,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1740" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47963,7 +47966,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1741" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47989,7 +47992,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1742" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48067,7 +48070,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1745" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48093,7 +48096,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1746" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48145,7 +48148,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1748" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48171,7 +48174,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1749" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48197,7 +48200,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1750" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48223,7 +48226,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1751" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48249,7 +48252,7 @@
         <v>4.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48275,7 +48278,7 @@
         <v>4.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48301,7 +48304,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1754" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48327,7 +48330,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1755" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48353,7 +48356,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1756" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48379,7 +48382,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1757" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48405,7 +48408,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48431,7 +48434,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1759" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48457,7 +48460,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1760" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48483,7 +48486,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1761" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48509,7 +48512,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1762" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48535,7 +48538,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1763" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48561,7 +48564,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48587,7 +48590,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1765" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48613,7 +48616,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1766" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48639,7 +48642,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1767" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48665,7 +48668,7 @@
         <v>4.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48691,7 +48694,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1769" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48717,7 +48720,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1770" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48743,7 +48746,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1771" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48769,7 +48772,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1772" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48795,7 +48798,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1773" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48821,7 +48824,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1774" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48847,7 +48850,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1775" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48873,7 +48876,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1776" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48899,7 +48902,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1777" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48925,7 +48928,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1778" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48951,7 +48954,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1779" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48977,7 +48980,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1780" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49003,7 +49006,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1781" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49029,7 +49032,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1782" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49055,7 +49058,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49081,7 +49084,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49107,7 +49110,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1785" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49133,7 +49136,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49159,7 +49162,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1787" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49185,7 +49188,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1788" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49211,7 +49214,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1789" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49237,7 +49240,7 @@
         <v>4.5</v>
       </c>
       <c r="G1790" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49263,7 +49266,7 @@
         <v>4.5</v>
       </c>
       <c r="G1791" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49289,7 +49292,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1792" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49315,7 +49318,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1793" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49341,7 +49344,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49367,7 +49370,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1795" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49393,7 +49396,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1796" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49419,7 +49422,7 @@
         <v>4.75</v>
       </c>
       <c r="G1797" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49445,7 +49448,7 @@
         <v>4.75</v>
       </c>
       <c r="G1798" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49471,7 +49474,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1799" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49497,7 +49500,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49549,7 +49552,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1802" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49575,7 +49578,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1803" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49601,7 +49604,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1804" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49627,7 +49630,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1805" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49653,7 +49656,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1806" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49679,7 +49682,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1807" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49705,7 +49708,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1808" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49731,7 +49734,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1809" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49757,7 +49760,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1810" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49783,7 +49786,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1811" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49809,7 +49812,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1812" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49835,7 +49838,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G1813" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49861,7 +49864,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1814" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49887,7 +49890,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1815" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49913,7 +49916,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1816" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49939,7 +49942,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1817" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49965,7 +49968,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49991,7 +49994,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1819" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50017,7 +50020,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1820" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50043,7 +50046,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1821" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50069,7 +50072,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1822" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50095,7 +50098,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1823" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50121,7 +50124,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1824" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50199,7 +50202,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1827" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50355,7 +50358,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50381,7 +50384,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1834" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50407,7 +50410,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1835" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50433,7 +50436,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1836" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50459,7 +50462,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1837" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50537,7 +50540,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1840" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50589,7 +50592,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1842" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50641,7 +50644,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1844" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50693,7 +50696,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1846" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50719,7 +50722,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1847" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50745,7 +50748,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1848" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50771,7 +50774,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1849" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50797,7 +50800,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1850" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50823,7 +50826,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1851" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50849,7 +50852,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1852" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50875,7 +50878,7 @@
         <v>4.25</v>
       </c>
       <c r="G1853" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50901,7 +50904,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1854" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50927,7 +50930,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1855" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50953,7 +50956,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1856" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50979,7 +50982,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51005,7 +51008,7 @@
         <v>4.5</v>
       </c>
       <c r="G1858" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51031,7 +51034,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1859" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51057,7 +51060,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51083,7 +51086,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1861" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51109,7 +51112,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51135,7 +51138,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1863" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51161,7 +51164,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1864" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51187,7 +51190,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1865" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51213,7 +51216,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1866" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51239,7 +51242,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51265,7 +51268,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1868" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51291,7 +51294,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1869" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51317,7 +51320,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1870" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51343,7 +51346,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1871" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51369,7 +51372,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1872" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51395,7 +51398,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1873" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51421,7 +51424,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1874" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51447,7 +51450,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1875" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51473,7 +51476,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1876" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51499,7 +51502,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1877" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51525,7 +51528,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1878" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51551,7 +51554,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1879" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51577,7 +51580,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1880" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51603,7 +51606,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1881" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51629,7 +51632,7 @@
         <v>4.5</v>
       </c>
       <c r="G1882" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51655,7 +51658,7 @@
         <v>4.5</v>
       </c>
       <c r="G1883" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51681,7 +51684,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51707,7 +51710,7 @@
         <v>4.5</v>
       </c>
       <c r="G1885" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51733,7 +51736,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1886" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51759,7 +51762,7 @@
         <v>4.5</v>
       </c>
       <c r="G1887" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51785,7 +51788,7 @@
         <v>4.5</v>
       </c>
       <c r="G1888" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51811,7 +51814,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51837,7 +51840,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1890" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51863,7 +51866,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1891" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51889,7 +51892,7 @@
         <v>4.5</v>
       </c>
       <c r="G1892" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51915,7 +51918,7 @@
         <v>4.5</v>
       </c>
       <c r="G1893" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51941,7 +51944,7 @@
         <v>4.5</v>
       </c>
       <c r="G1894" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51967,7 +51970,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51993,7 +51996,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1896" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52019,7 +52022,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1897" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52045,7 +52048,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1898" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52071,7 +52074,7 @@
         <v>4.5</v>
       </c>
       <c r="G1899" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52097,7 +52100,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1900" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52123,7 +52126,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1901" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52149,7 +52152,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1902" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52175,7 +52178,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1903" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52201,7 +52204,7 @@
         <v>4.5</v>
       </c>
       <c r="G1904" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52227,7 +52230,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1905" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52253,7 +52256,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1906" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52279,7 +52282,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1907" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52305,7 +52308,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1908" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52331,7 +52334,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1909" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52357,7 +52360,7 @@
         <v>4.75</v>
       </c>
       <c r="G1910" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52383,7 +52386,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1911" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52409,7 +52412,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1912" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52435,7 +52438,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1913" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52461,7 +52464,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1914" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52487,7 +52490,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1915" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52513,7 +52516,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1916" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52539,7 +52542,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1917" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52565,7 +52568,7 @@
         <v>4.75</v>
       </c>
       <c r="G1918" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52591,7 +52594,7 @@
         <v>4.75</v>
       </c>
       <c r="G1919" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52617,7 +52620,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1920" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52643,7 +52646,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1921" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52669,7 +52672,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1922" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52695,7 +52698,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52721,7 +52724,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1924" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52747,7 +52750,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52773,7 +52776,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1926" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52799,7 +52802,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1927" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52825,7 +52828,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1928" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52851,7 +52854,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1929" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52877,7 +52880,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1930" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52903,7 +52906,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1931" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52929,7 +52932,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1932" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52955,7 +52958,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1933" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52981,7 +52984,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G1934" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53007,7 +53010,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1935" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53033,7 +53036,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1936" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53059,7 +53062,7 @@
         <v>4.5</v>
       </c>
       <c r="G1937" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53085,7 +53088,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1938" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53111,7 +53114,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1939" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53137,7 +53140,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1940" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53163,7 +53166,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53189,7 +53192,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1942" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53215,7 +53218,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1943" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53241,7 +53244,7 @@
         <v>4.5</v>
       </c>
       <c r="G1944" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53267,7 +53270,7 @@
         <v>4.5</v>
       </c>
       <c r="G1945" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53293,7 +53296,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1946" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53319,7 +53322,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1947" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53345,7 +53348,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1948" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53371,7 +53374,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1949" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53397,7 +53400,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1950" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53423,7 +53426,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1951" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53449,7 +53452,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1952" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53475,7 +53478,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1953" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53501,7 +53504,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1954" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53527,7 +53530,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53553,7 +53556,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1956" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53579,7 +53582,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1957" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53605,7 +53608,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1958" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53631,7 +53634,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1959" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53657,7 +53660,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1960" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53683,7 +53686,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1961" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53709,7 +53712,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53735,7 +53738,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1963" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53761,7 +53764,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1964" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53787,7 +53790,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1965" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53813,7 +53816,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1966" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53839,7 +53842,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1967" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53865,7 +53868,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1968" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53891,7 +53894,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1969" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53917,7 +53920,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1970" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53943,7 +53946,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53969,7 +53972,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1972" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53995,7 +53998,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1973" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54021,7 +54024,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1974" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54047,7 +54050,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1975" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54073,7 +54076,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54099,7 +54102,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54125,7 +54128,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1978" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54151,7 +54154,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1979" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54177,7 +54180,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54203,7 +54206,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1981" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54229,7 +54232,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G1982" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54255,7 +54258,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G1983" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54281,7 +54284,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1984" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54307,7 +54310,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1985" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54333,7 +54336,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1986" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54359,7 +54362,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54385,7 +54388,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1988" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54411,7 +54414,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1989" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54437,7 +54440,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1990" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54463,7 +54466,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1991" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54489,7 +54492,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54515,7 +54518,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1993" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54541,7 +54544,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54567,7 +54570,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G1995" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54593,7 +54596,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1996" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54619,7 +54622,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1997" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54645,7 +54648,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54671,7 +54674,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1999" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54697,7 +54700,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2000" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54723,7 +54726,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2001" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54749,7 +54752,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2002" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54775,7 +54778,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2003" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54801,7 +54804,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2004" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54827,7 +54830,7 @@
         <v>4.75</v>
       </c>
       <c r="G2005" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54853,7 +54856,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2006" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54879,7 +54882,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2007" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54905,7 +54908,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2008" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54931,7 +54934,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2009" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54957,7 +54960,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2010" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54983,7 +54986,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2011" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55009,7 +55012,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2012" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55035,7 +55038,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55061,7 +55064,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2014" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55087,7 +55090,7 @@
         <v>4.5</v>
       </c>
       <c r="G2015" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55113,7 +55116,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2016" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55139,7 +55142,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2017" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55165,7 +55168,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2018" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55191,7 +55194,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2019" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55217,7 +55220,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2020" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55243,7 +55246,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2021" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55269,7 +55272,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2022" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55295,7 +55298,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2023" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55321,7 +55324,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2024" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55347,7 +55350,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2025" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55373,7 +55376,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2026" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55399,7 +55402,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G2027" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55425,7 +55428,7 @@
         <v>4.75</v>
       </c>
       <c r="G2028" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55451,7 +55454,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2029" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55477,7 +55480,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2030" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55503,7 +55506,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2031" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55529,7 +55532,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2032" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55555,7 +55558,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2033" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55581,7 +55584,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2034" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55607,7 +55610,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2035" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55633,7 +55636,7 @@
         <v>5</v>
       </c>
       <c r="G2036" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55659,7 +55662,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55685,7 +55688,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2038" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55711,7 +55714,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2039" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55737,7 +55740,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55763,7 +55766,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2041" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55789,7 +55792,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2042" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55815,7 +55818,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2043" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55841,7 +55844,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2044" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55867,7 +55870,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2045" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55893,7 +55896,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2046" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55919,7 +55922,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2047" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55945,7 +55948,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2048" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55971,7 +55974,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2049" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55997,7 +56000,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2050" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56023,7 +56026,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2051" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56049,7 +56052,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2052" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56075,7 +56078,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2053" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56101,7 +56104,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2054" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56127,7 +56130,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56153,7 +56156,7 @@
         <v>5</v>
       </c>
       <c r="G2056" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56179,7 +56182,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2057" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56205,7 +56208,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2058" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56231,7 +56234,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2059" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56257,7 +56260,7 @@
         <v>5</v>
       </c>
       <c r="G2060" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56283,7 +56286,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2061" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56309,7 +56312,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2062" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56335,7 +56338,7 @@
         <v>5</v>
       </c>
       <c r="G2063" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56361,7 +56364,7 @@
         <v>5</v>
       </c>
       <c r="G2064" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56387,7 +56390,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2065" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -56413,7 +56416,7 @@
         <v>5</v>
       </c>
       <c r="G2066" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -56439,7 +56442,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2067" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -56465,7 +56468,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2068" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -56491,7 +56494,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G2069" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -56517,7 +56520,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2070" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -56543,7 +56546,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2071" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -56569,7 +56572,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2072" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -56595,7 +56598,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2073" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -56621,7 +56624,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2074" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -56647,7 +56650,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2075" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56673,7 +56676,7 @@
         <v>5.5</v>
       </c>
       <c r="G2076" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56699,7 +56702,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56725,7 +56728,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2078" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56751,7 +56754,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G2079" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56777,7 +56780,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2080" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56803,7 +56806,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2081" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56829,7 +56832,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2082" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56855,7 +56858,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2083" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56881,7 +56884,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2084" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56907,7 +56910,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G2085" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56933,7 +56936,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2086" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56959,7 +56962,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2087" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56985,7 +56988,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2088" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57011,7 +57014,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2089" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57037,7 +57040,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2090" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57063,7 +57066,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57089,7 +57092,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G2092" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57115,7 +57118,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2093" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57141,7 +57144,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2094" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57167,7 +57170,7 @@
         <v>5</v>
       </c>
       <c r="G2095" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57193,7 +57196,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2096" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57219,7 +57222,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2097" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57245,7 +57248,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2098" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57271,7 +57274,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2099" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57297,7 +57300,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2100" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57323,7 +57326,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2101" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57349,7 +57352,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2102" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57375,7 +57378,7 @@
         <v>5</v>
       </c>
       <c r="G2103" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -57401,7 +57404,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -57427,7 +57430,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2105" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -57453,7 +57456,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2106" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -57479,7 +57482,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2107" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -57505,7 +57508,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2108" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -57531,7 +57534,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2109" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -57557,7 +57560,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -57583,7 +57586,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -57609,7 +57612,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2112" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -57635,7 +57638,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2113" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -57661,7 +57664,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2114" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57687,7 +57690,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2115" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57713,7 +57716,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57739,7 +57742,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G2117" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57765,7 +57768,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G2118" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57791,7 +57794,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2119" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57817,7 +57820,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2120" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57843,7 +57846,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2121" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57869,7 +57872,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2122" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57895,7 +57898,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2123" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57921,7 +57924,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2124" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57947,7 +57950,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2125" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57973,7 +57976,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G2126" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57999,7 +58002,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G2127" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58025,7 +58028,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G2128" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58051,7 +58054,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2129" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58077,7 +58080,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2130" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58103,7 +58106,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2131" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58129,7 +58132,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2132" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58155,7 +58158,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2133" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58181,7 +58184,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G2134" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58207,7 +58210,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2135" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58233,7 +58236,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2136" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58259,7 +58262,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G2137" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58285,7 +58288,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2138" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58311,7 +58314,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2139" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58337,7 +58340,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2140" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58363,7 +58366,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2141" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58389,7 +58392,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2142" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -58415,7 +58418,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G2143" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -58441,7 +58444,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2144" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -58467,7 +58470,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G2145" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -58493,7 +58496,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G2146" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -58519,7 +58522,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2147" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -58545,7 +58548,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2148" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -58571,7 +58574,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2149" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -58597,7 +58600,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -58623,7 +58626,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G2151" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -58649,7 +58652,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2152" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58675,7 +58678,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G2153" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58701,7 +58704,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G2154" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58727,7 +58730,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G2155" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58753,7 +58756,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2156" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58779,7 +58782,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G2157" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58805,7 +58808,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G2158" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58831,7 +58834,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58857,7 +58860,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2160" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58883,7 +58886,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58909,7 +58912,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2162" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58935,7 +58938,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2163" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58961,7 +58964,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2164" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58987,7 +58990,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2165" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59013,7 +59016,7 @@
         <v>4.75</v>
       </c>
       <c r="G2166" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59039,7 +59042,7 @@
         <v>4.75</v>
       </c>
       <c r="G2167" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59065,7 +59068,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2168" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59091,7 +59094,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2169" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59117,7 +59120,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2170" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59143,7 +59146,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59169,7 +59172,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2172" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59195,7 +59198,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2173" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59221,7 +59224,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2174" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59247,7 +59250,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2175" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59273,7 +59276,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59299,7 +59302,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2177" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59325,7 +59328,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2178" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59351,7 +59354,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2179" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59377,7 +59380,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2180" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -59403,7 +59406,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2181" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -59429,7 +59432,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2182" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -59455,7 +59458,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2183" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -59481,7 +59484,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2184" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -59507,7 +59510,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2185" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -59533,7 +59536,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2186" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -59559,7 +59562,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2187" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -59585,7 +59588,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2188" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -59611,7 +59614,7 @@
         <v>4.25</v>
       </c>
       <c r="G2189" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -59637,7 +59640,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2190" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -59663,7 +59666,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2191" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59689,7 +59692,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2192" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59715,7 +59718,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2193" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59741,7 +59744,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2194" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59767,7 +59770,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2195" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59793,7 +59796,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2196" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59819,7 +59822,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2197" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59845,7 +59848,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2198" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59871,7 +59874,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2199" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59897,7 +59900,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2200" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59923,7 +59926,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2201" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59949,7 +59952,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2202" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59975,7 +59978,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2203" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60001,7 +60004,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2204" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60027,7 +60030,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2205" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60053,7 +60056,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2206" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60079,7 +60082,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2207" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60105,7 +60108,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2208" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60131,7 +60134,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2209" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60157,7 +60160,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2210" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60183,7 +60186,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2211" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60209,7 +60212,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60235,7 +60238,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2213" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60261,7 +60264,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2214" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60287,7 +60290,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G2215" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60313,7 +60316,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G2216" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60339,7 +60342,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2217" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60365,7 +60368,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2218" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -60391,7 +60394,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2219" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -60417,7 +60420,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2220" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -60443,7 +60446,7 @@
         <v>4.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -60469,7 +60472,7 @@
         <v>4.5</v>
       </c>
       <c r="G2222" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -60495,7 +60498,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2223" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -60521,7 +60524,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2224" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -60547,7 +60550,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2225" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -60573,7 +60576,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2226" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -60599,7 +60602,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G2227" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -60625,7 +60628,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2228" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -60651,7 +60654,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2229" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60677,7 +60680,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2230" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60703,7 +60706,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2231" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60729,7 +60732,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G2232" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60755,7 +60758,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G2233" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60781,7 +60784,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G2234" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60807,7 +60810,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2235" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60833,7 +60836,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2236" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60859,7 +60862,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G2237" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60885,7 +60888,7 @@
         <v>4.5</v>
       </c>
       <c r="G2238" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60911,7 +60914,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G2239" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60937,7 +60940,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2240" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60963,7 +60966,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2241" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60989,7 +60992,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2242" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61015,7 +61018,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2243" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61041,7 +61044,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2244" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61067,7 +61070,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2245" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61093,7 +61096,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2246" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61119,7 +61122,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2247" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61145,7 +61148,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2248" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61171,7 +61174,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G2249" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61197,7 +61200,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2250" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61223,7 +61226,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2251" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61249,7 +61252,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2252" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61275,7 +61278,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2253" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61301,7 +61304,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G2254" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61327,7 +61330,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2255" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61353,7 +61356,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2256" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61379,7 +61382,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2257" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -61405,7 +61408,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2258" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -61431,7 +61434,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2259" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -61457,7 +61460,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G2260" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -61483,7 +61486,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2261" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -61509,7 +61512,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G2262" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -61535,7 +61538,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2263" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -61561,7 +61564,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2264" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -61587,7 +61590,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2265" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -61613,7 +61616,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2266" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -61639,7 +61642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2267" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -61665,7 +61668,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61691,7 +61694,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2269" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61717,7 +61720,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2270" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61743,7 +61746,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2271" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61769,7 +61772,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2272" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61795,7 +61798,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2273" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61821,7 +61824,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2274" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61847,7 +61850,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2275" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61873,7 +61876,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2276" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61899,7 +61902,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2277" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61925,7 +61928,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G2278" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61951,7 +61954,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2279" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61977,7 +61980,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2280" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62003,7 +62006,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2281" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62029,7 +62032,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2282" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62055,7 +62058,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2283" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62081,7 +62084,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2284" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62107,7 +62110,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2285" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62133,7 +62136,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62159,7 +62162,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2287" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62185,7 +62188,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2288" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62211,7 +62214,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G2289" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62237,7 +62240,7 @@
         <v>4.5</v>
       </c>
       <c r="G2290" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62263,7 +62266,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2291" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62289,7 +62292,7 @@
         <v>4.5</v>
       </c>
       <c r="G2292" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62315,7 +62318,7 @@
         <v>4.5</v>
       </c>
       <c r="G2293" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62341,7 +62344,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2294" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62367,7 +62370,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2295" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -62393,7 +62396,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2296" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -62419,7 +62422,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2297" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -62445,7 +62448,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2298" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -62471,7 +62474,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2299" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -62497,7 +62500,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2300" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -62523,7 +62526,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2301" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -62549,7 +62552,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2302" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -62575,7 +62578,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2303" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -62601,7 +62604,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -62627,7 +62630,7 @@
         <v>4.5</v>
       </c>
       <c r="G2305" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -62653,7 +62656,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2306" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62679,7 +62682,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2307" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62705,7 +62708,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2308" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62731,7 +62734,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G2309" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62757,7 +62760,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G2310" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -62783,7 +62786,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2311" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -62809,7 +62812,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G2312" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62835,7 +62838,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2313" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62861,7 +62864,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2314" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62887,7 +62890,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2315" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62913,7 +62916,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2316" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62939,7 +62942,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2317" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62965,7 +62968,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2318" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62991,7 +62994,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2319" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63017,7 +63020,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2320" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63043,7 +63046,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2321" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63069,7 +63072,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2322" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63095,7 +63098,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2323" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63121,7 +63124,7 @@
         <v>4.25</v>
       </c>
       <c r="G2324" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63147,7 +63150,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2325" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63173,7 +63176,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2326" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63199,7 +63202,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2327" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63225,7 +63228,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2328" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63251,7 +63254,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63277,7 +63280,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2330" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63303,7 +63306,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2331" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63329,7 +63332,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2332" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63355,7 +63358,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2333" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63381,7 +63384,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2334" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -63407,7 +63410,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2335" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -63433,7 +63436,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2336" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -63459,7 +63462,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2337" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -63485,7 +63488,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2338" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -63511,7 +63514,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2339" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -63537,7 +63540,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2340" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -63563,7 +63566,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2341" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -63589,7 +63592,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2342" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -63615,7 +63618,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2343" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -63641,7 +63644,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2344" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -63667,7 +63670,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2345" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -63693,7 +63696,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2346" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -63719,7 +63722,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2347" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -63745,7 +63748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2348" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -63771,7 +63774,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2349" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -63797,7 +63800,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2350" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63823,7 +63826,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2351" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63849,7 +63852,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2352" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63875,7 +63878,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2353" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63901,7 +63904,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2354" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63927,7 +63930,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2355" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63953,7 +63956,7 @@
         <v>4</v>
       </c>
       <c r="G2356" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63979,7 +63982,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2357" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64005,7 +64008,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2358" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64031,7 +64034,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G2359" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64057,7 +64060,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2360" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64083,7 +64086,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2361" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64109,7 +64112,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2362" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64135,7 +64138,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2363" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64161,7 +64164,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G2364" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64187,7 +64190,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2365" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64213,7 +64216,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2366" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64239,7 +64242,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2367" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64265,7 +64268,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2368" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64291,7 +64294,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2369" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64317,7 +64320,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2370" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64343,7 +64346,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2371" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64369,7 +64372,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2372" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -64395,7 +64398,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2373" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -64421,7 +64424,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2374" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -64447,7 +64450,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2375" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -64473,7 +64476,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2376" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -64499,7 +64502,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2377" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -64525,7 +64528,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2378" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -64551,7 +64554,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2379" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -64577,7 +64580,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2380" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -64603,7 +64606,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2381" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -64629,7 +64632,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2382" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -64655,7 +64658,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2383" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -64681,7 +64684,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -64707,7 +64710,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2385" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -64733,7 +64736,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2386" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -64759,7 +64762,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2387" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -64785,7 +64788,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2388" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64811,7 +64814,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2389" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64837,7 +64840,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2390" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64863,7 +64866,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2391" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64889,7 +64892,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2392" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64915,7 +64918,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2393" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64941,7 +64944,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2394" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64967,7 +64970,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2395" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64993,7 +64996,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2396" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65019,7 +65022,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65045,7 +65048,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2398" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65071,7 +65074,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2399" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65097,7 +65100,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2400" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65123,7 +65126,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2401" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65149,7 +65152,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2402" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65175,7 +65178,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2403" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65201,7 +65204,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2404" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65227,7 +65230,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2405" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65253,7 +65256,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2406" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65279,7 +65282,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2407" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65305,7 +65308,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2408" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65331,7 +65334,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2409" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65357,7 +65360,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2410" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65383,7 +65386,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -65409,7 +65412,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2412" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -65435,7 +65438,7 @@
         <v>4</v>
       </c>
       <c r="G2413" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -65461,7 +65464,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2414" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -65487,7 +65490,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2415" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -65513,7 +65516,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2416" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -65539,7 +65542,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G2417" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -65565,7 +65568,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2418" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -65591,7 +65594,7 @@
         <v>4</v>
       </c>
       <c r="G2419" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -65617,7 +65620,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2420" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -65643,7 +65646,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2421" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -65669,7 +65672,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2422" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -65695,7 +65698,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2423" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -65721,7 +65724,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -65747,7 +65750,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G2425" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -65773,7 +65776,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2426" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -65799,7 +65802,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G2427" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65825,7 +65828,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2428" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65851,7 +65854,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2429" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65877,7 +65880,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G2430" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65903,7 +65906,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2431" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65929,7 +65932,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2432" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65955,7 +65958,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2433" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65981,7 +65984,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2434" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66007,7 +66010,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2435" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66033,7 +66036,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2436" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66059,7 +66062,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2437" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66085,7 +66088,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2438" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66111,7 +66114,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2439" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66137,7 +66140,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2440" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66163,7 +66166,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66189,7 +66192,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2442" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66215,7 +66218,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2443" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66241,7 +66244,7 @@
         <v>4</v>
       </c>
       <c r="G2444" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66267,7 +66270,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2445" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66293,7 +66296,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2446" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66319,7 +66322,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2447" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66345,7 +66348,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2448" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66371,7 +66374,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G2449" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -66397,7 +66400,7 @@
         <v>4</v>
       </c>
       <c r="G2450" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -66423,7 +66426,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G2451" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -66449,7 +66452,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2452" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -66475,7 +66478,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2453" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -66501,7 +66504,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2454" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -66527,7 +66530,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2455" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -66553,7 +66556,7 @@
         <v>4</v>
       </c>
       <c r="G2456" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -66579,7 +66582,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2457" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -66605,7 +66608,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2458" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -66631,7 +66634,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2459" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -66657,7 +66660,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2460" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -66683,7 +66686,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2461" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -66709,7 +66712,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2462" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -66735,7 +66738,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2463" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -66761,7 +66764,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2464" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -66787,7 +66790,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2465" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66813,7 +66816,7 @@
         <v>4</v>
       </c>
       <c r="G2466" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66839,7 +66842,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2467" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66865,7 +66868,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2468" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66891,7 +66894,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2469" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66917,7 +66920,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2470" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66943,7 +66946,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2471" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66969,7 +66972,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2472" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66995,7 +66998,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2473" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67021,7 +67024,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2474" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67047,7 +67050,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2475" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67073,7 +67076,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2476" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67099,7 +67102,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2477" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67125,7 +67128,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2478" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67151,7 +67154,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2479" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67177,7 +67180,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2480" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67203,7 +67206,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2481" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67229,7 +67232,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2482" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67255,7 +67258,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G2483" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67281,7 +67284,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2484" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67307,7 +67310,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G2485" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67333,7 +67336,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2486" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67359,7 +67362,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2487" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67385,7 +67388,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2488" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -67411,7 +67414,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2489" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -67437,7 +67440,7 @@
         <v>4.25</v>
       </c>
       <c r="G2490" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -67463,7 +67466,7 @@
         <v>4.25</v>
       </c>
       <c r="G2491" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -67489,7 +67492,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2492" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -67515,7 +67518,7 @@
         <v>4.25</v>
       </c>
       <c r="G2493" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -67541,7 +67544,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -67567,7 +67570,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2495" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -67593,7 +67596,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2496" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -67619,7 +67622,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2497" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -67645,7 +67648,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2498" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -67671,7 +67674,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2499" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -67697,7 +67700,7 @@
         <v>4.25</v>
       </c>
       <c r="G2500" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -67723,7 +67726,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2501" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -67749,7 +67752,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2502" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -67775,7 +67778,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2503" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -67801,7 +67804,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2504" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67827,7 +67830,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G2505" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67853,7 +67856,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2506" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67879,7 +67882,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2507" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67905,7 +67908,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2508" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67931,7 +67934,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G2509" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67957,7 +67960,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2510" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67983,7 +67986,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2511" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68009,7 +68012,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2512" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68035,7 +68038,7 @@
         <v>4.25</v>
       </c>
       <c r="G2513" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68061,7 +68064,7 @@
         <v>4.25</v>
       </c>
       <c r="G2514" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68087,7 +68090,7 @@
         <v>4.25</v>
       </c>
       <c r="G2515" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68113,7 +68116,7 @@
         <v>4.25</v>
       </c>
       <c r="G2516" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68139,7 +68142,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2517" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68165,7 +68168,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2518" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68191,7 +68194,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2519" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68217,7 +68220,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G2520" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68243,7 +68246,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2521" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68269,7 +68272,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G2522" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68295,7 +68298,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2523" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68321,7 +68324,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2524" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68347,7 +68350,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2525" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -68373,7 +68376,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2526" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -68399,7 +68402,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2527" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -68425,7 +68428,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G2528" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -68451,7 +68454,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2529" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -68477,7 +68480,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G2530" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -68503,7 +68506,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2531" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -68529,7 +68532,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G2532" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -68555,7 +68558,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2533" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -68581,7 +68584,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2534" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -68607,7 +68610,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2535" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -68633,7 +68636,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2536" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -68659,7 +68662,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2537" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -68685,7 +68688,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2538" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -68711,7 +68714,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2539" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -68737,7 +68740,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2540" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -68763,7 +68766,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2541" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>

--- a/data/MASI.MI.xlsx
+++ b/data/MASI.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87282133102417</t>
+    <t xml:space="preserve">3.87282037734985</t>
   </si>
   <si>
     <t xml:space="preserve">MASI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87105989456177</t>
+    <t xml:space="preserve">3.87105965614319</t>
   </si>
   <si>
     <t xml:space="preserve">3.87458229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86577606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86401510238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78652405738831</t>
+    <t xml:space="preserve">3.86577653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86401534080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78652358055115</t>
   </si>
   <si>
     <t xml:space="preserve">3.74249458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79532933235168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77771782875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62977957725525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67733073234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65443587303162</t>
+    <t xml:space="preserve">3.79532885551453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62977910041809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67733120918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65443539619446</t>
   </si>
   <si>
     <t xml:space="preserve">3.66324138641357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64386868476868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4871244430542</t>
+    <t xml:space="preserve">3.6438684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48712420463562</t>
   </si>
   <si>
     <t xml:space="preserve">3.61040616035461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68965888023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66676378250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6033616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68085289001465</t>
+    <t xml:space="preserve">3.68965911865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66676354408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60336112976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68085336685181</t>
   </si>
   <si>
     <t xml:space="preserve">3.56637716293335</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">3.6156895160675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64915204048157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65267419815063</t>
+    <t xml:space="preserve">3.64915227890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65267443656921</t>
   </si>
   <si>
     <t xml:space="preserve">3.65091323852539</t>
@@ -122,16 +122,16 @@
     <t xml:space="preserve">3.64210748672485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59455561637878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71431493759155</t>
+    <t xml:space="preserve">3.59455537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71431541442871</t>
   </si>
   <si>
     <t xml:space="preserve">3.751300573349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81294107437134</t>
+    <t xml:space="preserve">3.81294131278992</t>
   </si>
   <si>
     <t xml:space="preserve">3.79356813430786</t>
@@ -143,94 +143,94 @@
     <t xml:space="preserve">3.81470227241516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80941891670227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73368811607361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73721051216125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71255397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73192715644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72135972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76891231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76538991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7495391368866</t>
+    <t xml:space="preserve">3.80941915512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73368787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73721027374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71255421638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73192691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.721360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76891183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76538896560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74953889846802</t>
   </si>
   <si>
     <t xml:space="preserve">3.74601697921753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73016595840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69846439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68613624572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72488212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82350850105286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95383524894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91861152648926</t>
+    <t xml:space="preserve">3.73016619682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69846534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72488260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82350826263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95383548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91861128807068</t>
   </si>
   <si>
     <t xml:space="preserve">3.93446183204651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98377442359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94326829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91508960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98553586006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91332817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89395499229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96088051795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89219403266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93622374534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92741799354553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88338756561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99916815757751</t>
+    <t xml:space="preserve">3.98377537727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9432680606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91508936882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98553681373596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91332793235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89395546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96088027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89219427108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93622279167175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92741751670837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88338828086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99916744232178</t>
   </si>
   <si>
     <t xml:space="preserve">4.02612829208374</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">3.97220754623413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99018120765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97759938240051</t>
+    <t xml:space="preserve">3.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97759890556335</t>
   </si>
   <si>
     <t xml:space="preserve">4.04410266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98299193382263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95423340797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93625926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88233828544617</t>
+    <t xml:space="preserve">3.98299169540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95423364639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93625950813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88233852386475</t>
   </si>
   <si>
     <t xml:space="preserve">3.92727255821228</t>
@@ -266,25 +266,25 @@
     <t xml:space="preserve">3.92367792129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83560681343079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89132499694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86436486244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86256670951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81943035125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70799255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655086517334</t>
+    <t xml:space="preserve">3.83560633659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8913254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86436438560486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86256718635559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81943011283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70799231529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76550889015198</t>
   </si>
   <si>
     <t xml:space="preserve">3.59475779533386</t>
@@ -299,121 +299,121 @@
     <t xml:space="preserve">3.6307053565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62171816825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65766596794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63789486885071</t>
+    <t xml:space="preserve">3.62171864509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65766644477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63789463043213</t>
   </si>
   <si>
     <t xml:space="preserve">3.68103218078613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57318925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61632633209229</t>
+    <t xml:space="preserve">3.57318902015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61632609367371</t>
   </si>
   <si>
     <t xml:space="preserve">3.60374474525452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64688181877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69181609153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73675060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75652146339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80325365066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86616230010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81763291358948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81044292449951</t>
+    <t xml:space="preserve">3.64688158035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6918158531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73675084114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75652194023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80325388908386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86616182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81763219833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81044268608093</t>
   </si>
   <si>
     <t xml:space="preserve">3.79246878623962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7439398765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77449512481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79067158699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7762930393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78887414932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74753499031067</t>
+    <t xml:space="preserve">3.74394011497498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77449607849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79067206382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77629327774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78887462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74753451347351</t>
   </si>
   <si>
     <t xml:space="preserve">3.75112962722778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80145573616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73315596580505</t>
+    <t xml:space="preserve">3.80145621299744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7331554889679</t>
   </si>
   <si>
     <t xml:space="preserve">3.78348231315613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7241690158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77090072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72057437896729</t>
+    <t xml:space="preserve">3.72416925430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77090048789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72057366371155</t>
   </si>
   <si>
     <t xml:space="preserve">3.76371145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72596621513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70978999137878</t>
+    <t xml:space="preserve">3.72596645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70978975296021</t>
   </si>
   <si>
     <t xml:space="preserve">3.70260047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73854804039001</t>
+    <t xml:space="preserve">3.73854780197144</t>
   </si>
   <si>
     <t xml:space="preserve">3.72956109046936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72237181663513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72776365280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75292706489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75831937789917</t>
+    <t xml:space="preserve">3.72237133979797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72776389122009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75292730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75831913948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.69541096687317</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">3.66485548019409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68822169303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73135852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338486671448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78168487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83380889892578</t>
+    <t xml:space="preserve">3.68822145462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73135876655579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7133846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78168535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8338086605072</t>
   </si>
   <si>
     <t xml:space="preserve">3.81224083900452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81583523750305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82661986351013</t>
+    <t xml:space="preserve">3.81583499908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82661962509155</t>
   </si>
   <si>
     <t xml:space="preserve">3.82841753959656</t>
@@ -458,46 +458,49 @@
     <t xml:space="preserve">3.92547535896301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92188024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9003119468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87335109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84639096260071</t>
+    <t xml:space="preserve">3.93446230888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90031266212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87335085868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84639072418213</t>
   </si>
   <si>
     <t xml:space="preserve">3.83740401268005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87514853477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9416515827179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90929841995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95243644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98119449615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97939729690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88413572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94884133338928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87874364852905</t>
+    <t xml:space="preserve">3.87514925003052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94165205955505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90929913520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95243525505066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98119401931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9793963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88413548469543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94884157180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87874388694763</t>
   </si>
   <si>
     <t xml:space="preserve">4.01534414291382</t>
@@ -506,7 +509,7 @@
     <t xml:space="preserve">4.02073669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00815534591675</t>
+    <t xml:space="preserve">4.00815486907959</t>
   </si>
   <si>
     <t xml:space="preserve">4.04050731658936</t>
@@ -515,10 +518,10 @@
     <t xml:space="preserve">4.0530891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01714181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06207609176636</t>
+    <t xml:space="preserve">4.01714134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06207656860352</t>
   </si>
   <si>
     <t xml:space="preserve">4.07106351852417</t>
@@ -530,13 +533,13 @@
     <t xml:space="preserve">4.06926584243774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08903646469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40357875823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37661790847778</t>
+    <t xml:space="preserve">4.08903741836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40357780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37661743164062</t>
   </si>
   <si>
     <t xml:space="preserve">4.34606218338013</t>
@@ -548,13 +551,13 @@
     <t xml:space="preserve">4.32808828353882</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27236986160278</t>
+    <t xml:space="preserve">4.27237033843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.11599731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03691244125366</t>
+    <t xml:space="preserve">4.03691339492798</t>
   </si>
   <si>
     <t xml:space="preserve">3.9847891330719</t>
@@ -563,22 +566,22 @@
     <t xml:space="preserve">4.04230546951294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95603060722351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92008280754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91828560829163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94704365730286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93266463279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84099936485291</t>
+    <t xml:space="preserve">3.95603084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92008328437805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91828608512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94704437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93266487121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84099864959717</t>
   </si>
   <si>
     <t xml:space="preserve">3.86795926094055</t>
@@ -587,142 +590,142 @@
     <t xml:space="preserve">3.90390682220459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94524621963501</t>
+    <t xml:space="preserve">3.94524645805359</t>
   </si>
   <si>
     <t xml:space="preserve">3.9635968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99112105369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98194622993469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06819105148315</t>
+    <t xml:space="preserve">3.99112153053284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98194694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06819152832031</t>
   </si>
   <si>
     <t xml:space="preserve">3.8901960849762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8718466758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92689728736877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06452083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.128746509552</t>
+    <t xml:space="preserve">3.87184596061707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92689681053162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06452131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.17462158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12691116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10672664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05901575088501</t>
+    <t xml:space="preserve">4.12691164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10672616958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05901622772217</t>
   </si>
   <si>
     <t xml:space="preserve">4.03699636459351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99479150772095</t>
+    <t xml:space="preserve">3.99479174613953</t>
   </si>
   <si>
     <t xml:space="preserve">4.05351161956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08287048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03332710266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07369613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0920467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08103656768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09021186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06268692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15260124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15627098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16544580459595</t>
+    <t xml:space="preserve">4.08287143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03332662582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07369661331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09204626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08103609085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05534648895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09021139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0626859664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15260171890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15627145767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16544675827026</t>
   </si>
   <si>
     <t xml:space="preserve">4.11039638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09388113021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20948600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15443706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13792181015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12507629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11957120895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13608598709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15076637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10305595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17278623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11223125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07002639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10122156143188</t>
+    <t xml:space="preserve">4.09388160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20948648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1544361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13792133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12507581710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11957168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13608646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15076589584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10305643081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17278671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11223077774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07002687454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10122108459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.16911697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18379688262939</t>
+    <t xml:space="preserve">4.18379592895508</t>
   </si>
   <si>
     <t xml:space="preserve">4.21132135391235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0975513458252</t>
+    <t xml:space="preserve">4.09755182266235</t>
   </si>
   <si>
     <t xml:space="preserve">4.05167627334595</t>
@@ -743,13 +746,13 @@
     <t xml:space="preserve">4.13241624832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12140655517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11590147018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11773586273193</t>
+    <t xml:space="preserve">4.12140703201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11590099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11773681640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.14709663391113</t>
@@ -758,97 +761,97 @@
     <t xml:space="preserve">4.14893102645874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1911358833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19297218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99662613868713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04433584213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98561692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94341111183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02048063278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92322659492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03516054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08654165267944</t>
+    <t xml:space="preserve">4.19113683700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19297170639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99662661552429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04433679580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9856162071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94341158866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02048206329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92322611808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03516101837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08654117584229</t>
   </si>
   <si>
     <t xml:space="preserve">4.04800701141357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96726632118225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92506170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91772198677063</t>
+    <t xml:space="preserve">3.96726608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92506194114685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91772174835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.00029706954956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97277140617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93790602684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99846124649048</t>
+    <t xml:space="preserve">3.97277188301086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93790650367737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99846172332764</t>
   </si>
   <si>
     <t xml:space="preserve">4.04617166519165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88102126121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95442152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83514618873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90854716300964</t>
+    <t xml:space="preserve">3.88102173805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85349702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95442128181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8351469039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89937210083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90854668617249</t>
   </si>
   <si>
     <t xml:space="preserve">3.93607139587402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86267185211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82597184181213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78927183151245</t>
+    <t xml:space="preserve">3.86267161369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82597160339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78927206993103</t>
   </si>
   <si>
     <t xml:space="preserve">3.807621717453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02039480209351</t>
+    <t xml:space="preserve">4.02039432525635</t>
   </si>
   <si>
     <t xml:space="preserve">4.04857444763184</t>
@@ -857,34 +860,34 @@
     <t xml:space="preserve">4.03918075561523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97342658042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99221324920654</t>
+    <t xml:space="preserve">3.97342705726624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99221420288086</t>
   </si>
   <si>
     <t xml:space="preserve">4.02978754043579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96403360366821</t>
+    <t xml:space="preserve">3.96403288841248</t>
   </si>
   <si>
     <t xml:space="preserve">3.89827942848206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9170663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77616429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70101714134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7573778629303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73859095573425</t>
+    <t xml:space="preserve">3.91706609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77616477012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70101690292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75737762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73859047889709</t>
   </si>
   <si>
     <t xml:space="preserve">3.71980404853821</t>
@@ -893,19 +896,19 @@
     <t xml:space="preserve">3.71041059494019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63526248931885</t>
+    <t xml:space="preserve">3.63526272773743</t>
   </si>
   <si>
     <t xml:space="preserve">3.62586951255798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52254152297974</t>
+    <t xml:space="preserve">3.52254176139832</t>
   </si>
   <si>
     <t xml:space="preserve">3.42860698699951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28770542144775</t>
+    <t xml:space="preserve">3.28770565986633</t>
   </si>
   <si>
     <t xml:space="preserve">3.35345959663391</t>
@@ -920,13 +923,13 @@
     <t xml:space="preserve">3.38163995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45678758621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46618103981018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36285305023193</t>
+    <t xml:space="preserve">3.45678782463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4661808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36285281181335</t>
   </si>
   <si>
     <t xml:space="preserve">3.44739413261414</t>
@@ -938,10 +941,10 @@
     <t xml:space="preserve">3.40042662620544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47557425498962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49436116218567</t>
+    <t xml:space="preserve">3.4755744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49436140060425</t>
   </si>
   <si>
     <t xml:space="preserve">3.3158860206604</t>
@@ -950,34 +953,34 @@
     <t xml:space="preserve">3.60708260536194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56950879096985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50375485420227</t>
+    <t xml:space="preserve">3.56950855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50375461578369</t>
   </si>
   <si>
     <t xml:space="preserve">3.65404987335205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48496794700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68222999572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59768915176392</t>
+    <t xml:space="preserve">3.48496770858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68223023414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59768891334534</t>
   </si>
   <si>
     <t xml:space="preserve">3.61647605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66344356536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58829545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55072212219238</t>
+    <t xml:space="preserve">3.66344332695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58829569816589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5507218837738</t>
   </si>
   <si>
     <t xml:space="preserve">3.53193497657776</t>
@@ -989,19 +992,19 @@
     <t xml:space="preserve">3.57890224456787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64465641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6728367805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51314830780029</t>
+    <t xml:space="preserve">3.64465665817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67283654212952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51314806938171</t>
   </si>
   <si>
     <t xml:space="preserve">3.70352864265442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5492148399353</t>
+    <t xml:space="preserve">3.54921531677246</t>
   </si>
   <si>
     <t xml:space="preserve">3.62637186050415</t>
@@ -1010,7 +1013,7 @@
     <t xml:space="preserve">3.58779358863831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66495037078857</t>
+    <t xml:space="preserve">3.66495013237</t>
   </si>
   <si>
     <t xml:space="preserve">3.68423938751221</t>
@@ -1022,13 +1025,13 @@
     <t xml:space="preserve">3.7999746799469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210715293884</t>
+    <t xml:space="preserve">3.74210739135742</t>
   </si>
   <si>
     <t xml:space="preserve">3.81926417350769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8385534286499</t>
+    <t xml:space="preserve">3.83855295181274</t>
   </si>
   <si>
     <t xml:space="preserve">3.85784244537354</t>
@@ -1043,9 +1046,6 @@
     <t xml:space="preserve">3.64566111564636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60708284378052</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.56850433349609</t>
   </si>
   <si>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">3.41419053077698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43347954750061</t>
+    <t xml:space="preserve">3.43347978591919</t>
   </si>
   <si>
     <t xml:space="preserve">3.45276880264282</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">3.33703374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27916622161865</t>
+    <t xml:space="preserve">3.27916598320007</t>
   </si>
   <si>
     <t xml:space="preserve">3.18271994590759</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">2.85480356216431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7197790145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83551430702209</t>
+    <t xml:space="preserve">2.71977877616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83551406860352</t>
   </si>
   <si>
     <t xml:space="preserve">2.97053861618042</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">3.12485241889954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98982763290405</t>
+    <t xml:space="preserve">2.98982787132263</t>
   </si>
   <si>
     <t xml:space="preserve">2.95124959945679</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">2.77764678001404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73906779289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54617595672607</t>
+    <t xml:space="preserve">2.73906803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54617619514465</t>
   </si>
   <si>
     <t xml:space="preserve">2.62333297729492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60404396057129</t>
+    <t xml:space="preserve">2.60404372215271</t>
   </si>
   <si>
     <t xml:space="preserve">2.5847544670105</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">2.33399486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16039204597473</t>
+    <t xml:space="preserve">2.16039180755615</t>
   </si>
   <si>
     <t xml:space="preserve">2.04465627670288</t>
@@ -1184,10 +1184,10 @@
     <t xml:space="preserve">2.14110255241394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23754858970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02536725997925</t>
+    <t xml:space="preserve">2.23754835128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02536749839783</t>
   </si>
   <si>
     <t xml:space="preserve">2.198970079422</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">2.25683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29541611671448</t>
+    <t xml:space="preserve">2.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">2.31470537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26648211479187</t>
+    <t xml:space="preserve">2.26648259162903</t>
   </si>
   <si>
     <t xml:space="preserve">2.41115140914917</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">2.47866368293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43044066429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27612709999084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28577160835266</t>
+    <t xml:space="preserve">2.43044090270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27612686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28577136993408</t>
   </si>
   <si>
     <t xml:space="preserve">2.3436393737793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36292839050293</t>
+    <t xml:space="preserve">2.36292862892151</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506110191345</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">2.24719309806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35328412055969</t>
+    <t xml:space="preserve">2.35328388214111</t>
   </si>
   <si>
     <t xml:space="preserve">2.32435011863708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17968082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18932557106018</t>
+    <t xml:space="preserve">2.17968106269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18932580947876</t>
   </si>
   <si>
     <t xml:space="preserve">2.17003631591797</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">2.1025242805481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11216902732849</t>
+    <t xml:space="preserve">2.11216855049133</t>
   </si>
   <si>
     <t xml:space="preserve">2.07359027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03501176834106</t>
+    <t xml:space="preserve">2.03501152992249</t>
   </si>
   <si>
     <t xml:space="preserve">1.98678886890411</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">1.92892122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93856573104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95785510540009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20861482620239</t>
+    <t xml:space="preserve">1.93856585025787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9578549861908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20861458778381</t>
   </si>
   <si>
     <t xml:space="preserve">2.15074706077576</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">2.37257313728333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38221788406372</t>
+    <t xml:space="preserve">2.38221764564514</t>
   </si>
   <si>
     <t xml:space="preserve">2.56546521186829</t>
@@ -1319,10 +1319,10 @@
     <t xml:space="preserve">2.65226674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61368823051453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53653144836426</t>
+    <t xml:space="preserve">2.61368846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53653168678284</t>
   </si>
   <si>
     <t xml:space="preserve">2.52688670158386</t>
@@ -1334,40 +1334,40 @@
     <t xml:space="preserve">2.70048975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71013402938843</t>
+    <t xml:space="preserve">2.71013450622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.69084501266479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78729128837585</t>
+    <t xml:space="preserve">2.72942328453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78729152679443</t>
   </si>
   <si>
     <t xml:space="preserve">2.94160485267639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99947261810303</t>
+    <t xml:space="preserve">2.99947237968445</t>
   </si>
   <si>
     <t xml:space="preserve">2.98018312454224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96089386940002</t>
+    <t xml:space="preserve">2.9608941078186</t>
   </si>
   <si>
     <t xml:space="preserve">3.03805088996887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16343092918396</t>
+    <t xml:space="preserve">3.16343069076538</t>
   </si>
   <si>
     <t xml:space="preserve">3.21165370941162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23094296455383</t>
+    <t xml:space="preserve">3.23094320297241</t>
   </si>
   <si>
     <t xml:space="preserve">3.24058747291565</t>
@@ -1376,40 +1376,40 @@
     <t xml:space="preserve">3.19236469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17307543754578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15378594398499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26952147483826</t>
+    <t xml:space="preserve">3.1730751991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13449716567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15378618240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26952171325684</t>
   </si>
   <si>
     <t xml:space="preserve">3.25987696647644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30809998512268</t>
+    <t xml:space="preserve">3.30810022354126</t>
   </si>
   <si>
     <t xml:space="preserve">3.32738900184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25023221969604</t>
+    <t xml:space="preserve">3.25023198127747</t>
   </si>
   <si>
     <t xml:space="preserve">3.09591865539551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0766294002533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05734014511108</t>
+    <t xml:space="preserve">3.07662916183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01876187324524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05734038352966</t>
   </si>
   <si>
     <t xml:space="preserve">2.92231559753418</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.931960105896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90302658081055</t>
+    <t xml:space="preserve">2.90302634239197</t>
   </si>
   <si>
     <t xml:space="preserve">2.88373732566833</t>
@@ -1430,46 +1430,46 @@
     <t xml:space="preserve">2.84515881538391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80658054351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11520791053772</t>
+    <t xml:space="preserve">2.80658030509949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11520767211914</t>
   </si>
   <si>
     <t xml:space="preserve">3.28881072998047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59743809700012</t>
+    <t xml:space="preserve">3.59743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.67459487915039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71317315101624</t>
+    <t xml:space="preserve">3.71317338943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.79033041000366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88677668571472</t>
+    <t xml:space="preserve">3.88677644729614</t>
   </si>
   <si>
     <t xml:space="preserve">3.95428848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94464421272278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98322248458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0507345199585</t>
+    <t xml:space="preserve">3.94464373588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9832227230072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05073499679565</t>
   </si>
   <si>
     <t xml:space="preserve">3.97357773780823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07002353668213</t>
+    <t xml:space="preserve">4.07002305984497</t>
   </si>
   <si>
     <t xml:space="preserve">4.20504856109619</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">4.23398208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34971809387207</t>
+    <t xml:space="preserve">4.34971714019775</t>
   </si>
   <si>
     <t xml:space="preserve">4.34007263183594</t>
@@ -1499,13 +1499,13 @@
     <t xml:space="preserve">4.45580816268921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22433805465698</t>
+    <t xml:space="preserve">4.22433710098267</t>
   </si>
   <si>
     <t xml:space="preserve">4.08931255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03144454956055</t>
+    <t xml:space="preserve">4.03144550323486</t>
   </si>
   <si>
     <t xml:space="preserve">4.24362659454346</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">4.31113862991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29185009002686</t>
+    <t xml:space="preserve">4.2918496131897</t>
   </si>
   <si>
     <t xml:space="preserve">4.40758514404297</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">4.50403070449829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53296422958374</t>
+    <t xml:space="preserve">4.53296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">4.43651866912842</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">4.36900663375854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1278920173645</t>
+    <t xml:space="preserve">4.12789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.16647005081177</t>
@@ -1541,37 +1541,37 @@
     <t xml:space="preserve">4.25327157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1857590675354</t>
+    <t xml:space="preserve">4.18575954437256</t>
   </si>
   <si>
     <t xml:space="preserve">4.14718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02180099487305</t>
+    <t xml:space="preserve">4.02180051803589</t>
   </si>
   <si>
     <t xml:space="preserve">4.0796685218811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17611408233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33042764663696</t>
+    <t xml:space="preserve">4.17611455917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33042812347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.51367568969727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46545267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37865114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48474216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47509717941284</t>
+    <t xml:space="preserve">4.46545314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37865161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48474168777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47509670257568</t>
   </si>
   <si>
     <t xml:space="preserve">4.49438619613647</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">4.44616365432739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41722965240479</t>
+    <t xml:space="preserve">4.41722917556763</t>
   </si>
   <si>
     <t xml:space="preserve">4.64870023727417</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">4.80301380157471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72585678100586</t>
+    <t xml:space="preserve">4.72585725784302</t>
   </si>
   <si>
     <t xml:space="preserve">4.63905572891235</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">4.6101222038269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57154321670532</t>
+    <t xml:space="preserve">4.57154273986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.27256011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11824655532837</t>
+    <t xml:space="preserve">4.11824703216553</t>
   </si>
   <si>
     <t xml:space="preserve">4.15682506561279</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">4.38829612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54260969161987</t>
+    <t xml:space="preserve">4.54260921478271</t>
   </si>
   <si>
     <t xml:space="preserve">4.61976623535156</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">4.67763376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78372478485107</t>
+    <t xml:space="preserve">4.78372430801392</t>
   </si>
   <si>
     <t xml:space="preserve">4.89945983886719</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">5.01519536972046</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45884704589844</t>
+    <t xml:space="preserve">5.45884656906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.59387159347534</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">5.3045334815979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42026805877686</t>
+    <t xml:space="preserve">5.42026901245117</t>
   </si>
   <si>
     <t xml:space="preserve">5.38169002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86088132858276</t>
+    <t xml:space="preserve">4.86088180541992</t>
   </si>
   <si>
     <t xml:space="preserve">4.84159231185913</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">4.86295795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87276268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96100187301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13748025894165</t>
+    <t xml:space="preserve">4.87276220321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9610013961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13747978210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.0198278427124</t>
@@ -1700,19 +1700,19 @@
     <t xml:space="preserve">4.90217542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00021886825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81393623352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79432725906372</t>
+    <t xml:space="preserve">5.00021934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81393671035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79432773590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.78452348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67667579650879</t>
+    <t xml:space="preserve">4.67667531967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.61784934997559</t>
@@ -1730,22 +1730,22 @@
     <t xml:space="preserve">4.89237117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72569704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80413246154785</t>
+    <t xml:space="preserve">4.72569751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80413198471069</t>
   </si>
   <si>
     <t xml:space="preserve">4.76491498947144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92178392410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83354520797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66687107086182</t>
+    <t xml:space="preserve">4.92178440093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83354473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66687154769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.69628429412842</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">4.64726209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74530649185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51000118255615</t>
+    <t xml:space="preserve">4.74530601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51000165939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.41195821762085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5982403755188</t>
+    <t xml:space="preserve">4.59824085235596</t>
   </si>
   <si>
     <t xml:space="preserve">4.52961015701294</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">4.53941488265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54921913146973</t>
+    <t xml:space="preserve">4.54921865463257</t>
   </si>
   <si>
     <t xml:space="preserve">4.58843612670898</t>
@@ -1820,40 +1820,40 @@
     <t xml:space="preserve">4.48058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38254451751709</t>
+    <t xml:space="preserve">4.38254499435425</t>
   </si>
   <si>
     <t xml:space="preserve">4.36293601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32371854782104</t>
+    <t xml:space="preserve">4.3237190246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391429901123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26489305496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21587133407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25508832931519</t>
+    <t xml:space="preserve">4.264892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21587085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25508880615234</t>
   </si>
   <si>
     <t xml:space="preserve">4.23547983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1374363899231</t>
+    <t xml:space="preserve">4.13743591308594</t>
   </si>
   <si>
     <t xml:space="preserve">4.39234924316406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33352375030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45117521286011</t>
+    <t xml:space="preserve">4.33352327346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45117568969727</t>
   </si>
   <si>
     <t xml:space="preserve">4.56882762908936</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">4.657066822052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37274074554443</t>
+    <t xml:space="preserve">4.37274026870728</t>
   </si>
   <si>
     <t xml:space="preserve">4.82374095916748</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">4.28450155258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16684913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19626235961914</t>
+    <t xml:space="preserve">4.1668496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1962628364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.24528408050537</t>
@@ -9373,7 +9373,7 @@
         <v>4.37799978256226</v>
       </c>
       <c r="G257" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9425,7 +9425,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G259" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9451,7 +9451,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G260" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9477,7 +9477,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G261" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9503,7 +9503,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G262" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9529,7 +9529,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G263" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9555,7 +9555,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G264" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9581,7 +9581,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G265" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9607,7 +9607,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G266" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9685,7 +9685,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G269" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9711,7 +9711,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G270" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9789,7 +9789,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G273" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9815,7 +9815,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -9867,7 +9867,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G276" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9893,7 +9893,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G277" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9919,7 +9919,7 @@
         <v>4.36399984359741</v>
       </c>
       <c r="G278" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -9945,7 +9945,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G279" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -9971,7 +9971,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G280" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10049,7 +10049,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G283" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10075,7 +10075,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G284" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10127,7 +10127,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G286" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10153,7 +10153,7 @@
         <v>4.39400005340576</v>
       </c>
       <c r="G287" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10205,7 +10205,7 @@
         <v>4.31599998474121</v>
       </c>
       <c r="G289" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10283,7 +10283,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G292" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10309,7 +10309,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G293" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10361,7 +10361,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G295" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10413,7 +10413,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G297" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10439,7 +10439,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G298" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10491,7 +10491,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G300" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -10543,7 +10543,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G302" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -10595,7 +10595,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G304" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -10621,7 +10621,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G305" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10699,7 +10699,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G308" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10803,7 +10803,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G312" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -10829,7 +10829,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G313" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10855,7 +10855,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G314" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -10881,7 +10881,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G315" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10907,7 +10907,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G316" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10933,7 +10933,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G317" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10959,7 +10959,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G318" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -10985,7 +10985,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G319" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11011,7 +11011,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G320" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11037,7 +11037,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11063,7 +11063,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11089,7 +11089,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G323" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11141,7 +11141,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G325" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11167,7 +11167,7 @@
         <v>4.46799993515015</v>
       </c>
       <c r="G326" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11193,7 +11193,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11219,7 +11219,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G328" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11349,7 +11349,7 @@
         <v>4.40199995040894</v>
       </c>
       <c r="G333" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11375,7 +11375,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G334" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11401,7 +11401,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G335" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11505,7 +11505,7 @@
         <v>4.39200019836426</v>
       </c>
       <c r="G339" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11531,7 +11531,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G340" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -11557,7 +11557,7 @@
         <v>4.27400016784668</v>
       </c>
       <c r="G341" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11583,7 +11583,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G342" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -11661,7 +11661,7 @@
         <v>4.30399990081787</v>
       </c>
       <c r="G345" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -11843,7 +11843,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G352" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11869,7 +11869,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G353" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11895,7 +11895,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G354" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11921,7 +11921,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G355" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11947,7 +11947,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G356" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -11973,7 +11973,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G357" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -11999,7 +11999,7 @@
         <v>4.43400001525879</v>
       </c>
       <c r="G358" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12025,7 +12025,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G359" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12051,7 +12051,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G360" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12077,7 +12077,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G361" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12103,7 +12103,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G362" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12129,7 +12129,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G363" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12155,7 +12155,7 @@
         <v>4.5</v>
       </c>
       <c r="G364" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12181,7 +12181,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G365" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12207,7 +12207,7 @@
         <v>4.4980001449585</v>
       </c>
       <c r="G366" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12233,7 +12233,7 @@
         <v>4.47599983215332</v>
       </c>
       <c r="G367" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12259,7 +12259,7 @@
         <v>4.42399978637695</v>
       </c>
       <c r="G368" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12285,7 +12285,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G369" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12311,7 +12311,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G370" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12337,7 +12337,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G371" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12363,7 +12363,7 @@
         <v>4.35400009155273</v>
       </c>
       <c r="G372" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12389,7 +12389,7 @@
         <v>4.41800022125244</v>
       </c>
       <c r="G373" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12415,7 +12415,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G374" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12441,7 +12441,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G375" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12467,7 +12467,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G376" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12493,7 +12493,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G377" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12519,7 +12519,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G378" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12545,7 +12545,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G379" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12571,7 +12571,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G380" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12597,7 +12597,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G381" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12623,7 +12623,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G382" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12649,7 +12649,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G383" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12675,7 +12675,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G384" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12701,7 +12701,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G385" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12727,7 +12727,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G386" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12753,7 +12753,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G387" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12779,7 +12779,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G388" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12805,7 +12805,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G389" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12831,7 +12831,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G390" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12857,7 +12857,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G391" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12883,7 +12883,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G392" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12909,7 +12909,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G393" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12935,7 +12935,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G394" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12961,7 +12961,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12987,7 +12987,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G396" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13013,7 +13013,7 @@
         <v>4.52600002288818</v>
       </c>
       <c r="G397" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13039,7 +13039,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G398" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13065,7 +13065,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G399" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13091,7 +13091,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G400" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13117,7 +13117,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G401" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13143,7 +13143,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G402" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G403" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13195,7 +13195,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G404" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13221,7 +13221,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G405" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13247,7 +13247,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G406" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13273,7 +13273,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G407" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13299,7 +13299,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G408" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13325,7 +13325,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G409" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13351,7 +13351,7 @@
         <v>4.49599981307983</v>
       </c>
       <c r="G410" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13377,7 +13377,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G411" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13403,7 +13403,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G412" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13429,7 +13429,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G413" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13455,7 +13455,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G414" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13481,7 +13481,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G415" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13507,7 +13507,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G416" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13533,7 +13533,7 @@
         <v>4.5</v>
       </c>
       <c r="G417" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13559,7 +13559,7 @@
         <v>4.5</v>
       </c>
       <c r="G418" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13585,7 +13585,7 @@
         <v>4.5</v>
       </c>
       <c r="G419" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13611,7 +13611,7 @@
         <v>4.47200012207031</v>
       </c>
       <c r="G420" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13637,7 +13637,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G421" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13663,7 +13663,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G422" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13689,7 +13689,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G423" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13715,7 +13715,7 @@
         <v>4.48199987411499</v>
       </c>
       <c r="G424" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13741,7 +13741,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G425" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13767,7 +13767,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G426" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13793,7 +13793,7 @@
         <v>4.5</v>
       </c>
       <c r="G427" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13819,7 +13819,7 @@
         <v>4.5</v>
       </c>
       <c r="G428" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13845,7 +13845,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G429" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13871,7 +13871,7 @@
         <v>4.54400014877319</v>
       </c>
       <c r="G430" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13897,7 +13897,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G431" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13923,7 +13923,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G432" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13949,7 +13949,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G433" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13975,7 +13975,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G434" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14001,7 +14001,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G435" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14027,7 +14027,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G436" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14053,7 +14053,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G437" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14079,7 +14079,7 @@
         <v>4.5479998588562</v>
       </c>
       <c r="G438" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14105,7 +14105,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G439" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14131,7 +14131,7 @@
         <v>4.46600008010864</v>
       </c>
       <c r="G440" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14157,7 +14157,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G441" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14183,7 +14183,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G442" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14209,7 +14209,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G443" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14235,7 +14235,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G444" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14261,7 +14261,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14287,7 +14287,7 @@
         <v>4.50600004196167</v>
       </c>
       <c r="G446" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14313,7 +14313,7 @@
         <v>4.5</v>
       </c>
       <c r="G447" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14339,7 +14339,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G448" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14365,7 +14365,7 @@
         <v>4.50400018692017</v>
       </c>
       <c r="G449" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14391,7 +14391,7 @@
         <v>4.5</v>
       </c>
       <c r="G450" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14417,7 +14417,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G451" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14443,7 +14443,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G452" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14469,7 +14469,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G453" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14495,7 +14495,7 @@
         <v>4.42399978637695</v>
       </c>
       <c r="G454" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14521,7 +14521,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G455" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14547,7 +14547,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G456" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14573,7 +14573,7 @@
         <v>4.49200010299683</v>
       </c>
       <c r="G457" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14599,7 +14599,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14625,7 +14625,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G459" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14651,7 +14651,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G460" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14677,7 +14677,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G461" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14703,7 +14703,7 @@
         <v>4.48799991607666</v>
       </c>
       <c r="G462" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14729,7 +14729,7 @@
         <v>4.46600008010864</v>
       </c>
       <c r="G463" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14755,7 +14755,7 @@
         <v>4.41599988937378</v>
       </c>
       <c r="G464" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14781,7 +14781,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G465" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14807,7 +14807,7 @@
         <v>4.42399978637695</v>
       </c>
       <c r="G466" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14833,7 +14833,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G467" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14859,7 +14859,7 @@
         <v>4.5</v>
       </c>
       <c r="G468" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14885,7 +14885,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G469" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14911,7 +14911,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14937,7 +14937,7 @@
         <v>4.5</v>
       </c>
       <c r="G471" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14963,7 +14963,7 @@
         <v>4.5</v>
       </c>
       <c r="G472" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14989,7 +14989,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G473" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15015,7 +15015,7 @@
         <v>4.59800004959106</v>
       </c>
       <c r="G474" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15041,7 +15041,7 @@
         <v>4.50799989700317</v>
       </c>
       <c r="G475" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15067,7 +15067,7 @@
         <v>4.52199983596802</v>
       </c>
       <c r="G476" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15093,7 +15093,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G477" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15119,7 +15119,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G478" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15145,7 +15145,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G479" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15171,7 +15171,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G480" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15197,7 +15197,7 @@
         <v>4.44799995422363</v>
       </c>
       <c r="G481" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15223,7 +15223,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G482" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15249,7 +15249,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G483" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15275,7 +15275,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G484" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15301,7 +15301,7 @@
         <v>4.3439998626709</v>
       </c>
       <c r="G485" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15327,7 +15327,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G486" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15353,7 +15353,7 @@
         <v>4.2979998588562</v>
       </c>
       <c r="G487" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15379,7 +15379,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G488" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15405,7 +15405,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G489" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15431,7 +15431,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G490" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15457,7 +15457,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G491" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15483,7 +15483,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G492" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15509,7 +15509,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G493" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15535,7 +15535,7 @@
         <v>4.27600002288818</v>
       </c>
       <c r="G494" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15561,7 +15561,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G495" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15587,7 +15587,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G496" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15613,7 +15613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G497" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15639,7 +15639,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G498" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15665,7 +15665,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G499" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15691,7 +15691,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G500" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15717,7 +15717,7 @@
         <v>4.41200017929077</v>
       </c>
       <c r="G501" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15743,7 +15743,7 @@
         <v>4.32399988174438</v>
       </c>
       <c r="G502" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15769,7 +15769,7 @@
         <v>4.27799987792969</v>
       </c>
       <c r="G503" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15795,7 +15795,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G504" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15821,7 +15821,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G505" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15847,7 +15847,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G506" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15873,7 +15873,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G507" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15899,7 +15899,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G508" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15925,7 +15925,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G509" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15951,7 +15951,7 @@
         <v>4.35799980163574</v>
       </c>
       <c r="G510" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15977,7 +15977,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G511" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16003,7 +16003,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16029,7 +16029,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G513" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16055,7 +16055,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G514" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16081,7 +16081,7 @@
         <v>4.5</v>
       </c>
       <c r="G515" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16107,7 +16107,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G516" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16133,7 +16133,7 @@
         <v>4.5</v>
       </c>
       <c r="G517" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16159,7 +16159,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G518" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16185,7 +16185,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G519" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16211,7 +16211,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G520" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16237,7 +16237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G521" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16263,7 +16263,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G522" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16289,7 +16289,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G523" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16315,7 +16315,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G524" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16341,7 +16341,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G525" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16367,7 +16367,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G526" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16393,7 +16393,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G527" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16419,7 +16419,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G528" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16445,7 +16445,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G529" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16471,7 +16471,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G530" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16497,7 +16497,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G531" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16523,7 +16523,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G532" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16549,7 +16549,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G533" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16575,7 +16575,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16601,7 +16601,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G535" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16627,7 +16627,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G536" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16653,7 +16653,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G537" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16679,7 +16679,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16705,7 +16705,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G539" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16731,7 +16731,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G540" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16757,7 +16757,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G541" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16783,7 +16783,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G542" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16809,7 +16809,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G543" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16835,7 +16835,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16861,7 +16861,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G545" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16887,7 +16887,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16913,7 +16913,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16939,7 +16939,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G548" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16965,7 +16965,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G549" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -16991,7 +16991,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G550" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17017,7 +17017,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G551" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17043,7 +17043,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G552" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17069,7 +17069,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G553" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17095,7 +17095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G554" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17121,7 +17121,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G555" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17147,7 +17147,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G556" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17173,7 +17173,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G557" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17199,7 +17199,7 @@
         <v>4.25</v>
       </c>
       <c r="G558" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17225,7 +17225,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G559" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17251,7 +17251,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G560" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17277,7 +17277,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G561" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17303,7 +17303,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G562" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17329,7 +17329,7 @@
         <v>4.25</v>
       </c>
       <c r="G563" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17355,7 +17355,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G564" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17381,7 +17381,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G565" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17407,7 +17407,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G566" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17433,7 +17433,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G567" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17459,7 +17459,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G568" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17485,7 +17485,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G569" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17511,7 +17511,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G570" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17537,7 +17537,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17563,7 +17563,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G572" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17589,7 +17589,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G573" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17615,7 +17615,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G574" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17641,7 +17641,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G575" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17667,7 +17667,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G576" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17693,7 +17693,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G577" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17719,7 +17719,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G578" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17745,7 +17745,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G579" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17771,7 +17771,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G580" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17797,7 +17797,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G581" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17823,7 +17823,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G582" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17849,7 +17849,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G583" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17875,7 +17875,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17901,7 +17901,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G585" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17927,7 +17927,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G586" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17953,7 +17953,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G587" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17979,7 +17979,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18005,7 +18005,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G589" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18031,7 +18031,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G590" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18057,7 +18057,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G591" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18083,7 +18083,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G592" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18109,7 +18109,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G593" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18135,7 +18135,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G594" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18161,7 +18161,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G595" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18187,7 +18187,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G596" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18213,7 +18213,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18239,7 +18239,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18265,7 +18265,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G599" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18291,7 +18291,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G600" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18317,7 +18317,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18343,7 +18343,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G602" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18369,7 +18369,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G603" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18395,7 +18395,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G604" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18421,7 +18421,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G605" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18447,7 +18447,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G606" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18473,7 +18473,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G607" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18499,7 +18499,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G608" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18525,7 +18525,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G609" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18551,7 +18551,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G610" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18577,7 +18577,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G611" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18603,7 +18603,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G612" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18629,7 +18629,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18655,7 +18655,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G614" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18681,7 +18681,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G615" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18707,7 +18707,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G616" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18733,7 +18733,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G617" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18759,7 +18759,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G618" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18785,7 +18785,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G619" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18811,7 +18811,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G620" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18837,7 +18837,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G621" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18863,7 +18863,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G622" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18889,7 +18889,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G623" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18915,7 +18915,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G624" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18941,7 +18941,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G625" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18967,7 +18967,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G626" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18993,7 +18993,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G627" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19019,7 +19019,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19045,7 +19045,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G629" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19071,7 +19071,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G630" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19097,7 +19097,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19123,7 +19123,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19149,7 +19149,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G633" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19175,7 +19175,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G634" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19201,7 +19201,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G635" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19227,7 +19227,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19253,7 +19253,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G637" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19279,7 +19279,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G638" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19305,7 +19305,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G639" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19331,7 +19331,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G640" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19357,7 +19357,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G641" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19383,7 +19383,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G642" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19409,7 +19409,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G643" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19435,7 +19435,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G644" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19461,7 +19461,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G645" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19487,7 +19487,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G646" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19513,7 +19513,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G647" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19539,7 +19539,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G648" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19565,7 +19565,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G649" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19591,7 +19591,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G650" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19617,7 +19617,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G651" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19643,7 +19643,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G652" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19669,7 +19669,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G653" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19695,7 +19695,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G654" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19721,7 +19721,7 @@
         <v>4.25</v>
       </c>
       <c r="G655" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19747,7 +19747,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G656" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19773,7 +19773,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G657" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19799,7 +19799,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19825,7 +19825,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G659" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19851,7 +19851,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G660" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19877,7 +19877,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19903,7 +19903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19929,7 +19929,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19955,7 +19955,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19981,7 +19981,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20007,7 +20007,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G666" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20033,7 +20033,7 @@
         <v>4.25</v>
       </c>
       <c r="G667" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20059,7 +20059,7 @@
         <v>4.25</v>
       </c>
       <c r="G668" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20085,7 +20085,7 @@
         <v>4.25</v>
       </c>
       <c r="G669" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20111,7 +20111,7 @@
         <v>4.25</v>
       </c>
       <c r="G670" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20137,7 +20137,7 @@
         <v>4.25</v>
       </c>
       <c r="G671" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20163,7 +20163,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G672" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20189,7 +20189,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G673" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20215,7 +20215,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G674" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20241,7 +20241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G675" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20267,7 +20267,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G676" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20293,7 +20293,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G677" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20319,7 +20319,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20345,7 +20345,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G679" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20371,7 +20371,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20397,7 +20397,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20423,7 +20423,7 @@
         <v>4.25</v>
       </c>
       <c r="G682" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20449,7 +20449,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20475,7 +20475,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20501,7 +20501,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20527,7 +20527,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G686" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20553,7 +20553,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G687" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20579,7 +20579,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G688" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20605,7 +20605,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G689" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20631,7 +20631,7 @@
         <v>4.25</v>
       </c>
       <c r="G690" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20657,7 +20657,7 @@
         <v>4.25</v>
       </c>
       <c r="G691" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20683,7 +20683,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G692" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20709,7 +20709,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G693" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20735,7 +20735,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G694" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20761,7 +20761,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20787,7 +20787,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G696" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20813,7 +20813,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G697" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20839,7 +20839,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G698" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20865,7 +20865,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G699" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20891,7 +20891,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G700" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20917,7 +20917,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G701" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20943,7 +20943,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G702" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20969,7 +20969,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G703" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20995,7 +20995,7 @@
         <v>4.25</v>
       </c>
       <c r="G704" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21021,7 +21021,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21047,7 +21047,7 @@
         <v>4.25</v>
       </c>
       <c r="G706" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21073,7 +21073,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G707" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21099,7 +21099,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G708" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21125,7 +21125,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21151,7 +21151,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21177,7 +21177,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G711" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21203,7 +21203,7 @@
         <v>4</v>
       </c>
       <c r="G712" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21229,7 +21229,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G713" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21255,7 +21255,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21281,7 +21281,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G715" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21307,7 +21307,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G716" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21333,7 +21333,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G717" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21359,7 +21359,7 @@
         <v>3.75</v>
       </c>
       <c r="G718" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21385,7 +21385,7 @@
         <v>3.75</v>
       </c>
       <c r="G719" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21411,7 +21411,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21437,7 +21437,7 @@
         <v>3.5</v>
       </c>
       <c r="G721" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21463,7 +21463,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G722" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21489,7 +21489,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G723" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21515,7 +21515,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G724" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21541,7 +21541,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G725" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21567,7 +21567,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G726" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21593,7 +21593,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G727" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21619,7 +21619,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G728" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21645,7 +21645,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G729" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21671,7 +21671,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G730" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21697,7 +21697,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G731" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21723,7 +21723,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G732" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21749,7 +21749,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G733" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21775,7 +21775,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G734" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21801,7 +21801,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G735" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21827,7 +21827,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G736" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21853,7 +21853,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G737" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21879,7 +21879,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G738" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21905,7 +21905,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G739" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21931,7 +21931,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G740" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21957,7 +21957,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G741" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21983,7 +21983,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G742" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22009,7 +22009,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G743" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22035,7 +22035,7 @@
         <v>3.75</v>
       </c>
       <c r="G744" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22061,7 +22061,7 @@
         <v>3.75</v>
       </c>
       <c r="G745" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22087,7 +22087,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G746" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22113,7 +22113,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G747" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22139,7 +22139,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G748" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22165,7 +22165,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G749" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22191,7 +22191,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G750" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22217,7 +22217,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G751" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22243,7 +22243,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G752" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22269,7 +22269,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G753" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22295,7 +22295,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G754" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22321,7 +22321,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G755" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22347,7 +22347,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G756" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22373,7 +22373,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G757" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22399,7 +22399,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G758" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22425,7 +22425,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G759" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22451,7 +22451,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G760" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22477,7 +22477,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G761" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22503,7 +22503,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22529,7 +22529,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G763" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22555,7 +22555,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G764" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22581,7 +22581,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G765" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22607,7 +22607,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G766" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22633,7 +22633,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G767" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22659,7 +22659,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G768" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22685,7 +22685,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G769" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22711,7 +22711,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G770" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22737,7 +22737,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G771" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22763,7 +22763,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G772" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22789,7 +22789,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22815,7 +22815,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G774" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22841,7 +22841,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G775" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22867,7 +22867,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G776" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22893,7 +22893,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G777" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22919,7 +22919,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G778" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22945,7 +22945,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G779" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22971,7 +22971,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G780" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22997,7 +22997,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G781" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23023,7 +23023,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G782" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23049,7 +23049,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G783" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23075,7 +23075,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G784" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23101,7 +23101,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G785" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23127,7 +23127,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G786" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23153,7 +23153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G787" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23179,7 +23179,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23205,7 +23205,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G789" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23231,7 +23231,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23257,7 +23257,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G791" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23283,7 +23283,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G792" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23309,7 +23309,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G793" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23335,7 +23335,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G794" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23361,7 +23361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G795" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23387,7 +23387,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G796" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23413,7 +23413,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G797" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23439,7 +23439,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G798" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23465,7 +23465,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G799" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23491,7 +23491,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G800" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23517,7 +23517,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23543,7 +23543,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G802" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23569,7 +23569,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G803" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23595,7 +23595,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G804" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23621,7 +23621,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G805" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23647,7 +23647,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G806" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23673,7 +23673,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G807" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23699,7 +23699,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G808" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23725,7 +23725,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G809" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23751,7 +23751,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G810" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23777,7 +23777,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G811" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23803,7 +23803,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G812" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23829,7 +23829,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G813" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23855,7 +23855,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G814" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23881,7 +23881,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G815" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23907,7 +23907,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G816" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23933,7 +23933,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23959,7 +23959,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G818" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23985,7 +23985,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G819" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24011,7 +24011,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G820" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24037,7 +24037,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G821" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24063,7 +24063,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G822" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24089,7 +24089,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24115,7 +24115,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G824" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24141,7 +24141,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G825" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24167,7 +24167,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G826" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24193,7 +24193,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G827" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24219,7 +24219,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G828" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24245,7 +24245,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G829" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24271,7 +24271,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G830" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24297,7 +24297,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24323,7 +24323,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G832" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24349,7 +24349,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G833" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24375,7 +24375,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G834" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24401,7 +24401,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G835" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24427,7 +24427,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G836" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24453,7 +24453,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G837" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24479,7 +24479,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G838" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24505,7 +24505,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G839" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24531,7 +24531,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G840" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24557,7 +24557,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G841" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24583,7 +24583,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24609,7 +24609,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G843" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24635,7 +24635,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G844" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24661,7 +24661,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G845" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24687,7 +24687,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G846" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24713,7 +24713,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G847" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24739,7 +24739,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G848" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24765,7 +24765,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G849" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24791,7 +24791,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G850" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24817,7 +24817,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G851" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24843,7 +24843,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G852" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24869,7 +24869,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G853" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24895,7 +24895,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G854" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24921,7 +24921,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G855" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24947,7 +24947,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G856" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24973,7 +24973,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G857" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24999,7 +24999,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G858" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25025,7 +25025,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G859" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25051,7 +25051,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G860" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25077,7 +25077,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G861" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25103,7 +25103,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G862" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25129,7 +25129,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G863" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25155,7 +25155,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G864" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25181,7 +25181,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G865" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25207,7 +25207,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G866" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25233,7 +25233,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G867" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25259,7 +25259,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G868" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25285,7 +25285,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G869" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25311,7 +25311,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G870" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25337,7 +25337,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G871" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25363,7 +25363,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G872" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25389,7 +25389,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G873" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25415,7 +25415,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G874" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25441,7 +25441,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G875" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25467,7 +25467,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G876" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25493,7 +25493,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G877" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25519,7 +25519,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G878" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25545,7 +25545,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G879" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25571,7 +25571,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G880" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25597,7 +25597,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G881" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25623,7 +25623,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G882" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25649,7 +25649,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G883" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25675,7 +25675,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G884" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25701,7 +25701,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G885" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25727,7 +25727,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G886" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25753,7 +25753,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G887" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25779,7 +25779,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G888" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25805,7 +25805,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G889" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25831,7 +25831,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G890" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25857,7 +25857,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G891" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25883,7 +25883,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G892" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25909,7 +25909,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G893" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25935,7 +25935,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G894" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25961,7 +25961,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25987,7 +25987,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G896" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26013,7 +26013,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G897" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26039,7 +26039,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G898" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26065,7 +26065,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G899" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26091,7 +26091,7 @@
         <v>4</v>
       </c>
       <c r="G900" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26117,7 +26117,7 @@
         <v>4</v>
       </c>
       <c r="G901" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26143,7 +26143,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G902" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26169,7 +26169,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G903" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26195,7 +26195,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26221,7 +26221,7 @@
         <v>4</v>
       </c>
       <c r="G905" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26247,7 +26247,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G906" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26273,7 +26273,7 @@
         <v>4</v>
       </c>
       <c r="G907" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26299,7 +26299,7 @@
         <v>4</v>
       </c>
       <c r="G908" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26325,7 +26325,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G909" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26351,7 +26351,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G910" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26377,7 +26377,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G911" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26403,7 +26403,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G912" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26429,7 +26429,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G913" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26455,7 +26455,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G914" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26481,7 +26481,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26507,7 +26507,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G916" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H916" t="s">
         <v>9<